--- a/Semiconductor/NVDA.xlsx
+++ b/Semiconductor/NVDA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameel/Library/CloudStorage/Dropbox/models/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameelbrannon/Library/CloudStorage/Dropbox/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC58F95-281C-144D-BC0D-D19824F00CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F6F2369-32CF-514E-95EB-1DF25C268C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23380" yWindow="820" windowWidth="21420" windowHeight="24380" activeTab="2" xr2:uid="{834EDAA3-D05C-5B48-B7D6-13D13D56A97E}"/>
+    <workbookView xWindow="13720" yWindow="680" windowWidth="33580" windowHeight="24380" xr2:uid="{834EDAA3-D05C-5B48-B7D6-13D13D56A97E}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="209">
   <si>
     <t>P</t>
   </si>
@@ -626,13 +626,53 @@
   </si>
   <si>
     <t>Colette Kress</t>
+  </si>
+  <si>
+    <t>Capex</t>
+  </si>
+  <si>
+    <t>Depre</t>
+  </si>
+  <si>
+    <t>cRPO</t>
+  </si>
+  <si>
+    <t>RPO</t>
+  </si>
+  <si>
+    <t>cRPO as % of RPO</t>
+  </si>
+  <si>
+    <t>Change in RPO</t>
+  </si>
+  <si>
+    <t>Deferred</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unbilled </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discount </t>
+  </si>
+  <si>
+    <t>NPV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate </t>
+  </si>
+  <si>
+    <t>Current</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="m/d;@"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
@@ -692,7 +732,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -702,6 +742,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -730,7 +776,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -748,8 +794,6 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -770,7 +814,43 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -793,16 +873,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>583081</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>31235</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:rowOff>5745</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>15975</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>135786</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>46213</xdr:colOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>52631</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -817,8 +897,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6757358" y="88900"/>
-          <a:ext cx="15975" cy="23410094"/>
+          <a:off x="9337009" y="5745"/>
+          <a:ext cx="14978" cy="25560279"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1221,7 +1301,7 @@
     <col min="6" max="6" width="4" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" style="16"/>
+    <col min="9" max="9" width="10.83203125" style="14"/>
     <col min="10" max="11" width="10.83203125" style="2"/>
     <col min="12" max="12" width="122.5" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="10.83203125" style="2"/>
@@ -1246,11 +1326,11 @@
         <v>1</v>
       </c>
       <c r="G4" s="2">
-        <f>24.4*1000</f>
-        <v>24400</v>
+        <f>24.3*1000</f>
+        <v>24300</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.2">
@@ -1265,7 +1345,7 @@
       </c>
       <c r="G5" s="5">
         <f>+G3*G4</f>
-        <v>4440800</v>
+        <v>4422600</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>108</v>
@@ -1276,11 +1356,12 @@
         <v>3</v>
       </c>
       <c r="G6" s="2">
-        <f>15234+38457</f>
-        <v>53691</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>6</v>
+        <f>11486+49122</f>
+        <v>60608</v>
+      </c>
+      <c r="H6" s="2" t="str">
+        <f>+H4</f>
+        <v>Q325</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>109</v>
@@ -1294,10 +1375,12 @@
         <v>4</v>
       </c>
       <c r="G7" s="2">
-        <v>8464</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>6</v>
+        <f>999+7468</f>
+        <v>8467</v>
+      </c>
+      <c r="H7" s="2" t="str">
+        <f>+H6</f>
+        <v>Q325</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>110</v>
@@ -1312,7 +1395,7 @@
       </c>
       <c r="G8" s="5">
         <f>+G5-G6+G7</f>
-        <v>4395573</v>
+        <v>4370459</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>111</v>
@@ -1331,7 +1414,7 @@
     <row r="11" spans="2:12" x14ac:dyDescent="0.2">
       <c r="G11" s="2">
         <f>+G5+175000000</f>
-        <v>179440800</v>
+        <v>179422600</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>114</v>
@@ -1340,25 +1423,25 @@
     <row r="12" spans="2:12" x14ac:dyDescent="0.2">
       <c r="G12" s="2">
         <f>+G11/G4</f>
-        <v>7354.1311475409839</v>
+        <v>7383.6460905349795</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="L13" s="22" t="s">
+      <c r="L13" s="20" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="L14" s="22" t="s">
+      <c r="L14" s="20" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="I15" s="18"/>
-      <c r="L15" s="22" t="s">
+      <c r="I15" s="16"/>
+      <c r="L15" s="20" t="s">
         <v>118</v>
       </c>
     </row>
@@ -1369,26 +1452,26 @@
       <c r="D16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="18" t="s">
+      <c r="I16" s="16" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="17">
         <v>45874</v>
       </c>
-      <c r="L17" s="20" t="s">
+      <c r="L17" s="18" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="I18" s="19">
+      <c r="I18" s="17">
         <v>40400</v>
       </c>
       <c r="L18" s="2" t="s">
@@ -1396,7 +1479,7 @@
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="I19" s="19">
+      <c r="I19" s="17">
         <v>45874</v>
       </c>
       <c r="L19" s="2" t="s">
@@ -1404,7 +1487,7 @@
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="I20" s="19">
+      <c r="I20" s="17">
         <v>45874</v>
       </c>
       <c r="L20" s="2" t="s">
@@ -1412,7 +1495,7 @@
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="I21" s="19">
+      <c r="I21" s="17">
         <v>45853</v>
       </c>
       <c r="L21" s="2" t="s">
@@ -1420,16 +1503,16 @@
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="I22" s="18"/>
+      <c r="I22" s="16"/>
       <c r="L22" s="2" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="I23" s="18"/>
+      <c r="I23" s="16"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="L25" s="13" t="s">
+      <c r="L25" s="11" t="s">
         <v>125</v>
       </c>
     </row>
@@ -1474,7 +1557,7 @@
       </c>
     </row>
     <row r="36" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L36" s="13" t="s">
+      <c r="L36" s="11" t="s">
         <v>137</v>
       </c>
     </row>
@@ -1484,7 +1567,7 @@
       </c>
     </row>
     <row r="38" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L38" s="21" t="s">
+      <c r="L38" s="19" t="s">
         <v>136</v>
       </c>
     </row>
@@ -1494,52 +1577,52 @@
       </c>
     </row>
     <row r="42" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L42" s="24" t="s">
+      <c r="L42" s="22" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="43" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L43" s="13" t="s">
+      <c r="L43" s="11" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="44" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L44" s="22" t="s">
+      <c r="L44" s="20" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="45" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L45" s="22" t="s">
+      <c r="L45" s="20" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="46" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L46" s="22" t="s">
+      <c r="L46" s="20" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="47" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L47" s="22" t="s">
+      <c r="L47" s="20" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="48" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L48" s="23" t="s">
+      <c r="L48" s="21" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="49" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L49" s="22" t="s">
+      <c r="L49" s="20" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="50" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L50" s="22" t="s">
+      <c r="L50" s="20" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="51" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L51" s="23" t="s">
+      <c r="L51" s="21" t="s">
         <v>147</v>
       </c>
     </row>
@@ -1554,7 +1637,7 @@
       </c>
     </row>
     <row r="56" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L56" s="13" t="s">
+      <c r="L56" s="11" t="s">
         <v>150</v>
       </c>
     </row>
@@ -1569,17 +1652,17 @@
       </c>
     </row>
     <row r="59" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L59" s="13" t="s">
+      <c r="L59" s="11" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="60" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L60" s="22" t="s">
+      <c r="L60" s="20" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="61" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L61" s="22" t="s">
+      <c r="L61" s="20" t="s">
         <v>155</v>
       </c>
     </row>
@@ -1604,7 +1687,7 @@
       </c>
     </row>
     <row r="68" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L68" s="13" t="s">
+      <c r="L68" s="11" t="s">
         <v>160</v>
       </c>
     </row>
@@ -1644,22 +1727,22 @@
       </c>
     </row>
     <row r="76" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L76" s="22" t="s">
+      <c r="L76" s="20" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="77" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L77" s="22" t="s">
+      <c r="L77" s="20" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="78" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L78" s="22" t="s">
+      <c r="L78" s="20" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="79" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L79" s="13" t="s">
+      <c r="L79" s="11" t="s">
         <v>171</v>
       </c>
     </row>
@@ -1716,47 +1799,47 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="15" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="15" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="15" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="15" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="15" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B12" s="17"/>
+      <c r="B12" s="15"/>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
@@ -1764,22 +1847,22 @@
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="15" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="15" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="15" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="15" t="s">
         <v>96</v>
       </c>
     </row>
@@ -1789,46 +1872,46 @@
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="15" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="15" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="15" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="15" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="15" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="15" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="15" t="s">
         <v>105</v>
       </c>
     </row>
@@ -1863,55 +1946,59 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3324D012-FEF5-4D43-9CF5-2CE00AF5A8E7}">
-  <dimension ref="B2:AY112"/>
+  <dimension ref="B2:ID124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="39.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="7.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="5.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.83203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.6640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.6640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.83203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="7.6640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="10.83203125" style="2"/>
     <col min="17" max="20" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="21" max="26" width="6.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="51" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="37" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="8.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="40" max="51" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="52" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:51" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D2" s="7">
+    <row r="2" spans="2:238" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C2" s="23"/>
+      <c r="D2" s="23">
         <v>45137</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="23">
         <v>45228</v>
       </c>
-      <c r="G2" s="7">
+      <c r="F2" s="23"/>
+      <c r="G2" s="23">
         <v>45410</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="23">
         <v>45501</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="23">
         <v>45592</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="23">
         <v>45683</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="23">
         <v>45774</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="23">
         <v>45896</v>
       </c>
+      <c r="M2" s="23"/>
       <c r="W2" s="7">
         <v>44227</v>
       </c>
@@ -1925,38 +2012,38 @@
         <v>45683</v>
       </c>
     </row>
-    <row r="3" spans="2:51" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C3" s="3" t="s">
+    <row r="3" spans="2:238" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="24" t="s">
         <v>19</v>
       </c>
       <c r="N3" s="3" t="s">
@@ -1970,7 +2057,7 @@
         <v>2016</v>
       </c>
       <c r="S3" s="3">
-        <f t="shared" ref="S3:AY3" si="0">+R3+1</f>
+        <f t="shared" ref="S3:AL3" si="0">+R3+1</f>
         <v>2017</v>
       </c>
       <c r="T3" s="3">
@@ -2050,90 +2137,844 @@
         <v>2036</v>
       </c>
       <c r="AM3" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="AM3" si="1">+AL3+1</f>
         <v>2037</v>
       </c>
       <c r="AN3" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="AN3" si="2">+AM3+1</f>
         <v>2038</v>
       </c>
       <c r="AO3" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="AO3" si="3">+AN3+1</f>
         <v>2039</v>
       </c>
       <c r="AP3" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="AP3" si="4">+AO3+1</f>
         <v>2040</v>
       </c>
       <c r="AQ3" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="AQ3" si="5">+AP3+1</f>
         <v>2041</v>
       </c>
       <c r="AR3" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="AR3" si="6">+AQ3+1</f>
         <v>2042</v>
       </c>
       <c r="AS3" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="AS3" si="7">+AR3+1</f>
         <v>2043</v>
       </c>
       <c r="AT3" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="AT3" si="8">+AS3+1</f>
         <v>2044</v>
       </c>
       <c r="AU3" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="AU3" si="9">+AT3+1</f>
         <v>2045</v>
       </c>
       <c r="AV3" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="AV3" si="10">+AU3+1</f>
         <v>2046</v>
       </c>
       <c r="AW3" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="AW3" si="11">+AV3+1</f>
         <v>2047</v>
       </c>
       <c r="AX3" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="AX3" si="12">+AW3+1</f>
         <v>2048</v>
       </c>
       <c r="AY3" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="AY3" si="13">+AX3+1</f>
         <v>2049</v>
       </c>
-    </row>
-    <row r="4" spans="2:51" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AZ3" s="3">
+        <f t="shared" ref="AZ3" si="14">+AY3+1</f>
+        <v>2050</v>
+      </c>
+      <c r="BA3" s="3">
+        <f t="shared" ref="BA3" si="15">+AZ3+1</f>
+        <v>2051</v>
+      </c>
+      <c r="BB3" s="3">
+        <f t="shared" ref="BB3" si="16">+BA3+1</f>
+        <v>2052</v>
+      </c>
+      <c r="BC3" s="3">
+        <f t="shared" ref="BC3" si="17">+BB3+1</f>
+        <v>2053</v>
+      </c>
+      <c r="BD3" s="3">
+        <f t="shared" ref="BD3" si="18">+BC3+1</f>
+        <v>2054</v>
+      </c>
+      <c r="BE3" s="3">
+        <f t="shared" ref="BE3" si="19">+BD3+1</f>
+        <v>2055</v>
+      </c>
+      <c r="BF3" s="3">
+        <f t="shared" ref="BF3" si="20">+BE3+1</f>
+        <v>2056</v>
+      </c>
+      <c r="BG3" s="3">
+        <f t="shared" ref="BG3" si="21">+BF3+1</f>
+        <v>2057</v>
+      </c>
+      <c r="BH3" s="3">
+        <f t="shared" ref="BH3" si="22">+BG3+1</f>
+        <v>2058</v>
+      </c>
+      <c r="BI3" s="3">
+        <f t="shared" ref="BI3" si="23">+BH3+1</f>
+        <v>2059</v>
+      </c>
+      <c r="BJ3" s="3">
+        <f t="shared" ref="BJ3" si="24">+BI3+1</f>
+        <v>2060</v>
+      </c>
+      <c r="BK3" s="3">
+        <f t="shared" ref="BK3" si="25">+BJ3+1</f>
+        <v>2061</v>
+      </c>
+      <c r="BL3" s="3">
+        <f t="shared" ref="BL3" si="26">+BK3+1</f>
+        <v>2062</v>
+      </c>
+      <c r="BM3" s="3">
+        <f t="shared" ref="BM3" si="27">+BL3+1</f>
+        <v>2063</v>
+      </c>
+      <c r="BN3" s="3">
+        <f t="shared" ref="BN3" si="28">+BM3+1</f>
+        <v>2064</v>
+      </c>
+      <c r="BO3" s="3">
+        <f t="shared" ref="BO3" si="29">+BN3+1</f>
+        <v>2065</v>
+      </c>
+      <c r="BP3" s="3">
+        <f t="shared" ref="BP3" si="30">+BO3+1</f>
+        <v>2066</v>
+      </c>
+      <c r="BQ3" s="3">
+        <f t="shared" ref="BQ3" si="31">+BP3+1</f>
+        <v>2067</v>
+      </c>
+      <c r="BR3" s="3">
+        <f t="shared" ref="BR3" si="32">+BQ3+1</f>
+        <v>2068</v>
+      </c>
+      <c r="BS3" s="3">
+        <f t="shared" ref="BS3" si="33">+BR3+1</f>
+        <v>2069</v>
+      </c>
+      <c r="BT3" s="3">
+        <f t="shared" ref="BT3" si="34">+BS3+1</f>
+        <v>2070</v>
+      </c>
+      <c r="BU3" s="3">
+        <f t="shared" ref="BU3" si="35">+BT3+1</f>
+        <v>2071</v>
+      </c>
+      <c r="BV3" s="3">
+        <f t="shared" ref="BV3" si="36">+BU3+1</f>
+        <v>2072</v>
+      </c>
+      <c r="BW3" s="3">
+        <f t="shared" ref="BW3" si="37">+BV3+1</f>
+        <v>2073</v>
+      </c>
+      <c r="BX3" s="3">
+        <f t="shared" ref="BX3" si="38">+BW3+1</f>
+        <v>2074</v>
+      </c>
+      <c r="BY3" s="3">
+        <f t="shared" ref="BY3" si="39">+BX3+1</f>
+        <v>2075</v>
+      </c>
+      <c r="BZ3" s="3">
+        <f t="shared" ref="BZ3" si="40">+BY3+1</f>
+        <v>2076</v>
+      </c>
+      <c r="CA3" s="3">
+        <f t="shared" ref="CA3" si="41">+BZ3+1</f>
+        <v>2077</v>
+      </c>
+      <c r="CB3" s="3">
+        <f t="shared" ref="CB3" si="42">+CA3+1</f>
+        <v>2078</v>
+      </c>
+      <c r="CC3" s="3">
+        <f t="shared" ref="CC3" si="43">+CB3+1</f>
+        <v>2079</v>
+      </c>
+      <c r="CD3" s="3">
+        <f t="shared" ref="CD3" si="44">+CC3+1</f>
+        <v>2080</v>
+      </c>
+      <c r="CE3" s="3">
+        <f t="shared" ref="CE3" si="45">+CD3+1</f>
+        <v>2081</v>
+      </c>
+      <c r="CF3" s="3">
+        <f t="shared" ref="CF3" si="46">+CE3+1</f>
+        <v>2082</v>
+      </c>
+      <c r="CG3" s="3">
+        <f t="shared" ref="CG3" si="47">+CF3+1</f>
+        <v>2083</v>
+      </c>
+      <c r="CH3" s="3">
+        <f t="shared" ref="CH3" si="48">+CG3+1</f>
+        <v>2084</v>
+      </c>
+      <c r="CI3" s="3">
+        <f t="shared" ref="CI3" si="49">+CH3+1</f>
+        <v>2085</v>
+      </c>
+      <c r="CJ3" s="3">
+        <f t="shared" ref="CJ3" si="50">+CI3+1</f>
+        <v>2086</v>
+      </c>
+      <c r="CK3" s="3">
+        <f t="shared" ref="CK3" si="51">+CJ3+1</f>
+        <v>2087</v>
+      </c>
+      <c r="CL3" s="3">
+        <f t="shared" ref="CL3" si="52">+CK3+1</f>
+        <v>2088</v>
+      </c>
+      <c r="CM3" s="3">
+        <f t="shared" ref="CM3" si="53">+CL3+1</f>
+        <v>2089</v>
+      </c>
+      <c r="CN3" s="3">
+        <f t="shared" ref="CN3" si="54">+CM3+1</f>
+        <v>2090</v>
+      </c>
+      <c r="CO3" s="3">
+        <f t="shared" ref="CO3" si="55">+CN3+1</f>
+        <v>2091</v>
+      </c>
+      <c r="CP3" s="3">
+        <f t="shared" ref="CP3" si="56">+CO3+1</f>
+        <v>2092</v>
+      </c>
+      <c r="CQ3" s="3">
+        <f t="shared" ref="CQ3" si="57">+CP3+1</f>
+        <v>2093</v>
+      </c>
+      <c r="CR3" s="3">
+        <f t="shared" ref="CR3" si="58">+CQ3+1</f>
+        <v>2094</v>
+      </c>
+      <c r="CS3" s="3">
+        <f t="shared" ref="CS3" si="59">+CR3+1</f>
+        <v>2095</v>
+      </c>
+      <c r="CT3" s="3">
+        <f t="shared" ref="CT3" si="60">+CS3+1</f>
+        <v>2096</v>
+      </c>
+      <c r="CU3" s="3">
+        <f t="shared" ref="CU3" si="61">+CT3+1</f>
+        <v>2097</v>
+      </c>
+      <c r="CV3" s="3">
+        <f t="shared" ref="CV3" si="62">+CU3+1</f>
+        <v>2098</v>
+      </c>
+      <c r="CW3" s="3">
+        <f t="shared" ref="CW3" si="63">+CV3+1</f>
+        <v>2099</v>
+      </c>
+      <c r="CX3" s="3">
+        <f t="shared" ref="CX3" si="64">+CW3+1</f>
+        <v>2100</v>
+      </c>
+      <c r="CY3" s="3">
+        <f t="shared" ref="CY3" si="65">+CX3+1</f>
+        <v>2101</v>
+      </c>
+      <c r="CZ3" s="3">
+        <f t="shared" ref="CZ3" si="66">+CY3+1</f>
+        <v>2102</v>
+      </c>
+      <c r="DA3" s="3">
+        <f t="shared" ref="DA3" si="67">+CZ3+1</f>
+        <v>2103</v>
+      </c>
+      <c r="DB3" s="3">
+        <f t="shared" ref="DB3" si="68">+DA3+1</f>
+        <v>2104</v>
+      </c>
+      <c r="DC3" s="3">
+        <f t="shared" ref="DC3" si="69">+DB3+1</f>
+        <v>2105</v>
+      </c>
+      <c r="DD3" s="3">
+        <f t="shared" ref="DD3" si="70">+DC3+1</f>
+        <v>2106</v>
+      </c>
+      <c r="DE3" s="3">
+        <f t="shared" ref="DE3" si="71">+DD3+1</f>
+        <v>2107</v>
+      </c>
+      <c r="DF3" s="3">
+        <f t="shared" ref="DF3" si="72">+DE3+1</f>
+        <v>2108</v>
+      </c>
+      <c r="DG3" s="3">
+        <f t="shared" ref="DG3" si="73">+DF3+1</f>
+        <v>2109</v>
+      </c>
+      <c r="DH3" s="3">
+        <f t="shared" ref="DH3" si="74">+DG3+1</f>
+        <v>2110</v>
+      </c>
+      <c r="DI3" s="3">
+        <f t="shared" ref="DI3" si="75">+DH3+1</f>
+        <v>2111</v>
+      </c>
+      <c r="DJ3" s="3">
+        <f t="shared" ref="DJ3" si="76">+DI3+1</f>
+        <v>2112</v>
+      </c>
+      <c r="DK3" s="3">
+        <f t="shared" ref="DK3" si="77">+DJ3+1</f>
+        <v>2113</v>
+      </c>
+      <c r="DL3" s="3">
+        <f t="shared" ref="DL3" si="78">+DK3+1</f>
+        <v>2114</v>
+      </c>
+      <c r="DM3" s="3">
+        <f t="shared" ref="DM3" si="79">+DL3+1</f>
+        <v>2115</v>
+      </c>
+      <c r="DN3" s="3">
+        <f t="shared" ref="DN3" si="80">+DM3+1</f>
+        <v>2116</v>
+      </c>
+      <c r="DO3" s="3">
+        <f t="shared" ref="DO3" si="81">+DN3+1</f>
+        <v>2117</v>
+      </c>
+      <c r="DP3" s="3">
+        <f t="shared" ref="DP3" si="82">+DO3+1</f>
+        <v>2118</v>
+      </c>
+      <c r="DQ3" s="3">
+        <f t="shared" ref="DQ3" si="83">+DP3+1</f>
+        <v>2119</v>
+      </c>
+      <c r="DR3" s="3">
+        <f t="shared" ref="DR3" si="84">+DQ3+1</f>
+        <v>2120</v>
+      </c>
+      <c r="DS3" s="3">
+        <f t="shared" ref="DS3" si="85">+DR3+1</f>
+        <v>2121</v>
+      </c>
+      <c r="DT3" s="3">
+        <f t="shared" ref="DT3" si="86">+DS3+1</f>
+        <v>2122</v>
+      </c>
+      <c r="DU3" s="3">
+        <f t="shared" ref="DU3" si="87">+DT3+1</f>
+        <v>2123</v>
+      </c>
+      <c r="DV3" s="3">
+        <f t="shared" ref="DV3" si="88">+DU3+1</f>
+        <v>2124</v>
+      </c>
+      <c r="DW3" s="3">
+        <f t="shared" ref="DW3" si="89">+DV3+1</f>
+        <v>2125</v>
+      </c>
+      <c r="DX3" s="3">
+        <f t="shared" ref="DX3" si="90">+DW3+1</f>
+        <v>2126</v>
+      </c>
+      <c r="DY3" s="3">
+        <f t="shared" ref="DY3" si="91">+DX3+1</f>
+        <v>2127</v>
+      </c>
+      <c r="DZ3" s="3">
+        <f t="shared" ref="DZ3" si="92">+DY3+1</f>
+        <v>2128</v>
+      </c>
+      <c r="EA3" s="3">
+        <f t="shared" ref="EA3" si="93">+DZ3+1</f>
+        <v>2129</v>
+      </c>
+      <c r="EB3" s="3">
+        <f t="shared" ref="EB3" si="94">+EA3+1</f>
+        <v>2130</v>
+      </c>
+      <c r="EC3" s="3">
+        <f t="shared" ref="EC3" si="95">+EB3+1</f>
+        <v>2131</v>
+      </c>
+      <c r="ED3" s="3">
+        <f t="shared" ref="ED3" si="96">+EC3+1</f>
+        <v>2132</v>
+      </c>
+      <c r="EE3" s="3">
+        <f t="shared" ref="EE3" si="97">+ED3+1</f>
+        <v>2133</v>
+      </c>
+      <c r="EF3" s="3">
+        <f t="shared" ref="EF3" si="98">+EE3+1</f>
+        <v>2134</v>
+      </c>
+      <c r="EG3" s="3">
+        <f t="shared" ref="EG3" si="99">+EF3+1</f>
+        <v>2135</v>
+      </c>
+      <c r="EH3" s="3">
+        <f t="shared" ref="EH3" si="100">+EG3+1</f>
+        <v>2136</v>
+      </c>
+      <c r="EI3" s="3">
+        <f t="shared" ref="EI3" si="101">+EH3+1</f>
+        <v>2137</v>
+      </c>
+      <c r="EJ3" s="3">
+        <f t="shared" ref="EJ3" si="102">+EI3+1</f>
+        <v>2138</v>
+      </c>
+      <c r="EK3" s="3">
+        <f t="shared" ref="EK3" si="103">+EJ3+1</f>
+        <v>2139</v>
+      </c>
+      <c r="EL3" s="3">
+        <f t="shared" ref="EL3" si="104">+EK3+1</f>
+        <v>2140</v>
+      </c>
+      <c r="EM3" s="3">
+        <f t="shared" ref="EM3" si="105">+EL3+1</f>
+        <v>2141</v>
+      </c>
+      <c r="EN3" s="3">
+        <f t="shared" ref="EN3" si="106">+EM3+1</f>
+        <v>2142</v>
+      </c>
+      <c r="EO3" s="3">
+        <f t="shared" ref="EO3" si="107">+EN3+1</f>
+        <v>2143</v>
+      </c>
+      <c r="EP3" s="3">
+        <f t="shared" ref="EP3" si="108">+EO3+1</f>
+        <v>2144</v>
+      </c>
+      <c r="EQ3" s="3">
+        <f t="shared" ref="EQ3" si="109">+EP3+1</f>
+        <v>2145</v>
+      </c>
+      <c r="ER3" s="3">
+        <f t="shared" ref="ER3" si="110">+EQ3+1</f>
+        <v>2146</v>
+      </c>
+      <c r="ES3" s="3">
+        <f t="shared" ref="ES3" si="111">+ER3+1</f>
+        <v>2147</v>
+      </c>
+      <c r="ET3" s="3">
+        <f t="shared" ref="ET3" si="112">+ES3+1</f>
+        <v>2148</v>
+      </c>
+      <c r="EU3" s="3">
+        <f t="shared" ref="EU3" si="113">+ET3+1</f>
+        <v>2149</v>
+      </c>
+      <c r="EV3" s="3">
+        <f t="shared" ref="EV3" si="114">+EU3+1</f>
+        <v>2150</v>
+      </c>
+      <c r="EW3" s="3">
+        <f t="shared" ref="EW3" si="115">+EV3+1</f>
+        <v>2151</v>
+      </c>
+      <c r="EX3" s="3">
+        <f t="shared" ref="EX3" si="116">+EW3+1</f>
+        <v>2152</v>
+      </c>
+      <c r="EY3" s="3">
+        <f t="shared" ref="EY3" si="117">+EX3+1</f>
+        <v>2153</v>
+      </c>
+      <c r="EZ3" s="3">
+        <f t="shared" ref="EZ3" si="118">+EY3+1</f>
+        <v>2154</v>
+      </c>
+      <c r="FA3" s="3">
+        <f t="shared" ref="FA3" si="119">+EZ3+1</f>
+        <v>2155</v>
+      </c>
+      <c r="FB3" s="3">
+        <f t="shared" ref="FB3" si="120">+FA3+1</f>
+        <v>2156</v>
+      </c>
+      <c r="FC3" s="3">
+        <f t="shared" ref="FC3" si="121">+FB3+1</f>
+        <v>2157</v>
+      </c>
+      <c r="FD3" s="3">
+        <f t="shared" ref="FD3" si="122">+FC3+1</f>
+        <v>2158</v>
+      </c>
+      <c r="FE3" s="3">
+        <f t="shared" ref="FE3" si="123">+FD3+1</f>
+        <v>2159</v>
+      </c>
+      <c r="FF3" s="3">
+        <f t="shared" ref="FF3" si="124">+FE3+1</f>
+        <v>2160</v>
+      </c>
+      <c r="FG3" s="3">
+        <f t="shared" ref="FG3" si="125">+FF3+1</f>
+        <v>2161</v>
+      </c>
+      <c r="FH3" s="3">
+        <f t="shared" ref="FH3" si="126">+FG3+1</f>
+        <v>2162</v>
+      </c>
+      <c r="FI3" s="3">
+        <f t="shared" ref="FI3" si="127">+FH3+1</f>
+        <v>2163</v>
+      </c>
+      <c r="FJ3" s="3">
+        <f t="shared" ref="FJ3" si="128">+FI3+1</f>
+        <v>2164</v>
+      </c>
+      <c r="FK3" s="3">
+        <f t="shared" ref="FK3" si="129">+FJ3+1</f>
+        <v>2165</v>
+      </c>
+      <c r="FL3" s="3">
+        <f t="shared" ref="FL3" si="130">+FK3+1</f>
+        <v>2166</v>
+      </c>
+      <c r="FM3" s="3">
+        <f t="shared" ref="FM3" si="131">+FL3+1</f>
+        <v>2167</v>
+      </c>
+      <c r="FN3" s="3">
+        <f t="shared" ref="FN3" si="132">+FM3+1</f>
+        <v>2168</v>
+      </c>
+      <c r="FO3" s="3">
+        <f t="shared" ref="FO3" si="133">+FN3+1</f>
+        <v>2169</v>
+      </c>
+      <c r="FP3" s="3">
+        <f t="shared" ref="FP3" si="134">+FO3+1</f>
+        <v>2170</v>
+      </c>
+      <c r="FQ3" s="3">
+        <f t="shared" ref="FQ3" si="135">+FP3+1</f>
+        <v>2171</v>
+      </c>
+      <c r="FR3" s="3">
+        <f t="shared" ref="FR3" si="136">+FQ3+1</f>
+        <v>2172</v>
+      </c>
+      <c r="FS3" s="3">
+        <f t="shared" ref="FS3" si="137">+FR3+1</f>
+        <v>2173</v>
+      </c>
+      <c r="FT3" s="3">
+        <f t="shared" ref="FT3" si="138">+FS3+1</f>
+        <v>2174</v>
+      </c>
+      <c r="FU3" s="3">
+        <f t="shared" ref="FU3" si="139">+FT3+1</f>
+        <v>2175</v>
+      </c>
+      <c r="FV3" s="3">
+        <f t="shared" ref="FV3" si="140">+FU3+1</f>
+        <v>2176</v>
+      </c>
+      <c r="FW3" s="3">
+        <f t="shared" ref="FW3" si="141">+FV3+1</f>
+        <v>2177</v>
+      </c>
+      <c r="FX3" s="3">
+        <f t="shared" ref="FX3" si="142">+FW3+1</f>
+        <v>2178</v>
+      </c>
+      <c r="FY3" s="3">
+        <f t="shared" ref="FY3" si="143">+FX3+1</f>
+        <v>2179</v>
+      </c>
+      <c r="FZ3" s="3">
+        <f t="shared" ref="FZ3" si="144">+FY3+1</f>
+        <v>2180</v>
+      </c>
+      <c r="GA3" s="3">
+        <f t="shared" ref="GA3" si="145">+FZ3+1</f>
+        <v>2181</v>
+      </c>
+      <c r="GB3" s="3">
+        <f t="shared" ref="GB3" si="146">+GA3+1</f>
+        <v>2182</v>
+      </c>
+      <c r="GC3" s="3">
+        <f t="shared" ref="GC3" si="147">+GB3+1</f>
+        <v>2183</v>
+      </c>
+      <c r="GD3" s="3">
+        <f t="shared" ref="GD3" si="148">+GC3+1</f>
+        <v>2184</v>
+      </c>
+      <c r="GE3" s="3">
+        <f t="shared" ref="GE3" si="149">+GD3+1</f>
+        <v>2185</v>
+      </c>
+      <c r="GF3" s="3">
+        <f t="shared" ref="GF3" si="150">+GE3+1</f>
+        <v>2186</v>
+      </c>
+      <c r="GG3" s="3">
+        <f t="shared" ref="GG3" si="151">+GF3+1</f>
+        <v>2187</v>
+      </c>
+      <c r="GH3" s="3">
+        <f t="shared" ref="GH3" si="152">+GG3+1</f>
+        <v>2188</v>
+      </c>
+      <c r="GI3" s="3">
+        <f t="shared" ref="GI3" si="153">+GH3+1</f>
+        <v>2189</v>
+      </c>
+      <c r="GJ3" s="3">
+        <f t="shared" ref="GJ3" si="154">+GI3+1</f>
+        <v>2190</v>
+      </c>
+      <c r="GK3" s="3">
+        <f t="shared" ref="GK3" si="155">+GJ3+1</f>
+        <v>2191</v>
+      </c>
+      <c r="GL3" s="3">
+        <f t="shared" ref="GL3" si="156">+GK3+1</f>
+        <v>2192</v>
+      </c>
+      <c r="GM3" s="3">
+        <f t="shared" ref="GM3" si="157">+GL3+1</f>
+        <v>2193</v>
+      </c>
+      <c r="GN3" s="3">
+        <f t="shared" ref="GN3" si="158">+GM3+1</f>
+        <v>2194</v>
+      </c>
+      <c r="GO3" s="3">
+        <f t="shared" ref="GO3" si="159">+GN3+1</f>
+        <v>2195</v>
+      </c>
+      <c r="GP3" s="3">
+        <f t="shared" ref="GP3" si="160">+GO3+1</f>
+        <v>2196</v>
+      </c>
+      <c r="GQ3" s="3">
+        <f t="shared" ref="GQ3" si="161">+GP3+1</f>
+        <v>2197</v>
+      </c>
+      <c r="GR3" s="3">
+        <f t="shared" ref="GR3" si="162">+GQ3+1</f>
+        <v>2198</v>
+      </c>
+      <c r="GS3" s="3">
+        <f t="shared" ref="GS3" si="163">+GR3+1</f>
+        <v>2199</v>
+      </c>
+      <c r="GT3" s="3">
+        <f t="shared" ref="GT3" si="164">+GS3+1</f>
+        <v>2200</v>
+      </c>
+      <c r="GU3" s="3">
+        <f t="shared" ref="GU3" si="165">+GT3+1</f>
+        <v>2201</v>
+      </c>
+      <c r="GV3" s="3">
+        <f t="shared" ref="GV3" si="166">+GU3+1</f>
+        <v>2202</v>
+      </c>
+      <c r="GW3" s="3">
+        <f t="shared" ref="GW3" si="167">+GV3+1</f>
+        <v>2203</v>
+      </c>
+      <c r="GX3" s="3">
+        <f t="shared" ref="GX3" si="168">+GW3+1</f>
+        <v>2204</v>
+      </c>
+      <c r="GY3" s="3">
+        <f t="shared" ref="GY3" si="169">+GX3+1</f>
+        <v>2205</v>
+      </c>
+      <c r="GZ3" s="3">
+        <f t="shared" ref="GZ3" si="170">+GY3+1</f>
+        <v>2206</v>
+      </c>
+      <c r="HA3" s="3">
+        <f t="shared" ref="HA3" si="171">+GZ3+1</f>
+        <v>2207</v>
+      </c>
+      <c r="HB3" s="3">
+        <f t="shared" ref="HB3" si="172">+HA3+1</f>
+        <v>2208</v>
+      </c>
+      <c r="HC3" s="3">
+        <f t="shared" ref="HC3" si="173">+HB3+1</f>
+        <v>2209</v>
+      </c>
+      <c r="HD3" s="3">
+        <f t="shared" ref="HD3" si="174">+HC3+1</f>
+        <v>2210</v>
+      </c>
+      <c r="HE3" s="3">
+        <f t="shared" ref="HE3" si="175">+HD3+1</f>
+        <v>2211</v>
+      </c>
+      <c r="HF3" s="3">
+        <f t="shared" ref="HF3" si="176">+HE3+1</f>
+        <v>2212</v>
+      </c>
+      <c r="HG3" s="3">
+        <f t="shared" ref="HG3" si="177">+HF3+1</f>
+        <v>2213</v>
+      </c>
+      <c r="HH3" s="3">
+        <f t="shared" ref="HH3" si="178">+HG3+1</f>
+        <v>2214</v>
+      </c>
+      <c r="HI3" s="3">
+        <f t="shared" ref="HI3" si="179">+HH3+1</f>
+        <v>2215</v>
+      </c>
+      <c r="HJ3" s="3">
+        <f t="shared" ref="HJ3" si="180">+HI3+1</f>
+        <v>2216</v>
+      </c>
+      <c r="HK3" s="3">
+        <f t="shared" ref="HK3" si="181">+HJ3+1</f>
+        <v>2217</v>
+      </c>
+      <c r="HL3" s="3">
+        <f t="shared" ref="HL3" si="182">+HK3+1</f>
+        <v>2218</v>
+      </c>
+      <c r="HM3" s="3">
+        <f t="shared" ref="HM3" si="183">+HL3+1</f>
+        <v>2219</v>
+      </c>
+      <c r="HN3" s="3">
+        <f t="shared" ref="HN3" si="184">+HM3+1</f>
+        <v>2220</v>
+      </c>
+      <c r="HO3" s="3">
+        <f t="shared" ref="HO3" si="185">+HN3+1</f>
+        <v>2221</v>
+      </c>
+      <c r="HP3" s="3">
+        <f t="shared" ref="HP3" si="186">+HO3+1</f>
+        <v>2222</v>
+      </c>
+      <c r="HQ3" s="3">
+        <f t="shared" ref="HQ3" si="187">+HP3+1</f>
+        <v>2223</v>
+      </c>
+      <c r="HR3" s="3">
+        <f t="shared" ref="HR3" si="188">+HQ3+1</f>
+        <v>2224</v>
+      </c>
+      <c r="HS3" s="3">
+        <f t="shared" ref="HS3" si="189">+HR3+1</f>
+        <v>2225</v>
+      </c>
+      <c r="HT3" s="3">
+        <f t="shared" ref="HT3" si="190">+HS3+1</f>
+        <v>2226</v>
+      </c>
+      <c r="HU3" s="3">
+        <f t="shared" ref="HU3" si="191">+HT3+1</f>
+        <v>2227</v>
+      </c>
+      <c r="HV3" s="3">
+        <f t="shared" ref="HV3" si="192">+HU3+1</f>
+        <v>2228</v>
+      </c>
+      <c r="HW3" s="3">
+        <f t="shared" ref="HW3" si="193">+HV3+1</f>
+        <v>2229</v>
+      </c>
+      <c r="HX3" s="3">
+        <f t="shared" ref="HX3" si="194">+HW3+1</f>
+        <v>2230</v>
+      </c>
+      <c r="HY3" s="3">
+        <f t="shared" ref="HY3" si="195">+HX3+1</f>
+        <v>2231</v>
+      </c>
+      <c r="HZ3" s="3">
+        <f t="shared" ref="HZ3" si="196">+HY3+1</f>
+        <v>2232</v>
+      </c>
+      <c r="IA3" s="3">
+        <f t="shared" ref="IA3" si="197">+HZ3+1</f>
+        <v>2233</v>
+      </c>
+      <c r="IB3" s="3">
+        <f t="shared" ref="IB3:ID3" si="198">+IA3+1</f>
+        <v>2234</v>
+      </c>
+      <c r="IC3" s="3">
+        <f t="shared" si="198"/>
+        <v>2235</v>
+      </c>
+      <c r="ID3" s="3">
+        <f t="shared" si="198"/>
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="4" spans="2:238" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="24">
         <v>3357</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="24">
         <v>8612</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="24">
         <v>11908</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="24">
         <f>+Z4-SUM(C4:E4)</f>
         <v>15073</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="25">
         <v>19392</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="24">
         <v>22604</v>
       </c>
-      <c r="I4" s="3">
-        <v>24644</v>
-      </c>
-      <c r="J4" s="2">
+      <c r="I4" s="24">
+        <v>27644</v>
+      </c>
+      <c r="J4" s="25">
         <f>+AA4-SUM(G4:I4)</f>
-        <v>35556</v>
-      </c>
-      <c r="K4" s="2">
+        <v>32556</v>
+      </c>
+      <c r="K4" s="25">
         <v>34155</v>
+      </c>
+      <c r="L4" s="24">
+        <v>33844</v>
+      </c>
+      <c r="M4" s="24">
+        <v>43028</v>
       </c>
       <c r="Y4" s="2">
         <v>11317</v>
@@ -2145,38 +2986,44 @@
         <v>102196</v>
       </c>
     </row>
-    <row r="5" spans="2:51" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:238" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="24">
         <v>927</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="24">
         <v>1711</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="24">
         <v>2606</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="24">
         <f>+Z5-SUM(C5:E5)</f>
         <v>3331</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="25">
         <v>3171</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="24">
         <v>3668</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="24">
         <v>3127</v>
       </c>
-      <c r="J5" s="2">
-        <f t="shared" ref="J5:J23" si="1">+AA5-SUM(G5:I5)</f>
+      <c r="J5" s="25">
+        <f t="shared" ref="J5:J23" si="199">+AA5-SUM(G5:I5)</f>
         <v>3024</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="25">
         <v>4957</v>
+      </c>
+      <c r="L5" s="24">
+        <v>7252</v>
+      </c>
+      <c r="M5" s="24">
+        <v>8187</v>
       </c>
       <c r="Y5" s="2">
         <v>3688</v>
@@ -2188,45 +3035,53 @@
         <v>12990</v>
       </c>
     </row>
-    <row r="6" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:238" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="2">
-        <f t="shared" ref="C6:I6" si="2">SUM(C4:C5)</f>
+      <c r="C6" s="25">
+        <f t="shared" ref="C6:I6" si="200">SUM(C4:C5)</f>
         <v>4284</v>
       </c>
-      <c r="D6" s="2">
-        <f t="shared" si="2"/>
+      <c r="D6" s="25">
+        <f t="shared" si="200"/>
         <v>10323</v>
       </c>
-      <c r="E6" s="2">
-        <f t="shared" si="2"/>
+      <c r="E6" s="25">
+        <f t="shared" si="200"/>
         <v>14514</v>
       </c>
-      <c r="F6" s="2">
-        <f t="shared" si="2"/>
+      <c r="F6" s="25">
+        <f t="shared" si="200"/>
         <v>18404</v>
       </c>
-      <c r="G6" s="2">
-        <f t="shared" si="2"/>
+      <c r="G6" s="25">
+        <f t="shared" si="200"/>
         <v>22563</v>
       </c>
-      <c r="H6" s="2">
-        <f t="shared" si="2"/>
+      <c r="H6" s="25">
+        <f t="shared" si="200"/>
         <v>26272</v>
       </c>
-      <c r="I6" s="2">
-        <f t="shared" si="2"/>
-        <v>27771</v>
-      </c>
-      <c r="J6" s="2">
-        <f t="shared" si="1"/>
-        <v>38580</v>
-      </c>
-      <c r="K6" s="2">
+      <c r="I6" s="25">
+        <f t="shared" si="200"/>
+        <v>30771</v>
+      </c>
+      <c r="J6" s="25">
+        <f t="shared" si="199"/>
+        <v>35580</v>
+      </c>
+      <c r="K6" s="25">
         <f>SUM(K4:K5)</f>
         <v>39112</v>
+      </c>
+      <c r="L6" s="25">
+        <f>SUM(L4:L5)</f>
+        <v>41096</v>
+      </c>
+      <c r="M6" s="25">
+        <f>SUM(M4:M5)</f>
+        <v>51215</v>
       </c>
       <c r="U6" s="2">
         <v>2932</v>
@@ -2253,38 +3108,44 @@
         <v>115186</v>
       </c>
     </row>
-    <row r="7" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:238" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="25">
         <v>2240</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="25">
         <v>2486</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="25">
         <v>2856</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="24">
         <f>+Z7-SUM(C7:E7)</f>
         <v>2865</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="25">
         <v>2647</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="25">
         <v>2880</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="25">
         <v>3279</v>
       </c>
-      <c r="J7" s="2">
-        <f t="shared" si="1"/>
+      <c r="J7" s="25">
+        <f t="shared" si="199"/>
         <v>2544</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="25">
         <v>3763</v>
+      </c>
+      <c r="L7" s="25">
+        <v>4287</v>
+      </c>
+      <c r="M7" s="25">
+        <v>4265</v>
       </c>
       <c r="U7" s="2">
         <v>6246</v>
@@ -2308,38 +3169,44 @@
         <v>11350</v>
       </c>
     </row>
-    <row r="8" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:238" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="25">
         <v>295</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="25">
         <v>379</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="25">
         <v>416</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="24">
         <f>+Z8-SUM(C8:E8)</f>
         <v>463</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="25">
         <v>427</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="25">
         <v>454</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="25">
         <v>486</v>
       </c>
-      <c r="J8" s="2">
-        <f t="shared" si="1"/>
+      <c r="J8" s="25">
+        <f t="shared" si="199"/>
         <v>511</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="25">
         <v>509</v>
+      </c>
+      <c r="L8" s="25">
+        <v>601</v>
+      </c>
+      <c r="M8" s="25">
+        <v>760</v>
       </c>
       <c r="U8" s="2">
         <v>1130</v>
@@ -2363,38 +3230,44 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="9" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:238" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="25">
         <v>296</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="25">
         <v>253</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="25">
         <v>261</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="24">
         <f>+Z9-SUM(C9:E9)</f>
         <v>281</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="25">
         <v>329</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="25">
         <v>346</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="25">
         <v>449</v>
       </c>
-      <c r="J9" s="2">
-        <f t="shared" si="1"/>
+      <c r="J9" s="25">
+        <f t="shared" si="199"/>
         <v>570</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="25">
         <v>567</v>
+      </c>
+      <c r="L9" s="25">
+        <v>586</v>
+      </c>
+      <c r="M9" s="25">
+        <v>592</v>
       </c>
       <c r="U9" s="2">
         <v>641</v>
@@ -2418,38 +3291,44 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="10" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:238" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="25">
         <v>77</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="25">
         <v>66</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="25">
         <v>73</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="24">
         <f>+Z10-SUM(C10:E10)</f>
         <v>90</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="25">
         <v>78</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="25">
         <v>88</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="25">
         <v>97</v>
       </c>
-      <c r="J10" s="2">
-        <f t="shared" si="1"/>
+      <c r="J10" s="25">
+        <f t="shared" si="199"/>
         <v>126</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="25">
         <v>111</v>
+      </c>
+      <c r="L10" s="25">
+        <v>173</v>
+      </c>
+      <c r="M10" s="25">
+        <v>174</v>
       </c>
       <c r="U10" s="2">
         <v>767</v>
@@ -2473,137 +3352,173 @@
         <v>389</v>
       </c>
     </row>
-    <row r="11" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:238" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="5">
-        <f t="shared" ref="C11:I11" si="3">SUM(C6:C10)</f>
+      <c r="C11" s="26">
+        <f t="shared" ref="C11:I11" si="201">SUM(C6:C10)</f>
         <v>7192</v>
       </c>
-      <c r="D11" s="5">
-        <f t="shared" si="3"/>
+      <c r="D11" s="26">
+        <f t="shared" si="201"/>
         <v>13507</v>
       </c>
-      <c r="E11" s="5">
-        <f t="shared" si="3"/>
+      <c r="E11" s="26">
+        <f t="shared" si="201"/>
         <v>18120</v>
       </c>
-      <c r="F11" s="5">
-        <f t="shared" si="3"/>
+      <c r="F11" s="26">
+        <f t="shared" si="201"/>
         <v>22103</v>
       </c>
-      <c r="G11" s="5">
-        <f t="shared" si="3"/>
+      <c r="G11" s="26">
+        <f t="shared" si="201"/>
         <v>26044</v>
       </c>
-      <c r="H11" s="5">
-        <f t="shared" si="3"/>
+      <c r="H11" s="26">
+        <f t="shared" si="201"/>
         <v>30040</v>
       </c>
-      <c r="I11" s="5">
-        <f t="shared" si="3"/>
-        <v>32082</v>
-      </c>
-      <c r="J11" s="5">
-        <f t="shared" si="1"/>
-        <v>42331</v>
-      </c>
-      <c r="K11" s="5">
+      <c r="I11" s="26">
+        <f t="shared" si="201"/>
+        <v>35082</v>
+      </c>
+      <c r="J11" s="26">
+        <f t="shared" si="199"/>
+        <v>39331</v>
+      </c>
+      <c r="K11" s="26">
         <f>SUM(K6:K10)</f>
         <v>44062</v>
       </c>
-      <c r="L11" s="5">
-        <f>AVERAGE(45000*0.98,45000*1.02)</f>
-        <v>45000</v>
-      </c>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
+      <c r="L11" s="26">
+        <f>SUM(L6:L10)</f>
+        <v>46743</v>
+      </c>
+      <c r="M11" s="26">
+        <f>SUM(M6:M10)</f>
+        <v>57006</v>
+      </c>
+      <c r="N11" s="5">
+        <f>AVERAGE(65*0.98,65*1.02) * 1000</f>
+        <v>65000</v>
+      </c>
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
       <c r="S11" s="5"/>
       <c r="T11" s="5"/>
       <c r="U11" s="5">
-        <f t="shared" ref="U11:AA11" si="4">SUM(U6:U10)</f>
+        <f t="shared" ref="U11:AA11" si="202">SUM(U6:U10)</f>
         <v>11716</v>
       </c>
       <c r="V11" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="202"/>
         <v>10918</v>
       </c>
       <c r="W11" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="202"/>
         <v>16675</v>
       </c>
       <c r="X11" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="202"/>
         <v>26914</v>
       </c>
       <c r="Y11" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="202"/>
         <v>26974</v>
       </c>
       <c r="Z11" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="202"/>
         <v>60922</v>
       </c>
       <c r="AA11" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="202"/>
         <v>130497</v>
       </c>
       <c r="AB11" s="5">
-        <v>176000</v>
-      </c>
-      <c r="AC11" s="5"/>
-      <c r="AD11" s="5"/>
-      <c r="AE11" s="5"/>
-      <c r="AF11" s="5"/>
-      <c r="AG11" s="5"/>
-      <c r="AH11" s="5"/>
-      <c r="AI11" s="5"/>
-      <c r="AJ11" s="5"/>
-      <c r="AK11" s="5"/>
-    </row>
-    <row r="12" spans="2:51" x14ac:dyDescent="0.2">
+        <f>SUM(K11:N11)</f>
+        <v>212811</v>
+      </c>
+      <c r="AC11" s="5">
+        <f>+AB11*1.4</f>
+        <v>297935.39999999997</v>
+      </c>
+      <c r="AD11" s="5">
+        <f t="shared" ref="AD11" si="203">+AC11*1.4</f>
+        <v>417109.55999999994</v>
+      </c>
+      <c r="AE11" s="5">
+        <f>+AD11*1.2</f>
+        <v>500531.47199999989</v>
+      </c>
+      <c r="AF11" s="5">
+        <f t="shared" ref="AF11" si="204">+AE11*1.2</f>
+        <v>600637.76639999985</v>
+      </c>
+      <c r="AG11" s="5">
+        <f>+AF11*1.1</f>
+        <v>660701.5430399999</v>
+      </c>
+      <c r="AH11" s="5">
+        <f>+AG11*1.1</f>
+        <v>726771.69734399999</v>
+      </c>
+      <c r="AI11" s="5">
+        <f>+AH11*1.1</f>
+        <v>799448.8670784001</v>
+      </c>
+      <c r="AJ11" s="5">
+        <f>+AI11*1.1</f>
+        <v>879393.75378624024</v>
+      </c>
+      <c r="AK11" s="5">
+        <f>+AJ11*1.1</f>
+        <v>967333.12916486431</v>
+      </c>
+    </row>
+    <row r="12" spans="2:238" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="25">
         <v>2544</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="25">
         <v>4045</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="25">
         <v>4720</v>
       </c>
-      <c r="F12" s="3">
-        <f t="shared" ref="F12:F18" si="5">+Z12-SUM(C12:E12)</f>
+      <c r="F12" s="24">
+        <f t="shared" ref="F12:F18" si="205">+Z12-SUM(C12:E12)</f>
         <v>5312</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="25">
         <v>5638</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="25">
         <v>7466</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="25">
         <v>8926</v>
       </c>
-      <c r="J12" s="2">
-        <f t="shared" si="1"/>
+      <c r="J12" s="25">
+        <f t="shared" si="199"/>
         <v>10609</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="25">
         <v>17394</v>
       </c>
-      <c r="L12" s="2">
-        <f>+L11*0.29</f>
-        <v>13050</v>
-      </c>
-      <c r="P12" s="2">
-        <f>44*4</f>
-        <v>176</v>
+      <c r="L12" s="25">
+        <v>12890</v>
+      </c>
+      <c r="M12" s="25">
+        <v>15157</v>
+      </c>
+      <c r="N12" s="2">
+        <f>+N11*0.26</f>
+        <v>16900</v>
       </c>
       <c r="U12" s="2">
         <v>4545</v>
@@ -2627,45 +3542,87 @@
         <v>32639</v>
       </c>
       <c r="AB12" s="2">
-        <f>+AB11*0.71</f>
-        <v>124960</v>
-      </c>
-    </row>
-    <row r="13" spans="2:51" x14ac:dyDescent="0.2">
+        <f>SUM(K12:N12)</f>
+        <v>62341</v>
+      </c>
+      <c r="AC12" s="2">
+        <f>+AC$11*(AB12/AB$11)</f>
+        <v>87277.39999999998</v>
+      </c>
+      <c r="AD12" s="2">
+        <f t="shared" ref="AD12:AK12" si="206">+AD$11*(AC12/AC$11)</f>
+        <v>122188.35999999997</v>
+      </c>
+      <c r="AE12" s="2">
+        <f t="shared" si="206"/>
+        <v>146626.03199999995</v>
+      </c>
+      <c r="AF12" s="2">
+        <f t="shared" si="206"/>
+        <v>175951.23839999991</v>
+      </c>
+      <c r="AG12" s="2">
+        <f t="shared" si="206"/>
+        <v>193546.36223999993</v>
+      </c>
+      <c r="AH12" s="2">
+        <f t="shared" si="206"/>
+        <v>212900.99846399995</v>
+      </c>
+      <c r="AI12" s="2">
+        <f t="shared" si="206"/>
+        <v>234191.09831039998</v>
+      </c>
+      <c r="AJ12" s="2">
+        <f t="shared" si="206"/>
+        <v>257610.20814144</v>
+      </c>
+      <c r="AK12" s="2">
+        <f t="shared" si="206"/>
+        <v>283371.228955584</v>
+      </c>
+    </row>
+    <row r="13" spans="2:238" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="25">
         <v>1875</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="25">
         <v>2040</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="25">
         <v>2294</v>
       </c>
-      <c r="F13" s="3">
-        <f t="shared" si="5"/>
+      <c r="F13" s="24">
+        <f t="shared" si="205"/>
         <v>2466</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="25">
         <v>2720</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="25">
         <v>3090</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="25">
         <v>3390</v>
       </c>
-      <c r="J13" s="2">
-        <f t="shared" si="1"/>
+      <c r="J13" s="25">
+        <f t="shared" si="199"/>
         <v>3714</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13" s="25">
         <v>3989</v>
       </c>
-      <c r="L13" s="2">
-        <v>4500</v>
+      <c r="L13" s="25">
+        <v>4291</v>
+      </c>
+      <c r="M13" s="25">
+        <v>4705</v>
+      </c>
+      <c r="N13" s="2">
+        <v>5000</v>
       </c>
       <c r="U13" s="2">
         <v>2376</v>
@@ -2689,45 +3646,87 @@
         <v>12914</v>
       </c>
       <c r="AB13" s="2">
-        <f>8.5*2*10^3</f>
-        <v>17000</v>
-      </c>
-    </row>
-    <row r="14" spans="2:51" x14ac:dyDescent="0.2">
+        <f>SUM(K13:N13)</f>
+        <v>17985</v>
+      </c>
+      <c r="AC13" s="2">
+        <f>+AC$11*(AB13/AB$11)</f>
+        <v>25178.999999999996</v>
+      </c>
+      <c r="AD13" s="2">
+        <f t="shared" ref="AD13:AK13" si="207">+AD$11*(AC13/AC$11)</f>
+        <v>35250.599999999991</v>
+      </c>
+      <c r="AE13" s="2">
+        <f t="shared" si="207"/>
+        <v>42300.719999999987</v>
+      </c>
+      <c r="AF13" s="2">
+        <f t="shared" si="207"/>
+        <v>50760.863999999987</v>
+      </c>
+      <c r="AG13" s="2">
+        <f t="shared" si="207"/>
+        <v>55836.950399999987</v>
+      </c>
+      <c r="AH13" s="2">
+        <f t="shared" si="207"/>
+        <v>61420.64544</v>
+      </c>
+      <c r="AI13" s="2">
+        <f t="shared" si="207"/>
+        <v>67562.709984000001</v>
+      </c>
+      <c r="AJ13" s="2">
+        <f t="shared" si="207"/>
+        <v>74318.980982400011</v>
+      </c>
+      <c r="AK13" s="2">
+        <f t="shared" si="207"/>
+        <v>81750.879080640007</v>
+      </c>
+    </row>
+    <row r="14" spans="2:238" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="25">
         <v>633</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="25">
         <v>622</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="25">
         <v>689</v>
       </c>
-      <c r="F14" s="3">
-        <f t="shared" si="5"/>
+      <c r="F14" s="24">
+        <f t="shared" si="205"/>
         <v>710</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="25">
         <v>777</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="25">
         <v>842</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="25">
         <v>897</v>
       </c>
-      <c r="J14" s="2">
-        <f t="shared" si="1"/>
+      <c r="J14" s="25">
+        <f t="shared" si="199"/>
         <v>975</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K14" s="25">
         <v>1041</v>
       </c>
-      <c r="L14" s="2">
-        <v>1200</v>
+      <c r="L14" s="25">
+        <v>1122</v>
+      </c>
+      <c r="M14" s="25">
+        <v>1134</v>
+      </c>
+      <c r="N14" s="2">
+        <v>1700</v>
       </c>
       <c r="U14" s="2">
         <v>991</v>
@@ -2751,118 +3750,209 @@
         <v>3491</v>
       </c>
       <c r="AB14" s="2">
-        <v>4400</v>
-      </c>
-    </row>
-    <row r="15" spans="2:51" x14ac:dyDescent="0.2">
+        <f t="shared" ref="AB14:AB23" si="208">SUM(K14:N14)</f>
+        <v>4997</v>
+      </c>
+      <c r="AC14" s="2">
+        <f>+AC$11*(AB14/AB$11)</f>
+        <v>6995.7999999999993</v>
+      </c>
+      <c r="AD14" s="2">
+        <f t="shared" ref="AD14:AK14" si="209">+AD$11*(AC14/AC$11)</f>
+        <v>9794.119999999999</v>
+      </c>
+      <c r="AE14" s="2">
+        <f t="shared" si="209"/>
+        <v>11752.943999999998</v>
+      </c>
+      <c r="AF14" s="2">
+        <f t="shared" si="209"/>
+        <v>14103.532799999997</v>
+      </c>
+      <c r="AG14" s="2">
+        <f t="shared" si="209"/>
+        <v>15513.886079999998</v>
+      </c>
+      <c r="AH14" s="2">
+        <f t="shared" si="209"/>
+        <v>17065.274688000001</v>
+      </c>
+      <c r="AI14" s="2">
+        <f t="shared" si="209"/>
+        <v>18771.802156800004</v>
+      </c>
+      <c r="AJ14" s="2">
+        <f t="shared" si="209"/>
+        <v>20648.982372480008</v>
+      </c>
+      <c r="AK14" s="2">
+        <f t="shared" si="209"/>
+        <v>22713.88060972801</v>
+      </c>
+    </row>
+    <row r="15" spans="2:238" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="25">
         <f>+C11-SUM(C12:C14)</f>
         <v>2140</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="25">
         <f>+D11-SUM(D12:D14)</f>
         <v>6800</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="25">
         <f>+E11-SUM(E12:E14)</f>
         <v>10417</v>
       </c>
-      <c r="F15" s="3">
-        <f t="shared" si="5"/>
+      <c r="F15" s="24">
+        <f t="shared" si="205"/>
         <v>13615</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="25">
         <f>+G11-SUM(G12:G14)</f>
         <v>16909</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="25">
         <f>+H11-SUM(H12:H14)</f>
         <v>18642</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="25">
         <f>+I11-SUM(I12:I14)</f>
-        <v>18869</v>
-      </c>
-      <c r="J15" s="2">
-        <f t="shared" si="1"/>
-        <v>27033</v>
-      </c>
-      <c r="K15" s="2">
+        <v>21869</v>
+      </c>
+      <c r="J15" s="25">
+        <f t="shared" si="199"/>
+        <v>24033</v>
+      </c>
+      <c r="K15" s="25">
         <f>+K11-SUM(K12:K14)</f>
         <v>21638</v>
       </c>
-      <c r="L15" s="2">
+      <c r="L15" s="25">
         <f>+L11-SUM(L12:L14)</f>
-        <v>26250</v>
+        <v>28440</v>
+      </c>
+      <c r="M15" s="25">
+        <f>+M11-SUM(M12:M14)</f>
+        <v>36010</v>
+      </c>
+      <c r="N15" s="25">
+        <f>+N11-SUM(N12:N14)</f>
+        <v>41400</v>
       </c>
       <c r="U15" s="2">
-        <f t="shared" ref="U15:AB15" si="6">+U11-SUM(U12:U14)</f>
+        <f t="shared" ref="U15:AC15" si="210">+U11-SUM(U12:U14)</f>
         <v>3804</v>
       </c>
       <c r="V15" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="210"/>
         <v>2846</v>
       </c>
       <c r="W15" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="210"/>
         <v>4532</v>
       </c>
       <c r="X15" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="210"/>
         <v>10041</v>
       </c>
       <c r="Y15" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="210"/>
         <v>5577</v>
       </c>
       <c r="Z15" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="210"/>
         <v>32972</v>
       </c>
       <c r="AA15" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="210"/>
         <v>81453</v>
       </c>
       <c r="AB15" s="2">
-        <f t="shared" si="6"/>
-        <v>29640</v>
-      </c>
-    </row>
-    <row r="16" spans="2:51" x14ac:dyDescent="0.2">
+        <f t="shared" si="208"/>
+        <v>127488</v>
+      </c>
+      <c r="AC15" s="2">
+        <f t="shared" si="210"/>
+        <v>178483.19999999998</v>
+      </c>
+      <c r="AD15" s="2">
+        <f t="shared" ref="AD15:AK15" si="211">+AD11-SUM(AD12:AD14)</f>
+        <v>249876.47999999998</v>
+      </c>
+      <c r="AE15" s="2">
+        <f t="shared" si="211"/>
+        <v>299851.77599999995</v>
+      </c>
+      <c r="AF15" s="2">
+        <f t="shared" si="211"/>
+        <v>359822.13119999995</v>
+      </c>
+      <c r="AG15" s="2">
+        <f t="shared" si="211"/>
+        <v>395804.34431999997</v>
+      </c>
+      <c r="AH15" s="2">
+        <f t="shared" si="211"/>
+        <v>435384.77875200007</v>
+      </c>
+      <c r="AI15" s="2">
+        <f t="shared" si="211"/>
+        <v>478923.25662720011</v>
+      </c>
+      <c r="AJ15" s="2">
+        <f t="shared" si="211"/>
+        <v>526815.58228992019</v>
+      </c>
+      <c r="AK15" s="2">
+        <f t="shared" si="211"/>
+        <v>579497.14051891235</v>
+      </c>
+    </row>
+    <row r="16" spans="2:238" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="25">
         <v>150</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="25">
         <v>187</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="25">
         <v>234</v>
       </c>
-      <c r="F16" s="3">
-        <f t="shared" si="5"/>
+      <c r="F16" s="24">
+        <f t="shared" si="205"/>
         <v>295</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="25">
         <v>515</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="25">
         <v>444</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="25">
         <v>472</v>
       </c>
-      <c r="J16" s="2">
-        <f t="shared" si="1"/>
+      <c r="J16" s="25">
+        <f t="shared" si="199"/>
         <v>355</v>
       </c>
-      <c r="K16" s="2">
+      <c r="K16" s="25">
         <v>515</v>
+      </c>
+      <c r="L16" s="25">
+        <v>592</v>
+      </c>
+      <c r="M16" s="25">
+        <v>624</v>
+      </c>
+      <c r="N16" s="2">
+        <f>+N$15*(M16/M$15)</f>
+        <v>717.40072202166061</v>
       </c>
       <c r="U16" s="2">
         <v>136</v>
@@ -2885,39 +3975,89 @@
       <c r="AA16" s="2">
         <v>1786</v>
       </c>
-    </row>
-    <row r="17" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB16" s="2">
+        <f t="shared" si="208"/>
+        <v>2448.4007220216608</v>
+      </c>
+      <c r="AC16" s="2">
+        <f>+AB16</f>
+        <v>2448.4007220216608</v>
+      </c>
+      <c r="AD16" s="2">
+        <f t="shared" ref="AD16:AK16" si="212">+AC16</f>
+        <v>2448.4007220216608</v>
+      </c>
+      <c r="AE16" s="2">
+        <f t="shared" si="212"/>
+        <v>2448.4007220216608</v>
+      </c>
+      <c r="AF16" s="2">
+        <f t="shared" si="212"/>
+        <v>2448.4007220216608</v>
+      </c>
+      <c r="AG16" s="2">
+        <f t="shared" si="212"/>
+        <v>2448.4007220216608</v>
+      </c>
+      <c r="AH16" s="2">
+        <f t="shared" si="212"/>
+        <v>2448.4007220216608</v>
+      </c>
+      <c r="AI16" s="2">
+        <f t="shared" si="212"/>
+        <v>2448.4007220216608</v>
+      </c>
+      <c r="AJ16" s="2">
+        <f t="shared" si="212"/>
+        <v>2448.4007220216608</v>
+      </c>
+      <c r="AK16" s="2">
+        <f t="shared" si="212"/>
+        <v>2448.4007220216608</v>
+      </c>
+    </row>
+    <row r="17" spans="2:238" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="25">
         <v>-66</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="25">
         <v>-65</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="25">
         <v>-63</v>
       </c>
-      <c r="F17" s="3">
-        <f t="shared" si="5"/>
+      <c r="F17" s="24">
+        <f t="shared" si="205"/>
         <v>-63</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="25">
         <v>-63</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="25">
         <v>-61</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="25">
         <v>-61</v>
       </c>
-      <c r="J17" s="2">
-        <f t="shared" si="1"/>
+      <c r="J17" s="25">
+        <f t="shared" si="199"/>
         <v>-62</v>
       </c>
-      <c r="K17" s="2">
+      <c r="K17" s="25">
         <v>-63</v>
+      </c>
+      <c r="L17" s="25">
+        <v>62</v>
+      </c>
+      <c r="M17" s="25">
+        <v>-61</v>
+      </c>
+      <c r="N17" s="2">
+        <f>+N$15*(M17/M$15)</f>
+        <v>-70.130519300194393</v>
       </c>
       <c r="U17" s="2">
         <v>-58</v>
@@ -2940,42 +4080,88 @@
       <c r="AA17" s="2">
         <v>-247</v>
       </c>
-    </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB17" s="2">
+        <f t="shared" si="208"/>
+        <v>-132.13051930019441</v>
+      </c>
+      <c r="AC17" s="2">
+        <f>+AB17</f>
+        <v>-132.13051930019441</v>
+      </c>
+      <c r="AD17" s="2">
+        <f t="shared" ref="AD17:AK17" si="213">+AC17</f>
+        <v>-132.13051930019441</v>
+      </c>
+      <c r="AE17" s="2">
+        <f t="shared" si="213"/>
+        <v>-132.13051930019441</v>
+      </c>
+      <c r="AF17" s="2">
+        <f t="shared" si="213"/>
+        <v>-132.13051930019441</v>
+      </c>
+      <c r="AG17" s="2">
+        <f t="shared" si="213"/>
+        <v>-132.13051930019441</v>
+      </c>
+      <c r="AH17" s="2">
+        <f t="shared" si="213"/>
+        <v>-132.13051930019441</v>
+      </c>
+      <c r="AI17" s="2">
+        <f t="shared" si="213"/>
+        <v>-132.13051930019441</v>
+      </c>
+      <c r="AJ17" s="2">
+        <f t="shared" si="213"/>
+        <v>-132.13051930019441</v>
+      </c>
+      <c r="AK17" s="2">
+        <f t="shared" si="213"/>
+        <v>-132.13051930019441</v>
+      </c>
+    </row>
+    <row r="18" spans="2:238" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="25">
         <v>-15</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="25">
         <v>59</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="25">
         <v>-66</v>
       </c>
-      <c r="F18" s="3">
-        <f t="shared" si="5"/>
+      <c r="F18" s="24">
+        <f t="shared" si="205"/>
         <v>259</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="25">
         <v>-180</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="25">
         <v>189</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18" s="25">
         <v>36</v>
       </c>
-      <c r="J18" s="2">
-        <f t="shared" si="1"/>
+      <c r="J18" s="25">
+        <f t="shared" si="199"/>
         <v>989</v>
       </c>
-      <c r="K18" s="2">
+      <c r="K18" s="25">
         <v>-180</v>
       </c>
-      <c r="L18" s="2">
-        <v>450</v>
+      <c r="L18" s="25">
+        <v>2236</v>
+      </c>
+      <c r="M18" s="25">
+        <v>1363</v>
+      </c>
+      <c r="N18" s="2">
+        <v>500</v>
       </c>
       <c r="U18" s="2">
         <v>14</v>
@@ -2999,122 +4185,209 @@
         <v>1034</v>
       </c>
       <c r="AB18" s="2">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.2">
+        <f t="shared" si="208"/>
+        <v>3919</v>
+      </c>
+      <c r="AC18" s="2">
+        <f>+AB18</f>
+        <v>3919</v>
+      </c>
+      <c r="AD18" s="2">
+        <f t="shared" ref="AD18:AK18" si="214">+AC18</f>
+        <v>3919</v>
+      </c>
+      <c r="AE18" s="2">
+        <f t="shared" si="214"/>
+        <v>3919</v>
+      </c>
+      <c r="AF18" s="2">
+        <f t="shared" si="214"/>
+        <v>3919</v>
+      </c>
+      <c r="AG18" s="2">
+        <f t="shared" si="214"/>
+        <v>3919</v>
+      </c>
+      <c r="AH18" s="2">
+        <f t="shared" si="214"/>
+        <v>3919</v>
+      </c>
+      <c r="AI18" s="2">
+        <f t="shared" si="214"/>
+        <v>3919</v>
+      </c>
+      <c r="AJ18" s="2">
+        <f t="shared" si="214"/>
+        <v>3919</v>
+      </c>
+      <c r="AK18" s="2">
+        <f t="shared" si="214"/>
+        <v>3919</v>
+      </c>
+    </row>
+    <row r="19" spans="2:238" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="2">
-        <f t="shared" ref="C19:I19" si="7">+SUM(C15:C18)</f>
+      <c r="C19" s="25">
+        <f t="shared" ref="C19:I19" si="215">+SUM(C15:C18)</f>
         <v>2209</v>
       </c>
-      <c r="D19" s="2">
-        <f t="shared" si="7"/>
+      <c r="D19" s="25">
+        <f t="shared" si="215"/>
         <v>6981</v>
       </c>
-      <c r="E19" s="2">
-        <f t="shared" si="7"/>
+      <c r="E19" s="25">
+        <f t="shared" si="215"/>
         <v>10522</v>
       </c>
-      <c r="F19" s="2">
-        <f t="shared" si="7"/>
+      <c r="F19" s="25">
+        <f t="shared" si="215"/>
         <v>14106</v>
       </c>
-      <c r="G19" s="2">
-        <f t="shared" si="7"/>
+      <c r="G19" s="25">
+        <f t="shared" si="215"/>
         <v>17181</v>
       </c>
-      <c r="H19" s="2">
-        <f t="shared" si="7"/>
+      <c r="H19" s="25">
+        <f t="shared" si="215"/>
         <v>19214</v>
       </c>
-      <c r="I19" s="2">
-        <f t="shared" si="7"/>
-        <v>19316</v>
-      </c>
-      <c r="J19" s="2">
-        <f t="shared" si="1"/>
-        <v>28315</v>
-      </c>
-      <c r="K19" s="2">
+      <c r="I19" s="25">
+        <f t="shared" si="215"/>
+        <v>22316</v>
+      </c>
+      <c r="J19" s="25">
+        <f t="shared" si="199"/>
+        <v>25315</v>
+      </c>
+      <c r="K19" s="25">
         <f>+SUM(K15:K18)</f>
         <v>21910</v>
       </c>
-      <c r="L19" s="2">
+      <c r="L19" s="25">
         <f>+SUM(L15:L18)</f>
-        <v>26700</v>
+        <v>31330</v>
+      </c>
+      <c r="M19" s="25">
+        <f>+SUM(M15:M18)</f>
+        <v>37936</v>
+      </c>
+      <c r="N19" s="25">
+        <f>+SUM(N15:N18)</f>
+        <v>42547.270202721462</v>
       </c>
       <c r="U19" s="2">
-        <f t="shared" ref="U19:AB19" si="8">+SUM(U15:U18)</f>
+        <f t="shared" ref="U19:AC19" si="216">+SUM(U15:U18)</f>
         <v>3896</v>
       </c>
       <c r="V19" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="216"/>
         <v>2970</v>
       </c>
       <c r="W19" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="216"/>
         <v>4409</v>
       </c>
       <c r="X19" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="216"/>
         <v>9941</v>
       </c>
       <c r="Y19" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="216"/>
         <v>5534</v>
       </c>
       <c r="Z19" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="216"/>
         <v>33818</v>
       </c>
       <c r="AA19" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="216"/>
         <v>84026</v>
       </c>
       <c r="AB19" s="2">
-        <f t="shared" si="8"/>
-        <v>30240</v>
-      </c>
-    </row>
-    <row r="20" spans="2:28" x14ac:dyDescent="0.2">
+        <f t="shared" si="208"/>
+        <v>133723.27020272147</v>
+      </c>
+      <c r="AC19" s="2">
+        <f t="shared" si="216"/>
+        <v>184718.47020272145</v>
+      </c>
+      <c r="AD19" s="2">
+        <f t="shared" ref="AD19:AK19" si="217">+SUM(AD15:AD18)</f>
+        <v>256111.75020272145</v>
+      </c>
+      <c r="AE19" s="2">
+        <f t="shared" si="217"/>
+        <v>306087.04620272142</v>
+      </c>
+      <c r="AF19" s="2">
+        <f t="shared" si="217"/>
+        <v>366057.40140272141</v>
+      </c>
+      <c r="AG19" s="2">
+        <f t="shared" si="217"/>
+        <v>402039.61452272144</v>
+      </c>
+      <c r="AH19" s="2">
+        <f t="shared" si="217"/>
+        <v>441620.04895472154</v>
+      </c>
+      <c r="AI19" s="2">
+        <f t="shared" si="217"/>
+        <v>485158.52682992158</v>
+      </c>
+      <c r="AJ19" s="2">
+        <f t="shared" si="217"/>
+        <v>533050.85249264166</v>
+      </c>
+      <c r="AK19" s="2">
+        <f t="shared" si="217"/>
+        <v>585732.41072163382</v>
+      </c>
+    </row>
+    <row r="20" spans="2:238" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="25">
         <v>166</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="25">
         <v>793</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="25">
         <v>1279</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="24">
         <f>+Z20-SUM(C20:E20)</f>
         <v>1820</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" s="25">
         <v>3135</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="25">
         <v>2615</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I20" s="25">
         <v>3007</v>
       </c>
-      <c r="J20" s="2">
-        <f t="shared" si="1"/>
+      <c r="J20" s="25">
+        <f t="shared" si="199"/>
         <v>-7611</v>
       </c>
-      <c r="K20" s="2">
+      <c r="K20" s="25">
         <v>3135</v>
       </c>
-      <c r="L20" s="2">
-        <f>+L19*0.165</f>
-        <v>4405.5</v>
+      <c r="L20" s="25">
+        <v>4784</v>
+      </c>
+      <c r="M20" s="25">
+        <v>6026</v>
+      </c>
+      <c r="N20" s="2">
+        <f>+N19*(M20/M19)</f>
+        <v>6758.4840320961493</v>
       </c>
       <c r="U20" s="2">
         <v>-245</v>
@@ -3138,123 +4411,1013 @@
         <v>1146</v>
       </c>
       <c r="AB20" s="2">
-        <f>+AB19*0.16</f>
-        <v>4838.4000000000005</v>
-      </c>
-    </row>
-    <row r="21" spans="2:28" x14ac:dyDescent="0.2">
+        <f t="shared" si="208"/>
+        <v>20703.484032096148</v>
+      </c>
+      <c r="AC20" s="2">
+        <f>+AC19*(AB20/AB19)</f>
+        <v>28598.731488376667</v>
+      </c>
+      <c r="AD20" s="2">
+        <f t="shared" ref="AD20:AK20" si="218">+AD19*(AC20/AC19)</f>
+        <v>39652.077927169397</v>
+      </c>
+      <c r="AE20" s="2">
+        <f t="shared" si="218"/>
+        <v>47389.420434324304</v>
+      </c>
+      <c r="AF20" s="2">
+        <f t="shared" si="218"/>
+        <v>56674.23144291019</v>
+      </c>
+      <c r="AG20" s="2">
+        <f t="shared" si="218"/>
+        <v>62245.118048061733</v>
+      </c>
+      <c r="AH20" s="2">
+        <f t="shared" si="218"/>
+        <v>68373.09331372843</v>
+      </c>
+      <c r="AI20" s="2">
+        <f t="shared" si="218"/>
+        <v>75113.866105961788</v>
+      </c>
+      <c r="AJ20" s="2">
+        <f t="shared" si="218"/>
+        <v>82528.716177418493</v>
+      </c>
+      <c r="AK20" s="2">
+        <f t="shared" si="218"/>
+        <v>90685.051256020874</v>
+      </c>
+    </row>
+    <row r="21" spans="2:238" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="2">
-        <f t="shared" ref="C21:I21" si="9">+C19-C20</f>
+      <c r="C21" s="25">
+        <f t="shared" ref="C21:I21" si="219">+C19-C20</f>
         <v>2043</v>
       </c>
-      <c r="D21" s="2">
-        <f t="shared" si="9"/>
+      <c r="D21" s="25">
+        <f t="shared" si="219"/>
         <v>6188</v>
       </c>
-      <c r="E21" s="2">
-        <f t="shared" si="9"/>
+      <c r="E21" s="25">
+        <f t="shared" si="219"/>
         <v>9243</v>
       </c>
-      <c r="F21" s="2">
-        <f t="shared" si="9"/>
+      <c r="F21" s="25">
+        <f t="shared" si="219"/>
         <v>12286</v>
       </c>
-      <c r="G21" s="2">
-        <f t="shared" si="9"/>
+      <c r="G21" s="25">
+        <f t="shared" si="219"/>
         <v>14046</v>
       </c>
-      <c r="H21" s="2">
-        <f t="shared" si="9"/>
+      <c r="H21" s="25">
+        <f t="shared" si="219"/>
         <v>16599</v>
       </c>
-      <c r="I21" s="2">
-        <f t="shared" si="9"/>
-        <v>16309</v>
-      </c>
-      <c r="J21" s="2">
-        <f t="shared" si="1"/>
-        <v>35926</v>
-      </c>
-      <c r="K21" s="2">
+      <c r="I21" s="25">
+        <f t="shared" si="219"/>
+        <v>19309</v>
+      </c>
+      <c r="J21" s="25">
+        <f t="shared" si="199"/>
+        <v>32926</v>
+      </c>
+      <c r="K21" s="25">
         <f>+K19-K20</f>
         <v>18775</v>
       </c>
-      <c r="L21" s="2">
+      <c r="L21" s="25">
         <f>+L19-L20</f>
-        <v>22294.5</v>
+        <v>26546</v>
+      </c>
+      <c r="M21" s="25">
+        <f>+M19-M20</f>
+        <v>31910</v>
+      </c>
+      <c r="N21" s="25">
+        <f>+N19-N20</f>
+        <v>35788.78617062531</v>
       </c>
       <c r="U21" s="2">
-        <f t="shared" ref="U21:AB21" si="10">+U19-U20</f>
+        <f t="shared" ref="U21:AC21" si="220">+U19-U20</f>
         <v>4141</v>
       </c>
       <c r="V21" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="220"/>
         <v>2796</v>
       </c>
       <c r="W21" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="220"/>
         <v>4332</v>
       </c>
       <c r="X21" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="220"/>
         <v>9752</v>
       </c>
       <c r="Y21" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="220"/>
         <v>5721</v>
       </c>
       <c r="Z21" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="220"/>
         <v>29760</v>
       </c>
       <c r="AA21" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="220"/>
         <v>82880</v>
       </c>
       <c r="AB21" s="2">
-        <f t="shared" si="10"/>
-        <v>25401.599999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="2:28" x14ac:dyDescent="0.2">
+        <f t="shared" si="208"/>
+        <v>113019.7861706253</v>
+      </c>
+      <c r="AC21" s="2">
+        <f t="shared" si="220"/>
+        <v>156119.7387143448</v>
+      </c>
+      <c r="AD21" s="2">
+        <f t="shared" ref="AD21:AK21" si="221">+AD19-AD20</f>
+        <v>216459.67227555206</v>
+      </c>
+      <c r="AE21" s="2">
+        <f t="shared" si="221"/>
+        <v>258697.62576839712</v>
+      </c>
+      <c r="AF21" s="2">
+        <f t="shared" si="221"/>
+        <v>309383.1699598112</v>
+      </c>
+      <c r="AG21" s="2">
+        <f t="shared" si="221"/>
+        <v>339794.49647465971</v>
+      </c>
+      <c r="AH21" s="2">
+        <f t="shared" si="221"/>
+        <v>373246.95564099308</v>
+      </c>
+      <c r="AI21" s="2">
+        <f t="shared" si="221"/>
+        <v>410044.66072395979</v>
+      </c>
+      <c r="AJ21" s="2">
+        <f t="shared" si="221"/>
+        <v>450522.13631522318</v>
+      </c>
+      <c r="AK21" s="2">
+        <f t="shared" si="221"/>
+        <v>495047.35946561291</v>
+      </c>
+      <c r="AL21" s="2">
+        <f>+AK21*(1+$AM$26)</f>
+        <v>499997.83306026907</v>
+      </c>
+      <c r="AM21" s="2">
+        <f t="shared" ref="AM21:CX21" si="222">+AL21*(1+$AM$26)</f>
+        <v>504997.81139087176</v>
+      </c>
+      <c r="AN21" s="2">
+        <f t="shared" si="222"/>
+        <v>510047.78950478049</v>
+      </c>
+      <c r="AO21" s="2">
+        <f t="shared" si="222"/>
+        <v>515148.2673998283</v>
+      </c>
+      <c r="AP21" s="2">
+        <f t="shared" si="222"/>
+        <v>520299.75007382658</v>
+      </c>
+      <c r="AQ21" s="2">
+        <f t="shared" si="222"/>
+        <v>525502.74757456488</v>
+      </c>
+      <c r="AR21" s="2">
+        <f t="shared" si="222"/>
+        <v>530757.77505031053</v>
+      </c>
+      <c r="AS21" s="2">
+        <f t="shared" si="222"/>
+        <v>536065.35280081362</v>
+      </c>
+      <c r="AT21" s="2">
+        <f t="shared" si="222"/>
+        <v>541426.00632882176</v>
+      </c>
+      <c r="AU21" s="2">
+        <f t="shared" si="222"/>
+        <v>546840.26639211003</v>
+      </c>
+      <c r="AV21" s="2">
+        <f t="shared" si="222"/>
+        <v>552308.66905603115</v>
+      </c>
+      <c r="AW21" s="2">
+        <f t="shared" si="222"/>
+        <v>557831.75574659149</v>
+      </c>
+      <c r="AX21" s="2">
+        <f t="shared" si="222"/>
+        <v>563410.07330405735</v>
+      </c>
+      <c r="AY21" s="2">
+        <f t="shared" si="222"/>
+        <v>569044.17403709795</v>
+      </c>
+      <c r="AZ21" s="2">
+        <f t="shared" si="222"/>
+        <v>574734.61577746889</v>
+      </c>
+      <c r="BA21" s="2">
+        <f t="shared" si="222"/>
+        <v>580481.96193524357</v>
+      </c>
+      <c r="BB21" s="2">
+        <f t="shared" si="222"/>
+        <v>586286.78155459603</v>
+      </c>
+      <c r="BC21" s="2">
+        <f t="shared" si="222"/>
+        <v>592149.64937014203</v>
+      </c>
+      <c r="BD21" s="2">
+        <f t="shared" si="222"/>
+        <v>598071.1458638435</v>
+      </c>
+      <c r="BE21" s="2">
+        <f t="shared" si="222"/>
+        <v>604051.85732248193</v>
+      </c>
+      <c r="BF21" s="2">
+        <f t="shared" si="222"/>
+        <v>610092.3758957067</v>
+      </c>
+      <c r="BG21" s="2">
+        <f t="shared" si="222"/>
+        <v>616193.29965466377</v>
+      </c>
+      <c r="BH21" s="2">
+        <f t="shared" si="222"/>
+        <v>622355.23265121039</v>
+      </c>
+      <c r="BI21" s="2">
+        <f t="shared" si="222"/>
+        <v>628578.78497772245</v>
+      </c>
+      <c r="BJ21" s="2">
+        <f t="shared" si="222"/>
+        <v>634864.57282749971</v>
+      </c>
+      <c r="BK21" s="2">
+        <f t="shared" si="222"/>
+        <v>641213.21855577466</v>
+      </c>
+      <c r="BL21" s="2">
+        <f t="shared" si="222"/>
+        <v>647625.3507413324</v>
+      </c>
+      <c r="BM21" s="2">
+        <f t="shared" si="222"/>
+        <v>654101.60424874572</v>
+      </c>
+      <c r="BN21" s="2">
+        <f t="shared" si="222"/>
+        <v>660642.62029123318</v>
+      </c>
+      <c r="BO21" s="2">
+        <f t="shared" si="222"/>
+        <v>667249.04649414553</v>
+      </c>
+      <c r="BP21" s="2">
+        <f t="shared" si="222"/>
+        <v>673921.53695908701</v>
+      </c>
+      <c r="BQ21" s="2">
+        <f t="shared" si="222"/>
+        <v>680660.75232867792</v>
+      </c>
+      <c r="BR21" s="2">
+        <f t="shared" si="222"/>
+        <v>687467.35985196475</v>
+      </c>
+      <c r="BS21" s="2">
+        <f t="shared" si="222"/>
+        <v>694342.03345048439</v>
+      </c>
+      <c r="BT21" s="2">
+        <f t="shared" si="222"/>
+        <v>701285.45378498919</v>
+      </c>
+      <c r="BU21" s="2">
+        <f t="shared" si="222"/>
+        <v>708298.30832283909</v>
+      </c>
+      <c r="BV21" s="2">
+        <f t="shared" si="222"/>
+        <v>715381.29140606744</v>
+      </c>
+      <c r="BW21" s="2">
+        <f t="shared" si="222"/>
+        <v>722535.1043201281</v>
+      </c>
+      <c r="BX21" s="2">
+        <f t="shared" si="222"/>
+        <v>729760.45536332938</v>
+      </c>
+      <c r="BY21" s="2">
+        <f t="shared" si="222"/>
+        <v>737058.05991696264</v>
+      </c>
+      <c r="BZ21" s="2">
+        <f t="shared" si="222"/>
+        <v>744428.64051613223</v>
+      </c>
+      <c r="CA21" s="2">
+        <f t="shared" si="222"/>
+        <v>751872.92692129361</v>
+      </c>
+      <c r="CB21" s="2">
+        <f t="shared" si="222"/>
+        <v>759391.65619050653</v>
+      </c>
+      <c r="CC21" s="2">
+        <f t="shared" si="222"/>
+        <v>766985.57275241159</v>
+      </c>
+      <c r="CD21" s="2">
+        <f t="shared" si="222"/>
+        <v>774655.42847993574</v>
+      </c>
+      <c r="CE21" s="2">
+        <f t="shared" si="222"/>
+        <v>782401.98276473512</v>
+      </c>
+      <c r="CF21" s="2">
+        <f t="shared" si="222"/>
+        <v>790226.00259238249</v>
+      </c>
+      <c r="CG21" s="2">
+        <f t="shared" si="222"/>
+        <v>798128.26261830633</v>
+      </c>
+      <c r="CH21" s="2">
+        <f t="shared" si="222"/>
+        <v>806109.54524448945</v>
+      </c>
+      <c r="CI21" s="2">
+        <f t="shared" si="222"/>
+        <v>814170.64069693431</v>
+      </c>
+      <c r="CJ21" s="2">
+        <f t="shared" si="222"/>
+        <v>822312.34710390365</v>
+      </c>
+      <c r="CK21" s="2">
+        <f t="shared" si="222"/>
+        <v>830535.47057494265</v>
+      </c>
+      <c r="CL21" s="2">
+        <f t="shared" si="222"/>
+        <v>838840.82528069208</v>
+      </c>
+      <c r="CM21" s="2">
+        <f t="shared" si="222"/>
+        <v>847229.23353349906</v>
+      </c>
+      <c r="CN21" s="2">
+        <f t="shared" si="222"/>
+        <v>855701.52586883411</v>
+      </c>
+      <c r="CO21" s="2">
+        <f t="shared" si="222"/>
+        <v>864258.54112752248</v>
+      </c>
+      <c r="CP21" s="2">
+        <f t="shared" si="222"/>
+        <v>872901.12653879775</v>
+      </c>
+      <c r="CQ21" s="2">
+        <f t="shared" si="222"/>
+        <v>881630.13780418574</v>
+      </c>
+      <c r="CR21" s="2">
+        <f t="shared" si="222"/>
+        <v>890446.43918222759</v>
+      </c>
+      <c r="CS21" s="2">
+        <f t="shared" si="222"/>
+        <v>899350.90357404982</v>
+      </c>
+      <c r="CT21" s="2">
+        <f t="shared" si="222"/>
+        <v>908344.41260979034</v>
+      </c>
+      <c r="CU21" s="2">
+        <f t="shared" si="222"/>
+        <v>917427.85673588829</v>
+      </c>
+      <c r="CV21" s="2">
+        <f t="shared" si="222"/>
+        <v>926602.13530324714</v>
+      </c>
+      <c r="CW21" s="2">
+        <f t="shared" si="222"/>
+        <v>935868.15665627958</v>
+      </c>
+      <c r="CX21" s="2">
+        <f t="shared" si="222"/>
+        <v>945226.83822284243</v>
+      </c>
+      <c r="CY21" s="2">
+        <f t="shared" ref="CY21:FJ21" si="223">+CX21*(1+$AM$26)</f>
+        <v>954679.10660507088</v>
+      </c>
+      <c r="CZ21" s="2">
+        <f t="shared" si="223"/>
+        <v>964225.89767112164</v>
+      </c>
+      <c r="DA21" s="2">
+        <f t="shared" si="223"/>
+        <v>973868.15664783283</v>
+      </c>
+      <c r="DB21" s="2">
+        <f t="shared" si="223"/>
+        <v>983606.83821431117</v>
+      </c>
+      <c r="DC21" s="2">
+        <f t="shared" si="223"/>
+        <v>993442.90659645433</v>
+      </c>
+      <c r="DD21" s="2">
+        <f t="shared" si="223"/>
+        <v>1003377.3356624189</v>
+      </c>
+      <c r="DE21" s="2">
+        <f t="shared" si="223"/>
+        <v>1013411.109019043</v>
+      </c>
+      <c r="DF21" s="2">
+        <f t="shared" si="223"/>
+        <v>1023545.2201092335</v>
+      </c>
+      <c r="DG21" s="2">
+        <f t="shared" si="223"/>
+        <v>1033780.6723103259</v>
+      </c>
+      <c r="DH21" s="2">
+        <f t="shared" si="223"/>
+        <v>1044118.4790334292</v>
+      </c>
+      <c r="DI21" s="2">
+        <f t="shared" si="223"/>
+        <v>1054559.6638237634</v>
+      </c>
+      <c r="DJ21" s="2">
+        <f t="shared" si="223"/>
+        <v>1065105.260462001</v>
+      </c>
+      <c r="DK21" s="2">
+        <f t="shared" si="223"/>
+        <v>1075756.3130666211</v>
+      </c>
+      <c r="DL21" s="2">
+        <f t="shared" si="223"/>
+        <v>1086513.8761972873</v>
+      </c>
+      <c r="DM21" s="2">
+        <f t="shared" si="223"/>
+        <v>1097379.0149592601</v>
+      </c>
+      <c r="DN21" s="2">
+        <f t="shared" si="223"/>
+        <v>1108352.8051088527</v>
+      </c>
+      <c r="DO21" s="2">
+        <f t="shared" si="223"/>
+        <v>1119436.3331599412</v>
+      </c>
+      <c r="DP21" s="2">
+        <f t="shared" si="223"/>
+        <v>1130630.6964915406</v>
+      </c>
+      <c r="DQ21" s="2">
+        <f t="shared" si="223"/>
+        <v>1141937.0034564561</v>
+      </c>
+      <c r="DR21" s="2">
+        <f t="shared" si="223"/>
+        <v>1153356.3734910206</v>
+      </c>
+      <c r="DS21" s="2">
+        <f t="shared" si="223"/>
+        <v>1164889.9372259309</v>
+      </c>
+      <c r="DT21" s="2">
+        <f t="shared" si="223"/>
+        <v>1176538.8365981902</v>
+      </c>
+      <c r="DU21" s="2">
+        <f t="shared" si="223"/>
+        <v>1188304.2249641721</v>
+      </c>
+      <c r="DV21" s="2">
+        <f t="shared" si="223"/>
+        <v>1200187.267213814</v>
+      </c>
+      <c r="DW21" s="2">
+        <f t="shared" si="223"/>
+        <v>1212189.139885952</v>
+      </c>
+      <c r="DX21" s="2">
+        <f t="shared" si="223"/>
+        <v>1224311.0312848114</v>
+      </c>
+      <c r="DY21" s="2">
+        <f t="shared" si="223"/>
+        <v>1236554.1415976596</v>
+      </c>
+      <c r="DZ21" s="2">
+        <f t="shared" si="223"/>
+        <v>1248919.6830136362</v>
+      </c>
+      <c r="EA21" s="2">
+        <f t="shared" si="223"/>
+        <v>1261408.8798437726</v>
+      </c>
+      <c r="EB21" s="2">
+        <f t="shared" si="223"/>
+        <v>1274022.9686422104</v>
+      </c>
+      <c r="EC21" s="2">
+        <f t="shared" si="223"/>
+        <v>1286763.1983286324</v>
+      </c>
+      <c r="ED21" s="2">
+        <f t="shared" si="223"/>
+        <v>1299630.8303119186</v>
+      </c>
+      <c r="EE21" s="2">
+        <f t="shared" si="223"/>
+        <v>1312627.1386150378</v>
+      </c>
+      <c r="EF21" s="2">
+        <f t="shared" si="223"/>
+        <v>1325753.4100011883</v>
+      </c>
+      <c r="EG21" s="2">
+        <f t="shared" si="223"/>
+        <v>1339010.9441012002</v>
+      </c>
+      <c r="EH21" s="2">
+        <f t="shared" si="223"/>
+        <v>1352401.0535422121</v>
+      </c>
+      <c r="EI21" s="2">
+        <f t="shared" si="223"/>
+        <v>1365925.0640776344</v>
+      </c>
+      <c r="EJ21" s="2">
+        <f t="shared" si="223"/>
+        <v>1379584.3147184106</v>
+      </c>
+      <c r="EK21" s="2">
+        <f t="shared" si="223"/>
+        <v>1393380.1578655948</v>
+      </c>
+      <c r="EL21" s="2">
+        <f t="shared" si="223"/>
+        <v>1407313.9594442509</v>
+      </c>
+      <c r="EM21" s="2">
+        <f t="shared" si="223"/>
+        <v>1421387.0990386934</v>
+      </c>
+      <c r="EN21" s="2">
+        <f t="shared" si="223"/>
+        <v>1435600.9700290803</v>
+      </c>
+      <c r="EO21" s="2">
+        <f t="shared" si="223"/>
+        <v>1449956.9797293711</v>
+      </c>
+      <c r="EP21" s="2">
+        <f t="shared" si="223"/>
+        <v>1464456.5495266649</v>
+      </c>
+      <c r="EQ21" s="2">
+        <f t="shared" si="223"/>
+        <v>1479101.1150219315</v>
+      </c>
+      <c r="ER21" s="2">
+        <f t="shared" si="223"/>
+        <v>1493892.1261721507</v>
+      </c>
+      <c r="ES21" s="2">
+        <f t="shared" si="223"/>
+        <v>1508831.0474338722</v>
+      </c>
+      <c r="ET21" s="2">
+        <f t="shared" si="223"/>
+        <v>1523919.3579082109</v>
+      </c>
+      <c r="EU21" s="2">
+        <f t="shared" si="223"/>
+        <v>1539158.5514872931</v>
+      </c>
+      <c r="EV21" s="2">
+        <f t="shared" si="223"/>
+        <v>1554550.1370021661</v>
+      </c>
+      <c r="EW21" s="2">
+        <f t="shared" si="223"/>
+        <v>1570095.6383721877</v>
+      </c>
+      <c r="EX21" s="2">
+        <f t="shared" si="223"/>
+        <v>1585796.5947559096</v>
+      </c>
+      <c r="EY21" s="2">
+        <f t="shared" si="223"/>
+        <v>1601654.5607034687</v>
+      </c>
+      <c r="EZ21" s="2">
+        <f t="shared" si="223"/>
+        <v>1617671.1063105036</v>
+      </c>
+      <c r="FA21" s="2">
+        <f t="shared" si="223"/>
+        <v>1633847.8173736087</v>
+      </c>
+      <c r="FB21" s="2">
+        <f t="shared" si="223"/>
+        <v>1650186.2955473447</v>
+      </c>
+      <c r="FC21" s="2">
+        <f t="shared" si="223"/>
+        <v>1666688.1585028181</v>
+      </c>
+      <c r="FD21" s="2">
+        <f t="shared" si="223"/>
+        <v>1683355.0400878463</v>
+      </c>
+      <c r="FE21" s="2">
+        <f t="shared" si="223"/>
+        <v>1700188.5904887249</v>
+      </c>
+      <c r="FF21" s="2">
+        <f t="shared" si="223"/>
+        <v>1717190.4763936121</v>
+      </c>
+      <c r="FG21" s="2">
+        <f t="shared" si="223"/>
+        <v>1734362.3811575482</v>
+      </c>
+      <c r="FH21" s="2">
+        <f t="shared" si="223"/>
+        <v>1751706.0049691238</v>
+      </c>
+      <c r="FI21" s="2">
+        <f t="shared" si="223"/>
+        <v>1769223.065018815</v>
+      </c>
+      <c r="FJ21" s="2">
+        <f t="shared" si="223"/>
+        <v>1786915.2956690032</v>
+      </c>
+      <c r="FK21" s="2">
+        <f t="shared" ref="FK21:GQ21" si="224">+FJ21*(1+$AM$26)</f>
+        <v>1804784.4486256931</v>
+      </c>
+      <c r="FL21" s="2">
+        <f t="shared" si="224"/>
+        <v>1822832.2931119502</v>
+      </c>
+      <c r="FM21" s="2">
+        <f t="shared" si="224"/>
+        <v>1841060.6160430696</v>
+      </c>
+      <c r="FN21" s="2">
+        <f t="shared" si="224"/>
+        <v>1859471.2222035003</v>
+      </c>
+      <c r="FO21" s="2">
+        <f t="shared" si="224"/>
+        <v>1878065.9344255354</v>
+      </c>
+      <c r="FP21" s="2">
+        <f t="shared" si="224"/>
+        <v>1896846.5937697908</v>
+      </c>
+      <c r="FQ21" s="2">
+        <f t="shared" si="224"/>
+        <v>1915815.0597074889</v>
+      </c>
+      <c r="FR21" s="2">
+        <f t="shared" si="224"/>
+        <v>1934973.2103045639</v>
+      </c>
+      <c r="FS21" s="2">
+        <f t="shared" si="224"/>
+        <v>1954322.9424076094</v>
+      </c>
+      <c r="FT21" s="2">
+        <f t="shared" si="224"/>
+        <v>1973866.1718316856</v>
+      </c>
+      <c r="FU21" s="2">
+        <f t="shared" si="224"/>
+        <v>1993604.8335500024</v>
+      </c>
+      <c r="FV21" s="2">
+        <f t="shared" si="224"/>
+        <v>2013540.8818855025</v>
+      </c>
+      <c r="FW21" s="2">
+        <f t="shared" si="224"/>
+        <v>2033676.2907043574</v>
+      </c>
+      <c r="FX21" s="2">
+        <f t="shared" si="224"/>
+        <v>2054013.053611401</v>
+      </c>
+      <c r="FY21" s="2">
+        <f t="shared" si="224"/>
+        <v>2074553.1841475151</v>
+      </c>
+      <c r="FZ21" s="2">
+        <f t="shared" si="224"/>
+        <v>2095298.7159889904</v>
+      </c>
+      <c r="GA21" s="2">
+        <f t="shared" si="224"/>
+        <v>2116251.7031488805</v>
+      </c>
+      <c r="GB21" s="2">
+        <f t="shared" si="224"/>
+        <v>2137414.2201803694</v>
+      </c>
+      <c r="GC21" s="2">
+        <f t="shared" si="224"/>
+        <v>2158788.3623821731</v>
+      </c>
+      <c r="GD21" s="2">
+        <f t="shared" si="224"/>
+        <v>2180376.2460059947</v>
+      </c>
+      <c r="GE21" s="2">
+        <f t="shared" si="224"/>
+        <v>2202180.0084660547</v>
+      </c>
+      <c r="GF21" s="2">
+        <f t="shared" si="224"/>
+        <v>2224201.8085507154</v>
+      </c>
+      <c r="GG21" s="2">
+        <f t="shared" si="224"/>
+        <v>2246443.8266362227</v>
+      </c>
+      <c r="GH21" s="2">
+        <f t="shared" si="224"/>
+        <v>2268908.2649025847</v>
+      </c>
+      <c r="GI21" s="2">
+        <f t="shared" si="224"/>
+        <v>2291597.3475516108</v>
+      </c>
+      <c r="GJ21" s="2">
+        <f t="shared" si="224"/>
+        <v>2314513.3210271271</v>
+      </c>
+      <c r="GK21" s="2">
+        <f t="shared" si="224"/>
+        <v>2337658.4542373982</v>
+      </c>
+      <c r="GL21" s="2">
+        <f t="shared" si="224"/>
+        <v>2361035.0387797724</v>
+      </c>
+      <c r="GM21" s="2">
+        <f t="shared" si="224"/>
+        <v>2384645.38916757</v>
+      </c>
+      <c r="GN21" s="2">
+        <f t="shared" si="224"/>
+        <v>2408491.843059246</v>
+      </c>
+      <c r="GO21" s="2">
+        <f t="shared" si="224"/>
+        <v>2432576.7614898384</v>
+      </c>
+      <c r="GP21" s="2">
+        <f t="shared" si="224"/>
+        <v>2456902.5291047366</v>
+      </c>
+      <c r="GQ21" s="2">
+        <f t="shared" si="224"/>
+        <v>2481471.5543957842</v>
+      </c>
+      <c r="GR21" s="2">
+        <f t="shared" ref="GR21:HO21" si="225">+GQ21*(1+$AM$26)</f>
+        <v>2506286.2699397421</v>
+      </c>
+      <c r="GS21" s="2">
+        <f t="shared" si="225"/>
+        <v>2531349.1326391394</v>
+      </c>
+      <c r="GT21" s="2">
+        <f t="shared" si="225"/>
+        <v>2556662.6239655307</v>
+      </c>
+      <c r="GU21" s="2">
+        <f t="shared" si="225"/>
+        <v>2582229.2502051862</v>
+      </c>
+      <c r="GV21" s="2">
+        <f t="shared" si="225"/>
+        <v>2608051.5427072379</v>
+      </c>
+      <c r="GW21" s="2">
+        <f t="shared" si="225"/>
+        <v>2634132.0581343104</v>
+      </c>
+      <c r="GX21" s="2">
+        <f t="shared" si="225"/>
+        <v>2660473.3787156534</v>
+      </c>
+      <c r="GY21" s="2">
+        <f t="shared" si="225"/>
+        <v>2687078.1125028101</v>
+      </c>
+      <c r="GZ21" s="2">
+        <f t="shared" si="225"/>
+        <v>2713948.8936278382</v>
+      </c>
+      <c r="HA21" s="2">
+        <f t="shared" si="225"/>
+        <v>2741088.3825641167</v>
+      </c>
+      <c r="HB21" s="2">
+        <f t="shared" si="225"/>
+        <v>2768499.2663897579</v>
+      </c>
+      <c r="HC21" s="2">
+        <f t="shared" si="225"/>
+        <v>2796184.2590536554</v>
+      </c>
+      <c r="HD21" s="2">
+        <f t="shared" si="225"/>
+        <v>2824146.1016441919</v>
+      </c>
+      <c r="HE21" s="2">
+        <f t="shared" si="225"/>
+        <v>2852387.5626606341</v>
+      </c>
+      <c r="HF21" s="2">
+        <f t="shared" si="225"/>
+        <v>2880911.4382872405</v>
+      </c>
+      <c r="HG21" s="2">
+        <f t="shared" si="225"/>
+        <v>2909720.5526701128</v>
+      </c>
+      <c r="HH21" s="2">
+        <f t="shared" si="225"/>
+        <v>2938817.758196814</v>
+      </c>
+      <c r="HI21" s="2">
+        <f t="shared" si="225"/>
+        <v>2968205.9357787822</v>
+      </c>
+      <c r="HJ21" s="2">
+        <f t="shared" si="225"/>
+        <v>2997887.9951365702</v>
+      </c>
+      <c r="HK21" s="2">
+        <f t="shared" si="225"/>
+        <v>3027866.8750879359</v>
+      </c>
+      <c r="HL21" s="2">
+        <f t="shared" si="225"/>
+        <v>3058145.5438388153</v>
+      </c>
+      <c r="HM21" s="2">
+        <f t="shared" si="225"/>
+        <v>3088726.9992772033</v>
+      </c>
+      <c r="HN21" s="2">
+        <f t="shared" si="225"/>
+        <v>3119614.2692699754</v>
+      </c>
+      <c r="HO21" s="2">
+        <f t="shared" si="225"/>
+        <v>3150810.4119626749</v>
+      </c>
+      <c r="HP21" s="2">
+        <f t="shared" ref="HP21:HW21" si="226">+HO21*(1+$AM$26)</f>
+        <v>3182318.5160823017</v>
+      </c>
+      <c r="HQ21" s="2">
+        <f t="shared" si="226"/>
+        <v>3214141.7012431249</v>
+      </c>
+      <c r="HR21" s="2">
+        <f t="shared" si="226"/>
+        <v>3246283.1182555561</v>
+      </c>
+      <c r="HS21" s="2">
+        <f t="shared" si="226"/>
+        <v>3278745.9494381119</v>
+      </c>
+      <c r="HT21" s="2">
+        <f t="shared" si="226"/>
+        <v>3311533.4089324931</v>
+      </c>
+      <c r="HU21" s="2">
+        <f t="shared" si="226"/>
+        <v>3344648.7430218179</v>
+      </c>
+      <c r="HV21" s="2">
+        <f t="shared" si="226"/>
+        <v>3378095.230452036</v>
+      </c>
+      <c r="HW21" s="2">
+        <f t="shared" si="226"/>
+        <v>3411876.1827565562</v>
+      </c>
+      <c r="HX21" s="2">
+        <f t="shared" ref="HX21:IB21" si="227">+HW21*(1+$AM$26)</f>
+        <v>3445994.9445841219</v>
+      </c>
+      <c r="HY21" s="2">
+        <f t="shared" si="227"/>
+        <v>3480454.8940299633</v>
+      </c>
+      <c r="HZ21" s="2">
+        <f t="shared" si="227"/>
+        <v>3515259.4429702628</v>
+      </c>
+      <c r="IA21" s="2">
+        <f t="shared" si="227"/>
+        <v>3550412.0373999653</v>
+      </c>
+      <c r="IB21" s="2">
+        <f t="shared" si="227"/>
+        <v>3585916.157773965</v>
+      </c>
+      <c r="IC21" s="2">
+        <f t="shared" ref="IC21:ID21" si="228">+IB21*(1+$AM$26)</f>
+        <v>3621775.3193517048</v>
+      </c>
+      <c r="ID21" s="2">
+        <f t="shared" si="228"/>
+        <v>3657993.072545222</v>
+      </c>
+    </row>
+    <row r="22" spans="2:238" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="25">
         <v>2490</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="25">
         <v>24994</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="25">
         <v>24940</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="25">
         <f>+F21/F23</f>
         <v>-50063.776450551275</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="25">
         <v>24611</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="25">
         <v>24848</v>
       </c>
-      <c r="I22" s="2">
+      <c r="I22" s="25">
         <v>24774</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J22" s="25">
         <f>+J21/J23</f>
-        <v>24873.585544144305</v>
-      </c>
-      <c r="K22" s="2">
+        <v>24882.698933667485</v>
+      </c>
+      <c r="K22" s="25">
         <v>24611</v>
       </c>
-      <c r="L22" s="2">
-        <f>+K22</f>
-        <v>24611</v>
+      <c r="L22" s="25">
+        <v>24532</v>
+      </c>
+      <c r="M22" s="25">
+        <v>24483</v>
+      </c>
+      <c r="N22" s="2">
+        <f>+M22</f>
+        <v>24483</v>
       </c>
       <c r="U22" s="2">
         <v>625</v>
@@ -3278,111 +5441,282 @@
         <v>24804</v>
       </c>
       <c r="AB22" s="2">
-        <f>+L22</f>
-        <v>24611</v>
-      </c>
-    </row>
-    <row r="23" spans="2:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
+        <f>+AB21/AB23</f>
+        <v>24515.682607508588</v>
+      </c>
+      <c r="AC22" s="2">
+        <f>+AB22</f>
+        <v>24515.682607508588</v>
+      </c>
+      <c r="AD22" s="2">
+        <f t="shared" ref="AD22:AK22" si="229">+AC22</f>
+        <v>24515.682607508588</v>
+      </c>
+      <c r="AE22" s="2">
+        <f t="shared" si="229"/>
+        <v>24515.682607508588</v>
+      </c>
+      <c r="AF22" s="2">
+        <f t="shared" si="229"/>
+        <v>24515.682607508588</v>
+      </c>
+      <c r="AG22" s="2">
+        <f t="shared" si="229"/>
+        <v>24515.682607508588</v>
+      </c>
+      <c r="AH22" s="2">
+        <f t="shared" si="229"/>
+        <v>24515.682607508588</v>
+      </c>
+      <c r="AI22" s="2">
+        <f t="shared" si="229"/>
+        <v>24515.682607508588</v>
+      </c>
+      <c r="AJ22" s="2">
+        <f t="shared" si="229"/>
+        <v>24515.682607508588</v>
+      </c>
+      <c r="AK22" s="2">
+        <f t="shared" si="229"/>
+        <v>24515.682607508588</v>
+      </c>
+    </row>
+    <row r="23" spans="2:238" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="27">
         <f>+C21/C22</f>
         <v>0.82048192771084338</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="27">
         <f>+D21/D22</f>
         <v>0.24757941906057454</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="27">
         <f>+E21/E22</f>
         <v>0.37060946271050521</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="27">
         <f>+Z23-SUM(C23:E23)</f>
         <v>-0.24540697628224395</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="27">
         <f>+G21/G22</f>
         <v>0.57072040957295522</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="27">
         <f>+H21/H22</f>
         <v>0.66802157115260785</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="27">
         <f>+I21/I22</f>
-        <v>0.65831113263905705</v>
-      </c>
-      <c r="J23" s="11">
-        <f t="shared" si="1"/>
-        <v>1.4443434355790989</v>
-      </c>
-      <c r="K23" s="11">
+        <v>0.77940582869136998</v>
+      </c>
+      <c r="J23" s="27">
+        <f t="shared" si="199"/>
+        <v>1.323248739526786</v>
+      </c>
+      <c r="K23" s="27">
         <f>+K21/K22</f>
         <v>0.7628702612652879</v>
       </c>
-      <c r="L23" s="1">
+      <c r="L23" s="28">
         <f>+L21/L22</f>
-        <v>0.90587542155946532</v>
+        <v>1.0820968530898418</v>
+      </c>
+      <c r="M23" s="28">
+        <f>+M21/M22</f>
+        <v>1.3033533472205203</v>
+      </c>
+      <c r="N23" s="1">
+        <f>+N21/N22</f>
+        <v>1.4617810795501087</v>
       </c>
       <c r="U23" s="1">
-        <f t="shared" ref="U23:AB23" si="11">+U21/U22</f>
+        <f t="shared" ref="U23:AA23" si="230">+U21/U22</f>
         <v>6.6256000000000004</v>
       </c>
       <c r="V23" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="230"/>
         <v>4.5242718446601939</v>
       </c>
       <c r="W23" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="230"/>
         <v>6.8980891719745223</v>
       </c>
       <c r="X23" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="230"/>
         <v>3.8469428007889546</v>
       </c>
       <c r="Y23" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="230"/>
         <v>0.22820103709613082</v>
       </c>
       <c r="Z23" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="230"/>
         <v>1.1932638331996792</v>
       </c>
       <c r="AA23" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="230"/>
         <v>3.341396548943719</v>
       </c>
-      <c r="AB23" s="1">
-        <f t="shared" si="11"/>
-        <v>1.0321238470602576</v>
-      </c>
-    </row>
-    <row r="25" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB23" s="2">
+        <f t="shared" si="208"/>
+        <v>4.6101015411257587</v>
+      </c>
+      <c r="AC23" s="1">
+        <f>+AC21/AC22</f>
+        <v>6.3681579344043602</v>
+      </c>
+      <c r="AD23" s="1">
+        <f t="shared" ref="AD23:AK23" si="231">+AD21/AD22</f>
+        <v>8.8294368849944025</v>
+      </c>
+      <c r="AE23" s="1">
+        <f t="shared" si="231"/>
+        <v>10.55233215040743</v>
+      </c>
+      <c r="AF23" s="1">
+        <f t="shared" si="231"/>
+        <v>12.619806468903063</v>
+      </c>
+      <c r="AG23" s="1">
+        <f t="shared" si="231"/>
+        <v>13.860291060000446</v>
+      </c>
+      <c r="AH23" s="1">
+        <f t="shared" si="231"/>
+        <v>15.224824110207567</v>
+      </c>
+      <c r="AI23" s="1">
+        <f t="shared" si="231"/>
+        <v>16.725810465435401</v>
+      </c>
+      <c r="AJ23" s="1">
+        <f t="shared" si="231"/>
+        <v>18.37689545618602</v>
+      </c>
+      <c r="AK23" s="1">
+        <f t="shared" si="231"/>
+        <v>20.193088946011699</v>
+      </c>
+    </row>
+    <row r="24" spans="2:238" x14ac:dyDescent="0.2">
+      <c r="G24" s="29">
+        <f>+G12/G11</f>
+        <v>0.21647980340961451</v>
+      </c>
+      <c r="H24" s="29">
+        <f t="shared" ref="H24:N24" si="232">+H12/H11</f>
+        <v>0.24853528628495339</v>
+      </c>
+      <c r="I24" s="29">
+        <f t="shared" si="232"/>
+        <v>0.25443247249301637</v>
+      </c>
+      <c r="J24" s="29">
+        <f t="shared" si="232"/>
+        <v>0.26973634029137322</v>
+      </c>
+      <c r="K24" s="29">
+        <f t="shared" si="232"/>
+        <v>0.39476192637646951</v>
+      </c>
+      <c r="L24" s="29">
+        <f t="shared" si="232"/>
+        <v>0.27576321588259206</v>
+      </c>
+      <c r="M24" s="29">
+        <f t="shared" si="232"/>
+        <v>0.2658842928814511</v>
+      </c>
+      <c r="N24" s="29">
+        <f t="shared" si="232"/>
+        <v>0.26</v>
+      </c>
+      <c r="U24" s="29">
+        <f>+U13/U11</f>
+        <v>0.20279959030385797</v>
+      </c>
+      <c r="V24" s="29">
+        <f t="shared" ref="V24:AD24" si="233">+V13/V11</f>
+        <v>0.25911339073090311</v>
+      </c>
+      <c r="W24" s="29">
+        <f t="shared" si="233"/>
+        <v>0.2353223388305847</v>
+      </c>
+      <c r="X24" s="29">
+        <f t="shared" si="233"/>
+        <v>0.19573456193802483</v>
+      </c>
+      <c r="Y24" s="29">
+        <f t="shared" si="233"/>
+        <v>0.27207681471046191</v>
+      </c>
+      <c r="Z24" s="29">
+        <f t="shared" si="233"/>
+        <v>0.14239519385443683</v>
+      </c>
+      <c r="AA24" s="29">
+        <f t="shared" si="233"/>
+        <v>9.8960129351632606E-2</v>
+      </c>
+      <c r="AB24" s="29">
+        <f t="shared" si="233"/>
+        <v>8.4511608892397477E-2</v>
+      </c>
+      <c r="AC24" s="29">
+        <f t="shared" si="233"/>
+        <v>8.4511608892397477E-2</v>
+      </c>
+      <c r="AD24" s="29">
+        <f t="shared" si="233"/>
+        <v>8.4511608892397477E-2</v>
+      </c>
+      <c r="AE24" s="29">
+        <f t="shared" ref="AE24" si="234">+AE13/AE11</f>
+        <v>8.4511608892397477E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:238" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="2:28" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:238" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H26" s="10">
-        <f t="shared" ref="H26:K33" si="12">+H4/D4-1</f>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29">
+        <f t="shared" ref="H26:M33" si="235">+H4/D4-1</f>
         <v>1.6247097073850441</v>
       </c>
-      <c r="I26" s="10">
-        <f t="shared" si="12"/>
-        <v>1.0695330870003361</v>
-      </c>
-      <c r="J26" s="10">
-        <f t="shared" si="12"/>
-        <v>1.3589199230411997</v>
-      </c>
-      <c r="K26" s="10">
-        <f t="shared" si="12"/>
+      <c r="I26" s="29">
+        <f t="shared" si="235"/>
+        <v>1.321464561639234</v>
+      </c>
+      <c r="J26" s="29">
+        <f t="shared" si="235"/>
+        <v>1.1598885424268559</v>
+      </c>
+      <c r="K26" s="29">
+        <f t="shared" si="235"/>
         <v>0.76129331683168311</v>
+      </c>
+      <c r="L26" s="29">
+        <f t="shared" si="235"/>
+        <v>0.49725712263316235</v>
+      </c>
+      <c r="M26" s="29">
+        <f t="shared" si="235"/>
+        <v>0.55650412386051218</v>
       </c>
       <c r="Z26" s="10">
         <f>+Z4/Y4-1</f>
@@ -3392,2134 +5726,3113 @@
         <f>+AA4/Z4-1</f>
         <v>1.6237740693196407</v>
       </c>
-    </row>
-    <row r="27" spans="2:28" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AL26" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="AM26" s="13">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="27" spans="2:238" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H27" s="10">
-        <f t="shared" si="12"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29">
+        <f t="shared" si="235"/>
         <v>1.1437755698421976</v>
       </c>
-      <c r="I27" s="10">
-        <f t="shared" si="12"/>
+      <c r="I27" s="29">
+        <f t="shared" si="235"/>
         <v>0.19992325402916356</v>
       </c>
-      <c r="J27" s="10">
-        <f t="shared" si="12"/>
+      <c r="J27" s="29">
+        <f t="shared" si="235"/>
         <v>-9.2164515160612415E-2</v>
       </c>
-      <c r="K27" s="10">
-        <f t="shared" si="12"/>
+      <c r="K27" s="29">
+        <f t="shared" si="235"/>
         <v>0.56322926521602024</v>
       </c>
+      <c r="L27" s="29">
+        <f t="shared" si="235"/>
+        <v>0.97709923664122145</v>
+      </c>
+      <c r="M27" s="29">
+        <f>+M5/I5-1</f>
+        <v>1.618164374800128</v>
+      </c>
       <c r="Z27" s="10">
-        <f t="shared" ref="Z27:AA33" si="13">+Z5/Y5-1</f>
+        <f t="shared" ref="Z27:AA33" si="236">+Z5/Y5-1</f>
         <v>1.3251084598698482</v>
       </c>
       <c r="AA27" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="236"/>
         <v>0.51486880466472296</v>
       </c>
-    </row>
-    <row r="28" spans="2:28" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AL27" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="AM27" s="13">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="28" spans="2:238" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B28" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H28" s="10">
-        <f t="shared" si="12"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29">
+        <f t="shared" si="235"/>
         <v>1.5449966095127388</v>
       </c>
-      <c r="I28" s="10">
-        <f t="shared" si="12"/>
-        <v>0.91339396444811904</v>
-      </c>
-      <c r="J28" s="10">
-        <f t="shared" si="12"/>
-        <v>1.0962834166485544</v>
-      </c>
-      <c r="K28" s="10">
-        <f t="shared" si="12"/>
+      <c r="I28" s="29">
+        <f t="shared" si="235"/>
+        <v>1.1200909466721787</v>
+      </c>
+      <c r="J28" s="29">
+        <f t="shared" si="235"/>
+        <v>0.93327537491849588</v>
+      </c>
+      <c r="K28" s="29">
+        <f t="shared" si="235"/>
         <v>0.73345743030625354</v>
       </c>
+      <c r="L28" s="29">
+        <f t="shared" si="235"/>
+        <v>0.56425091352009749</v>
+      </c>
+      <c r="M28" s="29">
+        <f t="shared" si="235"/>
+        <v>0.66439179747164534</v>
+      </c>
       <c r="V28" s="10">
-        <f t="shared" ref="V28" si="14">+V6/U6-1</f>
+        <f t="shared" ref="V28" si="237">+V6/U6-1</f>
         <v>1.7394270122783162E-2</v>
       </c>
       <c r="W28" s="10">
-        <f t="shared" ref="W28:X28" si="15">+W6/V6-1</f>
+        <f t="shared" ref="W28:X28" si="238">+W6/V6-1</f>
         <v>1.2447200804559166</v>
       </c>
       <c r="X28" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="238"/>
         <v>0.5849761051373954</v>
       </c>
       <c r="Y28" s="10">
-        <f t="shared" ref="Y28" si="16">+Y6/X6-1</f>
+        <f t="shared" ref="Y28" si="239">+Y6/X6-1</f>
         <v>0.4138320927164798</v>
       </c>
       <c r="Z28" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="236"/>
         <v>2.1672775741419525</v>
       </c>
       <c r="AA28" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="236"/>
         <v>1.4236927932667016</v>
       </c>
-    </row>
-    <row r="29" spans="2:28" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AL28" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="AM28" s="35">
+        <f>NPV(AM27,AB21:ID21)</f>
+        <v>5227669.9951672591</v>
+      </c>
+    </row>
+    <row r="29" spans="2:238" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B29" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="H29" s="10">
-        <f t="shared" si="12"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29">
+        <f t="shared" si="235"/>
         <v>0.15848753016894612</v>
       </c>
-      <c r="I29" s="10">
-        <f t="shared" si="12"/>
+      <c r="I29" s="29">
+        <f t="shared" si="235"/>
         <v>0.14810924369747891</v>
       </c>
-      <c r="J29" s="10">
-        <f t="shared" si="12"/>
+      <c r="J29" s="29">
+        <f t="shared" si="235"/>
         <v>-0.11204188481675392</v>
       </c>
-      <c r="K29" s="10">
-        <f t="shared" si="12"/>
+      <c r="K29" s="29">
+        <f t="shared" si="235"/>
         <v>0.42160936909709101</v>
       </c>
+      <c r="L29" s="29">
+        <f t="shared" si="235"/>
+        <v>0.48854166666666665</v>
+      </c>
+      <c r="M29" s="29">
+        <f t="shared" si="235"/>
+        <v>0.30070143336383048</v>
+      </c>
       <c r="V29" s="10">
-        <f t="shared" ref="V29" si="17">+V7/U7-1</f>
+        <f t="shared" ref="V29" si="240">+V7/U7-1</f>
         <v>-0.11655459494076204</v>
       </c>
       <c r="W29" s="10">
-        <f t="shared" ref="W29:X29" si="18">+W7/V7-1</f>
+        <f t="shared" ref="W29:X29" si="241">+W7/V7-1</f>
         <v>0.40612540775643358</v>
       </c>
       <c r="X29" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="241"/>
         <v>0.60613481118700863</v>
       </c>
       <c r="Y29" s="10">
-        <f t="shared" ref="Y29" si="19">+Y7/X7-1</f>
+        <f t="shared" ref="Y29" si="242">+Y7/X7-1</f>
         <v>-0.27242818167228378</v>
       </c>
       <c r="Z29" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="236"/>
         <v>0.15220028675416342</v>
       </c>
       <c r="AA29" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="236"/>
         <v>8.643629750167503E-2</v>
       </c>
-    </row>
-    <row r="30" spans="2:28" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AL29" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="AM29" s="2">
+        <f>+Main!G4</f>
+        <v>24300</v>
+      </c>
+    </row>
+    <row r="30" spans="2:238" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B30" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="H30" s="10">
-        <f t="shared" si="12"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29">
+        <f t="shared" si="235"/>
         <v>0.19788918205804751</v>
       </c>
-      <c r="I30" s="10">
-        <f t="shared" si="12"/>
+      <c r="I30" s="29">
+        <f t="shared" si="235"/>
         <v>0.16826923076923084</v>
       </c>
-      <c r="J30" s="10">
-        <f t="shared" si="12"/>
+      <c r="J30" s="29">
+        <f t="shared" si="235"/>
         <v>0.10367170626349886</v>
       </c>
-      <c r="K30" s="10">
-        <f t="shared" si="12"/>
+      <c r="K30" s="29">
+        <f t="shared" si="235"/>
         <v>0.19203747072599531</v>
       </c>
+      <c r="L30" s="29">
+        <f t="shared" si="235"/>
+        <v>0.32378854625550657</v>
+      </c>
+      <c r="M30" s="29">
+        <f t="shared" si="235"/>
+        <v>0.56378600823045266</v>
+      </c>
       <c r="V30" s="10">
-        <f t="shared" ref="V30" si="20">+V8/U8-1</f>
+        <f t="shared" ref="V30" si="243">+V8/U8-1</f>
         <v>7.2566371681415998E-2</v>
       </c>
       <c r="W30" s="10">
-        <f t="shared" ref="W30:X30" si="21">+W8/V8-1</f>
+        <f t="shared" ref="W30:X30" si="244">+W8/V8-1</f>
         <v>-0.13118811881188119</v>
       </c>
       <c r="X30" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="244"/>
         <v>1.0047483380816713</v>
       </c>
       <c r="Y30" s="10">
-        <f t="shared" ref="Y30" si="22">+Y8/X8-1</f>
+        <f t="shared" ref="Y30" si="245">+Y8/X8-1</f>
         <v>-0.26859308384651825</v>
       </c>
       <c r="Z30" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="236"/>
         <v>5.8290155440414715E-3</v>
       </c>
       <c r="AA30" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="236"/>
         <v>0.20927237604636195</v>
       </c>
-    </row>
-    <row r="31" spans="2:28" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AL30" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="AM30" s="3">
+        <f>+AM28/AM29</f>
+        <v>215.13045247601889</v>
+      </c>
+    </row>
+    <row r="31" spans="2:238" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B31" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="H31" s="10">
-        <f t="shared" si="12"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29">
+        <f t="shared" si="235"/>
         <v>0.36758893280632421</v>
       </c>
-      <c r="I31" s="10">
-        <f t="shared" si="12"/>
+      <c r="I31" s="29">
+        <f t="shared" si="235"/>
         <v>0.72030651340996177</v>
       </c>
-      <c r="J31" s="10">
-        <f t="shared" si="12"/>
+      <c r="J31" s="29">
+        <f t="shared" si="235"/>
         <v>1.0284697508896796</v>
       </c>
-      <c r="K31" s="10">
-        <f t="shared" si="12"/>
+      <c r="K31" s="29">
+        <f t="shared" si="235"/>
         <v>0.72340425531914887</v>
       </c>
+      <c r="L31" s="29">
+        <f t="shared" si="235"/>
+        <v>0.69364161849710992</v>
+      </c>
+      <c r="M31" s="29">
+        <f t="shared" si="235"/>
+        <v>0.31848552338530056</v>
+      </c>
       <c r="V31" s="10">
-        <f t="shared" ref="V31" si="23">+V9/U9-1</f>
+        <f t="shared" ref="V31" si="246">+V9/U9-1</f>
         <v>9.2043681747269845E-2</v>
       </c>
       <c r="W31" s="10">
-        <f t="shared" ref="W31:X31" si="24">+W9/V9-1</f>
+        <f t="shared" ref="W31:X31" si="247">+W9/V9-1</f>
         <v>-0.23428571428571432</v>
       </c>
       <c r="X31" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="247"/>
         <v>5.5970149253731449E-2</v>
       </c>
       <c r="Y31" s="10">
-        <f t="shared" ref="Y31" si="25">+Y9/X9-1</f>
+        <f t="shared" ref="Y31" si="248">+Y9/X9-1</f>
         <v>0.59540636042402828</v>
       </c>
       <c r="Z31" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="236"/>
         <v>0.20819490586932443</v>
       </c>
       <c r="AA31" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="236"/>
         <v>0.55270394133822176</v>
       </c>
-    </row>
-    <row r="32" spans="2:28" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AL31" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="AM31" s="3">
+        <f>+Main!G3</f>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="32" spans="2:238" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B32" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="H32" s="10">
-        <f t="shared" si="12"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29">
+        <f t="shared" si="235"/>
         <v>0.33333333333333326</v>
       </c>
-      <c r="I32" s="10">
-        <f t="shared" si="12"/>
+      <c r="I32" s="29">
+        <f t="shared" si="235"/>
         <v>0.32876712328767121</v>
       </c>
-      <c r="J32" s="10">
-        <f t="shared" si="12"/>
+      <c r="J32" s="29">
+        <f t="shared" si="235"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="K32" s="10">
-        <f t="shared" si="12"/>
+      <c r="K32" s="29">
+        <f t="shared" si="235"/>
         <v>0.42307692307692313</v>
       </c>
+      <c r="L32" s="29">
+        <f t="shared" si="235"/>
+        <v>0.96590909090909083</v>
+      </c>
+      <c r="M32" s="29">
+        <f t="shared" si="235"/>
+        <v>0.79381443298969079</v>
+      </c>
       <c r="V32" s="10">
-        <f t="shared" ref="V32" si="26">+V10/U10-1</f>
+        <f t="shared" ref="V32" si="249">+V10/U10-1</f>
         <v>-0.34159061277705349</v>
       </c>
       <c r="W32" s="10">
-        <f t="shared" ref="W32:X32" si="27">+W10/V10-1</f>
+        <f t="shared" ref="W32:X32" si="250">+W10/V10-1</f>
         <v>0.2495049504950495</v>
       </c>
       <c r="X32" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="250"/>
         <v>0.84152139461172748</v>
       </c>
       <c r="Y32" s="10">
-        <f t="shared" ref="Y32" si="28">+Y10/X10-1</f>
+        <f t="shared" ref="Y32" si="251">+Y10/X10-1</f>
         <v>-0.60843373493975905</v>
       </c>
       <c r="Z32" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="236"/>
         <v>-0.32747252747252742</v>
       </c>
       <c r="AA32" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="236"/>
         <v>0.2712418300653594</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AM32" s="10">
+        <f>+AM30/AM31-1</f>
+        <v>0.18203545316493885</v>
+      </c>
+    </row>
+    <row r="33" spans="2:37" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B33" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H33" s="10">
-        <f t="shared" si="12"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29">
+        <f t="shared" si="235"/>
         <v>1.2240319834160065</v>
       </c>
-      <c r="I33" s="10">
-        <f t="shared" si="12"/>
-        <v>0.77052980132450322</v>
-      </c>
-      <c r="J33" s="10">
-        <f t="shared" si="12"/>
-        <v>0.9151698864407547</v>
-      </c>
-      <c r="K33" s="10">
-        <f t="shared" si="12"/>
+      <c r="I33" s="29">
+        <f t="shared" si="235"/>
+        <v>0.93609271523178816</v>
+      </c>
+      <c r="J33" s="29">
+        <f t="shared" si="235"/>
+        <v>0.77944170474596208</v>
+      </c>
+      <c r="K33" s="29">
+        <f t="shared" si="235"/>
         <v>0.69182921210259551</v>
       </c>
+      <c r="L33" s="29">
+        <f t="shared" si="235"/>
+        <v>0.5560252996005326</v>
+      </c>
+      <c r="M33" s="29">
+        <f t="shared" si="235"/>
+        <v>0.62493586454592109</v>
+      </c>
       <c r="V33" s="10">
-        <f t="shared" ref="V33" si="29">+V11/U11-1</f>
+        <f t="shared" ref="V33" si="252">+V11/U11-1</f>
         <v>-6.8111983612154314E-2</v>
       </c>
       <c r="W33" s="10">
-        <f t="shared" ref="W33:X33" si="30">+W11/V11-1</f>
+        <f t="shared" ref="W33:X33" si="253">+W11/V11-1</f>
         <v>0.52729437625938824</v>
       </c>
       <c r="X33" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="253"/>
         <v>0.61403298350824587</v>
       </c>
       <c r="Y33" s="10">
-        <f t="shared" ref="Y33" si="31">+Y11/X11-1</f>
+        <f t="shared" ref="Y33" si="254">+Y11/X11-1</f>
         <v>2.2293230289069932E-3</v>
       </c>
       <c r="Z33" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="236"/>
         <v>1.2585452658115224</v>
       </c>
       <c r="AA33" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="236"/>
         <v>1.1420340763599355</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="10">
+        <f t="shared" ref="AB33" si="255">+AB11/AA11-1</f>
+        <v>0.63077312122117757</v>
+      </c>
+      <c r="AC33" s="10">
+        <f t="shared" ref="AC33" si="256">+AC11/AB11-1</f>
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="AD33" s="10">
+        <f t="shared" ref="AD33" si="257">+AD11/AC11-1</f>
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="AE33" s="10">
+        <f t="shared" ref="AE33" si="258">+AE11/AD11-1</f>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AF33" s="10">
+        <f t="shared" ref="AF33" si="259">+AF11/AE11-1</f>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AG33" s="10">
+        <f t="shared" ref="AG33" si="260">+AG11/AF11-1</f>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AH33" s="10">
+        <f t="shared" ref="AH33" si="261">+AH11/AG11-1</f>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AI33" s="10">
+        <f t="shared" ref="AI33" si="262">+AI11/AH11-1</f>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AJ33" s="10">
+        <f t="shared" ref="AJ33:AK33" si="263">+AJ11/AI11-1</f>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AK33" s="10">
+        <f t="shared" si="263"/>
+        <v>0.10000000000000009</v>
+      </c>
+    </row>
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="10">
-        <f t="shared" ref="D36:K37" si="32">+D4/$K$11</f>
+      <c r="D36" s="29">
+        <f t="shared" ref="D36:K37" si="264">+D4/$K$11</f>
         <v>0.19545186328355499</v>
       </c>
-      <c r="E36" s="10">
-        <f t="shared" si="32"/>
+      <c r="E36" s="29">
+        <f t="shared" si="264"/>
         <v>0.27025554899913756</v>
       </c>
-      <c r="F36" s="10">
-        <f t="shared" si="32"/>
+      <c r="F36" s="29">
+        <f t="shared" si="264"/>
         <v>0.34208615133221371</v>
       </c>
-      <c r="G36" s="10">
-        <f t="shared" si="32"/>
+      <c r="G36" s="29">
+        <f t="shared" si="264"/>
         <v>0.4401071217829422</v>
       </c>
-      <c r="H36" s="10">
-        <f t="shared" si="32"/>
+      <c r="H36" s="29">
+        <f t="shared" si="264"/>
         <v>0.51300440288684124</v>
       </c>
-      <c r="I36" s="10">
-        <f t="shared" si="32"/>
-        <v>0.55930280059915571</v>
-      </c>
-      <c r="J36" s="10">
-        <f t="shared" si="32"/>
-        <v>0.80695383777404561</v>
-      </c>
-      <c r="K36" s="10">
-        <f t="shared" si="32"/>
+      <c r="I36" s="29">
+        <f t="shared" si="264"/>
+        <v>0.62738867958785349</v>
+      </c>
+      <c r="J36" s="29">
+        <f t="shared" si="264"/>
+        <v>0.73886795878534794</v>
+      </c>
+      <c r="K36" s="29">
+        <f t="shared" si="264"/>
         <v>0.77515773228632379</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="L36" s="29">
+        <f t="shared" ref="L36:N36" si="265">+L4/$K$11</f>
+        <v>0.76809949616449547</v>
+      </c>
+      <c r="M36" s="29">
+        <f t="shared" si="265"/>
+        <v>0.97653306704189546</v>
+      </c>
+      <c r="N36" s="10">
+        <f t="shared" si="265"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D37" s="10">
-        <f t="shared" si="32"/>
+      <c r="D37" s="29">
+        <f t="shared" si="264"/>
         <v>3.8831646316553947E-2</v>
       </c>
-      <c r="E37" s="10">
-        <f t="shared" si="32"/>
+      <c r="E37" s="29">
+        <f t="shared" si="264"/>
         <v>5.9143933548182107E-2</v>
       </c>
-      <c r="F37" s="10">
-        <f t="shared" si="32"/>
+      <c r="F37" s="29">
+        <f t="shared" si="264"/>
         <v>7.5598020970450722E-2</v>
       </c>
-      <c r="G37" s="10">
-        <f t="shared" si="32"/>
+      <c r="G37" s="29">
+        <f t="shared" si="264"/>
         <v>7.1966774091053509E-2</v>
       </c>
-      <c r="H37" s="10">
-        <f t="shared" si="32"/>
+      <c r="H37" s="29">
+        <f t="shared" si="264"/>
         <v>8.3246334710181114E-2</v>
       </c>
-      <c r="I37" s="10">
-        <f t="shared" si="32"/>
+      <c r="I37" s="29">
+        <f t="shared" si="264"/>
         <v>7.0968181199219285E-2</v>
       </c>
-      <c r="J37" s="10">
-        <f t="shared" si="32"/>
+      <c r="J37" s="29">
+        <f t="shared" si="264"/>
         <v>6.8630566020607325E-2</v>
       </c>
-      <c r="K37" s="10">
-        <f t="shared" si="32"/>
+      <c r="K37" s="29">
+        <f t="shared" si="264"/>
         <v>0.1125005673823249</v>
       </c>
-    </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="L37" s="29">
+        <f t="shared" ref="L37:N37" si="266">+L5/$K$11</f>
+        <v>0.16458626480867869</v>
+      </c>
+      <c r="M37" s="29">
+        <f t="shared" si="266"/>
+        <v>0.18580636376015613</v>
+      </c>
+      <c r="N37" s="10">
+        <f t="shared" si="266"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B38" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D38" s="10">
-        <f t="shared" ref="D38" si="33">+D6/$K$11</f>
+      <c r="D38" s="29">
+        <f t="shared" ref="D38" si="267">+D6/$K$11</f>
         <v>0.23428350960010894</v>
       </c>
-      <c r="E38" s="10">
-        <f t="shared" ref="E38:F38" si="34">+E6/$K$11</f>
+      <c r="E38" s="29">
+        <f t="shared" ref="E38:F38" si="268">+E6/$K$11</f>
         <v>0.32939948254731971</v>
       </c>
-      <c r="F38" s="10">
-        <f t="shared" si="34"/>
+      <c r="F38" s="29">
+        <f t="shared" si="268"/>
         <v>0.41768417230266441</v>
       </c>
-      <c r="G38" s="10">
-        <f t="shared" ref="G38" si="35">+G6/$K$11</f>
+      <c r="G38" s="29">
+        <f t="shared" ref="G38" si="269">+G6/$K$11</f>
         <v>0.51207389587399577</v>
       </c>
-      <c r="H38" s="10">
-        <f t="shared" ref="H38" si="36">+H6/$K$11</f>
+      <c r="H38" s="29">
+        <f t="shared" ref="H38" si="270">+H6/$K$11</f>
         <v>0.59625073759702241</v>
       </c>
-      <c r="I38" s="10">
-        <f t="shared" ref="I38:K42" si="37">+I6/$K$11</f>
-        <v>0.63027098179837504</v>
-      </c>
-      <c r="J38" s="10">
-        <f t="shared" ref="J38" si="38">+J6/$K$11</f>
-        <v>0.87558440379465297</v>
-      </c>
-      <c r="K38" s="10">
-        <f t="shared" si="37"/>
+      <c r="I38" s="29">
+        <f t="shared" ref="I38:K42" si="271">+I6/$K$11</f>
+        <v>0.69835686078707271</v>
+      </c>
+      <c r="J38" s="29">
+        <f t="shared" ref="J38" si="272">+J6/$K$11</f>
+        <v>0.8074985248059553</v>
+      </c>
+      <c r="K38" s="29">
+        <f t="shared" si="271"/>
         <v>0.88765829966864873</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="L38" s="29">
+        <f t="shared" ref="L38:N38" si="273">+L6/$K$11</f>
+        <v>0.93268576097317413</v>
+      </c>
+      <c r="M38" s="29">
+        <f t="shared" si="273"/>
+        <v>1.1623394308020516</v>
+      </c>
+      <c r="N38" s="10">
+        <f t="shared" si="273"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B39" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D39" s="10">
-        <f t="shared" ref="D39" si="39">+D7/$K$11</f>
+      <c r="D39" s="29">
+        <f t="shared" ref="D39" si="274">+D7/$K$11</f>
         <v>5.6420498388634201E-2</v>
       </c>
-      <c r="E39" s="10">
-        <f t="shared" ref="E39:F39" si="40">+E7/$K$11</f>
+      <c r="E39" s="29">
+        <f t="shared" ref="E39:F39" si="275">+E7/$K$11</f>
         <v>6.481775679724025E-2</v>
       </c>
-      <c r="F39" s="10">
-        <f t="shared" si="40"/>
+      <c r="F39" s="29">
+        <f t="shared" si="275"/>
         <v>6.5022014434206341E-2</v>
       </c>
-      <c r="G39" s="10">
-        <f t="shared" ref="G39" si="41">+G7/$K$11</f>
+      <c r="G39" s="29">
+        <f t="shared" ref="G39" si="276">+G7/$K$11</f>
         <v>6.0074440561027641E-2</v>
       </c>
-      <c r="H39" s="10">
-        <f t="shared" ref="H39" si="42">+H7/$K$11</f>
+      <c r="H39" s="29">
+        <f t="shared" ref="H39" si="277">+H7/$K$11</f>
         <v>6.5362443829149838E-2</v>
       </c>
-      <c r="I39" s="10">
-        <f t="shared" si="37"/>
+      <c r="I39" s="29">
+        <f t="shared" si="271"/>
         <v>7.4417865734646635E-2</v>
       </c>
-      <c r="J39" s="10">
-        <f t="shared" ref="J39" si="43">+J7/$K$11</f>
+      <c r="J39" s="29">
+        <f t="shared" ref="J39" si="278">+J7/$K$11</f>
         <v>5.7736825382415688E-2</v>
       </c>
-      <c r="K39" s="10">
-        <f t="shared" si="37"/>
+      <c r="K39" s="29">
+        <f t="shared" si="271"/>
         <v>8.5402387544823211E-2</v>
       </c>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="L39" s="29">
+        <f t="shared" ref="L39:N39" si="279">+L7/$K$11</f>
+        <v>9.7294721074849072E-2</v>
+      </c>
+      <c r="M39" s="29">
+        <f t="shared" si="279"/>
+        <v>9.6795424628931953E-2</v>
+      </c>
+      <c r="N39" s="10">
+        <f t="shared" si="279"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B40" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D40" s="10">
-        <f t="shared" ref="D40" si="44">+D8/$K$11</f>
+      <c r="D40" s="29">
+        <f t="shared" ref="D40" si="280">+D8/$K$11</f>
         <v>8.6015160455721485E-3</v>
       </c>
-      <c r="E40" s="10">
-        <f t="shared" ref="E40:F40" si="45">+E8/$K$11</f>
+      <c r="E40" s="29">
+        <f t="shared" ref="E40:F40" si="281">+E8/$K$11</f>
         <v>9.4412418864327531E-3</v>
       </c>
-      <c r="F40" s="10">
-        <f t="shared" si="45"/>
+      <c r="F40" s="29">
+        <f t="shared" si="281"/>
         <v>1.0507920657255684E-2</v>
       </c>
-      <c r="G40" s="10">
-        <f t="shared" ref="G40" si="46">+G8/$K$11</f>
+      <c r="G40" s="29">
+        <f t="shared" ref="G40" si="282">+G8/$K$11</f>
         <v>9.6908901093913126E-3</v>
       </c>
-      <c r="H40" s="10">
-        <f t="shared" ref="H40" si="47">+H8/$K$11</f>
+      <c r="H40" s="29">
+        <f t="shared" ref="H40" si="283">+H8/$K$11</f>
         <v>1.0303663020289592E-2</v>
       </c>
-      <c r="I40" s="10">
-        <f t="shared" si="37"/>
+      <c r="I40" s="29">
+        <f t="shared" si="271"/>
         <v>1.1029912396169034E-2</v>
       </c>
-      <c r="J40" s="10">
-        <f t="shared" ref="J40" si="48">+J8/$K$11</f>
+      <c r="J40" s="29">
+        <f t="shared" ref="J40" si="284">+J8/$K$11</f>
         <v>1.1597294721074848E-2</v>
       </c>
-      <c r="K40" s="10">
-        <f t="shared" si="37"/>
+      <c r="K40" s="29">
+        <f t="shared" si="271"/>
         <v>1.1551904135082385E-2</v>
       </c>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="L40" s="29">
+        <f t="shared" ref="L40:N40" si="285">+L8/$K$11</f>
+        <v>1.3639871090735781E-2</v>
+      </c>
+      <c r="M40" s="29">
+        <f t="shared" si="285"/>
+        <v>1.7248422677136763E-2</v>
+      </c>
+      <c r="N40" s="10">
+        <f t="shared" si="285"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B41" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D41" s="10">
-        <f t="shared" ref="D41" si="49">+D9/$K$11</f>
+      <c r="D41" s="29">
+        <f t="shared" ref="D41" si="286">+D9/$K$11</f>
         <v>5.741909128046843E-3</v>
       </c>
-      <c r="E41" s="10">
-        <f t="shared" ref="E41:F41" si="50">+E9/$K$11</f>
+      <c r="E41" s="29">
+        <f t="shared" ref="E41:F41" si="287">+E9/$K$11</f>
         <v>5.923471472016704E-3</v>
       </c>
-      <c r="F41" s="10">
-        <f t="shared" si="50"/>
+      <c r="F41" s="29">
+        <f t="shared" si="287"/>
         <v>6.3773773319413555E-3</v>
       </c>
-      <c r="G41" s="10">
-        <f t="shared" ref="G41" si="51">+G9/$K$11</f>
+      <c r="G41" s="29">
+        <f t="shared" ref="G41" si="288">+G9/$K$11</f>
         <v>7.4667513957605196E-3</v>
       </c>
-      <c r="H41" s="10">
-        <f t="shared" ref="H41" si="52">+H9/$K$11</f>
+      <c r="H41" s="29">
+        <f t="shared" ref="H41" si="289">+H9/$K$11</f>
         <v>7.8525713766964735E-3</v>
       </c>
-      <c r="I41" s="10">
-        <f t="shared" si="37"/>
+      <c r="I41" s="29">
+        <f t="shared" si="271"/>
         <v>1.019018655530843E-2</v>
       </c>
-      <c r="J41" s="10">
-        <f t="shared" ref="J41" si="53">+J9/$K$11</f>
+      <c r="J41" s="29">
+        <f t="shared" ref="J41" si="290">+J9/$K$11</f>
         <v>1.2936317007852572E-2</v>
       </c>
-      <c r="K41" s="10">
-        <f t="shared" si="37"/>
+      <c r="K41" s="29">
+        <f t="shared" si="271"/>
         <v>1.2868231128863874E-2</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="L41" s="29">
+        <f t="shared" ref="L41:N41" si="291">+L9/$K$11</f>
+        <v>1.3299441695792292E-2</v>
+      </c>
+      <c r="M41" s="29">
+        <f t="shared" si="291"/>
+        <v>1.3435613453769688E-2</v>
+      </c>
+      <c r="N41" s="10">
+        <f t="shared" si="291"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B42" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D42" s="10">
-        <f t="shared" ref="D42" si="54">+D10/$K$11</f>
+      <c r="D42" s="29">
+        <f t="shared" ref="D42" si="292">+D10/$K$11</f>
         <v>1.4978893377513504E-3</v>
       </c>
-      <c r="E42" s="10">
-        <f t="shared" ref="E42:F42" si="55">+E10/$K$11</f>
+      <c r="E42" s="29">
+        <f t="shared" ref="E42:F42" si="293">+E10/$K$11</f>
         <v>1.6567563887249785E-3</v>
       </c>
-      <c r="F42" s="10">
-        <f t="shared" si="55"/>
+      <c r="F42" s="29">
+        <f t="shared" si="293"/>
         <v>2.0425763696609324E-3</v>
       </c>
-      <c r="G42" s="10">
-        <f t="shared" ref="G42" si="56">+G10/$K$11</f>
+      <c r="G42" s="29">
+        <f t="shared" ref="G42" si="294">+G10/$K$11</f>
         <v>1.7702328537061414E-3</v>
       </c>
-      <c r="H42" s="10">
-        <f t="shared" ref="H42" si="57">+H10/$K$11</f>
+      <c r="H42" s="29">
+        <f t="shared" ref="H42" si="295">+H10/$K$11</f>
         <v>1.9971857836684672E-3</v>
       </c>
-      <c r="I42" s="10">
-        <f t="shared" si="37"/>
+      <c r="I42" s="29">
+        <f t="shared" si="271"/>
         <v>2.2014434206345606E-3</v>
       </c>
-      <c r="J42" s="10">
-        <f t="shared" ref="J42" si="58">+J10/$K$11</f>
+      <c r="J42" s="29">
+        <f t="shared" ref="J42" si="296">+J10/$K$11</f>
         <v>2.8596069175253051E-3</v>
       </c>
-      <c r="K42" s="10">
-        <f t="shared" si="37"/>
+      <c r="K42" s="29">
+        <f t="shared" si="271"/>
         <v>2.5191775225818164E-3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="L42" s="29">
+        <f t="shared" ref="L42:N42" si="297">+L10/$K$11</f>
+        <v>3.9262856883482368E-3</v>
+      </c>
+      <c r="M42" s="29">
+        <f t="shared" si="297"/>
+        <v>3.9489809813444687E-3</v>
+      </c>
+      <c r="N42" s="10">
+        <f t="shared" si="297"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="10">
+      <c r="C44" s="29">
         <f>(C11-C12)/C11</f>
         <v>0.64627363737486099</v>
       </c>
-      <c r="D44" s="10">
-        <f t="shared" ref="D44:J44" si="59">(D11-D12)/D11</f>
+      <c r="D44" s="29">
+        <f t="shared" ref="D44:J44" si="298">(D11-D12)/D11</f>
         <v>0.7005256533649219</v>
       </c>
-      <c r="E44" s="10">
-        <f t="shared" si="59"/>
+      <c r="E44" s="29">
+        <f t="shared" si="298"/>
         <v>0.73951434878587197</v>
       </c>
-      <c r="F44" s="10">
-        <f t="shared" si="59"/>
+      <c r="F44" s="29">
+        <f t="shared" si="298"/>
         <v>0.75967063294575399</v>
       </c>
-      <c r="G44" s="10">
-        <f t="shared" si="59"/>
+      <c r="G44" s="29">
+        <f t="shared" si="298"/>
         <v>0.78352019659038552</v>
       </c>
-      <c r="H44" s="10">
-        <f t="shared" si="59"/>
+      <c r="H44" s="29">
+        <f t="shared" si="298"/>
         <v>0.75146471371504664</v>
       </c>
-      <c r="I44" s="10">
-        <f t="shared" si="59"/>
-        <v>0.72177545040832869</v>
-      </c>
-      <c r="J44" s="10">
-        <f t="shared" si="59"/>
-        <v>0.74937988708039027</v>
-      </c>
-      <c r="K44" s="10">
-        <f t="shared" ref="K44:L44" si="60">(K11-K12)/K11</f>
+      <c r="I44" s="29">
+        <f t="shared" si="298"/>
+        <v>0.74556752750698363</v>
+      </c>
+      <c r="J44" s="29">
+        <f t="shared" si="298"/>
+        <v>0.73026365970862683</v>
+      </c>
+      <c r="K44" s="29">
+        <f t="shared" ref="K44" si="299">(K11-K12)/K11</f>
         <v>0.60523807362353044</v>
       </c>
-      <c r="L44" s="15">
-        <f t="shared" si="60"/>
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="L44" s="29">
+        <f>(L11-L12)/L11</f>
+        <v>0.72423678411740799</v>
+      </c>
+      <c r="M44" s="29">
+        <f t="shared" ref="M44:N44" si="300">(M11-M12)/M11</f>
+        <v>0.7341157071185489</v>
+      </c>
+      <c r="N44" s="10">
+        <f t="shared" si="300"/>
+        <v>0.74</v>
+      </c>
+      <c r="V44" s="10">
+        <f t="shared" ref="V44:AJ44" si="301">(V11-V12)/V11</f>
+        <v>0.61989375343469499</v>
+      </c>
+      <c r="W44" s="10">
+        <f t="shared" si="301"/>
+        <v>0.62344827586206897</v>
+      </c>
+      <c r="X44" s="10">
+        <f t="shared" si="301"/>
+        <v>0.64929033216913135</v>
+      </c>
+      <c r="Y44" s="10">
+        <f t="shared" si="301"/>
+        <v>0.56928894490991322</v>
+      </c>
+      <c r="Z44" s="10">
+        <f t="shared" si="301"/>
+        <v>0.72717573290436954</v>
+      </c>
+      <c r="AA44" s="10">
+        <f t="shared" si="301"/>
+        <v>0.74988697058169917</v>
+      </c>
+      <c r="AB44" s="10">
+        <f t="shared" si="301"/>
+        <v>0.70705931554289958</v>
+      </c>
+      <c r="AC44" s="10">
+        <f t="shared" si="301"/>
+        <v>0.70705931554289969</v>
+      </c>
+      <c r="AD44" s="10">
+        <f t="shared" si="301"/>
+        <v>0.70705931554289958</v>
+      </c>
+      <c r="AE44" s="10">
+        <f t="shared" si="301"/>
+        <v>0.70705931554289958</v>
+      </c>
+      <c r="AF44" s="10">
+        <f t="shared" si="301"/>
+        <v>0.70705931554289969</v>
+      </c>
+      <c r="AG44" s="10">
+        <f t="shared" si="301"/>
+        <v>0.70705931554289958</v>
+      </c>
+      <c r="AH44" s="10">
+        <f t="shared" si="301"/>
+        <v>0.70705931554289969</v>
+      </c>
+      <c r="AI44" s="10">
+        <f t="shared" si="301"/>
+        <v>0.70705931554289969</v>
+      </c>
+      <c r="AJ44" s="10">
+        <f t="shared" si="301"/>
+        <v>0.70705931554289958</v>
+      </c>
+      <c r="AK44" s="10">
+        <f t="shared" ref="AK44" si="302">(AK11-AK12)/AK11</f>
+        <v>0.70705931554289969</v>
+      </c>
+    </row>
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="10">
+      <c r="C45" s="29">
         <f>+C15/C11</f>
         <v>0.29755283648498332</v>
       </c>
-      <c r="D45" s="10">
-        <f t="shared" ref="D45:J45" si="61">+D15/D11</f>
+      <c r="D45" s="29">
+        <f t="shared" ref="D45:J45" si="303">+D15/D11</f>
         <v>0.50344265936181243</v>
       </c>
-      <c r="E45" s="10">
-        <f t="shared" si="61"/>
+      <c r="E45" s="29">
+        <f t="shared" si="303"/>
         <v>0.5748896247240618</v>
       </c>
-      <c r="F45" s="10">
-        <f t="shared" si="61"/>
+      <c r="F45" s="29">
+        <f t="shared" si="303"/>
         <v>0.61597973125820027</v>
       </c>
-      <c r="G45" s="10">
-        <f t="shared" si="61"/>
+      <c r="G45" s="29">
+        <f t="shared" si="303"/>
         <v>0.64924742743050223</v>
       </c>
-      <c r="H45" s="10">
-        <f t="shared" si="61"/>
+      <c r="H45" s="29">
+        <f t="shared" si="303"/>
         <v>0.62057256990679099</v>
       </c>
-      <c r="I45" s="10">
-        <f t="shared" si="61"/>
-        <v>0.58814911788541857</v>
-      </c>
-      <c r="J45" s="10">
-        <f t="shared" si="61"/>
-        <v>0.63861000212610142</v>
-      </c>
-      <c r="K45" s="10">
-        <f t="shared" ref="K45:L45" si="62">+K15/K11</f>
+      <c r="I45" s="29">
+        <f t="shared" si="303"/>
+        <v>0.62336810900176731</v>
+      </c>
+      <c r="J45" s="29">
+        <f t="shared" si="303"/>
+        <v>0.61104472299204193</v>
+      </c>
+      <c r="K45" s="29">
+        <f t="shared" ref="K45" si="304">+K15/K11</f>
         <v>0.49108074985248057</v>
       </c>
-      <c r="L45" s="10">
-        <f t="shared" si="62"/>
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="29">
+        <f t="shared" ref="L45:N45" si="305">+L15/L11</f>
+        <v>0.60843334830883766</v>
+      </c>
+      <c r="M45" s="29">
+        <f t="shared" si="305"/>
+        <v>0.63168789250254365</v>
+      </c>
+      <c r="N45" s="10">
+        <f t="shared" si="305"/>
+        <v>0.63692307692307693</v>
+      </c>
+      <c r="V45" s="10">
+        <f t="shared" ref="V45:AJ45" si="306">+V15/V11</f>
+        <v>0.2606704524638212</v>
+      </c>
+      <c r="W45" s="10">
+        <f t="shared" si="306"/>
+        <v>0.27178410794602698</v>
+      </c>
+      <c r="X45" s="10">
+        <f t="shared" si="306"/>
+        <v>0.37307720888756779</v>
+      </c>
+      <c r="Y45" s="10">
+        <f t="shared" si="306"/>
+        <v>0.20675465262845702</v>
+      </c>
+      <c r="Z45" s="10">
+        <f t="shared" si="306"/>
+        <v>0.54121663766783756</v>
+      </c>
+      <c r="AA45" s="10">
+        <f t="shared" si="306"/>
+        <v>0.62417526839697468</v>
+      </c>
+      <c r="AB45" s="10">
+        <f t="shared" si="306"/>
+        <v>0.59906677756318982</v>
+      </c>
+      <c r="AC45" s="10">
+        <f t="shared" si="306"/>
+        <v>0.59906677756318993</v>
+      </c>
+      <c r="AD45" s="10">
+        <f t="shared" si="306"/>
+        <v>0.59906677756318993</v>
+      </c>
+      <c r="AE45" s="10">
+        <f t="shared" si="306"/>
+        <v>0.59906677756318993</v>
+      </c>
+      <c r="AF45" s="10">
+        <f t="shared" si="306"/>
+        <v>0.59906677756318993</v>
+      </c>
+      <c r="AG45" s="10">
+        <f t="shared" si="306"/>
+        <v>0.59906677756318993</v>
+      </c>
+      <c r="AH45" s="10">
+        <f t="shared" si="306"/>
+        <v>0.59906677756318993</v>
+      </c>
+      <c r="AI45" s="10">
+        <f t="shared" si="306"/>
+        <v>0.59906677756318993</v>
+      </c>
+      <c r="AJ45" s="10">
+        <f t="shared" si="306"/>
+        <v>0.59906677756318993</v>
+      </c>
+      <c r="AK45" s="10">
+        <f t="shared" ref="AK45" si="307">+AK15/AK11</f>
+        <v>0.59906677756319004</v>
+      </c>
+    </row>
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+      <c r="J46" s="29">
+        <f>+J33</f>
+        <v>0.77944170474596208</v>
+      </c>
+      <c r="K46" s="29">
+        <f>+K33</f>
+        <v>0.69182921210259551</v>
+      </c>
+      <c r="L46" s="29">
+        <f>+L33</f>
+        <v>0.5560252996005326</v>
+      </c>
+      <c r="M46" s="29">
+        <f>+M33</f>
+        <v>0.62493586454592109</v>
+      </c>
+      <c r="N46" s="10"/>
+    </row>
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+      <c r="J47" s="29">
+        <f>+J50/I50-1</f>
+        <v>0.30362290171254158</v>
+      </c>
+      <c r="K47" s="29">
+        <f>+K50/J50-1</f>
+        <v>-4.04508996314763E-2</v>
+      </c>
+      <c r="L47" s="29">
+        <f>+L50/K50-1</f>
+        <v>0.25646123260437381</v>
+      </c>
+      <c r="M47" s="29">
+        <f>+M50/L50-1</f>
+        <v>0.20076956271576529</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="2">
+      <c r="C49" s="25">
         <v>15320</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="25">
         <v>16023</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="25">
         <v>18281</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="25">
         <v>25984</v>
       </c>
-      <c r="G49" s="2">
+      <c r="G49" s="25">
         <v>31438</v>
       </c>
-      <c r="H49" s="2">
+      <c r="H49" s="25">
         <v>34800</v>
       </c>
-      <c r="I49" s="2">
+      <c r="I49" s="25">
         <v>38487</v>
       </c>
-      <c r="J49" s="2">
+      <c r="J49" s="25">
         <v>43210</v>
       </c>
-      <c r="K49" s="2">
+      <c r="K49" s="25">
         <v>53691</v>
       </c>
-    </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="25">
+        <f>11639+45152</f>
+        <v>56791</v>
+      </c>
+      <c r="M49" s="25">
+        <v>60608</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50" s="25">
         <v>4080</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="25">
         <v>7066</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E50" s="25">
         <v>8309</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="25">
         <v>9999</v>
       </c>
-      <c r="G50" s="2">
+      <c r="G50" s="25">
         <v>12365</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H50" s="25">
         <v>14132</v>
       </c>
-      <c r="I50" s="2">
+      <c r="I50" s="25">
         <v>17693</v>
       </c>
-      <c r="J50" s="2">
+      <c r="J50" s="25">
         <v>23065</v>
       </c>
-      <c r="K50" s="2">
+      <c r="K50" s="25">
         <v>22132</v>
       </c>
-    </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="25">
+        <v>27808</v>
+      </c>
+      <c r="M50" s="25">
+        <v>33391</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="25">
         <v>4611</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="25">
         <v>4319</v>
       </c>
-      <c r="E51" s="2">
+      <c r="E51" s="25">
         <v>4779</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="25">
         <v>5282</v>
       </c>
-      <c r="G51" s="2">
+      <c r="G51" s="25">
         <v>5864</v>
       </c>
-      <c r="H51" s="2">
+      <c r="H51" s="25">
         <v>6675</v>
       </c>
-      <c r="I51" s="2">
+      <c r="I51" s="25">
         <v>7654</v>
       </c>
-      <c r="J51" s="2">
+      <c r="J51" s="25">
         <v>10080</v>
       </c>
-      <c r="K51" s="2">
+      <c r="K51" s="25">
         <v>11333</v>
       </c>
-    </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="25">
+        <v>14962</v>
+      </c>
+      <c r="M51" s="25">
+        <v>19784</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52" s="25">
         <v>872</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="25">
         <v>1389</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E52" s="25">
         <v>1289</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="25">
         <v>3080</v>
       </c>
-      <c r="G52" s="2">
+      <c r="G52" s="25">
         <v>4062</v>
       </c>
-      <c r="H52" s="2">
+      <c r="H52" s="25">
         <v>4026</v>
       </c>
-      <c r="I52" s="2">
+      <c r="I52" s="25">
         <v>3806</v>
       </c>
-      <c r="J52" s="2">
+      <c r="J52" s="25">
         <v>3771</v>
       </c>
-      <c r="K52" s="2">
+      <c r="K52" s="25">
         <v>2779</v>
       </c>
-    </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="25">
+        <v>2658</v>
+      </c>
+      <c r="M52" s="25">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B53" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53" s="25">
         <v>3740</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="25">
         <v>3799</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E53" s="25">
         <v>3844</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="25">
         <v>3914</v>
       </c>
-      <c r="G53" s="2">
+      <c r="G53" s="25">
         <v>4006</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H53" s="25">
         <v>4885</v>
       </c>
-      <c r="I53" s="2">
+      <c r="I53" s="25">
         <v>5343</v>
       </c>
-      <c r="J53" s="2">
+      <c r="J53" s="25">
         <v>6283</v>
       </c>
-      <c r="K53" s="2">
+      <c r="K53" s="25">
         <v>7136</v>
       </c>
-    </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="25">
+        <v>9141</v>
+      </c>
+      <c r="M53" s="25">
+        <v>9780</v>
+      </c>
+    </row>
+    <row r="54" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B54" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54" s="25">
         <v>1094</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="25">
         <v>1235</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E54" s="25">
         <v>1316</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="25">
         <v>1346</v>
       </c>
-      <c r="G54" s="2">
+      <c r="G54" s="25">
         <v>1532</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H54" s="25">
         <v>1556</v>
       </c>
-      <c r="I54" s="2">
+      <c r="I54" s="25">
         <v>1755</v>
       </c>
-      <c r="J54" s="2">
+      <c r="J54" s="25">
         <v>1793</v>
       </c>
-      <c r="K54" s="2">
+      <c r="K54" s="25">
         <v>1810</v>
       </c>
-    </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="25">
+        <v>2084</v>
+      </c>
+      <c r="M54" s="25">
+        <v>2281</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B55" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55" s="25">
         <v>4430</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="25">
         <v>4430</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55" s="25">
         <v>4430</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="25">
         <v>4430</v>
       </c>
-      <c r="G55" s="2">
+      <c r="G55" s="25">
         <v>4453</v>
       </c>
-      <c r="H55" s="2">
+      <c r="H55" s="25">
         <v>4622</v>
       </c>
-      <c r="I55" s="2">
+      <c r="I55" s="25">
         <v>4724</v>
       </c>
-      <c r="J55" s="2">
+      <c r="J55" s="25">
         <v>5188</v>
       </c>
-      <c r="K55" s="2">
+      <c r="K55" s="25">
         <v>5498</v>
       </c>
-    </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="25">
+        <v>5755</v>
+      </c>
+      <c r="M55" s="25">
+        <v>6261</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B56" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C56" s="25">
         <v>1541</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="25">
         <v>1395</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="25">
         <v>1251</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="25">
         <v>1112</v>
       </c>
-      <c r="G56" s="2">
+      <c r="G56" s="25">
         <v>986</v>
       </c>
-      <c r="H56" s="2">
+      <c r="H56" s="25">
         <v>952</v>
       </c>
-      <c r="I56" s="2">
+      <c r="I56" s="25">
         <v>838</v>
       </c>
-      <c r="J56" s="2">
+      <c r="J56" s="25">
         <v>807</v>
       </c>
-      <c r="K56" s="2">
+      <c r="K56" s="25">
         <v>769</v>
       </c>
-    </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="25">
+        <v>755</v>
+      </c>
+      <c r="M56" s="25">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="57" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B57" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C57" s="25">
         <v>4568</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57" s="25">
         <v>5398</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E57" s="25">
         <v>5982</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="25">
         <v>6081</v>
       </c>
-      <c r="G57" s="2">
+      <c r="G57" s="25">
         <v>7798</v>
       </c>
-      <c r="H57" s="2">
+      <c r="H57" s="25">
         <v>9578</v>
       </c>
-      <c r="I57" s="2">
+      <c r="I57" s="25">
         <v>10276</v>
       </c>
-      <c r="J57" s="2">
+      <c r="J57" s="25">
         <v>10979</v>
       </c>
-      <c r="K57" s="2">
+      <c r="K57" s="25">
         <v>13318</v>
       </c>
-    </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="25">
+        <v>13570</v>
+      </c>
+      <c r="M57" s="25">
+        <v>13674</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B58" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C58" s="25">
         <v>4204</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="25">
         <v>4501</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58" s="25">
         <v>4667</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="25">
         <v>4500</v>
       </c>
-      <c r="G58" s="2">
+      <c r="G58" s="25">
         <v>4568</v>
       </c>
-      <c r="H58" s="2">
+      <c r="H58" s="25">
         <v>4001</v>
       </c>
-      <c r="I58" s="2">
+      <c r="I58" s="25">
         <v>5437</v>
       </c>
-      <c r="J58" s="2">
+      <c r="J58" s="25">
         <v>6425</v>
       </c>
-      <c r="K58" s="2">
+      <c r="K58" s="25">
         <v>6788</v>
       </c>
-    </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="25">
+        <v>7216</v>
+      </c>
+      <c r="M58" s="25">
+        <v>11724</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B59" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C59" s="2">
-        <f t="shared" ref="C59:K59" si="63">+SUM(C49:C58)</f>
+      <c r="C59" s="25">
+        <f t="shared" ref="C59:K59" si="308">+SUM(C49:C58)</f>
         <v>44460</v>
       </c>
-      <c r="D59" s="2">
-        <f t="shared" si="63"/>
+      <c r="D59" s="25">
+        <f t="shared" si="308"/>
         <v>49555</v>
       </c>
-      <c r="E59" s="2">
-        <f t="shared" si="63"/>
+      <c r="E59" s="25">
+        <f t="shared" si="308"/>
         <v>54148</v>
       </c>
-      <c r="F59" s="2">
-        <f t="shared" si="63"/>
+      <c r="F59" s="25">
+        <f t="shared" si="308"/>
         <v>65728</v>
       </c>
-      <c r="G59" s="2">
-        <f t="shared" si="63"/>
+      <c r="G59" s="25">
+        <f t="shared" si="308"/>
         <v>77072</v>
       </c>
-      <c r="H59" s="2">
-        <f t="shared" si="63"/>
+      <c r="H59" s="25">
+        <f t="shared" si="308"/>
         <v>85227</v>
       </c>
-      <c r="I59" s="2">
-        <f t="shared" si="63"/>
+      <c r="I59" s="25">
+        <f t="shared" si="308"/>
         <v>96013</v>
       </c>
-      <c r="J59" s="2">
-        <f t="shared" si="63"/>
+      <c r="J59" s="25">
+        <f t="shared" si="308"/>
         <v>111601</v>
       </c>
-      <c r="K59" s="2">
-        <f t="shared" si="63"/>
+      <c r="K59" s="25">
+        <f t="shared" si="308"/>
         <v>125254</v>
       </c>
-    </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="25">
+        <f>+SUM(L49:L58)</f>
+        <v>140740</v>
+      </c>
+      <c r="M59" s="25">
+        <f>+SUM(M49:M58)</f>
+        <v>161148</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B61" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C61" s="2">
+      <c r="C61" s="25">
         <v>1141</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61" s="25">
         <v>1929</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E61" s="25">
         <v>2380</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="25">
         <v>2699</v>
       </c>
-      <c r="G61" s="2">
+      <c r="G61" s="25">
         <v>2715</v>
       </c>
-      <c r="H61" s="2">
+      <c r="H61" s="25">
         <v>3680</v>
       </c>
-      <c r="I61" s="2">
+      <c r="I61" s="25">
         <v>5353</v>
       </c>
-      <c r="J61" s="2">
+      <c r="J61" s="25">
         <v>6310</v>
       </c>
-      <c r="K61" s="2">
+      <c r="K61" s="25">
         <v>7331</v>
       </c>
-    </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="25">
+        <v>9064</v>
+      </c>
+      <c r="M61" s="25">
+        <v>8624</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B62" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C62" s="25">
         <v>4869</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="25">
         <v>7156</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="25">
         <v>5472</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="25">
         <v>6682</v>
       </c>
-      <c r="G62" s="2">
+      <c r="G62" s="25">
         <v>11258</v>
       </c>
-      <c r="H62" s="2">
+      <c r="H62" s="25">
         <v>10289</v>
       </c>
-      <c r="I62" s="2">
+      <c r="I62" s="25">
         <v>11126</v>
       </c>
-      <c r="J62" s="2">
+      <c r="J62" s="25">
         <v>11737</v>
       </c>
-      <c r="K62" s="2">
+      <c r="K62" s="25">
         <v>19211</v>
       </c>
-    </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="25">
+        <v>15193</v>
+      </c>
+      <c r="M62" s="25">
+        <v>16452</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B63" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C63" s="25">
         <v>1250</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63" s="25">
         <v>1249</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E63" s="25">
         <v>1249</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="25">
         <v>1250</v>
       </c>
-      <c r="G63" s="2">
+      <c r="G63" s="25">
         <v>1250</v>
       </c>
-      <c r="H63" s="2">
+      <c r="H63" s="25">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="25">
+        <v>0</v>
+      </c>
+      <c r="M63" s="25">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B64" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C64" s="2">
+      <c r="C64" s="25">
         <v>9704</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="25">
         <v>8456</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="25">
         <v>8457</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="25">
         <v>8459</v>
       </c>
-      <c r="G64" s="2">
+      <c r="G64" s="25">
         <v>8460</v>
       </c>
-      <c r="H64" s="2">
+      <c r="H64" s="25">
         <v>8461</v>
       </c>
-      <c r="I64" s="2">
+      <c r="I64" s="25">
         <v>8462</v>
       </c>
-      <c r="J64" s="2">
+      <c r="J64" s="25">
         <v>8463</v>
       </c>
-      <c r="K64" s="2">
+      <c r="K64" s="25">
         <v>8464</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="25">
+        <v>8466</v>
+      </c>
+      <c r="M64" s="25">
+        <v>7468</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B65" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C65" s="2">
+      <c r="C65" s="25">
         <v>939</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="25">
         <v>1041</v>
       </c>
-      <c r="E65" s="2">
+      <c r="E65" s="25">
         <v>1091</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="25">
         <v>1119</v>
       </c>
-      <c r="G65" s="2">
+      <c r="G65" s="25">
         <v>1281</v>
       </c>
-      <c r="H65" s="2">
+      <c r="H65" s="25">
         <v>1304</v>
       </c>
-      <c r="I65" s="2">
+      <c r="I65" s="25">
         <v>1490</v>
       </c>
-      <c r="J65" s="2">
+      <c r="J65" s="25">
         <v>1519</v>
       </c>
-      <c r="K65" s="2">
+      <c r="K65" s="25">
         <v>1521</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="25">
+        <v>1831</v>
+      </c>
+      <c r="M65" s="25">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B66" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C66" s="2">
+      <c r="C66" s="25">
         <v>2037</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66" s="25">
         <v>2223</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E66" s="25">
         <v>2234</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="25">
         <v>2541</v>
       </c>
-      <c r="G66" s="2">
+      <c r="G66" s="25">
         <v>2966</v>
       </c>
-      <c r="H66" s="2">
+      <c r="H66" s="25">
         <v>3336</v>
       </c>
-      <c r="I66" s="2">
+      <c r="I66" s="25">
         <v>3683</v>
       </c>
-      <c r="J66" s="2">
+      <c r="J66" s="25">
         <v>4245</v>
       </c>
-      <c r="K66" s="2">
+      <c r="K66" s="25">
         <v>4884</v>
       </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="25">
+        <v>6055</v>
+      </c>
+      <c r="M66" s="25">
+        <v>6694</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B67" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C67" s="2">
+      <c r="C67" s="25">
         <v>24520</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="25">
         <v>27501</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="25">
         <v>33265</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="25">
         <v>42978</v>
       </c>
-      <c r="G67" s="2">
+      <c r="G67" s="25">
         <v>49142</v>
       </c>
-      <c r="H67" s="2">
+      <c r="H67" s="25">
         <v>58157</v>
       </c>
-      <c r="I67" s="2">
+      <c r="I67" s="25">
         <v>65899</v>
       </c>
-      <c r="J67" s="2">
+      <c r="J67" s="25">
         <v>79327</v>
       </c>
-      <c r="K67" s="2">
+      <c r="K67" s="25">
         <v>83843</v>
       </c>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="25">
+        <v>100131</v>
+      </c>
+      <c r="M67" s="25">
+        <v>118897</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B68" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C68" s="2">
-        <f t="shared" ref="C68:K68" si="64">+SUM(C61:C67)</f>
+      <c r="C68" s="25">
+        <f t="shared" ref="C68:K68" si="309">+SUM(C61:C67)</f>
         <v>44460</v>
       </c>
-      <c r="D68" s="2">
-        <f t="shared" si="64"/>
+      <c r="D68" s="25">
+        <f t="shared" si="309"/>
         <v>49555</v>
       </c>
-      <c r="E68" s="2">
-        <f t="shared" si="64"/>
+      <c r="E68" s="25">
+        <f t="shared" si="309"/>
         <v>54148</v>
       </c>
-      <c r="F68" s="2">
-        <f t="shared" si="64"/>
+      <c r="F68" s="25">
+        <f t="shared" si="309"/>
         <v>65728</v>
       </c>
-      <c r="G68" s="2">
-        <f t="shared" si="64"/>
+      <c r="G68" s="25">
+        <f t="shared" si="309"/>
         <v>77072</v>
       </c>
-      <c r="H68" s="2">
-        <f t="shared" si="64"/>
+      <c r="H68" s="25">
+        <f t="shared" si="309"/>
         <v>85227</v>
       </c>
-      <c r="I68" s="2">
-        <f t="shared" si="64"/>
+      <c r="I68" s="25">
+        <f t="shared" si="309"/>
         <v>96013</v>
       </c>
-      <c r="J68" s="2">
-        <f t="shared" si="64"/>
+      <c r="J68" s="25">
+        <f t="shared" si="309"/>
         <v>111601</v>
       </c>
-      <c r="K68" s="2">
-        <f t="shared" si="64"/>
+      <c r="K68" s="25">
+        <f t="shared" si="309"/>
         <v>125254</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="25">
+        <f t="shared" ref="L68:M68" si="310">+SUM(L61:L67)</f>
+        <v>140740</v>
+      </c>
+      <c r="M68" s="25">
+        <f t="shared" si="310"/>
+        <v>161148</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B70" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C70" s="2">
+      <c r="C70" s="25">
         <f>SUM(C63:C64)</f>
         <v>10954</v>
       </c>
-      <c r="D70" s="2">
-        <f t="shared" ref="D70:K70" si="65">SUM(D63:D64)</f>
+      <c r="D70" s="25">
+        <f t="shared" ref="D70:K70" si="311">SUM(D63:D64)</f>
         <v>9705</v>
       </c>
-      <c r="E70" s="2">
-        <f t="shared" si="65"/>
+      <c r="E70" s="25">
+        <f t="shared" si="311"/>
         <v>9706</v>
       </c>
-      <c r="F70" s="2">
-        <f t="shared" si="65"/>
+      <c r="F70" s="25">
+        <f t="shared" si="311"/>
         <v>9709</v>
       </c>
-      <c r="G70" s="2">
-        <f t="shared" si="65"/>
+      <c r="G70" s="25">
+        <f t="shared" si="311"/>
         <v>9710</v>
       </c>
-      <c r="H70" s="2">
-        <f t="shared" si="65"/>
+      <c r="H70" s="25">
+        <f t="shared" si="311"/>
         <v>8461</v>
       </c>
-      <c r="I70" s="2">
-        <f t="shared" si="65"/>
+      <c r="I70" s="25">
+        <f t="shared" si="311"/>
         <v>8462</v>
       </c>
-      <c r="J70" s="2">
-        <f t="shared" si="65"/>
+      <c r="J70" s="25">
+        <f t="shared" si="311"/>
         <v>8463</v>
       </c>
-      <c r="K70" s="2">
-        <f t="shared" si="65"/>
+      <c r="K70" s="25">
+        <f t="shared" si="311"/>
         <v>8464</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="25">
+        <f t="shared" ref="L70:M70" si="312">SUM(L63:L64)</f>
+        <v>8466</v>
+      </c>
+      <c r="M70" s="25">
+        <f t="shared" si="312"/>
+        <v>8467</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B71" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C71" s="2">
+      <c r="C71" s="25">
         <f>+C49</f>
         <v>15320</v>
       </c>
-      <c r="D71" s="2">
-        <f t="shared" ref="D71:K71" si="66">+D49</f>
+      <c r="D71" s="25">
+        <f t="shared" ref="D71:K71" si="313">+D49</f>
         <v>16023</v>
       </c>
-      <c r="E71" s="2">
-        <f t="shared" si="66"/>
+      <c r="E71" s="25">
+        <f t="shared" si="313"/>
         <v>18281</v>
       </c>
-      <c r="F71" s="2">
-        <f t="shared" si="66"/>
+      <c r="F71" s="25">
+        <f t="shared" si="313"/>
         <v>25984</v>
       </c>
-      <c r="G71" s="2">
-        <f t="shared" si="66"/>
+      <c r="G71" s="25">
+        <f t="shared" si="313"/>
         <v>31438</v>
       </c>
-      <c r="H71" s="2">
-        <f t="shared" si="66"/>
+      <c r="H71" s="25">
+        <f t="shared" si="313"/>
         <v>34800</v>
       </c>
-      <c r="I71" s="2">
-        <f t="shared" si="66"/>
+      <c r="I71" s="25">
+        <f t="shared" si="313"/>
         <v>38487</v>
       </c>
-      <c r="J71" s="2">
-        <f t="shared" si="66"/>
+      <c r="J71" s="25">
+        <f t="shared" si="313"/>
         <v>43210</v>
       </c>
-      <c r="K71" s="2">
-        <f t="shared" si="66"/>
+      <c r="K71" s="25">
+        <f t="shared" si="313"/>
         <v>53691</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="25">
+        <f t="shared" ref="L71:M71" si="314">+L49</f>
+        <v>56791</v>
+      </c>
+      <c r="M71" s="25">
+        <f t="shared" si="314"/>
+        <v>60608</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B72" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C72" s="2">
+      <c r="C72" s="25">
         <f>+C71-C70</f>
         <v>4366</v>
       </c>
-      <c r="D72" s="2">
-        <f t="shared" ref="D72:K72" si="67">+D71-D70</f>
+      <c r="D72" s="25">
+        <f t="shared" ref="D72:K72" si="315">+D71-D70</f>
         <v>6318</v>
       </c>
-      <c r="E72" s="2">
-        <f t="shared" si="67"/>
+      <c r="E72" s="25">
+        <f t="shared" si="315"/>
         <v>8575</v>
       </c>
-      <c r="F72" s="2">
-        <f t="shared" si="67"/>
+      <c r="F72" s="25">
+        <f t="shared" si="315"/>
         <v>16275</v>
       </c>
-      <c r="G72" s="2">
-        <f t="shared" si="67"/>
+      <c r="G72" s="25">
+        <f t="shared" si="315"/>
         <v>21728</v>
       </c>
-      <c r="H72" s="2">
-        <f t="shared" si="67"/>
+      <c r="H72" s="25">
+        <f t="shared" si="315"/>
         <v>26339</v>
       </c>
-      <c r="I72" s="2">
-        <f t="shared" si="67"/>
+      <c r="I72" s="25">
+        <f t="shared" si="315"/>
         <v>30025</v>
       </c>
-      <c r="J72" s="2">
-        <f t="shared" si="67"/>
+      <c r="J72" s="25">
+        <f t="shared" si="315"/>
         <v>34747</v>
       </c>
-      <c r="K72" s="2">
-        <f t="shared" si="67"/>
+      <c r="K72" s="25">
+        <f t="shared" si="315"/>
         <v>45227</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="25">
+        <f t="shared" ref="L72:M72" si="316">+L71-L70</f>
+        <v>48325</v>
+      </c>
+      <c r="M72" s="25">
+        <f t="shared" si="316"/>
+        <v>52141</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B73" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C73" s="2">
+      <c r="C73" s="25">
         <f>+C67-C56-C55</f>
         <v>18549</v>
       </c>
-      <c r="D73" s="2">
-        <f t="shared" ref="D73:K73" si="68">+D67-D56-D55</f>
+      <c r="D73" s="25">
+        <f t="shared" ref="D73:K73" si="317">+D67-D56-D55</f>
         <v>21676</v>
       </c>
-      <c r="E73" s="2">
-        <f t="shared" si="68"/>
+      <c r="E73" s="25">
+        <f t="shared" si="317"/>
         <v>27584</v>
       </c>
-      <c r="F73" s="2">
-        <f t="shared" si="68"/>
+      <c r="F73" s="25">
+        <f t="shared" si="317"/>
         <v>37436</v>
       </c>
-      <c r="G73" s="2">
-        <f t="shared" si="68"/>
+      <c r="G73" s="25">
+        <f t="shared" si="317"/>
         <v>43703</v>
       </c>
-      <c r="H73" s="2">
-        <f t="shared" si="68"/>
+      <c r="H73" s="25">
+        <f t="shared" si="317"/>
         <v>52583</v>
       </c>
-      <c r="I73" s="2">
-        <f t="shared" si="68"/>
+      <c r="I73" s="25">
+        <f t="shared" si="317"/>
         <v>60337</v>
       </c>
-      <c r="J73" s="2">
-        <f t="shared" si="68"/>
+      <c r="J73" s="25">
+        <f t="shared" si="317"/>
         <v>73332</v>
       </c>
-      <c r="K73" s="2">
-        <f t="shared" si="68"/>
+      <c r="K73" s="25">
+        <f t="shared" si="317"/>
         <v>77576</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H74" s="25">
-        <f t="shared" ref="H74:J74" si="69">SUM(E111:H111)/H73</f>
+      <c r="L73" s="25">
+        <f t="shared" ref="L73:M73" si="318">+L67-L56-L55</f>
+        <v>93621</v>
+      </c>
+      <c r="M73" s="25">
+        <f t="shared" si="318"/>
+        <v>111700</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="H74" s="30">
+        <f t="shared" ref="H74:J74" si="319">SUM(E111:H111)/H73</f>
         <v>0.63176311735732082</v>
       </c>
-      <c r="I74" s="25">
-        <f t="shared" si="69"/>
+      <c r="I74" s="30">
+        <f t="shared" si="319"/>
         <v>0.82927556888807863</v>
       </c>
-      <c r="J74" s="25">
-        <f t="shared" si="69"/>
+      <c r="J74" s="30">
+        <f t="shared" si="319"/>
         <v>0.89438444335351552</v>
       </c>
-      <c r="K74" s="25">
+      <c r="K74" s="30">
         <f>SUM(H111:K111)/K73</f>
         <v>0.9289728782097556</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="I75" s="12" t="s">
+      <c r="L74" s="30">
+        <f>SUM(I111:L111)/L73</f>
+        <v>0.76932525822198006</v>
+      </c>
+      <c r="M74" s="30">
+        <f>SUM(J111:M111)/M73</f>
+        <v>0.69222918531781563</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="I75" s="31" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B76" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G76" s="2">
+      <c r="G76" s="25">
         <v>14881</v>
       </c>
-      <c r="H76" s="2">
+      <c r="H76" s="25">
         <v>16599</v>
       </c>
-      <c r="I76" s="2">
+      <c r="I76" s="25">
         <v>19309</v>
       </c>
-      <c r="J76" s="2">
+      <c r="J76" s="25">
         <v>22091</v>
       </c>
-      <c r="K76" s="2">
+      <c r="K76" s="25">
         <v>18775</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B77" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G77" s="2">
+      <c r="G77" s="25">
         <v>1011</v>
       </c>
-      <c r="H77" s="2">
+      <c r="H77" s="25">
         <v>1154</v>
       </c>
-      <c r="I77" s="2">
+      <c r="I77" s="25">
         <v>1252</v>
       </c>
-      <c r="J77" s="2">
+      <c r="J77" s="25">
         <v>1321</v>
       </c>
-      <c r="K77" s="2">
+      <c r="K77" s="25">
         <v>1474</v>
       </c>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B78" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G78" s="2">
+      <c r="G78" s="25">
         <v>410</v>
       </c>
-      <c r="H78" s="2">
+      <c r="H78" s="25">
         <v>433</v>
       </c>
-      <c r="I78" s="2">
+      <c r="I78" s="25">
         <v>478</v>
       </c>
-      <c r="J78" s="2">
+      <c r="J78" s="25">
         <v>543</v>
       </c>
-      <c r="K78" s="2">
+      <c r="K78" s="25">
         <v>611</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L78" s="25">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G79" s="2">
+      <c r="G79" s="25">
         <v>-69</v>
       </c>
-      <c r="H79" s="2">
+      <c r="H79" s="25">
         <v>-193</v>
       </c>
-      <c r="I79" s="2">
+      <c r="I79" s="25">
         <v>-37</v>
       </c>
-      <c r="J79" s="2">
+      <c r="J79" s="25">
         <v>-727</v>
       </c>
-      <c r="K79" s="2">
+      <c r="K79" s="25">
         <v>175</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B80" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G80" s="2">
+      <c r="G80" s="25">
         <v>-1577</v>
       </c>
-      <c r="H80" s="2">
+      <c r="H80" s="25">
         <v>-1699</v>
       </c>
-      <c r="I80" s="2">
+      <c r="I80" s="25">
         <v>-602</v>
       </c>
-      <c r="J80" s="2">
+      <c r="J80" s="25">
         <v>-598</v>
       </c>
-      <c r="K80" s="2">
+      <c r="K80" s="25">
         <v>-2177</v>
       </c>
     </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B81" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G81" s="2">
+      <c r="G81" s="25">
         <v>-145</v>
       </c>
-      <c r="H81" s="2">
+      <c r="H81" s="25">
         <v>-144</v>
       </c>
-      <c r="I81" s="2">
+      <c r="I81" s="25">
         <v>-79</v>
       </c>
-      <c r="J81" s="2">
+      <c r="J81" s="25">
         <v>-138</v>
       </c>
-      <c r="K81" s="2">
+      <c r="K81" s="25">
         <v>-98</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B82" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="G82" s="2">
+      <c r="G82" s="25">
         <v>2366</v>
       </c>
-      <c r="H82" s="2">
+      <c r="H82" s="25">
         <v>-1767</v>
       </c>
-      <c r="I82" s="2">
+      <c r="I82" s="25">
         <v>-3561</v>
       </c>
-      <c r="J82" s="2">
+      <c r="J82" s="25">
         <v>-5370</v>
       </c>
-      <c r="K82" s="2">
+      <c r="K82" s="25">
         <v>933</v>
       </c>
     </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B83" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G83" s="2">
+      <c r="G83" s="25">
         <v>-577</v>
       </c>
-      <c r="H83" s="2">
+      <c r="H83" s="25">
         <v>-803</v>
       </c>
-      <c r="I83" s="2">
+      <c r="I83" s="25">
         <v>-978</v>
       </c>
-      <c r="J83" s="2">
+      <c r="J83" s="25">
         <v>-2424</v>
       </c>
-      <c r="K83" s="2">
+      <c r="K83" s="25">
         <v>-1258</v>
       </c>
     </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B84" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G84" s="2">
+      <c r="G84" s="25">
         <v>-726</v>
       </c>
-      <c r="H84" s="2">
+      <c r="H84" s="25">
         <v>714</v>
       </c>
-      <c r="I84" s="2">
+      <c r="I84" s="25">
         <v>-714</v>
       </c>
-      <c r="J84" s="2">
+      <c r="J84" s="25">
         <v>331</v>
       </c>
-      <c r="K84" s="2">
+      <c r="K84" s="25">
         <v>560</v>
       </c>
     </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B85" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G85" s="2">
+      <c r="G85" s="25">
         <v>-22</v>
       </c>
-      <c r="H85" s="2">
+      <c r="H85" s="25">
         <v>823</v>
       </c>
-      <c r="I85" s="2">
+      <c r="I85" s="25">
         <v>1689</v>
       </c>
-      <c r="J85" s="2">
+      <c r="J85" s="25">
         <v>867</v>
       </c>
-      <c r="K85" s="2">
+      <c r="K85" s="25">
         <v>941</v>
       </c>
     </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B86" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G86" s="2">
+      <c r="G86" s="25">
         <v>4202</v>
       </c>
-      <c r="H86" s="2">
+      <c r="H86" s="25">
         <v>-888</v>
       </c>
-      <c r="I86" s="2">
+      <c r="I86" s="25">
         <v>606</v>
       </c>
-      <c r="J86" s="2">
+      <c r="J86" s="25">
         <v>360</v>
       </c>
-      <c r="K86" s="2">
+      <c r="K86" s="25">
         <v>7128</v>
       </c>
     </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B87" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G87" s="2">
+      <c r="G87" s="25">
         <v>323</v>
       </c>
-      <c r="H87" s="2">
+      <c r="H87" s="25">
         <v>260</v>
       </c>
-      <c r="I87" s="2">
+      <c r="I87" s="25">
         <v>266</v>
       </c>
-      <c r="J87" s="2">
+      <c r="J87" s="25">
         <v>372</v>
       </c>
-      <c r="K87" s="2">
+      <c r="K87" s="25">
         <v>350</v>
       </c>
     </row>
-    <row r="88" spans="2:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="13" t="s">
+    <row r="88" spans="2:13" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B88" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G88" s="13">
+      <c r="C88" s="32"/>
+      <c r="D88" s="32"/>
+      <c r="E88" s="32"/>
+      <c r="F88" s="32"/>
+      <c r="G88" s="32">
         <f>+SUM(G76:G87)</f>
         <v>20077</v>
       </c>
-      <c r="H88" s="13">
+      <c r="H88" s="32">
         <f>+SUM(H76:H87)</f>
         <v>14489</v>
       </c>
-      <c r="I88" s="13">
+      <c r="I88" s="32">
         <f>+SUM(I76:I87)</f>
         <v>17629</v>
       </c>
-      <c r="J88" s="13">
+      <c r="J88" s="32">
         <f>+SUM(J76:J87)</f>
         <v>16628</v>
       </c>
-      <c r="K88" s="13">
+      <c r="K88" s="32">
         <f>+SUM(K76:K87)</f>
         <v>27414</v>
       </c>
-    </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="32">
+        <v>15365</v>
+      </c>
+      <c r="M88" s="32">
+        <v>23750</v>
+      </c>
+    </row>
+    <row r="90" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B90" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="G90" s="2">
+      <c r="G90" s="25">
         <v>4004</v>
       </c>
-      <c r="H90" s="2">
+      <c r="H90" s="25">
         <v>4094</v>
       </c>
-      <c r="I90" s="2">
+      <c r="I90" s="25">
         <v>1386</v>
       </c>
-      <c r="J90" s="2">
+      <c r="J90" s="25">
         <v>1710</v>
       </c>
-      <c r="K90" s="2">
+      <c r="K90" s="25">
         <v>3122</v>
       </c>
     </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B91" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="G91" s="2">
+      <c r="G91" s="25">
         <v>149</v>
       </c>
-      <c r="H91" s="2">
+      <c r="H91" s="25">
         <v>15</v>
       </c>
-      <c r="I91" s="2">
+      <c r="I91" s="25">
         <v>154</v>
       </c>
-      <c r="J91" s="2">
+      <c r="J91" s="25">
         <v>177</v>
       </c>
-      <c r="K91" s="2">
+      <c r="K91" s="25">
         <v>467</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B92" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="G92" s="2">
+      <c r="G92" s="25">
         <v>55</v>
       </c>
-      <c r="H92" s="2">
+      <c r="H92" s="25">
         <v>0</v>
       </c>
-      <c r="I92" s="2">
+      <c r="I92" s="25">
         <v>0</v>
       </c>
-      <c r="J92" s="2">
+      <c r="J92" s="25">
         <v>0</v>
       </c>
-      <c r="K92" s="2">
+      <c r="K92" s="25">
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B93" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="G93" s="2">
+      <c r="G93" s="25">
         <v>-9303</v>
       </c>
-      <c r="H93" s="2">
+      <c r="H93" s="25">
         <v>-5744</v>
       </c>
-      <c r="I93" s="2">
+      <c r="I93" s="25">
         <v>-4518</v>
       </c>
-      <c r="J93" s="2">
+      <c r="J93" s="25">
         <v>-7010</v>
       </c>
-      <c r="K93" s="2">
+      <c r="K93" s="25">
         <v>-6456</v>
       </c>
     </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B94" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="G94" s="2">
+      <c r="G94" s="25">
         <v>-369</v>
       </c>
-      <c r="H94" s="2">
+      <c r="H94" s="25">
         <v>-977</v>
       </c>
-      <c r="I94" s="2">
+      <c r="I94" s="25">
         <v>-813</v>
       </c>
-      <c r="J94" s="2">
+      <c r="J94" s="25">
         <v>-1077</v>
       </c>
-      <c r="K94" s="2">
+      <c r="K94" s="25">
         <v>-1227</v>
       </c>
-    </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="25">
+        <v>-1894</v>
+      </c>
+      <c r="M94" s="25">
+        <v>-1637</v>
+      </c>
+    </row>
+    <row r="95" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B95" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="G95" s="2">
+      <c r="G95" s="25">
         <v>-190</v>
       </c>
-      <c r="H95" s="2">
+      <c r="H95" s="25">
         <v>0</v>
       </c>
-      <c r="I95" s="2">
+      <c r="I95" s="25">
         <v>0</v>
       </c>
-      <c r="J95" s="2">
+      <c r="J95" s="25">
         <v>-478</v>
       </c>
-      <c r="K95" s="2">
+      <c r="K95" s="25">
         <v>-649</v>
       </c>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B96" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G96" s="2">
+      <c r="G96" s="25">
         <v>-39</v>
       </c>
-      <c r="H96" s="2">
+      <c r="H96" s="25">
         <v>-279</v>
       </c>
-      <c r="I96" s="2">
+      <c r="I96" s="25">
         <v>-147</v>
       </c>
-      <c r="J96" s="2">
+      <c r="J96" s="25">
         <v>-542</v>
       </c>
-      <c r="K96" s="2">
+      <c r="K96" s="25">
         <v>-383</v>
       </c>
     </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B97" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="H97" s="2">
+      <c r="H97" s="25">
         <v>-344</v>
       </c>
-      <c r="I97" s="2">
+      <c r="I97" s="25">
         <v>66</v>
       </c>
-      <c r="J97" s="2">
+      <c r="J97" s="25">
         <v>22</v>
       </c>
     </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B98" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="H98" s="2">
+      <c r="H98" s="25">
         <v>50</v>
       </c>
-      <c r="I98" s="2">
+      <c r="I98" s="25">
         <v>-473</v>
       </c>
     </row>
-    <row r="99" spans="2:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B99" s="13" t="s">
+    <row r="99" spans="2:13" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B99" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="G99" s="13">
+      <c r="C99" s="32"/>
+      <c r="D99" s="32"/>
+      <c r="E99" s="32"/>
+      <c r="F99" s="32"/>
+      <c r="G99" s="32">
         <f>+SUM(G90:G96)</f>
         <v>-5693</v>
       </c>
-      <c r="H99" s="13">
+      <c r="H99" s="32">
         <f>+SUM(H90:H98)</f>
         <v>-3185</v>
       </c>
-      <c r="I99" s="13">
+      <c r="I99" s="32">
         <f>+SUM(I90:I98)</f>
         <v>-4345</v>
       </c>
-      <c r="J99" s="13">
+      <c r="J99" s="32">
         <f>+SUM(J90:J98)</f>
         <v>-7198</v>
       </c>
-      <c r="K99" s="13">
+      <c r="K99" s="32">
         <f>+SUM(K90:K96)</f>
         <v>-5126</v>
       </c>
-    </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="32"/>
+      <c r="M99" s="32"/>
+    </row>
+    <row r="101" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B101" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="G101" s="2">
+      <c r="G101" s="25">
         <v>285</v>
       </c>
-      <c r="H101" s="2">
+      <c r="H101" s="25">
         <v>0</v>
       </c>
-      <c r="I101" s="2">
+      <c r="I101" s="25">
         <v>204</v>
       </c>
-      <c r="J101" s="2">
+      <c r="J101" s="25">
         <v>0</v>
       </c>
-      <c r="K101" s="2">
+      <c r="K101" s="25">
         <v>370</v>
       </c>
     </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B102" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="G102" s="2">
+      <c r="G102" s="25">
         <v>-7740</v>
       </c>
-      <c r="H102" s="2">
+      <c r="H102" s="25">
         <v>-7158</v>
       </c>
-      <c r="I102" s="2">
+      <c r="I102" s="25">
         <v>-10998</v>
       </c>
-      <c r="J102" s="2">
+      <c r="J102" s="25">
         <v>-7810</v>
       </c>
-      <c r="K102" s="2">
+      <c r="K102" s="25">
         <v>-14095</v>
       </c>
     </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B103" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="H103" s="2">
+      <c r="H103" s="25">
         <v>-1250</v>
       </c>
-      <c r="J103" s="2">
+      <c r="J103" s="25">
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B104" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G104" s="2">
+      <c r="G104" s="25">
         <v>-1752</v>
       </c>
-      <c r="H104" s="2">
+      <c r="H104" s="25">
         <v>-1637</v>
       </c>
-      <c r="I104" s="2">
+      <c r="I104" s="25">
         <v>-1680</v>
       </c>
-      <c r="J104" s="2">
+      <c r="J104" s="25">
         <v>-1861</v>
       </c>
-      <c r="K104" s="2">
+      <c r="K104" s="25">
         <v>-1532</v>
       </c>
     </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B105" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G105" s="2">
+      <c r="G105" s="25">
         <v>-98</v>
       </c>
-      <c r="H105" s="2">
+      <c r="H105" s="25">
         <v>-246</v>
       </c>
-      <c r="I105" s="2">
+      <c r="I105" s="25">
         <v>-245</v>
       </c>
-      <c r="J105" s="2">
+      <c r="J105" s="25">
         <v>-245</v>
       </c>
-      <c r="K105" s="2">
+      <c r="K105" s="25">
         <v>-244</v>
       </c>
     </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B106" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="G106" s="2">
+      <c r="G106" s="25">
         <v>-40</v>
       </c>
-      <c r="H106" s="2">
+      <c r="H106" s="25">
         <v>-29</v>
       </c>
-      <c r="I106" s="2">
+      <c r="I106" s="25">
         <v>-29</v>
       </c>
-      <c r="J106" s="2">
+      <c r="J106" s="25">
         <v>-32</v>
       </c>
-      <c r="K106" s="2">
+      <c r="K106" s="25">
         <v>-52</v>
       </c>
     </row>
-    <row r="107" spans="2:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B107" s="13" t="s">
+    <row r="107" spans="2:13" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B107" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="G107" s="13">
+      <c r="C107" s="32"/>
+      <c r="D107" s="32"/>
+      <c r="E107" s="32"/>
+      <c r="F107" s="32"/>
+      <c r="G107" s="32">
         <f>+SUM(G101:G106)</f>
         <v>-9345</v>
       </c>
-      <c r="H107" s="13">
+      <c r="H107" s="32">
         <f>+SUM(H101:H106)</f>
         <v>-10320</v>
       </c>
-      <c r="I107" s="13">
+      <c r="I107" s="32">
         <f>+SUM(I101:I106)</f>
         <v>-12748</v>
       </c>
-      <c r="J107" s="13">
+      <c r="J107" s="32">
         <f>+SUM(J101:J106)</f>
         <v>-9948</v>
       </c>
-      <c r="K107" s="13">
+      <c r="K107" s="32">
         <f>+SUM(K101:K106)</f>
         <v>-15553</v>
       </c>
-    </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L107" s="32"/>
+      <c r="M107" s="32"/>
+    </row>
+    <row r="109" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B109" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="G109" s="2">
+      <c r="G109" s="25">
         <f>SUM(G88,G99,G107)</f>
         <v>5039</v>
       </c>
-      <c r="H109" s="2">
+      <c r="H109" s="25">
         <f>SUM(H88,H99,H107)</f>
         <v>984</v>
       </c>
-      <c r="I109" s="2">
+      <c r="I109" s="25">
         <f>SUM(I88,I99,I107)</f>
         <v>536</v>
       </c>
-      <c r="J109" s="2">
+      <c r="J109" s="25">
         <f>SUM(J88,J99,J107)</f>
         <v>-518</v>
       </c>
-      <c r="K109" s="2">
+      <c r="K109" s="25">
         <f>SUM(K88,K99,K107)</f>
         <v>6735</v>
       </c>
     </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B111" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G111" s="2">
-        <f>+G88+G94</f>
+      <c r="G111" s="25">
+        <f t="shared" ref="G111:M111" si="320">+G88+G94</f>
         <v>19708</v>
       </c>
-      <c r="H111" s="2">
-        <f>+H88+H94</f>
+      <c r="H111" s="25">
+        <f t="shared" si="320"/>
         <v>13512</v>
       </c>
-      <c r="I111" s="2">
-        <f>+I88+I94</f>
+      <c r="I111" s="25">
+        <f t="shared" si="320"/>
         <v>16816</v>
       </c>
-      <c r="J111" s="2">
-        <f>+J88+J94</f>
+      <c r="J111" s="25">
+        <f t="shared" si="320"/>
         <v>15551</v>
       </c>
-      <c r="K111" s="2">
-        <f>+K88+K94</f>
+      <c r="K111" s="25">
+        <f t="shared" si="320"/>
         <v>26187</v>
       </c>
-    </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L111" s="25">
+        <f t="shared" si="320"/>
+        <v>13471</v>
+      </c>
+      <c r="M111" s="25">
+        <f t="shared" si="320"/>
+        <v>22113</v>
+      </c>
+    </row>
+    <row r="112" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B112" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G112" s="2">
-        <f>+G21</f>
+      <c r="G112" s="25">
+        <f t="shared" ref="G112:M112" si="321">+G21</f>
         <v>14046</v>
       </c>
-      <c r="H112" s="2">
-        <f>+H21</f>
+      <c r="H112" s="25">
+        <f t="shared" si="321"/>
         <v>16599</v>
       </c>
-      <c r="I112" s="2">
-        <f>+I21</f>
-        <v>16309</v>
-      </c>
-      <c r="J112" s="2">
-        <f>+J21</f>
-        <v>35926</v>
-      </c>
-      <c r="K112" s="2">
-        <f>+K21</f>
+      <c r="I112" s="25">
+        <f t="shared" si="321"/>
+        <v>19309</v>
+      </c>
+      <c r="J112" s="25">
+        <f t="shared" si="321"/>
+        <v>32926</v>
+      </c>
+      <c r="K112" s="25">
+        <f t="shared" si="321"/>
         <v>18775</v>
+      </c>
+      <c r="L112" s="25">
+        <f t="shared" si="321"/>
+        <v>26546</v>
+      </c>
+      <c r="M112" s="25">
+        <f t="shared" si="321"/>
+        <v>31910</v>
+      </c>
+    </row>
+    <row r="114" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B114" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="G114" s="25">
+        <f>+G94</f>
+        <v>-369</v>
+      </c>
+      <c r="H114" s="25">
+        <f t="shared" ref="H114:L114" si="322">+H94</f>
+        <v>-977</v>
+      </c>
+      <c r="I114" s="25">
+        <f t="shared" si="322"/>
+        <v>-813</v>
+      </c>
+      <c r="J114" s="25">
+        <f t="shared" si="322"/>
+        <v>-1077</v>
+      </c>
+      <c r="K114" s="25">
+        <f t="shared" si="322"/>
+        <v>-1227</v>
+      </c>
+      <c r="L114" s="25">
+        <f t="shared" si="322"/>
+        <v>-1894</v>
+      </c>
+    </row>
+    <row r="115" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B115" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G115" s="25">
+        <f>+G78</f>
+        <v>410</v>
+      </c>
+      <c r="H115" s="25">
+        <f t="shared" ref="H115:L115" si="323">+H78</f>
+        <v>433</v>
+      </c>
+      <c r="I115" s="25">
+        <f t="shared" si="323"/>
+        <v>478</v>
+      </c>
+      <c r="J115" s="25">
+        <f t="shared" si="323"/>
+        <v>543</v>
+      </c>
+      <c r="K115" s="25">
+        <f t="shared" si="323"/>
+        <v>611</v>
+      </c>
+      <c r="L115" s="25">
+        <f t="shared" si="323"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="118" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B118" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H118" s="25">
+        <v>1300</v>
+      </c>
+      <c r="I118" s="25">
+        <v>1400</v>
+      </c>
+      <c r="J118" s="25">
+        <v>1600</v>
+      </c>
+      <c r="K118" s="25">
+        <v>1600</v>
+      </c>
+      <c r="L118" s="25">
+        <v>1800</v>
+      </c>
+      <c r="M118" s="25">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="119" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B119" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H119" s="25">
+        <v>123</v>
+      </c>
+      <c r="I119" s="25">
+        <v>187</v>
+      </c>
+      <c r="J119" s="25">
+        <v>151</v>
+      </c>
+      <c r="K119" s="25">
+        <v>160</v>
+      </c>
+      <c r="L119" s="25">
+        <v>118</v>
+      </c>
+      <c r="M119" s="25">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="120" spans="2:13" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B120" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C120" s="32">
+        <v>639</v>
+      </c>
+      <c r="D120" s="32">
+        <v>717</v>
+      </c>
+      <c r="E120" s="32">
+        <v>896</v>
+      </c>
+      <c r="F120" s="32">
+        <v>1100</v>
+      </c>
+      <c r="G120" s="32">
+        <v>1300</v>
+      </c>
+      <c r="H120" s="32">
+        <f t="shared" ref="H120:M120" si="324">SUM(H118:H119)</f>
+        <v>1423</v>
+      </c>
+      <c r="I120" s="32">
+        <f t="shared" si="324"/>
+        <v>1587</v>
+      </c>
+      <c r="J120" s="32">
+        <f t="shared" si="324"/>
+        <v>1751</v>
+      </c>
+      <c r="K120" s="32">
+        <f t="shared" si="324"/>
+        <v>1760</v>
+      </c>
+      <c r="L120" s="32">
+        <f t="shared" si="324"/>
+        <v>1918</v>
+      </c>
+      <c r="M120" s="32">
+        <f t="shared" si="324"/>
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="121" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B121" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C121" s="25">
+        <f>+C120*0.46</f>
+        <v>293.94</v>
+      </c>
+      <c r="D121" s="25">
+        <f>+D120*0.44</f>
+        <v>315.48</v>
+      </c>
+      <c r="E121" s="25">
+        <f>+E120*0.42</f>
+        <v>376.32</v>
+      </c>
+      <c r="F121" s="25">
+        <f>+F120*0.4</f>
+        <v>440</v>
+      </c>
+      <c r="G121" s="25">
+        <f>+G120*0.38</f>
+        <v>494</v>
+      </c>
+      <c r="H121" s="25">
+        <f>+H120*0.37</f>
+        <v>526.51</v>
+      </c>
+      <c r="I121" s="25">
+        <f>+I120*0.37</f>
+        <v>587.18999999999994</v>
+      </c>
+      <c r="J121" s="25">
+        <f>+J120*0.39</f>
+        <v>682.89</v>
+      </c>
+      <c r="K121" s="25">
+        <f>+K120*0.39</f>
+        <v>686.4</v>
+      </c>
+      <c r="L121" s="25">
+        <f>+L120*0.4</f>
+        <v>767.2</v>
+      </c>
+      <c r="M121" s="25">
+        <f>+M120*0.4</f>
+        <v>979.6</v>
+      </c>
+    </row>
+    <row r="122" spans="2:13" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B122" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="C122" s="33">
+        <f>+C121/C120</f>
+        <v>0.46</v>
+      </c>
+      <c r="D122" s="33">
+        <f t="shared" ref="D122:M122" si="325">+D121/D120</f>
+        <v>0.44</v>
+      </c>
+      <c r="E122" s="33">
+        <f t="shared" si="325"/>
+        <v>0.42</v>
+      </c>
+      <c r="F122" s="33">
+        <f t="shared" si="325"/>
+        <v>0.4</v>
+      </c>
+      <c r="G122" s="33">
+        <f t="shared" si="325"/>
+        <v>0.38</v>
+      </c>
+      <c r="H122" s="33">
+        <f t="shared" si="325"/>
+        <v>0.37</v>
+      </c>
+      <c r="I122" s="33">
+        <f t="shared" si="325"/>
+        <v>0.36999999999999994</v>
+      </c>
+      <c r="J122" s="33">
+        <f t="shared" si="325"/>
+        <v>0.39</v>
+      </c>
+      <c r="K122" s="33">
+        <f t="shared" si="325"/>
+        <v>0.39</v>
+      </c>
+      <c r="L122" s="33">
+        <f t="shared" si="325"/>
+        <v>0.4</v>
+      </c>
+      <c r="M122" s="33">
+        <f t="shared" si="325"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="123" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="D123" s="29">
+        <f t="shared" ref="D123:L123" si="326">+D120/C120-1</f>
+        <v>0.1220657276995305</v>
+      </c>
+      <c r="E123" s="29">
+        <f t="shared" si="326"/>
+        <v>0.24965132496513243</v>
+      </c>
+      <c r="F123" s="29">
+        <f t="shared" si="326"/>
+        <v>0.2276785714285714</v>
+      </c>
+      <c r="G123" s="29">
+        <f t="shared" si="326"/>
+        <v>0.18181818181818188</v>
+      </c>
+      <c r="H123" s="29">
+        <f t="shared" si="326"/>
+        <v>9.4615384615384546E-2</v>
+      </c>
+      <c r="I123" s="29">
+        <f t="shared" si="326"/>
+        <v>0.11524947294448351</v>
+      </c>
+      <c r="J123" s="29">
+        <f t="shared" si="326"/>
+        <v>0.10333963453056083</v>
+      </c>
+      <c r="K123" s="29">
+        <f t="shared" si="326"/>
+        <v>5.1399200456880845E-3</v>
+      </c>
+      <c r="L123" s="29">
+        <f t="shared" si="326"/>
+        <v>8.9772727272727337E-2</v>
+      </c>
+      <c r="M123" s="29">
+        <f>+M120/L120-1</f>
+        <v>0.27685088633993749</v>
+      </c>
+    </row>
+    <row r="124" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B124" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D124" s="25">
+        <f t="shared" ref="D124:L124" si="327">+D120-C120</f>
+        <v>78</v>
+      </c>
+      <c r="E124" s="25">
+        <f t="shared" si="327"/>
+        <v>179</v>
+      </c>
+      <c r="F124" s="25">
+        <f t="shared" si="327"/>
+        <v>204</v>
+      </c>
+      <c r="G124" s="25">
+        <f t="shared" si="327"/>
+        <v>200</v>
+      </c>
+      <c r="H124" s="25">
+        <f t="shared" si="327"/>
+        <v>123</v>
+      </c>
+      <c r="I124" s="25">
+        <f t="shared" si="327"/>
+        <v>164</v>
+      </c>
+      <c r="J124" s="25">
+        <f t="shared" si="327"/>
+        <v>164</v>
+      </c>
+      <c r="K124" s="25">
+        <f t="shared" si="327"/>
+        <v>9</v>
+      </c>
+      <c r="L124" s="25">
+        <f t="shared" si="327"/>
+        <v>158</v>
+      </c>
+      <c r="M124" s="34">
+        <f>+M120-L120</f>
+        <v>531</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="B6:J21 B26:I27 B23:J25 B22:E22 G22:I22" formula="1"/>
+    <ignoredError sqref="B6:J21 B26:I27 B23:J23 B22:E22 G22:I22 B25:J25 B24:F24 AB15:AB24" formula="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Semiconductor/NVDA.xlsx
+++ b/Semiconductor/NVDA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameelbrannon/Library/CloudStorage/Dropbox/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F6F2369-32CF-514E-95EB-1DF25C268C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1737A9A-C692-254B-9D3D-84AF3029D2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13720" yWindow="680" windowWidth="33580" windowHeight="24380" xr2:uid="{834EDAA3-D05C-5B48-B7D6-13D13D56A97E}"/>
+    <workbookView xWindow="14320" yWindow="1320" windowWidth="44260" windowHeight="24640" activeTab="2" xr2:uid="{834EDAA3-D05C-5B48-B7D6-13D13D56A97E}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="213">
   <si>
     <t>P</t>
   </si>
@@ -172,9 +172,6 @@
     <t>OEM &amp; Other</t>
   </si>
   <si>
-    <t xml:space="preserve">Growth Analysis </t>
-  </si>
-  <si>
     <t xml:space="preserve">Rev Segment % Total </t>
   </si>
   <si>
@@ -665,6 +662,21 @@
   </si>
   <si>
     <t>Current</t>
+  </si>
+  <si>
+    <t>Growth Analysis YY</t>
+  </si>
+  <si>
+    <t>DSO</t>
+  </si>
+  <si>
+    <t>DIO</t>
+  </si>
+  <si>
+    <t>DPO</t>
+  </si>
+  <si>
+    <t>CC</t>
   </si>
 </sst>
 </file>
@@ -881,7 +893,7 @@
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>46213</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>136</xdr:row>
       <xdr:rowOff>52631</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1320,7 +1332,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>1</v>
@@ -1338,7 +1350,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>2</v>
@@ -1348,7 +1360,7 @@
         <v>4422600</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.2">
@@ -1364,7 +1376,7 @@
         <v>Q325</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.2">
@@ -1383,7 +1395,7 @@
         <v>Q325</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.2">
@@ -1398,17 +1410,17 @@
         <v>4370459</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L9" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L10" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.2">
@@ -1417,7 +1429,7 @@
         <v>179422600</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.2">
@@ -1426,34 +1438,34 @@
         <v>7383.6460905349795</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L13" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L14" s="20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.2">
       <c r="I15" s="16"/>
       <c r="L15" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B16" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.2">
@@ -1461,13 +1473,13 @@
         <v>17</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I17" s="17">
         <v>45874</v>
       </c>
       <c r="L17" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
@@ -1475,7 +1487,7 @@
         <v>40400</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
@@ -1483,7 +1495,7 @@
         <v>45874</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.2">
@@ -1491,7 +1503,7 @@
         <v>45874</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
@@ -1499,13 +1511,13 @@
         <v>45853</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="I22" s="16"/>
       <c r="L22" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.2">
@@ -1513,267 +1525,267 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L25" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L26" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L27" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L28" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L29" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L30" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L31" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L33" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L34" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L36" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L37" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L38" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L39" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L42" s="22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L43" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L44" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L45" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L46" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="47" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L47" s="20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L48" s="21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L49" s="20" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="50" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L50" s="20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="51" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L51" s="21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L52" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L53" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="56" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L56" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L57" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L58" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="59" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L59" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L60" s="20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="61" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L61" s="20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="62" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L62" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="63" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L63" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="64" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L64" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="65" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L65" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="68" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L68" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="69" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L69" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="70" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L70" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="71" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L71" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="72" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L72" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="73" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L73" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="74" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L74" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="75" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L75" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="76" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L76" s="20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="77" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L77" s="20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="78" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L78" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="79" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L79" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="80" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L80" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L81" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="82" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L82" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="83" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L83" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="84" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L84" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="87" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L87" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -1800,42 +1812,42 @@
   <sheetData>
     <row r="3" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B3" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B5" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B6" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B7" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B8" s="15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B9" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B10" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B11" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.2">
@@ -1843,76 +1855,76 @@
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B14" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B15" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B16" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B17" s="15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B20" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B21" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B22" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B25" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B26" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1946,7 +1958,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3324D012-FEF5-4D43-9CF5-2CE00AF5A8E7}">
-  <dimension ref="B2:ID124"/>
+  <dimension ref="B2:ID133"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="2" customWidth="1"/>
@@ -5681,8 +5693,8 @@
       </c>
     </row>
     <row r="25" spans="2:238" x14ac:dyDescent="0.2">
-      <c r="B25" s="2" t="s">
-        <v>44</v>
+      <c r="B25" s="11" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="26" spans="2:238" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -5727,7 +5739,7 @@
         <v>1.6237740693196407</v>
       </c>
       <c r="AL26" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AM26" s="13">
         <v>0.01</v>
@@ -5775,7 +5787,7 @@
         <v>0.51486880466472296</v>
       </c>
       <c r="AL27" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AM27" s="13">
         <v>0.08</v>
@@ -5839,7 +5851,7 @@
         <v>1.4236927932667016</v>
       </c>
       <c r="AL28" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AM28" s="35">
         <f>NPV(AM27,AB21:ID21)</f>
@@ -5969,7 +5981,7 @@
         <v>0.20927237604636195</v>
       </c>
       <c r="AL30" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM30" s="3">
         <f>+AM28/AM29</f>
@@ -6034,7 +6046,7 @@
         <v>0.55270394133822176</v>
       </c>
       <c r="AL31" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AM31" s="3">
         <f>+Main!G3</f>
@@ -6203,7 +6215,7 @@
     </row>
     <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="2:37" x14ac:dyDescent="0.2">
@@ -6551,7 +6563,7 @@
     </row>
     <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C44" s="29">
         <f>(C11-C12)/C11</f>
@@ -6668,7 +6680,7 @@
     </row>
     <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C45" s="29">
         <f>+C15/C11</f>
@@ -6822,7 +6834,7 @@
     </row>
     <row r="49" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C49" s="25">
         <v>15320</v>
@@ -6861,7 +6873,7 @@
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C50" s="25">
         <v>4080</v>
@@ -6899,7 +6911,7 @@
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C51" s="25">
         <v>4611</v>
@@ -6937,7 +6949,7 @@
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C52" s="25">
         <v>872</v>
@@ -6975,7 +6987,7 @@
     </row>
     <row r="53" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B53" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C53" s="25">
         <v>3740</v>
@@ -7013,7 +7025,7 @@
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B54" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C54" s="25">
         <v>1094</v>
@@ -7051,7 +7063,7 @@
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B55" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C55" s="25">
         <v>4430</v>
@@ -7089,7 +7101,7 @@
     </row>
     <row r="56" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B56" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C56" s="25">
         <v>1541</v>
@@ -7127,7 +7139,7 @@
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B57" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C57" s="25">
         <v>4568</v>
@@ -7165,7 +7177,7 @@
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B58" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C58" s="25">
         <v>4204</v>
@@ -7203,7 +7215,7 @@
     </row>
     <row r="59" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B59" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C59" s="25">
         <f t="shared" ref="C59:K59" si="308">+SUM(C49:C58)</f>
@@ -7252,7 +7264,7 @@
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B61" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C61" s="25">
         <v>1141</v>
@@ -7290,7 +7302,7 @@
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B62" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C62" s="25">
         <v>4869</v>
@@ -7328,7 +7340,7 @@
     </row>
     <row r="63" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B63" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C63" s="25">
         <v>1250</v>
@@ -7357,7 +7369,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B64" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C64" s="25">
         <v>9704</v>
@@ -7395,7 +7407,7 @@
     </row>
     <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B65" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C65" s="25">
         <v>939</v>
@@ -7433,7 +7445,7 @@
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B66" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C66" s="25">
         <v>2037</v>
@@ -7471,7 +7483,7 @@
     </row>
     <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B67" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C67" s="25">
         <v>24520</v>
@@ -7509,7 +7521,7 @@
     </row>
     <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B68" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C68" s="25">
         <f t="shared" ref="C68:K68" si="309">+SUM(C61:C67)</f>
@@ -7558,7 +7570,7 @@
     </row>
     <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B70" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C70" s="25">
         <f>SUM(C63:C64)</f>
@@ -7607,7 +7619,7 @@
     </row>
     <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B71" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C71" s="25">
         <f>+C49</f>
@@ -7656,7 +7668,7 @@
     </row>
     <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B72" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C72" s="25">
         <f>+C71-C70</f>
@@ -7705,7 +7717,7 @@
     </row>
     <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B73" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C73" s="25">
         <f>+C67-C56-C55</f>
@@ -7754,7 +7766,7 @@
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="H74" s="30">
-        <f t="shared" ref="H74:J74" si="319">SUM(E111:H111)/H73</f>
+        <f t="shared" ref="H74:J74" si="319">SUM(E120:H120)/H73</f>
         <v>0.63176311735732082</v>
       </c>
       <c r="I74" s="30">
@@ -7766,1073 +7778,1264 @@
         <v>0.89438444335351552</v>
       </c>
       <c r="K74" s="30">
-        <f>SUM(H111:K111)/K73</f>
+        <f>SUM(H120:K120)/K73</f>
         <v>0.9289728782097556</v>
       </c>
       <c r="L74" s="30">
-        <f>SUM(I111:L111)/L73</f>
+        <f>SUM(I120:L120)/L73</f>
         <v>0.76932525822198006</v>
       </c>
       <c r="M74" s="30">
-        <f>SUM(J111:M111)/M73</f>
+        <f>SUM(J120:M120)/M73</f>
         <v>0.69222918531781563</v>
       </c>
     </row>
     <row r="75" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="I75" s="31" t="s">
-        <v>66</v>
-      </c>
+      <c r="H75" s="30"/>
+      <c r="I75" s="30"/>
+      <c r="J75" s="30"/>
+      <c r="K75" s="30"/>
+      <c r="L75" s="30"/>
+      <c r="M75" s="30"/>
     </row>
     <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B76" s="2" t="s">
-        <v>34</v>
+        <v>209</v>
+      </c>
+      <c r="F76" s="25">
+        <f t="shared" ref="F76:L76" si="320">+F50/SUM(C11:F11) * 365</f>
+        <v>59.906683956534586</v>
       </c>
       <c r="G76" s="25">
-        <v>14881</v>
+        <f t="shared" si="320"/>
+        <v>56.575137262767313</v>
       </c>
       <c r="H76" s="25">
-        <v>16599</v>
+        <f t="shared" si="320"/>
+        <v>53.559762011068763</v>
       </c>
       <c r="I76" s="25">
-        <v>19309</v>
+        <f t="shared" si="320"/>
+        <v>57.014231607942151</v>
       </c>
       <c r="J76" s="25">
-        <v>22091</v>
+        <f t="shared" si="320"/>
+        <v>64.512785734537957</v>
       </c>
       <c r="K76" s="25">
-        <v>18775</v>
+        <f t="shared" si="320"/>
+        <v>54.393024273642396</v>
+      </c>
+      <c r="L76" s="25">
+        <f t="shared" si="320"/>
+        <v>61.433499981842175</v>
+      </c>
+      <c r="M76" s="25">
+        <f>+M50/SUM(J11:M11) * 365</f>
+        <v>65.125492941189037</v>
       </c>
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B77" s="2" t="s">
-        <v>68</v>
+        <v>210</v>
+      </c>
+      <c r="F77" s="25">
+        <f t="shared" ref="F77:L77" si="321">(+F51/SUM(C12:F12)) * 365</f>
+        <v>115.99362252572048</v>
       </c>
       <c r="G77" s="25">
-        <v>1011</v>
+        <f t="shared" si="321"/>
+        <v>108.56505199086989</v>
       </c>
       <c r="H77" s="25">
-        <v>1154</v>
+        <f t="shared" si="321"/>
+        <v>105.30666493775932</v>
       </c>
       <c r="I77" s="25">
-        <v>1252</v>
+        <f t="shared" si="321"/>
+        <v>102.17650501060639</v>
       </c>
       <c r="J77" s="25">
-        <v>1321</v>
+        <f t="shared" si="321"/>
+        <v>112.72404179049603</v>
       </c>
       <c r="K77" s="25">
-        <v>1474</v>
+        <f t="shared" si="321"/>
+        <v>93.175920711791875</v>
+      </c>
+      <c r="L77" s="25">
+        <f t="shared" si="321"/>
+        <v>109.61942230875771</v>
+      </c>
+      <c r="M77" s="25">
+        <f>(+M51/SUM(J12:M12)) * 365</f>
+        <v>128.83425512934878</v>
       </c>
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B78" s="2" t="s">
-        <v>69</v>
+        <v>211</v>
+      </c>
+      <c r="F78" s="25">
+        <f t="shared" ref="F78:L78" si="322">+(F61/SUM(C12:F12)) * 365</f>
+        <v>59.270501173214605</v>
       </c>
       <c r="G78" s="25">
-        <v>410</v>
+        <f t="shared" si="322"/>
+        <v>50.265026629469943</v>
       </c>
       <c r="H78" s="25">
-        <v>433</v>
+        <f t="shared" si="322"/>
+        <v>58.056708160442597</v>
       </c>
       <c r="I78" s="25">
-        <v>478</v>
+        <f t="shared" si="322"/>
+        <v>71.459476263623728</v>
       </c>
       <c r="J78" s="25">
-        <v>543</v>
+        <f t="shared" si="322"/>
+        <v>70.564355525598216</v>
       </c>
       <c r="K78" s="25">
-        <v>611</v>
+        <f t="shared" si="322"/>
+        <v>60.272891091339112</v>
       </c>
       <c r="L78" s="25">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B79" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G79" s="25">
-        <v>-69</v>
-      </c>
-      <c r="H79" s="25">
-        <v>-193</v>
-      </c>
-      <c r="I79" s="25">
-        <v>-37</v>
-      </c>
-      <c r="J79" s="25">
-        <v>-727</v>
-      </c>
-      <c r="K79" s="25">
-        <v>175</v>
+        <f t="shared" si="322"/>
+        <v>66.407595495694423</v>
+      </c>
+      <c r="M78" s="25">
+        <f>+(M61/SUM(J12:M12)) * 365</f>
+        <v>56.159857270294381</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B79" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="C79" s="32"/>
+      <c r="D79" s="32"/>
+      <c r="E79" s="32"/>
+      <c r="F79" s="32">
+        <f t="shared" ref="F79:L79" si="323">+SUM(F76:F77)-F78</f>
+        <v>116.62980530904048</v>
+      </c>
+      <c r="G79" s="32">
+        <f t="shared" si="323"/>
+        <v>114.87516262416726</v>
+      </c>
+      <c r="H79" s="32">
+        <f t="shared" si="323"/>
+        <v>100.8097187883855</v>
+      </c>
+      <c r="I79" s="32">
+        <f t="shared" si="323"/>
+        <v>87.731260354924828</v>
+      </c>
+      <c r="J79" s="32">
+        <f t="shared" si="323"/>
+        <v>106.67247199943577</v>
+      </c>
+      <c r="K79" s="32">
+        <f t="shared" si="323"/>
+        <v>87.296053894095138</v>
+      </c>
+      <c r="L79" s="32">
+        <f t="shared" si="323"/>
+        <v>104.64532679490547</v>
+      </c>
+      <c r="M79" s="32">
+        <f>+SUM(M76:M77)-M78</f>
+        <v>137.79989080024342</v>
       </c>
     </row>
     <row r="80" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B80" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G80" s="25">
-        <v>-1577</v>
-      </c>
-      <c r="H80" s="25">
-        <v>-1699</v>
-      </c>
-      <c r="I80" s="25">
-        <v>-602</v>
-      </c>
-      <c r="J80" s="25">
-        <v>-598</v>
-      </c>
-      <c r="K80" s="25">
-        <v>-2177</v>
-      </c>
+      <c r="H80" s="30"/>
+      <c r="I80" s="30"/>
+      <c r="J80" s="30"/>
+      <c r="K80" s="30"/>
+      <c r="L80" s="30"/>
+      <c r="M80" s="30"/>
     </row>
     <row r="81" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B81" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G81" s="25">
-        <v>-145</v>
-      </c>
-      <c r="H81" s="25">
-        <v>-144</v>
-      </c>
-      <c r="I81" s="25">
-        <v>-79</v>
-      </c>
-      <c r="J81" s="25">
-        <v>-138</v>
-      </c>
-      <c r="K81" s="25">
-        <v>-98</v>
-      </c>
+      <c r="H81" s="30"/>
+      <c r="I81" s="30"/>
+      <c r="J81" s="30"/>
+      <c r="K81" s="30"/>
+      <c r="L81" s="30"/>
+      <c r="M81" s="30"/>
     </row>
     <row r="82" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B82" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G82" s="25">
-        <v>2366</v>
-      </c>
-      <c r="H82" s="25">
-        <v>-1767</v>
-      </c>
-      <c r="I82" s="25">
-        <v>-3561</v>
-      </c>
-      <c r="J82" s="25">
-        <v>-5370</v>
-      </c>
-      <c r="K82" s="25">
-        <v>933</v>
-      </c>
+      <c r="H82" s="30"/>
+      <c r="I82" s="30"/>
+      <c r="J82" s="30"/>
+      <c r="K82" s="30"/>
+      <c r="L82" s="30"/>
+      <c r="M82" s="30"/>
     </row>
     <row r="83" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B83" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G83" s="25">
-        <v>-577</v>
-      </c>
-      <c r="H83" s="25">
-        <v>-803</v>
-      </c>
-      <c r="I83" s="25">
-        <v>-978</v>
-      </c>
-      <c r="J83" s="25">
-        <v>-2424</v>
-      </c>
-      <c r="K83" s="25">
-        <v>-1258</v>
-      </c>
+      <c r="H83" s="30"/>
+      <c r="I83" s="30"/>
+      <c r="J83" s="30"/>
+      <c r="K83" s="30"/>
+      <c r="L83" s="30"/>
+      <c r="M83" s="30"/>
     </row>
     <row r="84" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B84" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G84" s="25">
-        <v>-726</v>
-      </c>
-      <c r="H84" s="25">
-        <v>714</v>
-      </c>
-      <c r="I84" s="25">
-        <v>-714</v>
-      </c>
-      <c r="J84" s="25">
-        <v>331</v>
-      </c>
-      <c r="K84" s="25">
-        <v>560</v>
+      <c r="I84" s="31" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="85" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B85" s="2" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G85" s="25">
-        <v>-22</v>
+        <v>14881</v>
       </c>
       <c r="H85" s="25">
-        <v>823</v>
+        <v>16599</v>
       </c>
       <c r="I85" s="25">
-        <v>1689</v>
+        <v>19309</v>
       </c>
       <c r="J85" s="25">
-        <v>867</v>
+        <v>22091</v>
       </c>
       <c r="K85" s="25">
-        <v>941</v>
+        <v>18775</v>
       </c>
     </row>
     <row r="86" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B86" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G86" s="25">
-        <v>4202</v>
+        <v>1011</v>
       </c>
       <c r="H86" s="25">
-        <v>-888</v>
+        <v>1154</v>
       </c>
       <c r="I86" s="25">
-        <v>606</v>
+        <v>1252</v>
       </c>
       <c r="J86" s="25">
-        <v>360</v>
+        <v>1321</v>
       </c>
       <c r="K86" s="25">
-        <v>7128</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="87" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B87" s="2" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G87" s="25">
-        <v>323</v>
+        <v>410</v>
       </c>
       <c r="H87" s="25">
-        <v>260</v>
+        <v>433</v>
       </c>
       <c r="I87" s="25">
-        <v>266</v>
+        <v>478</v>
       </c>
       <c r="J87" s="25">
-        <v>372</v>
+        <v>543</v>
       </c>
       <c r="K87" s="25">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="88" spans="2:13" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C88" s="32"/>
-      <c r="D88" s="32"/>
-      <c r="E88" s="32"/>
-      <c r="F88" s="32"/>
-      <c r="G88" s="32">
-        <f>+SUM(G76:G87)</f>
-        <v>20077</v>
-      </c>
-      <c r="H88" s="32">
-        <f>+SUM(H76:H87)</f>
-        <v>14489</v>
-      </c>
-      <c r="I88" s="32">
-        <f>+SUM(I76:I87)</f>
-        <v>17629</v>
-      </c>
-      <c r="J88" s="32">
-        <f>+SUM(J76:J87)</f>
-        <v>16628</v>
-      </c>
-      <c r="K88" s="32">
-        <f>+SUM(K76:K87)</f>
-        <v>27414</v>
-      </c>
-      <c r="L88" s="32">
-        <v>15365</v>
-      </c>
-      <c r="M88" s="32">
-        <v>23750</v>
+        <v>611</v>
+      </c>
+      <c r="L87" s="25">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="88" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B88" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G88" s="25">
+        <v>-69</v>
+      </c>
+      <c r="H88" s="25">
+        <v>-193</v>
+      </c>
+      <c r="I88" s="25">
+        <v>-37</v>
+      </c>
+      <c r="J88" s="25">
+        <v>-727</v>
+      </c>
+      <c r="K88" s="25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="89" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B89" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G89" s="25">
+        <v>-1577</v>
+      </c>
+      <c r="H89" s="25">
+        <v>-1699</v>
+      </c>
+      <c r="I89" s="25">
+        <v>-602</v>
+      </c>
+      <c r="J89" s="25">
+        <v>-598</v>
+      </c>
+      <c r="K89" s="25">
+        <v>-2177</v>
       </c>
     </row>
     <row r="90" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B90" s="2" t="s">
-        <v>178</v>
+        <v>24</v>
       </c>
       <c r="G90" s="25">
-        <v>4004</v>
+        <v>-145</v>
       </c>
       <c r="H90" s="25">
-        <v>4094</v>
+        <v>-144</v>
       </c>
       <c r="I90" s="25">
-        <v>1386</v>
+        <v>-79</v>
       </c>
       <c r="J90" s="25">
-        <v>1710</v>
+        <v>-138</v>
       </c>
       <c r="K90" s="25">
-        <v>3122</v>
+        <v>-98</v>
       </c>
     </row>
     <row r="91" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B91" s="2" t="s">
-        <v>179</v>
+        <v>56</v>
       </c>
       <c r="G91" s="25">
-        <v>149</v>
+        <v>2366</v>
       </c>
       <c r="H91" s="25">
-        <v>15</v>
+        <v>-1767</v>
       </c>
       <c r="I91" s="25">
-        <v>154</v>
+        <v>-3561</v>
       </c>
       <c r="J91" s="25">
-        <v>177</v>
+        <v>-5370</v>
       </c>
       <c r="K91" s="25">
-        <v>467</v>
+        <v>933</v>
       </c>
     </row>
     <row r="92" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B92" s="2" t="s">
-        <v>180</v>
+        <v>57</v>
       </c>
       <c r="G92" s="25">
-        <v>55</v>
+        <v>-577</v>
       </c>
       <c r="H92" s="25">
-        <v>0</v>
+        <v>-803</v>
       </c>
       <c r="I92" s="25">
-        <v>0</v>
+        <v>-978</v>
       </c>
       <c r="J92" s="25">
-        <v>0</v>
+        <v>-2424</v>
       </c>
       <c r="K92" s="25">
-        <v>0</v>
+        <v>-1258</v>
       </c>
     </row>
     <row r="93" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B93" s="2" t="s">
-        <v>181</v>
+        <v>70</v>
       </c>
       <c r="G93" s="25">
-        <v>-9303</v>
+        <v>-726</v>
       </c>
       <c r="H93" s="25">
-        <v>-5744</v>
+        <v>714</v>
       </c>
       <c r="I93" s="25">
-        <v>-4518</v>
+        <v>-714</v>
       </c>
       <c r="J93" s="25">
-        <v>-7010</v>
+        <v>331</v>
       </c>
       <c r="K93" s="25">
-        <v>-6456</v>
+        <v>560</v>
       </c>
     </row>
     <row r="94" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B94" s="2" t="s">
-        <v>182</v>
+        <v>49</v>
       </c>
       <c r="G94" s="25">
-        <v>-369</v>
+        <v>-22</v>
       </c>
       <c r="H94" s="25">
-        <v>-977</v>
+        <v>823</v>
       </c>
       <c r="I94" s="25">
-        <v>-813</v>
+        <v>1689</v>
       </c>
       <c r="J94" s="25">
-        <v>-1077</v>
+        <v>867</v>
       </c>
       <c r="K94" s="25">
-        <v>-1227</v>
-      </c>
-      <c r="L94" s="25">
-        <v>-1894</v>
-      </c>
-      <c r="M94" s="25">
-        <v>-1637</v>
+        <v>941</v>
       </c>
     </row>
     <row r="95" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B95" s="2" t="s">
-        <v>183</v>
+        <v>71</v>
       </c>
       <c r="G95" s="25">
-        <v>-190</v>
+        <v>4202</v>
       </c>
       <c r="H95" s="25">
-        <v>0</v>
+        <v>-888</v>
       </c>
       <c r="I95" s="25">
-        <v>0</v>
+        <v>606</v>
       </c>
       <c r="J95" s="25">
-        <v>-478</v>
+        <v>360</v>
       </c>
       <c r="K95" s="25">
-        <v>-649</v>
+        <v>7128</v>
       </c>
     </row>
     <row r="96" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B96" s="2" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="G96" s="25">
-        <v>-39</v>
+        <v>323</v>
       </c>
       <c r="H96" s="25">
-        <v>-279</v>
+        <v>260</v>
       </c>
       <c r="I96" s="25">
-        <v>-147</v>
+        <v>266</v>
       </c>
       <c r="J96" s="25">
-        <v>-542</v>
+        <v>372</v>
       </c>
       <c r="K96" s="25">
-        <v>-383</v>
-      </c>
-    </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B97" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="H97" s="25">
-        <v>-344</v>
-      </c>
-      <c r="I97" s="25">
-        <v>66</v>
-      </c>
-      <c r="J97" s="25">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B98" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="H98" s="25">
-        <v>50</v>
-      </c>
-      <c r="I98" s="25">
-        <v>-473</v>
-      </c>
-    </row>
-    <row r="99" spans="2:13" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B99" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C99" s="32"/>
-      <c r="D99" s="32"/>
-      <c r="E99" s="32"/>
-      <c r="F99" s="32"/>
-      <c r="G99" s="32">
-        <f>+SUM(G90:G96)</f>
-        <v>-5693</v>
-      </c>
-      <c r="H99" s="32">
-        <f>+SUM(H90:H98)</f>
-        <v>-3185</v>
-      </c>
-      <c r="I99" s="32">
-        <f>+SUM(I90:I98)</f>
-        <v>-4345</v>
-      </c>
-      <c r="J99" s="32">
-        <f>+SUM(J90:J98)</f>
-        <v>-7198</v>
-      </c>
-      <c r="K99" s="32">
-        <f>+SUM(K90:K96)</f>
-        <v>-5126</v>
-      </c>
-      <c r="L99" s="32"/>
-      <c r="M99" s="32"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="97" spans="2:13" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B97" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C97" s="32"/>
+      <c r="D97" s="32"/>
+      <c r="E97" s="32"/>
+      <c r="F97" s="32"/>
+      <c r="G97" s="32">
+        <f>+SUM(G85:G96)</f>
+        <v>20077</v>
+      </c>
+      <c r="H97" s="32">
+        <f>+SUM(H85:H96)</f>
+        <v>14489</v>
+      </c>
+      <c r="I97" s="32">
+        <f>+SUM(I85:I96)</f>
+        <v>17629</v>
+      </c>
+      <c r="J97" s="32">
+        <f>+SUM(J85:J96)</f>
+        <v>16628</v>
+      </c>
+      <c r="K97" s="32">
+        <f>+SUM(K85:K96)</f>
+        <v>27414</v>
+      </c>
+      <c r="L97" s="32">
+        <v>15365</v>
+      </c>
+      <c r="M97" s="32">
+        <v>23750</v>
+      </c>
+    </row>
+    <row r="99" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B99" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G99" s="25">
+        <v>4004</v>
+      </c>
+      <c r="H99" s="25">
+        <v>4094</v>
+      </c>
+      <c r="I99" s="25">
+        <v>1386</v>
+      </c>
+      <c r="J99" s="25">
+        <v>1710</v>
+      </c>
+      <c r="K99" s="25">
+        <v>3122</v>
+      </c>
+    </row>
+    <row r="100" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B100" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G100" s="25">
+        <v>149</v>
+      </c>
+      <c r="H100" s="25">
+        <v>15</v>
+      </c>
+      <c r="I100" s="25">
+        <v>154</v>
+      </c>
+      <c r="J100" s="25">
+        <v>177</v>
+      </c>
+      <c r="K100" s="25">
+        <v>467</v>
+      </c>
     </row>
     <row r="101" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B101" s="2" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="G101" s="25">
-        <v>285</v>
+        <v>55</v>
       </c>
       <c r="H101" s="25">
         <v>0</v>
       </c>
       <c r="I101" s="25">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="J101" s="25">
         <v>0</v>
       </c>
       <c r="K101" s="25">
-        <v>370</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B102" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="G102" s="25">
-        <v>-7740</v>
+        <v>-9303</v>
       </c>
       <c r="H102" s="25">
-        <v>-7158</v>
+        <v>-5744</v>
       </c>
       <c r="I102" s="25">
-        <v>-10998</v>
+        <v>-4518</v>
       </c>
       <c r="J102" s="25">
-        <v>-7810</v>
+        <v>-7010</v>
       </c>
       <c r="K102" s="25">
-        <v>-14095</v>
+        <v>-6456</v>
       </c>
     </row>
     <row r="103" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B103" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
+      </c>
+      <c r="G103" s="25">
+        <v>-369</v>
       </c>
       <c r="H103" s="25">
-        <v>-1250</v>
+        <v>-977</v>
+      </c>
+      <c r="I103" s="25">
+        <v>-813</v>
       </c>
       <c r="J103" s="25">
-        <v>0</v>
+        <v>-1077</v>
+      </c>
+      <c r="K103" s="25">
+        <v>-1227</v>
+      </c>
+      <c r="L103" s="25">
+        <v>-1894</v>
+      </c>
+      <c r="M103" s="25">
+        <v>-1637</v>
       </c>
     </row>
     <row r="104" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B104" s="2" t="s">
-        <v>76</v>
+        <v>182</v>
       </c>
       <c r="G104" s="25">
-        <v>-1752</v>
+        <v>-190</v>
       </c>
       <c r="H104" s="25">
-        <v>-1637</v>
+        <v>0</v>
       </c>
       <c r="I104" s="25">
-        <v>-1680</v>
+        <v>0</v>
       </c>
       <c r="J104" s="25">
-        <v>-1861</v>
+        <v>-478</v>
       </c>
       <c r="K104" s="25">
-        <v>-1532</v>
+        <v>-649</v>
       </c>
     </row>
     <row r="105" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B105" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G105" s="25">
-        <v>-98</v>
+        <v>-39</v>
       </c>
       <c r="H105" s="25">
-        <v>-246</v>
+        <v>-279</v>
       </c>
       <c r="I105" s="25">
-        <v>-245</v>
+        <v>-147</v>
       </c>
       <c r="J105" s="25">
-        <v>-245</v>
+        <v>-542</v>
       </c>
       <c r="K105" s="25">
-        <v>-244</v>
+        <v>-383</v>
       </c>
     </row>
     <row r="106" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B106" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="G106" s="25">
-        <v>-40</v>
+        <v>183</v>
       </c>
       <c r="H106" s="25">
-        <v>-29</v>
+        <v>-344</v>
       </c>
       <c r="I106" s="25">
-        <v>-29</v>
+        <v>66</v>
       </c>
       <c r="J106" s="25">
-        <v>-32</v>
-      </c>
-      <c r="K106" s="25">
-        <v>-52</v>
-      </c>
-    </row>
-    <row r="107" spans="2:13" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B107" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C107" s="32"/>
-      <c r="D107" s="32"/>
-      <c r="E107" s="32"/>
-      <c r="F107" s="32"/>
-      <c r="G107" s="32">
-        <f>+SUM(G101:G106)</f>
-        <v>-9345</v>
-      </c>
-      <c r="H107" s="32">
-        <f>+SUM(H101:H106)</f>
-        <v>-10320</v>
-      </c>
-      <c r="I107" s="32">
-        <f>+SUM(I101:I106)</f>
-        <v>-12748</v>
-      </c>
-      <c r="J107" s="32">
-        <f>+SUM(J101:J106)</f>
-        <v>-9948</v>
-      </c>
-      <c r="K107" s="32">
-        <f>+SUM(K101:K106)</f>
-        <v>-15553</v>
-      </c>
-      <c r="L107" s="32"/>
-      <c r="M107" s="32"/>
-    </row>
-    <row r="109" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B109" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G109" s="25">
-        <f>SUM(G88,G99,G107)</f>
-        <v>5039</v>
-      </c>
-      <c r="H109" s="25">
-        <f>SUM(H88,H99,H107)</f>
-        <v>984</v>
-      </c>
-      <c r="I109" s="25">
-        <f>SUM(I88,I99,I107)</f>
-        <v>536</v>
-      </c>
-      <c r="J109" s="25">
-        <f>SUM(J88,J99,J107)</f>
-        <v>-518</v>
-      </c>
-      <c r="K109" s="25">
-        <f>SUM(K88,K99,K107)</f>
-        <v>6735</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="107" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B107" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H107" s="25">
+        <v>50</v>
+      </c>
+      <c r="I107" s="25">
+        <v>-473</v>
+      </c>
+    </row>
+    <row r="108" spans="2:13" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B108" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C108" s="32"/>
+      <c r="D108" s="32"/>
+      <c r="E108" s="32"/>
+      <c r="F108" s="32"/>
+      <c r="G108" s="32">
+        <f>+SUM(G99:G105)</f>
+        <v>-5693</v>
+      </c>
+      <c r="H108" s="32">
+        <f>+SUM(H99:H107)</f>
+        <v>-3185</v>
+      </c>
+      <c r="I108" s="32">
+        <f>+SUM(I99:I107)</f>
+        <v>-4345</v>
+      </c>
+      <c r="J108" s="32">
+        <f>+SUM(J99:J107)</f>
+        <v>-7198</v>
+      </c>
+      <c r="K108" s="32">
+        <f>+SUM(K99:K105)</f>
+        <v>-5126</v>
+      </c>
+      <c r="L108" s="32"/>
+      <c r="M108" s="32"/>
+    </row>
+    <row r="110" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B110" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G110" s="25">
+        <v>285</v>
+      </c>
+      <c r="H110" s="25">
+        <v>0</v>
+      </c>
+      <c r="I110" s="25">
+        <v>204</v>
+      </c>
+      <c r="J110" s="25">
+        <v>0</v>
+      </c>
+      <c r="K110" s="25">
+        <v>370</v>
       </c>
     </row>
     <row r="111" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B111" s="2" t="s">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="G111" s="25">
-        <f t="shared" ref="G111:M111" si="320">+G88+G94</f>
-        <v>19708</v>
+        <v>-7740</v>
       </c>
       <c r="H111" s="25">
-        <f t="shared" si="320"/>
-        <v>13512</v>
+        <v>-7158</v>
       </c>
       <c r="I111" s="25">
-        <f t="shared" si="320"/>
-        <v>16816</v>
+        <v>-10998</v>
       </c>
       <c r="J111" s="25">
-        <f t="shared" si="320"/>
-        <v>15551</v>
+        <v>-7810</v>
       </c>
       <c r="K111" s="25">
-        <f t="shared" si="320"/>
-        <v>26187</v>
-      </c>
-      <c r="L111" s="25">
-        <f t="shared" si="320"/>
-        <v>13471</v>
-      </c>
-      <c r="M111" s="25">
-        <f t="shared" si="320"/>
-        <v>22113</v>
+        <v>-14095</v>
       </c>
     </row>
     <row r="112" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B112" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G112" s="25">
-        <f t="shared" ref="G112:M112" si="321">+G21</f>
-        <v>14046</v>
+        <v>188</v>
       </c>
       <c r="H112" s="25">
-        <f t="shared" si="321"/>
-        <v>16599</v>
-      </c>
-      <c r="I112" s="25">
-        <f t="shared" si="321"/>
-        <v>19309</v>
+        <v>-1250</v>
       </c>
       <c r="J112" s="25">
-        <f t="shared" si="321"/>
-        <v>32926</v>
-      </c>
-      <c r="K112" s="25">
-        <f t="shared" si="321"/>
-        <v>18775</v>
-      </c>
-      <c r="L112" s="25">
-        <f t="shared" si="321"/>
-        <v>26546</v>
-      </c>
-      <c r="M112" s="25">
-        <f t="shared" si="321"/>
-        <v>31910</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B113" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G113" s="25">
+        <v>-1752</v>
+      </c>
+      <c r="H113" s="25">
+        <v>-1637</v>
+      </c>
+      <c r="I113" s="25">
+        <v>-1680</v>
+      </c>
+      <c r="J113" s="25">
+        <v>-1861</v>
+      </c>
+      <c r="K113" s="25">
+        <v>-1532</v>
       </c>
     </row>
     <row r="114" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B114" s="2" t="s">
-        <v>196</v>
+        <v>76</v>
       </c>
       <c r="G114" s="25">
-        <f>+G94</f>
-        <v>-369</v>
+        <v>-98</v>
       </c>
       <c r="H114" s="25">
-        <f t="shared" ref="H114:L114" si="322">+H94</f>
-        <v>-977</v>
+        <v>-246</v>
       </c>
       <c r="I114" s="25">
-        <f t="shared" si="322"/>
-        <v>-813</v>
+        <v>-245</v>
       </c>
       <c r="J114" s="25">
-        <f t="shared" si="322"/>
-        <v>-1077</v>
+        <v>-245</v>
       </c>
       <c r="K114" s="25">
-        <f t="shared" si="322"/>
-        <v>-1227</v>
-      </c>
-      <c r="L114" s="25">
-        <f t="shared" si="322"/>
-        <v>-1894</v>
+        <v>-244</v>
       </c>
     </row>
     <row r="115" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B115" s="2" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="G115" s="25">
-        <f>+G78</f>
-        <v>410</v>
+        <v>-40</v>
       </c>
       <c r="H115" s="25">
-        <f t="shared" ref="H115:L115" si="323">+H78</f>
-        <v>433</v>
+        <v>-29</v>
       </c>
       <c r="I115" s="25">
-        <f t="shared" si="323"/>
-        <v>478</v>
+        <v>-29</v>
       </c>
       <c r="J115" s="25">
-        <f t="shared" si="323"/>
-        <v>543</v>
+        <v>-32</v>
       </c>
       <c r="K115" s="25">
-        <f t="shared" si="323"/>
-        <v>611</v>
-      </c>
-      <c r="L115" s="25">
-        <f t="shared" si="323"/>
-        <v>668</v>
-      </c>
+        <v>-52</v>
+      </c>
+    </row>
+    <row r="116" spans="2:13" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B116" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C116" s="32"/>
+      <c r="D116" s="32"/>
+      <c r="E116" s="32"/>
+      <c r="F116" s="32"/>
+      <c r="G116" s="32">
+        <f>+SUM(G110:G115)</f>
+        <v>-9345</v>
+      </c>
+      <c r="H116" s="32">
+        <f>+SUM(H110:H115)</f>
+        <v>-10320</v>
+      </c>
+      <c r="I116" s="32">
+        <f>+SUM(I110:I115)</f>
+        <v>-12748</v>
+      </c>
+      <c r="J116" s="32">
+        <f>+SUM(J110:J115)</f>
+        <v>-9948</v>
+      </c>
+      <c r="K116" s="32">
+        <f>+SUM(K110:K115)</f>
+        <v>-15553</v>
+      </c>
+      <c r="L116" s="32"/>
+      <c r="M116" s="32"/>
     </row>
     <row r="118" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B118" s="2" t="s">
-        <v>202</v>
+        <v>189</v>
+      </c>
+      <c r="G118" s="25">
+        <f>SUM(G97,G108,G116)</f>
+        <v>5039</v>
       </c>
       <c r="H118" s="25">
-        <v>1300</v>
+        <f>SUM(H97,H108,H116)</f>
+        <v>984</v>
       </c>
       <c r="I118" s="25">
-        <v>1400</v>
+        <f>SUM(I97,I108,I116)</f>
+        <v>536</v>
       </c>
       <c r="J118" s="25">
-        <v>1600</v>
+        <f>SUM(J97,J108,J116)</f>
+        <v>-518</v>
       </c>
       <c r="K118" s="25">
-        <v>1600</v>
-      </c>
-      <c r="L118" s="25">
-        <v>1800</v>
-      </c>
-      <c r="M118" s="25">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="119" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B119" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="H119" s="25">
-        <v>123</v>
-      </c>
-      <c r="I119" s="25">
-        <v>187</v>
-      </c>
-      <c r="J119" s="25">
-        <v>151</v>
-      </c>
-      <c r="K119" s="25">
-        <v>160</v>
-      </c>
-      <c r="L119" s="25">
-        <v>118</v>
-      </c>
-      <c r="M119" s="25">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="120" spans="2:13" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="C120" s="32">
-        <v>639</v>
-      </c>
-      <c r="D120" s="32">
-        <v>717</v>
-      </c>
-      <c r="E120" s="32">
-        <v>896</v>
-      </c>
-      <c r="F120" s="32">
-        <v>1100</v>
-      </c>
-      <c r="G120" s="32">
-        <v>1300</v>
-      </c>
-      <c r="H120" s="32">
-        <f t="shared" ref="H120:M120" si="324">SUM(H118:H119)</f>
-        <v>1423</v>
-      </c>
-      <c r="I120" s="32">
+        <f>SUM(K97,K108,K116)</f>
+        <v>6735</v>
+      </c>
+    </row>
+    <row r="120" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B120" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G120" s="25">
+        <f t="shared" ref="G120:M120" si="324">+G97+G103</f>
+        <v>19708</v>
+      </c>
+      <c r="H120" s="25">
         <f t="shared" si="324"/>
-        <v>1587</v>
-      </c>
-      <c r="J120" s="32">
+        <v>13512</v>
+      </c>
+      <c r="I120" s="25">
         <f t="shared" si="324"/>
-        <v>1751</v>
-      </c>
-      <c r="K120" s="32">
+        <v>16816</v>
+      </c>
+      <c r="J120" s="25">
         <f t="shared" si="324"/>
-        <v>1760</v>
-      </c>
-      <c r="L120" s="32">
+        <v>15551</v>
+      </c>
+      <c r="K120" s="25">
         <f t="shared" si="324"/>
-        <v>1918</v>
-      </c>
-      <c r="M120" s="32">
+        <v>26187</v>
+      </c>
+      <c r="L120" s="25">
         <f t="shared" si="324"/>
-        <v>2449</v>
+        <v>13471</v>
+      </c>
+      <c r="M120" s="25">
+        <f t="shared" si="324"/>
+        <v>22113</v>
       </c>
     </row>
     <row r="121" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B121" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C121" s="25">
-        <f>+C120*0.46</f>
-        <v>293.94</v>
-      </c>
-      <c r="D121" s="25">
-        <f>+D120*0.44</f>
-        <v>315.48</v>
-      </c>
-      <c r="E121" s="25">
-        <f>+E120*0.42</f>
-        <v>376.32</v>
-      </c>
-      <c r="F121" s="25">
-        <f>+F120*0.4</f>
-        <v>440</v>
+        <v>79</v>
       </c>
       <c r="G121" s="25">
-        <f>+G120*0.38</f>
-        <v>494</v>
+        <f t="shared" ref="G121:M121" si="325">+G21</f>
+        <v>14046</v>
       </c>
       <c r="H121" s="25">
-        <f>+H120*0.37</f>
-        <v>526.51</v>
+        <f t="shared" si="325"/>
+        <v>16599</v>
       </c>
       <c r="I121" s="25">
-        <f>+I120*0.37</f>
-        <v>587.18999999999994</v>
+        <f t="shared" si="325"/>
+        <v>19309</v>
       </c>
       <c r="J121" s="25">
-        <f>+J120*0.39</f>
-        <v>682.89</v>
+        <f t="shared" si="325"/>
+        <v>32926</v>
       </c>
       <c r="K121" s="25">
-        <f>+K120*0.39</f>
-        <v>686.4</v>
+        <f t="shared" si="325"/>
+        <v>18775</v>
       </c>
       <c r="L121" s="25">
-        <f>+L120*0.4</f>
-        <v>767.2</v>
+        <f t="shared" si="325"/>
+        <v>26546</v>
       </c>
       <c r="M121" s="25">
-        <f>+M120*0.4</f>
-        <v>979.6</v>
-      </c>
-    </row>
-    <row r="122" spans="2:13" s="19" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B122" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="C122" s="33">
-        <f>+C121/C120</f>
-        <v>0.46</v>
-      </c>
-      <c r="D122" s="33">
-        <f t="shared" ref="D122:M122" si="325">+D121/D120</f>
-        <v>0.44</v>
-      </c>
-      <c r="E122" s="33">
         <f t="shared" si="325"/>
-        <v>0.42</v>
-      </c>
-      <c r="F122" s="33">
-        <f t="shared" si="325"/>
-        <v>0.4</v>
-      </c>
-      <c r="G122" s="33">
-        <f t="shared" si="325"/>
-        <v>0.38</v>
-      </c>
-      <c r="H122" s="33">
-        <f t="shared" si="325"/>
-        <v>0.37</v>
-      </c>
-      <c r="I122" s="33">
-        <f t="shared" si="325"/>
-        <v>0.36999999999999994</v>
-      </c>
-      <c r="J122" s="33">
-        <f t="shared" si="325"/>
-        <v>0.39</v>
-      </c>
-      <c r="K122" s="33">
-        <f t="shared" si="325"/>
-        <v>0.39</v>
-      </c>
-      <c r="L122" s="33">
-        <f t="shared" si="325"/>
-        <v>0.4</v>
-      </c>
-      <c r="M122" s="33">
-        <f t="shared" si="325"/>
-        <v>0.4</v>
+        <v>31910</v>
       </c>
     </row>
     <row r="123" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="D123" s="29">
-        <f t="shared" ref="D123:L123" si="326">+D120/C120-1</f>
-        <v>0.1220657276995305</v>
-      </c>
-      <c r="E123" s="29">
+      <c r="B123" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G123" s="25">
+        <f>+G103</f>
+        <v>-369</v>
+      </c>
+      <c r="H123" s="25">
+        <f t="shared" ref="H123:L123" si="326">+H103</f>
+        <v>-977</v>
+      </c>
+      <c r="I123" s="25">
         <f t="shared" si="326"/>
-        <v>0.24965132496513243</v>
-      </c>
-      <c r="F123" s="29">
+        <v>-813</v>
+      </c>
+      <c r="J123" s="25">
         <f t="shared" si="326"/>
-        <v>0.2276785714285714</v>
-      </c>
-      <c r="G123" s="29">
+        <v>-1077</v>
+      </c>
+      <c r="K123" s="25">
         <f t="shared" si="326"/>
-        <v>0.18181818181818188</v>
-      </c>
-      <c r="H123" s="29">
+        <v>-1227</v>
+      </c>
+      <c r="L123" s="25">
         <f t="shared" si="326"/>
-        <v>9.4615384615384546E-2</v>
-      </c>
-      <c r="I123" s="29">
-        <f t="shared" si="326"/>
-        <v>0.11524947294448351</v>
-      </c>
-      <c r="J123" s="29">
-        <f t="shared" si="326"/>
-        <v>0.10333963453056083</v>
-      </c>
-      <c r="K123" s="29">
-        <f t="shared" si="326"/>
-        <v>5.1399200456880845E-3</v>
-      </c>
-      <c r="L123" s="29">
-        <f t="shared" si="326"/>
-        <v>8.9772727272727337E-2</v>
-      </c>
-      <c r="M123" s="29">
-        <f>+M120/L120-1</f>
-        <v>0.27685088633993749</v>
+        <v>-1894</v>
       </c>
     </row>
     <row r="124" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B124" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D124" s="25">
-        <f t="shared" ref="D124:L124" si="327">+D120-C120</f>
-        <v>78</v>
-      </c>
-      <c r="E124" s="25">
-        <f t="shared" si="327"/>
-        <v>179</v>
-      </c>
-      <c r="F124" s="25">
-        <f t="shared" si="327"/>
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G124" s="25">
-        <f t="shared" si="327"/>
-        <v>200</v>
+        <f>+G87</f>
+        <v>410</v>
       </c>
       <c r="H124" s="25">
-        <f t="shared" si="327"/>
-        <v>123</v>
+        <f t="shared" ref="H124:L124" si="327">+H87</f>
+        <v>433</v>
       </c>
       <c r="I124" s="25">
         <f t="shared" si="327"/>
-        <v>164</v>
+        <v>478</v>
       </c>
       <c r="J124" s="25">
         <f t="shared" si="327"/>
-        <v>164</v>
+        <v>543</v>
       </c>
       <c r="K124" s="25">
         <f t="shared" si="327"/>
-        <v>9</v>
+        <v>611</v>
       </c>
       <c r="L124" s="25">
         <f t="shared" si="327"/>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="127" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B127" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="H127" s="25">
+        <v>1300</v>
+      </c>
+      <c r="I127" s="25">
+        <v>1400</v>
+      </c>
+      <c r="J127" s="25">
+        <v>1600</v>
+      </c>
+      <c r="K127" s="25">
+        <v>1600</v>
+      </c>
+      <c r="L127" s="25">
+        <v>1800</v>
+      </c>
+      <c r="M127" s="25">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="128" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B128" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H128" s="25">
+        <v>123</v>
+      </c>
+      <c r="I128" s="25">
+        <v>187</v>
+      </c>
+      <c r="J128" s="25">
+        <v>151</v>
+      </c>
+      <c r="K128" s="25">
+        <v>160</v>
+      </c>
+      <c r="L128" s="25">
+        <v>118</v>
+      </c>
+      <c r="M128" s="25">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="129" spans="2:13" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B129" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C129" s="32">
+        <v>639</v>
+      </c>
+      <c r="D129" s="32">
+        <v>717</v>
+      </c>
+      <c r="E129" s="32">
+        <v>896</v>
+      </c>
+      <c r="F129" s="32">
+        <v>1100</v>
+      </c>
+      <c r="G129" s="32">
+        <v>1300</v>
+      </c>
+      <c r="H129" s="32">
+        <f t="shared" ref="H129:M129" si="328">SUM(H127:H128)</f>
+        <v>1423</v>
+      </c>
+      <c r="I129" s="32">
+        <f t="shared" si="328"/>
+        <v>1587</v>
+      </c>
+      <c r="J129" s="32">
+        <f t="shared" si="328"/>
+        <v>1751</v>
+      </c>
+      <c r="K129" s="32">
+        <f t="shared" si="328"/>
+        <v>1760</v>
+      </c>
+      <c r="L129" s="32">
+        <f t="shared" si="328"/>
+        <v>1918</v>
+      </c>
+      <c r="M129" s="32">
+        <f t="shared" si="328"/>
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="130" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B130" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C130" s="25">
+        <f>+C129*0.46</f>
+        <v>293.94</v>
+      </c>
+      <c r="D130" s="25">
+        <f>+D129*0.44</f>
+        <v>315.48</v>
+      </c>
+      <c r="E130" s="25">
+        <f>+E129*0.42</f>
+        <v>376.32</v>
+      </c>
+      <c r="F130" s="25">
+        <f>+F129*0.4</f>
+        <v>440</v>
+      </c>
+      <c r="G130" s="25">
+        <f>+G129*0.38</f>
+        <v>494</v>
+      </c>
+      <c r="H130" s="25">
+        <f>+H129*0.37</f>
+        <v>526.51</v>
+      </c>
+      <c r="I130" s="25">
+        <f>+I129*0.37</f>
+        <v>587.18999999999994</v>
+      </c>
+      <c r="J130" s="25">
+        <f>+J129*0.39</f>
+        <v>682.89</v>
+      </c>
+      <c r="K130" s="25">
+        <f>+K129*0.39</f>
+        <v>686.4</v>
+      </c>
+      <c r="L130" s="25">
+        <f>+L129*0.4</f>
+        <v>767.2</v>
+      </c>
+      <c r="M130" s="25">
+        <f>+M129*0.4</f>
+        <v>979.6</v>
+      </c>
+    </row>
+    <row r="131" spans="2:13" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B131" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="C131" s="33">
+        <f>+C130/C129</f>
+        <v>0.46</v>
+      </c>
+      <c r="D131" s="33">
+        <f t="shared" ref="D131:M131" si="329">+D130/D129</f>
+        <v>0.44</v>
+      </c>
+      <c r="E131" s="33">
+        <f t="shared" si="329"/>
+        <v>0.42</v>
+      </c>
+      <c r="F131" s="33">
+        <f t="shared" si="329"/>
+        <v>0.4</v>
+      </c>
+      <c r="G131" s="33">
+        <f t="shared" si="329"/>
+        <v>0.38</v>
+      </c>
+      <c r="H131" s="33">
+        <f t="shared" si="329"/>
+        <v>0.37</v>
+      </c>
+      <c r="I131" s="33">
+        <f t="shared" si="329"/>
+        <v>0.36999999999999994</v>
+      </c>
+      <c r="J131" s="33">
+        <f t="shared" si="329"/>
+        <v>0.39</v>
+      </c>
+      <c r="K131" s="33">
+        <f t="shared" si="329"/>
+        <v>0.39</v>
+      </c>
+      <c r="L131" s="33">
+        <f t="shared" si="329"/>
+        <v>0.4</v>
+      </c>
+      <c r="M131" s="33">
+        <f t="shared" si="329"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="132" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="D132" s="29">
+        <f t="shared" ref="D132:L132" si="330">+D129/C129-1</f>
+        <v>0.1220657276995305</v>
+      </c>
+      <c r="E132" s="29">
+        <f t="shared" si="330"/>
+        <v>0.24965132496513243</v>
+      </c>
+      <c r="F132" s="29">
+        <f t="shared" si="330"/>
+        <v>0.2276785714285714</v>
+      </c>
+      <c r="G132" s="29">
+        <f t="shared" si="330"/>
+        <v>0.18181818181818188</v>
+      </c>
+      <c r="H132" s="29">
+        <f t="shared" si="330"/>
+        <v>9.4615384615384546E-2</v>
+      </c>
+      <c r="I132" s="29">
+        <f t="shared" si="330"/>
+        <v>0.11524947294448351</v>
+      </c>
+      <c r="J132" s="29">
+        <f t="shared" si="330"/>
+        <v>0.10333963453056083</v>
+      </c>
+      <c r="K132" s="29">
+        <f t="shared" si="330"/>
+        <v>5.1399200456880845E-3</v>
+      </c>
+      <c r="L132" s="29">
+        <f t="shared" si="330"/>
+        <v>8.9772727272727337E-2</v>
+      </c>
+      <c r="M132" s="29">
+        <f>+M129/L129-1</f>
+        <v>0.27685088633993749</v>
+      </c>
+    </row>
+    <row r="133" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B133" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D133" s="25">
+        <f t="shared" ref="D133:L133" si="331">+D129-C129</f>
+        <v>78</v>
+      </c>
+      <c r="E133" s="25">
+        <f t="shared" si="331"/>
+        <v>179</v>
+      </c>
+      <c r="F133" s="25">
+        <f t="shared" si="331"/>
+        <v>204</v>
+      </c>
+      <c r="G133" s="25">
+        <f t="shared" si="331"/>
+        <v>200</v>
+      </c>
+      <c r="H133" s="25">
+        <f t="shared" si="331"/>
+        <v>123</v>
+      </c>
+      <c r="I133" s="25">
+        <f t="shared" si="331"/>
+        <v>164</v>
+      </c>
+      <c r="J133" s="25">
+        <f t="shared" si="331"/>
+        <v>164</v>
+      </c>
+      <c r="K133" s="25">
+        <f t="shared" si="331"/>
+        <v>9</v>
+      </c>
+      <c r="L133" s="25">
+        <f t="shared" si="331"/>
         <v>158</v>
       </c>
-      <c r="M124" s="34">
-        <f>+M120-L120</f>
+      <c r="M133" s="34">
+        <f>+M129-L129</f>
         <v>531</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="B6:J21 B26:I27 B23:J23 B22:E22 G22:I22 B25:J25 B24:F24 AB15:AB24" formula="1"/>
+    <ignoredError sqref="B6:J21 B26:I27 B23:J23 B22:E22 G22:I22 C25:J25 B24:F24 AB15:AB24" formula="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Semiconductor/NVDA.xlsx
+++ b/Semiconductor/NVDA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameelbrannon/Library/CloudStorage/Dropbox/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1737A9A-C692-254B-9D3D-84AF3029D2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC5C2CB-34EA-5B4B-82AE-2B5E4A541B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14320" yWindow="1320" windowWidth="44260" windowHeight="24640" activeTab="2" xr2:uid="{834EDAA3-D05C-5B48-B7D6-13D13D56A97E}"/>
+    <workbookView xWindow="6940" yWindow="1320" windowWidth="44260" windowHeight="24640" activeTab="2" xr2:uid="{834EDAA3-D05C-5B48-B7D6-13D13D56A97E}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="214">
   <si>
     <t>P</t>
   </si>
@@ -677,6 +677,9 @@
   </si>
   <si>
     <t>CC</t>
+  </si>
+  <si>
+    <t>$M</t>
   </si>
 </sst>
 </file>
@@ -1970,8 +1973,7 @@
     <col min="7" max="7" width="6.6640625" style="25" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="7.33203125" style="25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.83203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="7.6640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="8" style="25" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="10.83203125" style="2"/>
     <col min="17" max="20" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
@@ -1984,6 +1986,9 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:238" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="7" t="s">
+        <v>213</v>
+      </c>
       <c r="C2" s="23"/>
       <c r="D2" s="23">
         <v>45137</v>
@@ -3453,40 +3458,40 @@
         <v>212811</v>
       </c>
       <c r="AC11" s="5">
-        <f>+AB11*1.4</f>
-        <v>297935.39999999997</v>
+        <f>+AB11*1.3</f>
+        <v>276654.3</v>
       </c>
       <c r="AD11" s="5">
-        <f t="shared" ref="AD11" si="203">+AC11*1.4</f>
-        <v>417109.55999999994</v>
+        <f>+AC11*1.25</f>
+        <v>345817.875</v>
       </c>
       <c r="AE11" s="5">
         <f>+AD11*1.2</f>
-        <v>500531.47199999989</v>
+        <v>414981.45</v>
       </c>
       <c r="AF11" s="5">
-        <f t="shared" ref="AF11" si="204">+AE11*1.2</f>
-        <v>600637.76639999985</v>
+        <f t="shared" ref="AF11" si="203">+AE11*1.2</f>
+        <v>497977.74</v>
       </c>
       <c r="AG11" s="5">
         <f>+AF11*1.1</f>
-        <v>660701.5430399999</v>
+        <v>547775.51400000008</v>
       </c>
       <c r="AH11" s="5">
         <f>+AG11*1.1</f>
-        <v>726771.69734399999</v>
+        <v>602553.0654000002</v>
       </c>
       <c r="AI11" s="5">
         <f>+AH11*1.1</f>
-        <v>799448.8670784001</v>
+        <v>662808.37194000022</v>
       </c>
       <c r="AJ11" s="5">
         <f>+AI11*1.1</f>
-        <v>879393.75378624024</v>
+        <v>729089.20913400035</v>
       </c>
       <c r="AK11" s="5">
         <f>+AJ11*1.1</f>
-        <v>967333.12916486431</v>
+        <v>801998.13004740048</v>
       </c>
     </row>
     <row r="12" spans="2:238" x14ac:dyDescent="0.2">
@@ -3503,7 +3508,7 @@
         <v>4720</v>
       </c>
       <c r="F12" s="24">
-        <f t="shared" ref="F12:F18" si="205">+Z12-SUM(C12:E12)</f>
+        <f t="shared" ref="F12:F18" si="204">+Z12-SUM(C12:E12)</f>
         <v>5312</v>
       </c>
       <c r="G12" s="25">
@@ -3559,39 +3564,39 @@
       </c>
       <c r="AC12" s="2">
         <f>+AC$11*(AB12/AB$11)</f>
-        <v>87277.39999999998</v>
+        <v>81043.299999999988</v>
       </c>
       <c r="AD12" s="2">
-        <f t="shared" ref="AD12:AK12" si="206">+AD$11*(AC12/AC$11)</f>
-        <v>122188.35999999997</v>
+        <f t="shared" ref="AD12:AK12" si="205">+AD$11*(AC12/AC$11)</f>
+        <v>101304.125</v>
       </c>
       <c r="AE12" s="2">
-        <f t="shared" si="206"/>
-        <v>146626.03199999995</v>
+        <f t="shared" si="205"/>
+        <v>121564.95</v>
       </c>
       <c r="AF12" s="2">
-        <f t="shared" si="206"/>
-        <v>175951.23839999991</v>
+        <f t="shared" si="205"/>
+        <v>145877.94</v>
       </c>
       <c r="AG12" s="2">
-        <f t="shared" si="206"/>
-        <v>193546.36223999993</v>
+        <f t="shared" si="205"/>
+        <v>160465.73400000003</v>
       </c>
       <c r="AH12" s="2">
-        <f t="shared" si="206"/>
-        <v>212900.99846399995</v>
+        <f t="shared" si="205"/>
+        <v>176512.30740000005</v>
       </c>
       <c r="AI12" s="2">
-        <f t="shared" si="206"/>
-        <v>234191.09831039998</v>
+        <f t="shared" si="205"/>
+        <v>194163.53814000005</v>
       </c>
       <c r="AJ12" s="2">
-        <f t="shared" si="206"/>
-        <v>257610.20814144</v>
+        <f t="shared" si="205"/>
+        <v>213579.89195400011</v>
       </c>
       <c r="AK12" s="2">
-        <f t="shared" si="206"/>
-        <v>283371.228955584</v>
+        <f t="shared" si="205"/>
+        <v>234937.88114940014</v>
       </c>
     </row>
     <row r="13" spans="2:238" x14ac:dyDescent="0.2">
@@ -3608,7 +3613,7 @@
         <v>2294</v>
       </c>
       <c r="F13" s="24">
-        <f t="shared" si="205"/>
+        <f t="shared" si="204"/>
         <v>2466</v>
       </c>
       <c r="G13" s="25">
@@ -3663,39 +3668,39 @@
       </c>
       <c r="AC13" s="2">
         <f>+AC$11*(AB13/AB$11)</f>
-        <v>25178.999999999996</v>
+        <v>23380.5</v>
       </c>
       <c r="AD13" s="2">
-        <f t="shared" ref="AD13:AK13" si="207">+AD$11*(AC13/AC$11)</f>
-        <v>35250.599999999991</v>
+        <f t="shared" ref="AD13:AK13" si="206">+AD$11*(AC13/AC$11)</f>
+        <v>29225.625</v>
       </c>
       <c r="AE13" s="2">
-        <f t="shared" si="207"/>
-        <v>42300.719999999987</v>
+        <f t="shared" si="206"/>
+        <v>35070.75</v>
       </c>
       <c r="AF13" s="2">
-        <f t="shared" si="207"/>
-        <v>50760.863999999987</v>
+        <f t="shared" si="206"/>
+        <v>42084.9</v>
       </c>
       <c r="AG13" s="2">
-        <f t="shared" si="207"/>
-        <v>55836.950399999987</v>
+        <f t="shared" si="206"/>
+        <v>46293.390000000007</v>
       </c>
       <c r="AH13" s="2">
-        <f t="shared" si="207"/>
-        <v>61420.64544</v>
+        <f t="shared" si="206"/>
+        <v>50922.729000000014</v>
       </c>
       <c r="AI13" s="2">
-        <f t="shared" si="207"/>
-        <v>67562.709984000001</v>
+        <f t="shared" si="206"/>
+        <v>56015.001900000017</v>
       </c>
       <c r="AJ13" s="2">
-        <f t="shared" si="207"/>
-        <v>74318.980982400011</v>
+        <f t="shared" si="206"/>
+        <v>61616.502090000031</v>
       </c>
       <c r="AK13" s="2">
-        <f t="shared" si="207"/>
-        <v>81750.879080640007</v>
+        <f t="shared" si="206"/>
+        <v>67778.152299000038</v>
       </c>
     </row>
     <row r="14" spans="2:238" x14ac:dyDescent="0.2">
@@ -3712,7 +3717,7 @@
         <v>689</v>
       </c>
       <c r="F14" s="24">
-        <f t="shared" si="205"/>
+        <f t="shared" si="204"/>
         <v>710</v>
       </c>
       <c r="G14" s="25">
@@ -3762,44 +3767,44 @@
         <v>3491</v>
       </c>
       <c r="AB14" s="2">
-        <f t="shared" ref="AB14:AB23" si="208">SUM(K14:N14)</f>
+        <f t="shared" ref="AB14:AB23" si="207">SUM(K14:N14)</f>
         <v>4997</v>
       </c>
       <c r="AC14" s="2">
         <f>+AC$11*(AB14/AB$11)</f>
-        <v>6995.7999999999993</v>
+        <v>6496.1</v>
       </c>
       <c r="AD14" s="2">
-        <f t="shared" ref="AD14:AK14" si="209">+AD$11*(AC14/AC$11)</f>
-        <v>9794.119999999999</v>
+        <f t="shared" ref="AD14:AK14" si="208">+AD$11*(AC14/AC$11)</f>
+        <v>8120.1250000000009</v>
       </c>
       <c r="AE14" s="2">
-        <f t="shared" si="209"/>
-        <v>11752.943999999998</v>
+        <f t="shared" si="208"/>
+        <v>9744.1500000000015</v>
       </c>
       <c r="AF14" s="2">
-        <f t="shared" si="209"/>
-        <v>14103.532799999997</v>
+        <f t="shared" si="208"/>
+        <v>11692.980000000001</v>
       </c>
       <c r="AG14" s="2">
-        <f t="shared" si="209"/>
-        <v>15513.886079999998</v>
+        <f t="shared" si="208"/>
+        <v>12862.278000000002</v>
       </c>
       <c r="AH14" s="2">
-        <f t="shared" si="209"/>
-        <v>17065.274688000001</v>
+        <f t="shared" si="208"/>
+        <v>14148.505800000006</v>
       </c>
       <c r="AI14" s="2">
-        <f t="shared" si="209"/>
-        <v>18771.802156800004</v>
+        <f t="shared" si="208"/>
+        <v>15563.356380000007</v>
       </c>
       <c r="AJ14" s="2">
-        <f t="shared" si="209"/>
-        <v>20648.982372480008</v>
+        <f t="shared" si="208"/>
+        <v>17119.692018000009</v>
       </c>
       <c r="AK14" s="2">
-        <f t="shared" si="209"/>
-        <v>22713.88060972801</v>
+        <f t="shared" si="208"/>
+        <v>18831.661219800011</v>
       </c>
     </row>
     <row r="15" spans="2:238" x14ac:dyDescent="0.2">
@@ -3819,7 +3824,7 @@
         <v>10417</v>
       </c>
       <c r="F15" s="24">
-        <f t="shared" si="205"/>
+        <f t="shared" si="204"/>
         <v>13615</v>
       </c>
       <c r="G15" s="25">
@@ -3855,72 +3860,72 @@
         <v>41400</v>
       </c>
       <c r="U15" s="2">
-        <f t="shared" ref="U15:AC15" si="210">+U11-SUM(U12:U14)</f>
+        <f t="shared" ref="U15:AC15" si="209">+U11-SUM(U12:U14)</f>
         <v>3804</v>
       </c>
       <c r="V15" s="2">
+        <f t="shared" si="209"/>
+        <v>2846</v>
+      </c>
+      <c r="W15" s="2">
+        <f t="shared" si="209"/>
+        <v>4532</v>
+      </c>
+      <c r="X15" s="2">
+        <f t="shared" si="209"/>
+        <v>10041</v>
+      </c>
+      <c r="Y15" s="2">
+        <f t="shared" si="209"/>
+        <v>5577</v>
+      </c>
+      <c r="Z15" s="2">
+        <f t="shared" si="209"/>
+        <v>32972</v>
+      </c>
+      <c r="AA15" s="2">
+        <f t="shared" si="209"/>
+        <v>81453</v>
+      </c>
+      <c r="AB15" s="2">
+        <f t="shared" si="207"/>
+        <v>127488</v>
+      </c>
+      <c r="AC15" s="2">
+        <f t="shared" si="209"/>
+        <v>165734.39999999999</v>
+      </c>
+      <c r="AD15" s="2">
+        <f t="shared" ref="AD15:AK15" si="210">+AD11-SUM(AD12:AD14)</f>
+        <v>207168</v>
+      </c>
+      <c r="AE15" s="2">
         <f t="shared" si="210"/>
-        <v>2846</v>
-      </c>
-      <c r="W15" s="2">
+        <v>248601.60000000001</v>
+      </c>
+      <c r="AF15" s="2">
         <f t="shared" si="210"/>
-        <v>4532</v>
-      </c>
-      <c r="X15" s="2">
+        <v>298321.91999999998</v>
+      </c>
+      <c r="AG15" s="2">
         <f t="shared" si="210"/>
-        <v>10041</v>
-      </c>
-      <c r="Y15" s="2">
+        <v>328154.11200000008</v>
+      </c>
+      <c r="AH15" s="2">
         <f t="shared" si="210"/>
-        <v>5577</v>
-      </c>
-      <c r="Z15" s="2">
+        <v>360969.52320000011</v>
+      </c>
+      <c r="AI15" s="2">
         <f t="shared" si="210"/>
-        <v>32972</v>
-      </c>
-      <c r="AA15" s="2">
+        <v>397066.47552000015</v>
+      </c>
+      <c r="AJ15" s="2">
         <f t="shared" si="210"/>
-        <v>81453</v>
-      </c>
-      <c r="AB15" s="2">
-        <f t="shared" si="208"/>
-        <v>127488</v>
-      </c>
-      <c r="AC15" s="2">
+        <v>436773.12307200022</v>
+      </c>
+      <c r="AK15" s="2">
         <f t="shared" si="210"/>
-        <v>178483.19999999998</v>
-      </c>
-      <c r="AD15" s="2">
-        <f t="shared" ref="AD15:AK15" si="211">+AD11-SUM(AD12:AD14)</f>
-        <v>249876.47999999998</v>
-      </c>
-      <c r="AE15" s="2">
-        <f t="shared" si="211"/>
-        <v>299851.77599999995</v>
-      </c>
-      <c r="AF15" s="2">
-        <f t="shared" si="211"/>
-        <v>359822.13119999995</v>
-      </c>
-      <c r="AG15" s="2">
-        <f t="shared" si="211"/>
-        <v>395804.34431999997</v>
-      </c>
-      <c r="AH15" s="2">
-        <f t="shared" si="211"/>
-        <v>435384.77875200007</v>
-      </c>
-      <c r="AI15" s="2">
-        <f t="shared" si="211"/>
-        <v>478923.25662720011</v>
-      </c>
-      <c r="AJ15" s="2">
-        <f t="shared" si="211"/>
-        <v>526815.58228992019</v>
-      </c>
-      <c r="AK15" s="2">
-        <f t="shared" si="211"/>
-        <v>579497.14051891235</v>
+        <v>480450.43537920027</v>
       </c>
     </row>
     <row r="16" spans="2:238" x14ac:dyDescent="0.2">
@@ -3937,7 +3942,7 @@
         <v>234</v>
       </c>
       <c r="F16" s="24">
-        <f t="shared" si="205"/>
+        <f t="shared" si="204"/>
         <v>295</v>
       </c>
       <c r="G16" s="25">
@@ -3988,7 +3993,7 @@
         <v>1786</v>
       </c>
       <c r="AB16" s="2">
-        <f t="shared" si="208"/>
+        <f t="shared" si="207"/>
         <v>2448.4007220216608</v>
       </c>
       <c r="AC16" s="2">
@@ -3996,35 +4001,35 @@
         <v>2448.4007220216608</v>
       </c>
       <c r="AD16" s="2">
-        <f t="shared" ref="AD16:AK16" si="212">+AC16</f>
+        <f t="shared" ref="AD16:AK16" si="211">+AC16</f>
         <v>2448.4007220216608</v>
       </c>
       <c r="AE16" s="2">
-        <f t="shared" si="212"/>
+        <f t="shared" si="211"/>
         <v>2448.4007220216608</v>
       </c>
       <c r="AF16" s="2">
-        <f t="shared" si="212"/>
+        <f t="shared" si="211"/>
         <v>2448.4007220216608</v>
       </c>
       <c r="AG16" s="2">
-        <f t="shared" si="212"/>
+        <f t="shared" si="211"/>
         <v>2448.4007220216608</v>
       </c>
       <c r="AH16" s="2">
-        <f t="shared" si="212"/>
+        <f t="shared" si="211"/>
         <v>2448.4007220216608</v>
       </c>
       <c r="AI16" s="2">
-        <f t="shared" si="212"/>
+        <f t="shared" si="211"/>
         <v>2448.4007220216608</v>
       </c>
       <c r="AJ16" s="2">
-        <f t="shared" si="212"/>
+        <f t="shared" si="211"/>
         <v>2448.4007220216608</v>
       </c>
       <c r="AK16" s="2">
-        <f t="shared" si="212"/>
+        <f t="shared" si="211"/>
         <v>2448.4007220216608</v>
       </c>
     </row>
@@ -4042,7 +4047,7 @@
         <v>-63</v>
       </c>
       <c r="F17" s="24">
-        <f t="shared" si="205"/>
+        <f t="shared" si="204"/>
         <v>-63</v>
       </c>
       <c r="G17" s="25">
@@ -4093,7 +4098,7 @@
         <v>-247</v>
       </c>
       <c r="AB17" s="2">
-        <f t="shared" si="208"/>
+        <f t="shared" si="207"/>
         <v>-132.13051930019441</v>
       </c>
       <c r="AC17" s="2">
@@ -4101,35 +4106,35 @@
         <v>-132.13051930019441</v>
       </c>
       <c r="AD17" s="2">
-        <f t="shared" ref="AD17:AK17" si="213">+AC17</f>
+        <f t="shared" ref="AD17:AK17" si="212">+AC17</f>
         <v>-132.13051930019441</v>
       </c>
       <c r="AE17" s="2">
-        <f t="shared" si="213"/>
+        <f t="shared" si="212"/>
         <v>-132.13051930019441</v>
       </c>
       <c r="AF17" s="2">
-        <f t="shared" si="213"/>
+        <f t="shared" si="212"/>
         <v>-132.13051930019441</v>
       </c>
       <c r="AG17" s="2">
-        <f t="shared" si="213"/>
+        <f t="shared" si="212"/>
         <v>-132.13051930019441</v>
       </c>
       <c r="AH17" s="2">
-        <f t="shared" si="213"/>
+        <f t="shared" si="212"/>
         <v>-132.13051930019441</v>
       </c>
       <c r="AI17" s="2">
-        <f t="shared" si="213"/>
+        <f t="shared" si="212"/>
         <v>-132.13051930019441</v>
       </c>
       <c r="AJ17" s="2">
-        <f t="shared" si="213"/>
+        <f t="shared" si="212"/>
         <v>-132.13051930019441</v>
       </c>
       <c r="AK17" s="2">
-        <f t="shared" si="213"/>
+        <f t="shared" si="212"/>
         <v>-132.13051930019441</v>
       </c>
     </row>
@@ -4147,7 +4152,7 @@
         <v>-66</v>
       </c>
       <c r="F18" s="24">
-        <f t="shared" si="205"/>
+        <f t="shared" si="204"/>
         <v>259</v>
       </c>
       <c r="G18" s="25">
@@ -4197,7 +4202,7 @@
         <v>1034</v>
       </c>
       <c r="AB18" s="2">
-        <f t="shared" si="208"/>
+        <f t="shared" si="207"/>
         <v>3919</v>
       </c>
       <c r="AC18" s="2">
@@ -4205,35 +4210,35 @@
         <v>3919</v>
       </c>
       <c r="AD18" s="2">
-        <f t="shared" ref="AD18:AK18" si="214">+AC18</f>
+        <f t="shared" ref="AD18:AK18" si="213">+AC18</f>
         <v>3919</v>
       </c>
       <c r="AE18" s="2">
-        <f t="shared" si="214"/>
+        <f t="shared" si="213"/>
         <v>3919</v>
       </c>
       <c r="AF18" s="2">
-        <f t="shared" si="214"/>
+        <f t="shared" si="213"/>
         <v>3919</v>
       </c>
       <c r="AG18" s="2">
-        <f t="shared" si="214"/>
+        <f t="shared" si="213"/>
         <v>3919</v>
       </c>
       <c r="AH18" s="2">
-        <f t="shared" si="214"/>
+        <f t="shared" si="213"/>
         <v>3919</v>
       </c>
       <c r="AI18" s="2">
-        <f t="shared" si="214"/>
+        <f t="shared" si="213"/>
         <v>3919</v>
       </c>
       <c r="AJ18" s="2">
-        <f t="shared" si="214"/>
+        <f t="shared" si="213"/>
         <v>3919</v>
       </c>
       <c r="AK18" s="2">
-        <f t="shared" si="214"/>
+        <f t="shared" si="213"/>
         <v>3919</v>
       </c>
     </row>
@@ -4242,31 +4247,31 @@
         <v>32</v>
       </c>
       <c r="C19" s="25">
-        <f t="shared" ref="C19:I19" si="215">+SUM(C15:C18)</f>
+        <f t="shared" ref="C19:I19" si="214">+SUM(C15:C18)</f>
         <v>2209</v>
       </c>
       <c r="D19" s="25">
-        <f t="shared" si="215"/>
+        <f t="shared" si="214"/>
         <v>6981</v>
       </c>
       <c r="E19" s="25">
-        <f t="shared" si="215"/>
+        <f t="shared" si="214"/>
         <v>10522</v>
       </c>
       <c r="F19" s="25">
-        <f t="shared" si="215"/>
+        <f t="shared" si="214"/>
         <v>14106</v>
       </c>
       <c r="G19" s="25">
-        <f t="shared" si="215"/>
+        <f t="shared" si="214"/>
         <v>17181</v>
       </c>
       <c r="H19" s="25">
-        <f t="shared" si="215"/>
+        <f t="shared" si="214"/>
         <v>19214</v>
       </c>
       <c r="I19" s="25">
-        <f t="shared" si="215"/>
+        <f t="shared" si="214"/>
         <v>22316</v>
       </c>
       <c r="J19" s="25">
@@ -4290,72 +4295,72 @@
         <v>42547.270202721462</v>
       </c>
       <c r="U19" s="2">
-        <f t="shared" ref="U19:AC19" si="216">+SUM(U15:U18)</f>
+        <f t="shared" ref="U19:AC19" si="215">+SUM(U15:U18)</f>
         <v>3896</v>
       </c>
       <c r="V19" s="2">
+        <f t="shared" si="215"/>
+        <v>2970</v>
+      </c>
+      <c r="W19" s="2">
+        <f t="shared" si="215"/>
+        <v>4409</v>
+      </c>
+      <c r="X19" s="2">
+        <f t="shared" si="215"/>
+        <v>9941</v>
+      </c>
+      <c r="Y19" s="2">
+        <f t="shared" si="215"/>
+        <v>5534</v>
+      </c>
+      <c r="Z19" s="2">
+        <f t="shared" si="215"/>
+        <v>33818</v>
+      </c>
+      <c r="AA19" s="2">
+        <f t="shared" si="215"/>
+        <v>84026</v>
+      </c>
+      <c r="AB19" s="2">
+        <f t="shared" si="207"/>
+        <v>133723.27020272147</v>
+      </c>
+      <c r="AC19" s="2">
+        <f t="shared" si="215"/>
+        <v>171969.67020272146</v>
+      </c>
+      <c r="AD19" s="2">
+        <f t="shared" ref="AD19:AK19" si="216">+SUM(AD15:AD18)</f>
+        <v>213403.27020272147</v>
+      </c>
+      <c r="AE19" s="2">
         <f t="shared" si="216"/>
-        <v>2970</v>
-      </c>
-      <c r="W19" s="2">
+        <v>254836.87020272147</v>
+      </c>
+      <c r="AF19" s="2">
         <f t="shared" si="216"/>
-        <v>4409</v>
-      </c>
-      <c r="X19" s="2">
+        <v>304557.19020272145</v>
+      </c>
+      <c r="AG19" s="2">
         <f t="shared" si="216"/>
-        <v>9941</v>
-      </c>
-      <c r="Y19" s="2">
+        <v>334389.38220272155</v>
+      </c>
+      <c r="AH19" s="2">
         <f t="shared" si="216"/>
-        <v>5534</v>
-      </c>
-      <c r="Z19" s="2">
+        <v>367204.79340272158</v>
+      </c>
+      <c r="AI19" s="2">
         <f t="shared" si="216"/>
-        <v>33818</v>
-      </c>
-      <c r="AA19" s="2">
+        <v>403301.74572272162</v>
+      </c>
+      <c r="AJ19" s="2">
         <f t="shared" si="216"/>
-        <v>84026</v>
-      </c>
-      <c r="AB19" s="2">
-        <f t="shared" si="208"/>
-        <v>133723.27020272147</v>
-      </c>
-      <c r="AC19" s="2">
+        <v>443008.39327472169</v>
+      </c>
+      <c r="AK19" s="2">
         <f t="shared" si="216"/>
-        <v>184718.47020272145</v>
-      </c>
-      <c r="AD19" s="2">
-        <f t="shared" ref="AD19:AK19" si="217">+SUM(AD15:AD18)</f>
-        <v>256111.75020272145</v>
-      </c>
-      <c r="AE19" s="2">
-        <f t="shared" si="217"/>
-        <v>306087.04620272142</v>
-      </c>
-      <c r="AF19" s="2">
-        <f t="shared" si="217"/>
-        <v>366057.40140272141</v>
-      </c>
-      <c r="AG19" s="2">
-        <f t="shared" si="217"/>
-        <v>402039.61452272144</v>
-      </c>
-      <c r="AH19" s="2">
-        <f t="shared" si="217"/>
-        <v>441620.04895472154</v>
-      </c>
-      <c r="AI19" s="2">
-        <f t="shared" si="217"/>
-        <v>485158.52682992158</v>
-      </c>
-      <c r="AJ19" s="2">
-        <f t="shared" si="217"/>
-        <v>533050.85249264166</v>
-      </c>
-      <c r="AK19" s="2">
-        <f t="shared" si="217"/>
-        <v>585732.41072163382</v>
+        <v>486685.70558192173</v>
       </c>
     </row>
     <row r="20" spans="2:238" x14ac:dyDescent="0.2">
@@ -4423,44 +4428,44 @@
         <v>1146</v>
       </c>
       <c r="AB20" s="2">
-        <f t="shared" si="208"/>
+        <f t="shared" si="207"/>
         <v>20703.484032096148</v>
       </c>
       <c r="AC20" s="2">
         <f>+AC19*(AB20/AB19)</f>
-        <v>28598.731488376667</v>
+        <v>26624.919624306538</v>
       </c>
       <c r="AD20" s="2">
-        <f t="shared" ref="AD20:AK20" si="218">+AD19*(AC20/AC19)</f>
-        <v>39652.077927169397</v>
+        <f t="shared" ref="AD20:AK20" si="217">+AD19*(AC20/AC19)</f>
+        <v>33039.808182534463</v>
       </c>
       <c r="AE20" s="2">
-        <f t="shared" si="218"/>
-        <v>47389.420434324304</v>
+        <f t="shared" si="217"/>
+        <v>39454.696740762389</v>
       </c>
       <c r="AF20" s="2">
-        <f t="shared" si="218"/>
-        <v>56674.23144291019</v>
+        <f t="shared" si="217"/>
+        <v>47152.563010635888</v>
       </c>
       <c r="AG20" s="2">
-        <f t="shared" si="218"/>
-        <v>62245.118048061733</v>
+        <f t="shared" si="217"/>
+        <v>51771.282772560007</v>
       </c>
       <c r="AH20" s="2">
-        <f t="shared" si="218"/>
-        <v>68373.09331372843</v>
+        <f t="shared" si="217"/>
+        <v>56851.874510676527</v>
       </c>
       <c r="AI20" s="2">
-        <f t="shared" si="218"/>
-        <v>75113.866105961788</v>
+        <f t="shared" si="217"/>
+        <v>62440.525422604704</v>
       </c>
       <c r="AJ20" s="2">
-        <f t="shared" si="218"/>
-        <v>82528.716177418493</v>
+        <f t="shared" si="217"/>
+        <v>68588.041425725693</v>
       </c>
       <c r="AK20" s="2">
-        <f t="shared" si="218"/>
-        <v>90685.051256020874</v>
+        <f t="shared" si="217"/>
+        <v>75350.309029158787</v>
       </c>
     </row>
     <row r="21" spans="2:238" x14ac:dyDescent="0.2">
@@ -4468,31 +4473,31 @@
         <v>34</v>
       </c>
       <c r="C21" s="25">
-        <f t="shared" ref="C21:I21" si="219">+C19-C20</f>
+        <f t="shared" ref="C21:I21" si="218">+C19-C20</f>
         <v>2043</v>
       </c>
       <c r="D21" s="25">
-        <f t="shared" si="219"/>
+        <f t="shared" si="218"/>
         <v>6188</v>
       </c>
       <c r="E21" s="25">
-        <f t="shared" si="219"/>
+        <f t="shared" si="218"/>
         <v>9243</v>
       </c>
       <c r="F21" s="25">
-        <f t="shared" si="219"/>
+        <f t="shared" si="218"/>
         <v>12286</v>
       </c>
       <c r="G21" s="25">
-        <f t="shared" si="219"/>
+        <f t="shared" si="218"/>
         <v>14046</v>
       </c>
       <c r="H21" s="25">
-        <f t="shared" si="219"/>
+        <f t="shared" si="218"/>
         <v>16599</v>
       </c>
       <c r="I21" s="25">
-        <f t="shared" si="219"/>
+        <f t="shared" si="218"/>
         <v>19309</v>
       </c>
       <c r="J21" s="25">
@@ -4516,876 +4521,876 @@
         <v>35788.78617062531</v>
       </c>
       <c r="U21" s="2">
-        <f t="shared" ref="U21:AC21" si="220">+U19-U20</f>
+        <f t="shared" ref="U21:AC21" si="219">+U19-U20</f>
         <v>4141</v>
       </c>
       <c r="V21" s="2">
+        <f t="shared" si="219"/>
+        <v>2796</v>
+      </c>
+      <c r="W21" s="2">
+        <f t="shared" si="219"/>
+        <v>4332</v>
+      </c>
+      <c r="X21" s="2">
+        <f t="shared" si="219"/>
+        <v>9752</v>
+      </c>
+      <c r="Y21" s="2">
+        <f t="shared" si="219"/>
+        <v>5721</v>
+      </c>
+      <c r="Z21" s="2">
+        <f t="shared" si="219"/>
+        <v>29760</v>
+      </c>
+      <c r="AA21" s="2">
+        <f t="shared" si="219"/>
+        <v>82880</v>
+      </c>
+      <c r="AB21" s="2">
+        <f t="shared" si="207"/>
+        <v>113019.7861706253</v>
+      </c>
+      <c r="AC21" s="2">
+        <f t="shared" si="219"/>
+        <v>145344.75057841494</v>
+      </c>
+      <c r="AD21" s="2">
+        <f t="shared" ref="AD21:AK21" si="220">+AD19-AD20</f>
+        <v>180363.462020187</v>
+      </c>
+      <c r="AE21" s="2">
         <f t="shared" si="220"/>
-        <v>2796</v>
-      </c>
-      <c r="W21" s="2">
+        <v>215382.17346195909</v>
+      </c>
+      <c r="AF21" s="2">
         <f t="shared" si="220"/>
-        <v>4332</v>
-      </c>
-      <c r="X21" s="2">
+        <v>257404.62719208555</v>
+      </c>
+      <c r="AG21" s="2">
         <f t="shared" si="220"/>
-        <v>9752</v>
-      </c>
-      <c r="Y21" s="2">
+        <v>282618.09943016153</v>
+      </c>
+      <c r="AH21" s="2">
         <f t="shared" si="220"/>
-        <v>5721</v>
-      </c>
-      <c r="Z21" s="2">
+        <v>310352.91889204504</v>
+      </c>
+      <c r="AI21" s="2">
         <f t="shared" si="220"/>
-        <v>29760</v>
-      </c>
-      <c r="AA21" s="2">
+        <v>340861.22030011693</v>
+      </c>
+      <c r="AJ21" s="2">
         <f t="shared" si="220"/>
-        <v>82880</v>
-      </c>
-      <c r="AB21" s="2">
-        <f t="shared" si="208"/>
-        <v>113019.7861706253</v>
-      </c>
-      <c r="AC21" s="2">
+        <v>374420.35184899601</v>
+      </c>
+      <c r="AK21" s="2">
         <f t="shared" si="220"/>
-        <v>156119.7387143448</v>
-      </c>
-      <c r="AD21" s="2">
-        <f t="shared" ref="AD21:AK21" si="221">+AD19-AD20</f>
-        <v>216459.67227555206</v>
-      </c>
-      <c r="AE21" s="2">
-        <f t="shared" si="221"/>
-        <v>258697.62576839712</v>
-      </c>
-      <c r="AF21" s="2">
-        <f t="shared" si="221"/>
-        <v>309383.1699598112</v>
-      </c>
-      <c r="AG21" s="2">
-        <f t="shared" si="221"/>
-        <v>339794.49647465971</v>
-      </c>
-      <c r="AH21" s="2">
-        <f t="shared" si="221"/>
-        <v>373246.95564099308</v>
-      </c>
-      <c r="AI21" s="2">
-        <f t="shared" si="221"/>
-        <v>410044.66072395979</v>
-      </c>
-      <c r="AJ21" s="2">
-        <f t="shared" si="221"/>
-        <v>450522.13631522318</v>
-      </c>
-      <c r="AK21" s="2">
-        <f t="shared" si="221"/>
-        <v>495047.35946561291</v>
+        <v>411335.39655276295</v>
       </c>
       <c r="AL21" s="2">
         <f>+AK21*(1+$AM$26)</f>
-        <v>499997.83306026907</v>
+        <v>415448.75051829056</v>
       </c>
       <c r="AM21" s="2">
-        <f t="shared" ref="AM21:CX21" si="222">+AL21*(1+$AM$26)</f>
-        <v>504997.81139087176</v>
+        <f t="shared" ref="AM21:CX21" si="221">+AL21*(1+$AM$26)</f>
+        <v>419603.23802347347</v>
       </c>
       <c r="AN21" s="2">
+        <f t="shared" si="221"/>
+        <v>423799.27040370821</v>
+      </c>
+      <c r="AO21" s="2">
+        <f t="shared" si="221"/>
+        <v>428037.26310774533</v>
+      </c>
+      <c r="AP21" s="2">
+        <f t="shared" si="221"/>
+        <v>432317.63573882281</v>
+      </c>
+      <c r="AQ21" s="2">
+        <f t="shared" si="221"/>
+        <v>436640.81209621101</v>
+      </c>
+      <c r="AR21" s="2">
+        <f t="shared" si="221"/>
+        <v>441007.2202171731</v>
+      </c>
+      <c r="AS21" s="2">
+        <f t="shared" si="221"/>
+        <v>445417.29241934483</v>
+      </c>
+      <c r="AT21" s="2">
+        <f t="shared" si="221"/>
+        <v>449871.46534353826</v>
+      </c>
+      <c r="AU21" s="2">
+        <f t="shared" si="221"/>
+        <v>454370.17999697366</v>
+      </c>
+      <c r="AV21" s="2">
+        <f t="shared" si="221"/>
+        <v>458913.88179694337</v>
+      </c>
+      <c r="AW21" s="2">
+        <f t="shared" si="221"/>
+        <v>463503.02061491279</v>
+      </c>
+      <c r="AX21" s="2">
+        <f t="shared" si="221"/>
+        <v>468138.05082106194</v>
+      </c>
+      <c r="AY21" s="2">
+        <f t="shared" si="221"/>
+        <v>472819.43132927257</v>
+      </c>
+      <c r="AZ21" s="2">
+        <f t="shared" si="221"/>
+        <v>477547.62564256531</v>
+      </c>
+      <c r="BA21" s="2">
+        <f t="shared" si="221"/>
+        <v>482323.10189899098</v>
+      </c>
+      <c r="BB21" s="2">
+        <f t="shared" si="221"/>
+        <v>487146.33291798091</v>
+      </c>
+      <c r="BC21" s="2">
+        <f t="shared" si="221"/>
+        <v>492017.7962471607</v>
+      </c>
+      <c r="BD21" s="2">
+        <f t="shared" si="221"/>
+        <v>496937.97420963232</v>
+      </c>
+      <c r="BE21" s="2">
+        <f t="shared" si="221"/>
+        <v>501907.35395172867</v>
+      </c>
+      <c r="BF21" s="2">
+        <f t="shared" si="221"/>
+        <v>506926.42749124597</v>
+      </c>
+      <c r="BG21" s="2">
+        <f t="shared" si="221"/>
+        <v>511995.69176615844</v>
+      </c>
+      <c r="BH21" s="2">
+        <f t="shared" si="221"/>
+        <v>517115.64868382004</v>
+      </c>
+      <c r="BI21" s="2">
+        <f t="shared" si="221"/>
+        <v>522286.80517065822</v>
+      </c>
+      <c r="BJ21" s="2">
+        <f t="shared" si="221"/>
+        <v>527509.67322236486</v>
+      </c>
+      <c r="BK21" s="2">
+        <f t="shared" si="221"/>
+        <v>532784.7699545885</v>
+      </c>
+      <c r="BL21" s="2">
+        <f t="shared" si="221"/>
+        <v>538112.6176541344</v>
+      </c>
+      <c r="BM21" s="2">
+        <f t="shared" si="221"/>
+        <v>543493.74383067572</v>
+      </c>
+      <c r="BN21" s="2">
+        <f t="shared" si="221"/>
+        <v>548928.68126898247</v>
+      </c>
+      <c r="BO21" s="2">
+        <f t="shared" si="221"/>
+        <v>554417.96808167233</v>
+      </c>
+      <c r="BP21" s="2">
+        <f t="shared" si="221"/>
+        <v>559962.14776248904</v>
+      </c>
+      <c r="BQ21" s="2">
+        <f t="shared" si="221"/>
+        <v>565561.76924011391</v>
+      </c>
+      <c r="BR21" s="2">
+        <f t="shared" si="221"/>
+        <v>571217.38693251507</v>
+      </c>
+      <c r="BS21" s="2">
+        <f t="shared" si="221"/>
+        <v>576929.56080184027</v>
+      </c>
+      <c r="BT21" s="2">
+        <f t="shared" si="221"/>
+        <v>582698.85640985868</v>
+      </c>
+      <c r="BU21" s="2">
+        <f t="shared" si="221"/>
+        <v>588525.84497395728</v>
+      </c>
+      <c r="BV21" s="2">
+        <f t="shared" si="221"/>
+        <v>594411.10342369683</v>
+      </c>
+      <c r="BW21" s="2">
+        <f t="shared" si="221"/>
+        <v>600355.21445793379</v>
+      </c>
+      <c r="BX21" s="2">
+        <f t="shared" si="221"/>
+        <v>606358.76660251315</v>
+      </c>
+      <c r="BY21" s="2">
+        <f t="shared" si="221"/>
+        <v>612422.3542685383</v>
+      </c>
+      <c r="BZ21" s="2">
+        <f t="shared" si="221"/>
+        <v>618546.57781122369</v>
+      </c>
+      <c r="CA21" s="2">
+        <f t="shared" si="221"/>
+        <v>624732.04358933598</v>
+      </c>
+      <c r="CB21" s="2">
+        <f t="shared" si="221"/>
+        <v>630979.36402522936</v>
+      </c>
+      <c r="CC21" s="2">
+        <f t="shared" si="221"/>
+        <v>637289.15766548167</v>
+      </c>
+      <c r="CD21" s="2">
+        <f t="shared" si="221"/>
+        <v>643662.04924213653</v>
+      </c>
+      <c r="CE21" s="2">
+        <f t="shared" si="221"/>
+        <v>650098.66973455786</v>
+      </c>
+      <c r="CF21" s="2">
+        <f t="shared" si="221"/>
+        <v>656599.65643190348</v>
+      </c>
+      <c r="CG21" s="2">
+        <f t="shared" si="221"/>
+        <v>663165.65299622249</v>
+      </c>
+      <c r="CH21" s="2">
+        <f t="shared" si="221"/>
+        <v>669797.30952618469</v>
+      </c>
+      <c r="CI21" s="2">
+        <f t="shared" si="221"/>
+        <v>676495.28262144653</v>
+      </c>
+      <c r="CJ21" s="2">
+        <f t="shared" si="221"/>
+        <v>683260.23544766102</v>
+      </c>
+      <c r="CK21" s="2">
+        <f t="shared" si="221"/>
+        <v>690092.8378021376</v>
+      </c>
+      <c r="CL21" s="2">
+        <f t="shared" si="221"/>
+        <v>696993.76618015894</v>
+      </c>
+      <c r="CM21" s="2">
+        <f t="shared" si="221"/>
+        <v>703963.70384196052</v>
+      </c>
+      <c r="CN21" s="2">
+        <f t="shared" si="221"/>
+        <v>711003.34088038013</v>
+      </c>
+      <c r="CO21" s="2">
+        <f t="shared" si="221"/>
+        <v>718113.37428918399</v>
+      </c>
+      <c r="CP21" s="2">
+        <f t="shared" si="221"/>
+        <v>725294.50803207583</v>
+      </c>
+      <c r="CQ21" s="2">
+        <f t="shared" si="221"/>
+        <v>732547.45311239664</v>
+      </c>
+      <c r="CR21" s="2">
+        <f t="shared" si="221"/>
+        <v>739872.92764352064</v>
+      </c>
+      <c r="CS21" s="2">
+        <f t="shared" si="221"/>
+        <v>747271.65691995586</v>
+      </c>
+      <c r="CT21" s="2">
+        <f t="shared" si="221"/>
+        <v>754744.37348915543</v>
+      </c>
+      <c r="CU21" s="2">
+        <f t="shared" si="221"/>
+        <v>762291.81722404703</v>
+      </c>
+      <c r="CV21" s="2">
+        <f t="shared" si="221"/>
+        <v>769914.73539628752</v>
+      </c>
+      <c r="CW21" s="2">
+        <f t="shared" si="221"/>
+        <v>777613.8827502504</v>
+      </c>
+      <c r="CX21" s="2">
+        <f t="shared" si="221"/>
+        <v>785390.02157775289</v>
+      </c>
+      <c r="CY21" s="2">
+        <f t="shared" ref="CY21:FJ21" si="222">+CX21*(1+$AM$26)</f>
+        <v>793243.92179353046</v>
+      </c>
+      <c r="CZ21" s="2">
         <f t="shared" si="222"/>
-        <v>510047.78950478049</v>
-      </c>
-      <c r="AO21" s="2">
+        <v>801176.36101146578</v>
+      </c>
+      <c r="DA21" s="2">
         <f t="shared" si="222"/>
-        <v>515148.2673998283</v>
-      </c>
-      <c r="AP21" s="2">
+        <v>809188.12462158047</v>
+      </c>
+      <c r="DB21" s="2">
         <f t="shared" si="222"/>
-        <v>520299.75007382658</v>
-      </c>
-      <c r="AQ21" s="2">
+        <v>817280.00586779625</v>
+      </c>
+      <c r="DC21" s="2">
         <f t="shared" si="222"/>
-        <v>525502.74757456488</v>
-      </c>
-      <c r="AR21" s="2">
+        <v>825452.80592647428</v>
+      </c>
+      <c r="DD21" s="2">
         <f t="shared" si="222"/>
-        <v>530757.77505031053</v>
-      </c>
-      <c r="AS21" s="2">
+        <v>833707.33398573904</v>
+      </c>
+      <c r="DE21" s="2">
         <f t="shared" si="222"/>
-        <v>536065.35280081362</v>
-      </c>
-      <c r="AT21" s="2">
+        <v>842044.40732559643</v>
+      </c>
+      <c r="DF21" s="2">
         <f t="shared" si="222"/>
-        <v>541426.00632882176</v>
-      </c>
-      <c r="AU21" s="2">
+        <v>850464.85139885242</v>
+      </c>
+      <c r="DG21" s="2">
         <f t="shared" si="222"/>
-        <v>546840.26639211003</v>
-      </c>
-      <c r="AV21" s="2">
+        <v>858969.4999128409</v>
+      </c>
+      <c r="DH21" s="2">
         <f t="shared" si="222"/>
-        <v>552308.66905603115</v>
-      </c>
-      <c r="AW21" s="2">
+        <v>867559.19491196936</v>
+      </c>
+      <c r="DI21" s="2">
         <f t="shared" si="222"/>
-        <v>557831.75574659149</v>
-      </c>
-      <c r="AX21" s="2">
+        <v>876234.78686108906</v>
+      </c>
+      <c r="DJ21" s="2">
         <f t="shared" si="222"/>
-        <v>563410.07330405735</v>
-      </c>
-      <c r="AY21" s="2">
+        <v>884997.13472969993</v>
+      </c>
+      <c r="DK21" s="2">
         <f t="shared" si="222"/>
-        <v>569044.17403709795</v>
-      </c>
-      <c r="AZ21" s="2">
+        <v>893847.10607699689</v>
+      </c>
+      <c r="DL21" s="2">
         <f t="shared" si="222"/>
-        <v>574734.61577746889</v>
-      </c>
-      <c r="BA21" s="2">
+        <v>902785.57713776687</v>
+      </c>
+      <c r="DM21" s="2">
         <f t="shared" si="222"/>
-        <v>580481.96193524357</v>
-      </c>
-      <c r="BB21" s="2">
+        <v>911813.43290914455</v>
+      </c>
+      <c r="DN21" s="2">
         <f t="shared" si="222"/>
-        <v>586286.78155459603</v>
-      </c>
-      <c r="BC21" s="2">
+        <v>920931.56723823596</v>
+      </c>
+      <c r="DO21" s="2">
         <f t="shared" si="222"/>
-        <v>592149.64937014203</v>
-      </c>
-      <c r="BD21" s="2">
+        <v>930140.88291061833</v>
+      </c>
+      <c r="DP21" s="2">
         <f t="shared" si="222"/>
-        <v>598071.1458638435</v>
-      </c>
-      <c r="BE21" s="2">
+        <v>939442.29173972446</v>
+      </c>
+      <c r="DQ21" s="2">
         <f t="shared" si="222"/>
-        <v>604051.85732248193</v>
-      </c>
-      <c r="BF21" s="2">
+        <v>948836.71465712169</v>
+      </c>
+      <c r="DR21" s="2">
         <f t="shared" si="222"/>
-        <v>610092.3758957067</v>
-      </c>
-      <c r="BG21" s="2">
+        <v>958325.08180369297</v>
+      </c>
+      <c r="DS21" s="2">
         <f t="shared" si="222"/>
-        <v>616193.29965466377</v>
-      </c>
-      <c r="BH21" s="2">
+        <v>967908.33262172993</v>
+      </c>
+      <c r="DT21" s="2">
         <f t="shared" si="222"/>
-        <v>622355.23265121039</v>
-      </c>
-      <c r="BI21" s="2">
+        <v>977587.41594794719</v>
+      </c>
+      <c r="DU21" s="2">
         <f t="shared" si="222"/>
-        <v>628578.78497772245</v>
-      </c>
-      <c r="BJ21" s="2">
+        <v>987363.2901074267</v>
+      </c>
+      <c r="DV21" s="2">
         <f t="shared" si="222"/>
-        <v>634864.57282749971</v>
-      </c>
-      <c r="BK21" s="2">
+        <v>997236.92300850095</v>
+      </c>
+      <c r="DW21" s="2">
         <f t="shared" si="222"/>
-        <v>641213.21855577466</v>
-      </c>
-      <c r="BL21" s="2">
+        <v>1007209.292238586</v>
+      </c>
+      <c r="DX21" s="2">
         <f t="shared" si="222"/>
-        <v>647625.3507413324</v>
-      </c>
-      <c r="BM21" s="2">
+        <v>1017281.3851609719</v>
+      </c>
+      <c r="DY21" s="2">
         <f t="shared" si="222"/>
-        <v>654101.60424874572</v>
-      </c>
-      <c r="BN21" s="2">
+        <v>1027454.1990125816</v>
+      </c>
+      <c r="DZ21" s="2">
         <f t="shared" si="222"/>
-        <v>660642.62029123318</v>
-      </c>
-      <c r="BO21" s="2">
+        <v>1037728.7410027074</v>
+      </c>
+      <c r="EA21" s="2">
         <f t="shared" si="222"/>
-        <v>667249.04649414553</v>
-      </c>
-      <c r="BP21" s="2">
+        <v>1048106.0284127345</v>
+      </c>
+      <c r="EB21" s="2">
         <f t="shared" si="222"/>
-        <v>673921.53695908701</v>
-      </c>
-      <c r="BQ21" s="2">
+        <v>1058587.0886968619</v>
+      </c>
+      <c r="EC21" s="2">
         <f t="shared" si="222"/>
-        <v>680660.75232867792</v>
-      </c>
-      <c r="BR21" s="2">
+        <v>1069172.9595838306</v>
+      </c>
+      <c r="ED21" s="2">
         <f t="shared" si="222"/>
-        <v>687467.35985196475</v>
-      </c>
-      <c r="BS21" s="2">
+        <v>1079864.6891796689</v>
+      </c>
+      <c r="EE21" s="2">
         <f t="shared" si="222"/>
-        <v>694342.03345048439</v>
-      </c>
-      <c r="BT21" s="2">
+        <v>1090663.3360714656</v>
+      </c>
+      <c r="EF21" s="2">
         <f t="shared" si="222"/>
-        <v>701285.45378498919</v>
-      </c>
-      <c r="BU21" s="2">
+        <v>1101569.9694321803</v>
+      </c>
+      <c r="EG21" s="2">
         <f t="shared" si="222"/>
-        <v>708298.30832283909</v>
-      </c>
-      <c r="BV21" s="2">
+        <v>1112585.669126502</v>
+      </c>
+      <c r="EH21" s="2">
         <f t="shared" si="222"/>
-        <v>715381.29140606744</v>
-      </c>
-      <c r="BW21" s="2">
+        <v>1123711.525817767</v>
+      </c>
+      <c r="EI21" s="2">
         <f t="shared" si="222"/>
-        <v>722535.1043201281</v>
-      </c>
-      <c r="BX21" s="2">
+        <v>1134948.6410759448</v>
+      </c>
+      <c r="EJ21" s="2">
         <f t="shared" si="222"/>
-        <v>729760.45536332938</v>
-      </c>
-      <c r="BY21" s="2">
+        <v>1146298.1274867042</v>
+      </c>
+      <c r="EK21" s="2">
         <f t="shared" si="222"/>
-        <v>737058.05991696264</v>
-      </c>
-      <c r="BZ21" s="2">
+        <v>1157761.1087615711</v>
+      </c>
+      <c r="EL21" s="2">
         <f t="shared" si="222"/>
-        <v>744428.64051613223</v>
-      </c>
-      <c r="CA21" s="2">
+        <v>1169338.7198491869</v>
+      </c>
+      <c r="EM21" s="2">
         <f t="shared" si="222"/>
-        <v>751872.92692129361</v>
-      </c>
-      <c r="CB21" s="2">
+        <v>1181032.1070476789</v>
+      </c>
+      <c r="EN21" s="2">
         <f t="shared" si="222"/>
-        <v>759391.65619050653</v>
-      </c>
-      <c r="CC21" s="2">
+        <v>1192842.4281181558</v>
+      </c>
+      <c r="EO21" s="2">
         <f t="shared" si="222"/>
-        <v>766985.57275241159</v>
-      </c>
-      <c r="CD21" s="2">
+        <v>1204770.8523993373</v>
+      </c>
+      <c r="EP21" s="2">
         <f t="shared" si="222"/>
-        <v>774655.42847993574</v>
-      </c>
-      <c r="CE21" s="2">
+        <v>1216818.5609233307</v>
+      </c>
+      <c r="EQ21" s="2">
         <f t="shared" si="222"/>
-        <v>782401.98276473512</v>
-      </c>
-      <c r="CF21" s="2">
+        <v>1228986.7465325641</v>
+      </c>
+      <c r="ER21" s="2">
         <f t="shared" si="222"/>
-        <v>790226.00259238249</v>
-      </c>
-      <c r="CG21" s="2">
+        <v>1241276.6139978897</v>
+      </c>
+      <c r="ES21" s="2">
         <f t="shared" si="222"/>
-        <v>798128.26261830633</v>
-      </c>
-      <c r="CH21" s="2">
+        <v>1253689.3801378687</v>
+      </c>
+      <c r="ET21" s="2">
         <f t="shared" si="222"/>
-        <v>806109.54524448945</v>
-      </c>
-      <c r="CI21" s="2">
+        <v>1266226.2739392475</v>
+      </c>
+      <c r="EU21" s="2">
         <f t="shared" si="222"/>
-        <v>814170.64069693431</v>
-      </c>
-      <c r="CJ21" s="2">
+        <v>1278888.5366786399</v>
+      </c>
+      <c r="EV21" s="2">
         <f t="shared" si="222"/>
-        <v>822312.34710390365</v>
-      </c>
-      <c r="CK21" s="2">
+        <v>1291677.4220454264</v>
+      </c>
+      <c r="EW21" s="2">
         <f t="shared" si="222"/>
-        <v>830535.47057494265</v>
-      </c>
-      <c r="CL21" s="2">
+        <v>1304594.1962658807</v>
+      </c>
+      <c r="EX21" s="2">
         <f t="shared" si="222"/>
-        <v>838840.82528069208</v>
-      </c>
-      <c r="CM21" s="2">
+        <v>1317640.1382285396</v>
+      </c>
+      <c r="EY21" s="2">
         <f t="shared" si="222"/>
-        <v>847229.23353349906</v>
-      </c>
-      <c r="CN21" s="2">
+        <v>1330816.539610825</v>
+      </c>
+      <c r="EZ21" s="2">
         <f t="shared" si="222"/>
-        <v>855701.52586883411</v>
-      </c>
-      <c r="CO21" s="2">
+        <v>1344124.7050069333</v>
+      </c>
+      <c r="FA21" s="2">
         <f t="shared" si="222"/>
-        <v>864258.54112752248</v>
-      </c>
-      <c r="CP21" s="2">
+        <v>1357565.9520570026</v>
+      </c>
+      <c r="FB21" s="2">
         <f t="shared" si="222"/>
-        <v>872901.12653879775</v>
-      </c>
-      <c r="CQ21" s="2">
+        <v>1371141.6115775725</v>
+      </c>
+      <c r="FC21" s="2">
         <f t="shared" si="222"/>
-        <v>881630.13780418574</v>
-      </c>
-      <c r="CR21" s="2">
+        <v>1384853.0276933482</v>
+      </c>
+      <c r="FD21" s="2">
         <f t="shared" si="222"/>
-        <v>890446.43918222759</v>
-      </c>
-      <c r="CS21" s="2">
+        <v>1398701.5579702817</v>
+      </c>
+      <c r="FE21" s="2">
         <f t="shared" si="222"/>
-        <v>899350.90357404982</v>
-      </c>
-      <c r="CT21" s="2">
+        <v>1412688.5735499845</v>
+      </c>
+      <c r="FF21" s="2">
         <f t="shared" si="222"/>
-        <v>908344.41260979034</v>
-      </c>
-      <c r="CU21" s="2">
+        <v>1426815.4592854844</v>
+      </c>
+      <c r="FG21" s="2">
         <f t="shared" si="222"/>
-        <v>917427.85673588829</v>
-      </c>
-      <c r="CV21" s="2">
+        <v>1441083.6138783393</v>
+      </c>
+      <c r="FH21" s="2">
         <f t="shared" si="222"/>
-        <v>926602.13530324714</v>
-      </c>
-      <c r="CW21" s="2">
+        <v>1455494.4500171228</v>
+      </c>
+      <c r="FI21" s="2">
         <f t="shared" si="222"/>
-        <v>935868.15665627958</v>
-      </c>
-      <c r="CX21" s="2">
+        <v>1470049.3945172941</v>
+      </c>
+      <c r="FJ21" s="2">
         <f t="shared" si="222"/>
-        <v>945226.83822284243</v>
-      </c>
-      <c r="CY21" s="2">
-        <f t="shared" ref="CY21:FJ21" si="223">+CX21*(1+$AM$26)</f>
-        <v>954679.10660507088</v>
-      </c>
-      <c r="CZ21" s="2">
+        <v>1484749.8884624671</v>
+      </c>
+      <c r="FK21" s="2">
+        <f t="shared" ref="FK21:GQ21" si="223">+FJ21*(1+$AM$26)</f>
+        <v>1499597.3873470917</v>
+      </c>
+      <c r="FL21" s="2">
         <f t="shared" si="223"/>
-        <v>964225.89767112164</v>
-      </c>
-      <c r="DA21" s="2">
+        <v>1514593.3612205626</v>
+      </c>
+      <c r="FM21" s="2">
         <f t="shared" si="223"/>
-        <v>973868.15664783283</v>
-      </c>
-      <c r="DB21" s="2">
+        <v>1529739.2948327682</v>
+      </c>
+      <c r="FN21" s="2">
         <f t="shared" si="223"/>
-        <v>983606.83821431117</v>
-      </c>
-      <c r="DC21" s="2">
+        <v>1545036.6877810957</v>
+      </c>
+      <c r="FO21" s="2">
         <f t="shared" si="223"/>
-        <v>993442.90659645433</v>
-      </c>
-      <c r="DD21" s="2">
+        <v>1560487.0546589068</v>
+      </c>
+      <c r="FP21" s="2">
         <f t="shared" si="223"/>
-        <v>1003377.3356624189</v>
-      </c>
-      <c r="DE21" s="2">
+        <v>1576091.9252054959</v>
+      </c>
+      <c r="FQ21" s="2">
         <f t="shared" si="223"/>
-        <v>1013411.109019043</v>
-      </c>
-      <c r="DF21" s="2">
+        <v>1591852.8444575509</v>
+      </c>
+      <c r="FR21" s="2">
         <f t="shared" si="223"/>
-        <v>1023545.2201092335</v>
-      </c>
-      <c r="DG21" s="2">
+        <v>1607771.3729021265</v>
+      </c>
+      <c r="FS21" s="2">
         <f t="shared" si="223"/>
-        <v>1033780.6723103259</v>
-      </c>
-      <c r="DH21" s="2">
+        <v>1623849.0866311479</v>
+      </c>
+      <c r="FT21" s="2">
         <f t="shared" si="223"/>
-        <v>1044118.4790334292</v>
-      </c>
-      <c r="DI21" s="2">
+        <v>1640087.5774974595</v>
+      </c>
+      <c r="FU21" s="2">
         <f t="shared" si="223"/>
-        <v>1054559.6638237634</v>
-      </c>
-      <c r="DJ21" s="2">
+        <v>1656488.4532724342</v>
+      </c>
+      <c r="FV21" s="2">
         <f t="shared" si="223"/>
-        <v>1065105.260462001</v>
-      </c>
-      <c r="DK21" s="2">
+        <v>1673053.3378051585</v>
+      </c>
+      <c r="FW21" s="2">
         <f t="shared" si="223"/>
-        <v>1075756.3130666211</v>
-      </c>
-      <c r="DL21" s="2">
+        <v>1689783.8711832101</v>
+      </c>
+      <c r="FX21" s="2">
         <f t="shared" si="223"/>
-        <v>1086513.8761972873</v>
-      </c>
-      <c r="DM21" s="2">
+        <v>1706681.7098950422</v>
+      </c>
+      <c r="FY21" s="2">
         <f t="shared" si="223"/>
-        <v>1097379.0149592601</v>
-      </c>
-      <c r="DN21" s="2">
+        <v>1723748.5269939927</v>
+      </c>
+      <c r="FZ21" s="2">
         <f t="shared" si="223"/>
-        <v>1108352.8051088527</v>
-      </c>
-      <c r="DO21" s="2">
+        <v>1740986.0122639327</v>
+      </c>
+      <c r="GA21" s="2">
         <f t="shared" si="223"/>
-        <v>1119436.3331599412</v>
-      </c>
-      <c r="DP21" s="2">
+        <v>1758395.8723865722</v>
+      </c>
+      <c r="GB21" s="2">
         <f t="shared" si="223"/>
-        <v>1130630.6964915406</v>
-      </c>
-      <c r="DQ21" s="2">
+        <v>1775979.8311104379</v>
+      </c>
+      <c r="GC21" s="2">
         <f t="shared" si="223"/>
-        <v>1141937.0034564561</v>
-      </c>
-      <c r="DR21" s="2">
+        <v>1793739.6294215422</v>
+      </c>
+      <c r="GD21" s="2">
         <f t="shared" si="223"/>
-        <v>1153356.3734910206</v>
-      </c>
-      <c r="DS21" s="2">
+        <v>1811677.0257157576</v>
+      </c>
+      <c r="GE21" s="2">
         <f t="shared" si="223"/>
-        <v>1164889.9372259309</v>
-      </c>
-      <c r="DT21" s="2">
+        <v>1829793.7959729151</v>
+      </c>
+      <c r="GF21" s="2">
         <f t="shared" si="223"/>
-        <v>1176538.8365981902</v>
-      </c>
-      <c r="DU21" s="2">
+        <v>1848091.7339326444</v>
+      </c>
+      <c r="GG21" s="2">
         <f t="shared" si="223"/>
-        <v>1188304.2249641721</v>
-      </c>
-      <c r="DV21" s="2">
+        <v>1866572.6512719707</v>
+      </c>
+      <c r="GH21" s="2">
         <f t="shared" si="223"/>
-        <v>1200187.267213814</v>
-      </c>
-      <c r="DW21" s="2">
+        <v>1885238.3777846904</v>
+      </c>
+      <c r="GI21" s="2">
         <f t="shared" si="223"/>
-        <v>1212189.139885952</v>
-      </c>
-      <c r="DX21" s="2">
+        <v>1904090.7615625372</v>
+      </c>
+      <c r="GJ21" s="2">
         <f t="shared" si="223"/>
-        <v>1224311.0312848114</v>
-      </c>
-      <c r="DY21" s="2">
+        <v>1923131.6691781625</v>
+      </c>
+      <c r="GK21" s="2">
         <f t="shared" si="223"/>
-        <v>1236554.1415976596</v>
-      </c>
-      <c r="DZ21" s="2">
+        <v>1942362.9858699441</v>
+      </c>
+      <c r="GL21" s="2">
         <f t="shared" si="223"/>
-        <v>1248919.6830136362</v>
-      </c>
-      <c r="EA21" s="2">
+        <v>1961786.6157286435</v>
+      </c>
+      <c r="GM21" s="2">
         <f t="shared" si="223"/>
-        <v>1261408.8798437726</v>
-      </c>
-      <c r="EB21" s="2">
+        <v>1981404.4818859301</v>
+      </c>
+      <c r="GN21" s="2">
         <f t="shared" si="223"/>
-        <v>1274022.9686422104</v>
-      </c>
-      <c r="EC21" s="2">
+        <v>2001218.5267047894</v>
+      </c>
+      <c r="GO21" s="2">
         <f t="shared" si="223"/>
-        <v>1286763.1983286324</v>
-      </c>
-      <c r="ED21" s="2">
+        <v>2021230.7119718373</v>
+      </c>
+      <c r="GP21" s="2">
         <f t="shared" si="223"/>
-        <v>1299630.8303119186</v>
-      </c>
-      <c r="EE21" s="2">
+        <v>2041443.0190915556</v>
+      </c>
+      <c r="GQ21" s="2">
         <f t="shared" si="223"/>
-        <v>1312627.1386150378</v>
-      </c>
-      <c r="EF21" s="2">
-        <f t="shared" si="223"/>
-        <v>1325753.4100011883</v>
-      </c>
-      <c r="EG21" s="2">
-        <f t="shared" si="223"/>
-        <v>1339010.9441012002</v>
-      </c>
-      <c r="EH21" s="2">
-        <f t="shared" si="223"/>
-        <v>1352401.0535422121</v>
-      </c>
-      <c r="EI21" s="2">
-        <f t="shared" si="223"/>
-        <v>1365925.0640776344</v>
-      </c>
-      <c r="EJ21" s="2">
-        <f t="shared" si="223"/>
-        <v>1379584.3147184106</v>
-      </c>
-      <c r="EK21" s="2">
-        <f t="shared" si="223"/>
-        <v>1393380.1578655948</v>
-      </c>
-      <c r="EL21" s="2">
-        <f t="shared" si="223"/>
-        <v>1407313.9594442509</v>
-      </c>
-      <c r="EM21" s="2">
-        <f t="shared" si="223"/>
-        <v>1421387.0990386934</v>
-      </c>
-      <c r="EN21" s="2">
-        <f t="shared" si="223"/>
-        <v>1435600.9700290803</v>
-      </c>
-      <c r="EO21" s="2">
-        <f t="shared" si="223"/>
-        <v>1449956.9797293711</v>
-      </c>
-      <c r="EP21" s="2">
-        <f t="shared" si="223"/>
-        <v>1464456.5495266649</v>
-      </c>
-      <c r="EQ21" s="2">
-        <f t="shared" si="223"/>
-        <v>1479101.1150219315</v>
-      </c>
-      <c r="ER21" s="2">
-        <f t="shared" si="223"/>
-        <v>1493892.1261721507</v>
-      </c>
-      <c r="ES21" s="2">
-        <f t="shared" si="223"/>
-        <v>1508831.0474338722</v>
-      </c>
-      <c r="ET21" s="2">
-        <f t="shared" si="223"/>
-        <v>1523919.3579082109</v>
-      </c>
-      <c r="EU21" s="2">
-        <f t="shared" si="223"/>
-        <v>1539158.5514872931</v>
-      </c>
-      <c r="EV21" s="2">
-        <f t="shared" si="223"/>
-        <v>1554550.1370021661</v>
-      </c>
-      <c r="EW21" s="2">
-        <f t="shared" si="223"/>
-        <v>1570095.6383721877</v>
-      </c>
-      <c r="EX21" s="2">
-        <f t="shared" si="223"/>
-        <v>1585796.5947559096</v>
-      </c>
-      <c r="EY21" s="2">
-        <f t="shared" si="223"/>
-        <v>1601654.5607034687</v>
-      </c>
-      <c r="EZ21" s="2">
-        <f t="shared" si="223"/>
-        <v>1617671.1063105036</v>
-      </c>
-      <c r="FA21" s="2">
-        <f t="shared" si="223"/>
-        <v>1633847.8173736087</v>
-      </c>
-      <c r="FB21" s="2">
-        <f t="shared" si="223"/>
-        <v>1650186.2955473447</v>
-      </c>
-      <c r="FC21" s="2">
-        <f t="shared" si="223"/>
-        <v>1666688.1585028181</v>
-      </c>
-      <c r="FD21" s="2">
-        <f t="shared" si="223"/>
-        <v>1683355.0400878463</v>
-      </c>
-      <c r="FE21" s="2">
-        <f t="shared" si="223"/>
-        <v>1700188.5904887249</v>
-      </c>
-      <c r="FF21" s="2">
-        <f t="shared" si="223"/>
-        <v>1717190.4763936121</v>
-      </c>
-      <c r="FG21" s="2">
-        <f t="shared" si="223"/>
-        <v>1734362.3811575482</v>
-      </c>
-      <c r="FH21" s="2">
-        <f t="shared" si="223"/>
-        <v>1751706.0049691238</v>
-      </c>
-      <c r="FI21" s="2">
-        <f t="shared" si="223"/>
-        <v>1769223.065018815</v>
-      </c>
-      <c r="FJ21" s="2">
-        <f t="shared" si="223"/>
-        <v>1786915.2956690032</v>
-      </c>
-      <c r="FK21" s="2">
-        <f t="shared" ref="FK21:GQ21" si="224">+FJ21*(1+$AM$26)</f>
-        <v>1804784.4486256931</v>
-      </c>
-      <c r="FL21" s="2">
+        <v>2061857.4492824711</v>
+      </c>
+      <c r="GR21" s="2">
+        <f t="shared" ref="GR21:HO21" si="224">+GQ21*(1+$AM$26)</f>
+        <v>2082476.0237752958</v>
+      </c>
+      <c r="GS21" s="2">
         <f t="shared" si="224"/>
-        <v>1822832.2931119502</v>
-      </c>
-      <c r="FM21" s="2">
+        <v>2103300.7840130487</v>
+      </c>
+      <c r="GT21" s="2">
         <f t="shared" si="224"/>
-        <v>1841060.6160430696</v>
-      </c>
-      <c r="FN21" s="2">
+        <v>2124333.7918531792</v>
+      </c>
+      <c r="GU21" s="2">
         <f t="shared" si="224"/>
-        <v>1859471.2222035003</v>
-      </c>
-      <c r="FO21" s="2">
+        <v>2145577.1297717108</v>
+      </c>
+      <c r="GV21" s="2">
         <f t="shared" si="224"/>
-        <v>1878065.9344255354</v>
-      </c>
-      <c r="FP21" s="2">
+        <v>2167032.9010694278</v>
+      </c>
+      <c r="GW21" s="2">
         <f t="shared" si="224"/>
-        <v>1896846.5937697908</v>
-      </c>
-      <c r="FQ21" s="2">
+        <v>2188703.2300801221</v>
+      </c>
+      <c r="GX21" s="2">
         <f t="shared" si="224"/>
-        <v>1915815.0597074889</v>
-      </c>
-      <c r="FR21" s="2">
+        <v>2210590.2623809231</v>
+      </c>
+      <c r="GY21" s="2">
         <f t="shared" si="224"/>
-        <v>1934973.2103045639</v>
-      </c>
-      <c r="FS21" s="2">
+        <v>2232696.1650047326</v>
+      </c>
+      <c r="GZ21" s="2">
         <f t="shared" si="224"/>
-        <v>1954322.9424076094</v>
-      </c>
-      <c r="FT21" s="2">
+        <v>2255023.12665478</v>
+      </c>
+      <c r="HA21" s="2">
         <f t="shared" si="224"/>
-        <v>1973866.1718316856</v>
-      </c>
-      <c r="FU21" s="2">
+        <v>2277573.3579213279</v>
+      </c>
+      <c r="HB21" s="2">
         <f t="shared" si="224"/>
-        <v>1993604.8335500024</v>
-      </c>
-      <c r="FV21" s="2">
+        <v>2300349.0915005412</v>
+      </c>
+      <c r="HC21" s="2">
         <f t="shared" si="224"/>
-        <v>2013540.8818855025</v>
-      </c>
-      <c r="FW21" s="2">
+        <v>2323352.5824155468</v>
+      </c>
+      <c r="HD21" s="2">
         <f t="shared" si="224"/>
-        <v>2033676.2907043574</v>
-      </c>
-      <c r="FX21" s="2">
+        <v>2346586.1082397024</v>
+      </c>
+      <c r="HE21" s="2">
         <f t="shared" si="224"/>
-        <v>2054013.053611401</v>
-      </c>
-      <c r="FY21" s="2">
+        <v>2370051.9693220994</v>
+      </c>
+      <c r="HF21" s="2">
         <f t="shared" si="224"/>
-        <v>2074553.1841475151</v>
-      </c>
-      <c r="FZ21" s="2">
+        <v>2393752.4890153203</v>
+      </c>
+      <c r="HG21" s="2">
         <f t="shared" si="224"/>
-        <v>2095298.7159889904</v>
-      </c>
-      <c r="GA21" s="2">
+        <v>2417690.0139054735</v>
+      </c>
+      <c r="HH21" s="2">
         <f t="shared" si="224"/>
-        <v>2116251.7031488805</v>
-      </c>
-      <c r="GB21" s="2">
+        <v>2441866.9140445283</v>
+      </c>
+      <c r="HI21" s="2">
         <f t="shared" si="224"/>
-        <v>2137414.2201803694</v>
-      </c>
-      <c r="GC21" s="2">
+        <v>2466285.5831849738</v>
+      </c>
+      <c r="HJ21" s="2">
         <f t="shared" si="224"/>
-        <v>2158788.3623821731</v>
-      </c>
-      <c r="GD21" s="2">
+        <v>2490948.4390168237</v>
+      </c>
+      <c r="HK21" s="2">
         <f t="shared" si="224"/>
-        <v>2180376.2460059947</v>
-      </c>
-      <c r="GE21" s="2">
+        <v>2515857.9234069921</v>
+      </c>
+      <c r="HL21" s="2">
         <f t="shared" si="224"/>
-        <v>2202180.0084660547</v>
-      </c>
-      <c r="GF21" s="2">
+        <v>2541016.5026410623</v>
+      </c>
+      <c r="HM21" s="2">
         <f t="shared" si="224"/>
-        <v>2224201.8085507154</v>
-      </c>
-      <c r="GG21" s="2">
+        <v>2566426.6676674727</v>
+      </c>
+      <c r="HN21" s="2">
         <f t="shared" si="224"/>
-        <v>2246443.8266362227</v>
-      </c>
-      <c r="GH21" s="2">
+        <v>2592090.9343441473</v>
+      </c>
+      <c r="HO21" s="2">
         <f t="shared" si="224"/>
-        <v>2268908.2649025847</v>
-      </c>
-      <c r="GI21" s="2">
-        <f t="shared" si="224"/>
-        <v>2291597.3475516108</v>
-      </c>
-      <c r="GJ21" s="2">
-        <f t="shared" si="224"/>
-        <v>2314513.3210271271</v>
-      </c>
-      <c r="GK21" s="2">
-        <f t="shared" si="224"/>
-        <v>2337658.4542373982</v>
-      </c>
-      <c r="GL21" s="2">
-        <f t="shared" si="224"/>
-        <v>2361035.0387797724</v>
-      </c>
-      <c r="GM21" s="2">
-        <f t="shared" si="224"/>
-        <v>2384645.38916757</v>
-      </c>
-      <c r="GN21" s="2">
-        <f t="shared" si="224"/>
-        <v>2408491.843059246</v>
-      </c>
-      <c r="GO21" s="2">
-        <f t="shared" si="224"/>
-        <v>2432576.7614898384</v>
-      </c>
-      <c r="GP21" s="2">
-        <f t="shared" si="224"/>
-        <v>2456902.5291047366</v>
-      </c>
-      <c r="GQ21" s="2">
-        <f t="shared" si="224"/>
-        <v>2481471.5543957842</v>
-      </c>
-      <c r="GR21" s="2">
-        <f t="shared" ref="GR21:HO21" si="225">+GQ21*(1+$AM$26)</f>
-        <v>2506286.2699397421</v>
-      </c>
-      <c r="GS21" s="2">
+        <v>2618011.8436875888</v>
+      </c>
+      <c r="HP21" s="2">
+        <f t="shared" ref="HP21:HW21" si="225">+HO21*(1+$AM$26)</f>
+        <v>2644191.9621244646</v>
+      </c>
+      <c r="HQ21" s="2">
         <f t="shared" si="225"/>
-        <v>2531349.1326391394</v>
-      </c>
-      <c r="GT21" s="2">
+        <v>2670633.8817457091</v>
+      </c>
+      <c r="HR21" s="2">
         <f t="shared" si="225"/>
-        <v>2556662.6239655307</v>
-      </c>
-      <c r="GU21" s="2">
+        <v>2697340.2205631663</v>
+      </c>
+      <c r="HS21" s="2">
         <f t="shared" si="225"/>
-        <v>2582229.2502051862</v>
-      </c>
-      <c r="GV21" s="2">
+        <v>2724313.6227687979</v>
+      </c>
+      <c r="HT21" s="2">
         <f t="shared" si="225"/>
-        <v>2608051.5427072379</v>
-      </c>
-      <c r="GW21" s="2">
+        <v>2751556.7589964857</v>
+      </c>
+      <c r="HU21" s="2">
         <f t="shared" si="225"/>
-        <v>2634132.0581343104</v>
-      </c>
-      <c r="GX21" s="2">
+        <v>2779072.3265864505</v>
+      </c>
+      <c r="HV21" s="2">
         <f t="shared" si="225"/>
-        <v>2660473.3787156534</v>
-      </c>
-      <c r="GY21" s="2">
+        <v>2806863.0498523149</v>
+      </c>
+      <c r="HW21" s="2">
         <f t="shared" si="225"/>
-        <v>2687078.1125028101</v>
-      </c>
-      <c r="GZ21" s="2">
-        <f t="shared" si="225"/>
-        <v>2713948.8936278382</v>
-      </c>
-      <c r="HA21" s="2">
-        <f t="shared" si="225"/>
-        <v>2741088.3825641167</v>
-      </c>
-      <c r="HB21" s="2">
-        <f t="shared" si="225"/>
-        <v>2768499.2663897579</v>
-      </c>
-      <c r="HC21" s="2">
-        <f t="shared" si="225"/>
-        <v>2796184.2590536554</v>
-      </c>
-      <c r="HD21" s="2">
-        <f t="shared" si="225"/>
-        <v>2824146.1016441919</v>
-      </c>
-      <c r="HE21" s="2">
-        <f t="shared" si="225"/>
-        <v>2852387.5626606341</v>
-      </c>
-      <c r="HF21" s="2">
-        <f t="shared" si="225"/>
-        <v>2880911.4382872405</v>
-      </c>
-      <c r="HG21" s="2">
-        <f t="shared" si="225"/>
-        <v>2909720.5526701128</v>
-      </c>
-      <c r="HH21" s="2">
-        <f t="shared" si="225"/>
-        <v>2938817.758196814</v>
-      </c>
-      <c r="HI21" s="2">
-        <f t="shared" si="225"/>
-        <v>2968205.9357787822</v>
-      </c>
-      <c r="HJ21" s="2">
-        <f t="shared" si="225"/>
-        <v>2997887.9951365702</v>
-      </c>
-      <c r="HK21" s="2">
-        <f t="shared" si="225"/>
-        <v>3027866.8750879359</v>
-      </c>
-      <c r="HL21" s="2">
-        <f t="shared" si="225"/>
-        <v>3058145.5438388153</v>
-      </c>
-      <c r="HM21" s="2">
-        <f t="shared" si="225"/>
-        <v>3088726.9992772033</v>
-      </c>
-      <c r="HN21" s="2">
-        <f t="shared" si="225"/>
-        <v>3119614.2692699754</v>
-      </c>
-      <c r="HO21" s="2">
-        <f t="shared" si="225"/>
-        <v>3150810.4119626749</v>
-      </c>
-      <c r="HP21" s="2">
-        <f t="shared" ref="HP21:HW21" si="226">+HO21*(1+$AM$26)</f>
-        <v>3182318.5160823017</v>
-      </c>
-      <c r="HQ21" s="2">
+        <v>2834931.6803508382</v>
+      </c>
+      <c r="HX21" s="2">
+        <f t="shared" ref="HX21:IB21" si="226">+HW21*(1+$AM$26)</f>
+        <v>2863280.9971543467</v>
+      </c>
+      <c r="HY21" s="2">
         <f t="shared" si="226"/>
-        <v>3214141.7012431249</v>
-      </c>
-      <c r="HR21" s="2">
+        <v>2891913.8071258902</v>
+      </c>
+      <c r="HZ21" s="2">
         <f t="shared" si="226"/>
-        <v>3246283.1182555561</v>
-      </c>
-      <c r="HS21" s="2">
+        <v>2920832.9451971492</v>
+      </c>
+      <c r="IA21" s="2">
         <f t="shared" si="226"/>
-        <v>3278745.9494381119</v>
-      </c>
-      <c r="HT21" s="2">
+        <v>2950041.2746491209</v>
+      </c>
+      <c r="IB21" s="2">
         <f t="shared" si="226"/>
-        <v>3311533.4089324931</v>
-      </c>
-      <c r="HU21" s="2">
-        <f t="shared" si="226"/>
-        <v>3344648.7430218179</v>
-      </c>
-      <c r="HV21" s="2">
-        <f t="shared" si="226"/>
-        <v>3378095.230452036</v>
-      </c>
-      <c r="HW21" s="2">
-        <f t="shared" si="226"/>
-        <v>3411876.1827565562</v>
-      </c>
-      <c r="HX21" s="2">
-        <f t="shared" ref="HX21:IB21" si="227">+HW21*(1+$AM$26)</f>
-        <v>3445994.9445841219</v>
-      </c>
-      <c r="HY21" s="2">
+        <v>2979541.6873956122</v>
+      </c>
+      <c r="IC21" s="2">
+        <f t="shared" ref="IC21:ID21" si="227">+IB21*(1+$AM$26)</f>
+        <v>3009337.1042695683</v>
+      </c>
+      <c r="ID21" s="2">
         <f t="shared" si="227"/>
-        <v>3480454.8940299633</v>
-      </c>
-      <c r="HZ21" s="2">
-        <f t="shared" si="227"/>
-        <v>3515259.4429702628</v>
-      </c>
-      <c r="IA21" s="2">
-        <f t="shared" si="227"/>
-        <v>3550412.0373999653</v>
-      </c>
-      <c r="IB21" s="2">
-        <f t="shared" si="227"/>
-        <v>3585916.157773965</v>
-      </c>
-      <c r="IC21" s="2">
-        <f t="shared" ref="IC21:ID21" si="228">+IB21*(1+$AM$26)</f>
-        <v>3621775.3193517048</v>
-      </c>
-      <c r="ID21" s="2">
-        <f t="shared" si="228"/>
-        <v>3657993.072545222</v>
+        <v>3039430.4753122642</v>
       </c>
     </row>
     <row r="22" spans="2:238" x14ac:dyDescent="0.2">
@@ -5461,35 +5466,35 @@
         <v>24515.682607508588</v>
       </c>
       <c r="AD22" s="2">
-        <f t="shared" ref="AD22:AK22" si="229">+AC22</f>
+        <f t="shared" ref="AD22:AK22" si="228">+AC22</f>
         <v>24515.682607508588</v>
       </c>
       <c r="AE22" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="228"/>
         <v>24515.682607508588</v>
       </c>
       <c r="AF22" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="228"/>
         <v>24515.682607508588</v>
       </c>
       <c r="AG22" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="228"/>
         <v>24515.682607508588</v>
       </c>
       <c r="AH22" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="228"/>
         <v>24515.682607508588</v>
       </c>
       <c r="AI22" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="228"/>
         <v>24515.682607508588</v>
       </c>
       <c r="AJ22" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="228"/>
         <v>24515.682607508588</v>
       </c>
       <c r="AK22" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="228"/>
         <v>24515.682607508588</v>
       </c>
     </row>
@@ -5546,72 +5551,72 @@
         <v>1.4617810795501087</v>
       </c>
       <c r="U23" s="1">
-        <f t="shared" ref="U23:AA23" si="230">+U21/U22</f>
+        <f t="shared" ref="U23:AA23" si="229">+U21/U22</f>
         <v>6.6256000000000004</v>
       </c>
       <c r="V23" s="1">
-        <f t="shared" si="230"/>
+        <f t="shared" si="229"/>
         <v>4.5242718446601939</v>
       </c>
       <c r="W23" s="1">
-        <f t="shared" si="230"/>
+        <f t="shared" si="229"/>
         <v>6.8980891719745223</v>
       </c>
       <c r="X23" s="1">
-        <f t="shared" si="230"/>
+        <f t="shared" si="229"/>
         <v>3.8469428007889546</v>
       </c>
       <c r="Y23" s="1">
-        <f t="shared" si="230"/>
+        <f t="shared" si="229"/>
         <v>0.22820103709613082</v>
       </c>
       <c r="Z23" s="1">
-        <f t="shared" si="230"/>
+        <f t="shared" si="229"/>
         <v>1.1932638331996792</v>
       </c>
       <c r="AA23" s="1">
-        <f t="shared" si="230"/>
+        <f t="shared" si="229"/>
         <v>3.341396548943719</v>
       </c>
       <c r="AB23" s="2">
-        <f t="shared" si="208"/>
+        <f t="shared" si="207"/>
         <v>4.6101015411257587</v>
       </c>
       <c r="AC23" s="1">
         <f>+AC21/AC22</f>
-        <v>6.3681579344043602</v>
+        <v>5.9286438360847109</v>
       </c>
       <c r="AD23" s="1">
-        <f t="shared" ref="AD23:AK23" si="231">+AD21/AD22</f>
-        <v>8.8294368849944025</v>
+        <f t="shared" ref="AD23:AK23" si="230">+AD21/AD22</f>
+        <v>7.3570646556235735</v>
       </c>
       <c r="AE23" s="1">
-        <f t="shared" si="231"/>
-        <v>10.55233215040743</v>
+        <f t="shared" si="230"/>
+        <v>8.7854854751624369</v>
       </c>
       <c r="AF23" s="1">
-        <f t="shared" si="231"/>
-        <v>12.619806468903063</v>
+        <f t="shared" si="230"/>
+        <v>10.499590458609072</v>
       </c>
       <c r="AG23" s="1">
-        <f t="shared" si="231"/>
-        <v>13.860291060000446</v>
+        <f t="shared" si="230"/>
+        <v>11.528053448677056</v>
       </c>
       <c r="AH23" s="1">
-        <f t="shared" si="231"/>
-        <v>15.224824110207567</v>
+        <f t="shared" si="230"/>
+        <v>12.659362737751838</v>
       </c>
       <c r="AI23" s="1">
-        <f t="shared" si="231"/>
-        <v>16.725810465435401</v>
+        <f t="shared" si="230"/>
+        <v>13.903802955734099</v>
       </c>
       <c r="AJ23" s="1">
-        <f t="shared" si="231"/>
-        <v>18.37689545618602</v>
+        <f t="shared" si="230"/>
+        <v>15.272687195514584</v>
       </c>
       <c r="AK23" s="1">
-        <f t="shared" si="231"/>
-        <v>20.193088946011699</v>
+        <f t="shared" si="230"/>
+        <v>16.778459859273116</v>
       </c>
     </row>
     <row r="24" spans="2:238" x14ac:dyDescent="0.2">
@@ -5620,31 +5625,31 @@
         <v>0.21647980340961451</v>
       </c>
       <c r="H24" s="29">
-        <f t="shared" ref="H24:N24" si="232">+H12/H11</f>
+        <f t="shared" ref="H24:N24" si="231">+H12/H11</f>
         <v>0.24853528628495339</v>
       </c>
       <c r="I24" s="29">
-        <f t="shared" si="232"/>
+        <f t="shared" si="231"/>
         <v>0.25443247249301637</v>
       </c>
       <c r="J24" s="29">
-        <f t="shared" si="232"/>
+        <f t="shared" si="231"/>
         <v>0.26973634029137322</v>
       </c>
       <c r="K24" s="29">
-        <f t="shared" si="232"/>
+        <f t="shared" si="231"/>
         <v>0.39476192637646951</v>
       </c>
       <c r="L24" s="29">
-        <f t="shared" si="232"/>
+        <f t="shared" si="231"/>
         <v>0.27576321588259206</v>
       </c>
       <c r="M24" s="29">
-        <f t="shared" si="232"/>
+        <f t="shared" si="231"/>
         <v>0.2658842928814511</v>
       </c>
       <c r="N24" s="29">
-        <f t="shared" si="232"/>
+        <f t="shared" si="231"/>
         <v>0.26</v>
       </c>
       <c r="U24" s="29">
@@ -5652,43 +5657,43 @@
         <v>0.20279959030385797</v>
       </c>
       <c r="V24" s="29">
-        <f t="shared" ref="V24:AD24" si="233">+V13/V11</f>
+        <f t="shared" ref="V24:AD24" si="232">+V13/V11</f>
         <v>0.25911339073090311</v>
       </c>
       <c r="W24" s="29">
-        <f t="shared" si="233"/>
+        <f t="shared" si="232"/>
         <v>0.2353223388305847</v>
       </c>
       <c r="X24" s="29">
-        <f t="shared" si="233"/>
+        <f t="shared" si="232"/>
         <v>0.19573456193802483</v>
       </c>
       <c r="Y24" s="29">
-        <f t="shared" si="233"/>
+        <f t="shared" si="232"/>
         <v>0.27207681471046191</v>
       </c>
       <c r="Z24" s="29">
-        <f t="shared" si="233"/>
+        <f t="shared" si="232"/>
         <v>0.14239519385443683</v>
       </c>
       <c r="AA24" s="29">
-        <f t="shared" si="233"/>
+        <f t="shared" si="232"/>
         <v>9.8960129351632606E-2</v>
       </c>
       <c r="AB24" s="29">
-        <f t="shared" si="233"/>
+        <f t="shared" si="232"/>
         <v>8.4511608892397477E-2</v>
       </c>
       <c r="AC24" s="29">
-        <f t="shared" si="233"/>
+        <f t="shared" si="232"/>
         <v>8.4511608892397477E-2</v>
       </c>
       <c r="AD24" s="29">
-        <f t="shared" si="233"/>
+        <f t="shared" si="232"/>
         <v>8.4511608892397477E-2</v>
       </c>
       <c r="AE24" s="29">
-        <f t="shared" ref="AE24" si="234">+AE13/AE11</f>
+        <f t="shared" ref="AE24" si="233">+AE13/AE11</f>
         <v>8.4511608892397477E-2</v>
       </c>
     </row>
@@ -5707,27 +5712,27 @@
       <c r="F26" s="29"/>
       <c r="G26" s="29"/>
       <c r="H26" s="29">
-        <f t="shared" ref="H26:M33" si="235">+H4/D4-1</f>
+        <f t="shared" ref="H26:M33" si="234">+H4/D4-1</f>
         <v>1.6247097073850441</v>
       </c>
       <c r="I26" s="29">
-        <f t="shared" si="235"/>
+        <f t="shared" si="234"/>
         <v>1.321464561639234</v>
       </c>
       <c r="J26" s="29">
-        <f t="shared" si="235"/>
+        <f t="shared" si="234"/>
         <v>1.1598885424268559</v>
       </c>
       <c r="K26" s="29">
-        <f t="shared" si="235"/>
+        <f t="shared" si="234"/>
         <v>0.76129331683168311</v>
       </c>
       <c r="L26" s="29">
-        <f t="shared" si="235"/>
+        <f t="shared" si="234"/>
         <v>0.49725712263316235</v>
       </c>
       <c r="M26" s="29">
-        <f t="shared" si="235"/>
+        <f t="shared" si="234"/>
         <v>0.55650412386051218</v>
       </c>
       <c r="Z26" s="10">
@@ -5755,23 +5760,23 @@
       <c r="F27" s="29"/>
       <c r="G27" s="29"/>
       <c r="H27" s="29">
-        <f t="shared" si="235"/>
+        <f t="shared" si="234"/>
         <v>1.1437755698421976</v>
       </c>
       <c r="I27" s="29">
-        <f t="shared" si="235"/>
+        <f t="shared" si="234"/>
         <v>0.19992325402916356</v>
       </c>
       <c r="J27" s="29">
-        <f t="shared" si="235"/>
+        <f t="shared" si="234"/>
         <v>-9.2164515160612415E-2</v>
       </c>
       <c r="K27" s="29">
-        <f t="shared" si="235"/>
+        <f t="shared" si="234"/>
         <v>0.56322926521602024</v>
       </c>
       <c r="L27" s="29">
-        <f t="shared" si="235"/>
+        <f t="shared" si="234"/>
         <v>0.97709923664122145</v>
       </c>
       <c r="M27" s="29">
@@ -5779,11 +5784,11 @@
         <v>1.618164374800128</v>
       </c>
       <c r="Z27" s="10">
-        <f t="shared" ref="Z27:AA33" si="236">+Z5/Y5-1</f>
+        <f t="shared" ref="Z27:AA33" si="235">+Z5/Y5-1</f>
         <v>1.3251084598698482</v>
       </c>
       <c r="AA27" s="10">
-        <f t="shared" si="236"/>
+        <f t="shared" si="235"/>
         <v>0.51486880466472296</v>
       </c>
       <c r="AL27" s="10" t="s">
@@ -5803,51 +5808,51 @@
       <c r="F28" s="29"/>
       <c r="G28" s="29"/>
       <c r="H28" s="29">
+        <f t="shared" si="234"/>
+        <v>1.5449966095127388</v>
+      </c>
+      <c r="I28" s="29">
+        <f t="shared" si="234"/>
+        <v>1.1200909466721787</v>
+      </c>
+      <c r="J28" s="29">
+        <f t="shared" si="234"/>
+        <v>0.93327537491849588</v>
+      </c>
+      <c r="K28" s="29">
+        <f t="shared" si="234"/>
+        <v>0.73345743030625354</v>
+      </c>
+      <c r="L28" s="29">
+        <f t="shared" si="234"/>
+        <v>0.56425091352009749</v>
+      </c>
+      <c r="M28" s="29">
+        <f t="shared" si="234"/>
+        <v>0.66439179747164534</v>
+      </c>
+      <c r="V28" s="10">
+        <f t="shared" ref="V28" si="236">+V6/U6-1</f>
+        <v>1.7394270122783162E-2</v>
+      </c>
+      <c r="W28" s="10">
+        <f t="shared" ref="W28:X28" si="237">+W6/V6-1</f>
+        <v>1.2447200804559166</v>
+      </c>
+      <c r="X28" s="10">
+        <f t="shared" si="237"/>
+        <v>0.5849761051373954</v>
+      </c>
+      <c r="Y28" s="10">
+        <f t="shared" ref="Y28" si="238">+Y6/X6-1</f>
+        <v>0.4138320927164798</v>
+      </c>
+      <c r="Z28" s="10">
         <f t="shared" si="235"/>
-        <v>1.5449966095127388</v>
-      </c>
-      <c r="I28" s="29">
+        <v>2.1672775741419525</v>
+      </c>
+      <c r="AA28" s="10">
         <f t="shared" si="235"/>
-        <v>1.1200909466721787</v>
-      </c>
-      <c r="J28" s="29">
-        <f t="shared" si="235"/>
-        <v>0.93327537491849588</v>
-      </c>
-      <c r="K28" s="29">
-        <f t="shared" si="235"/>
-        <v>0.73345743030625354</v>
-      </c>
-      <c r="L28" s="29">
-        <f t="shared" si="235"/>
-        <v>0.56425091352009749</v>
-      </c>
-      <c r="M28" s="29">
-        <f t="shared" si="235"/>
-        <v>0.66439179747164534</v>
-      </c>
-      <c r="V28" s="10">
-        <f t="shared" ref="V28" si="237">+V6/U6-1</f>
-        <v>1.7394270122783162E-2</v>
-      </c>
-      <c r="W28" s="10">
-        <f t="shared" ref="W28:X28" si="238">+W6/V6-1</f>
-        <v>1.2447200804559166</v>
-      </c>
-      <c r="X28" s="10">
-        <f t="shared" si="238"/>
-        <v>0.5849761051373954</v>
-      </c>
-      <c r="Y28" s="10">
-        <f t="shared" ref="Y28" si="239">+Y6/X6-1</f>
-        <v>0.4138320927164798</v>
-      </c>
-      <c r="Z28" s="10">
-        <f t="shared" si="236"/>
-        <v>2.1672775741419525</v>
-      </c>
-      <c r="AA28" s="10">
-        <f t="shared" si="236"/>
         <v>1.4236927932667016</v>
       </c>
       <c r="AL28" s="10" t="s">
@@ -5855,7 +5860,7 @@
       </c>
       <c r="AM28" s="35">
         <f>NPV(AM27,AB21:ID21)</f>
-        <v>5227669.9951672591</v>
+        <v>4376148.0390042346</v>
       </c>
     </row>
     <row r="29" spans="2:238" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -5868,51 +5873,51 @@
       <c r="F29" s="29"/>
       <c r="G29" s="29"/>
       <c r="H29" s="29">
+        <f t="shared" si="234"/>
+        <v>0.15848753016894612</v>
+      </c>
+      <c r="I29" s="29">
+        <f t="shared" si="234"/>
+        <v>0.14810924369747891</v>
+      </c>
+      <c r="J29" s="29">
+        <f t="shared" si="234"/>
+        <v>-0.11204188481675392</v>
+      </c>
+      <c r="K29" s="29">
+        <f t="shared" si="234"/>
+        <v>0.42160936909709101</v>
+      </c>
+      <c r="L29" s="29">
+        <f t="shared" si="234"/>
+        <v>0.48854166666666665</v>
+      </c>
+      <c r="M29" s="29">
+        <f t="shared" si="234"/>
+        <v>0.30070143336383048</v>
+      </c>
+      <c r="V29" s="10">
+        <f t="shared" ref="V29" si="239">+V7/U7-1</f>
+        <v>-0.11655459494076204</v>
+      </c>
+      <c r="W29" s="10">
+        <f t="shared" ref="W29:X29" si="240">+W7/V7-1</f>
+        <v>0.40612540775643358</v>
+      </c>
+      <c r="X29" s="10">
+        <f t="shared" si="240"/>
+        <v>0.60613481118700863</v>
+      </c>
+      <c r="Y29" s="10">
+        <f t="shared" ref="Y29" si="241">+Y7/X7-1</f>
+        <v>-0.27242818167228378</v>
+      </c>
+      <c r="Z29" s="10">
         <f t="shared" si="235"/>
-        <v>0.15848753016894612</v>
-      </c>
-      <c r="I29" s="29">
+        <v>0.15220028675416342</v>
+      </c>
+      <c r="AA29" s="10">
         <f t="shared" si="235"/>
-        <v>0.14810924369747891</v>
-      </c>
-      <c r="J29" s="29">
-        <f t="shared" si="235"/>
-        <v>-0.11204188481675392</v>
-      </c>
-      <c r="K29" s="29">
-        <f t="shared" si="235"/>
-        <v>0.42160936909709101</v>
-      </c>
-      <c r="L29" s="29">
-        <f t="shared" si="235"/>
-        <v>0.48854166666666665</v>
-      </c>
-      <c r="M29" s="29">
-        <f t="shared" si="235"/>
-        <v>0.30070143336383048</v>
-      </c>
-      <c r="V29" s="10">
-        <f t="shared" ref="V29" si="240">+V7/U7-1</f>
-        <v>-0.11655459494076204</v>
-      </c>
-      <c r="W29" s="10">
-        <f t="shared" ref="W29:X29" si="241">+W7/V7-1</f>
-        <v>0.40612540775643358</v>
-      </c>
-      <c r="X29" s="10">
-        <f t="shared" si="241"/>
-        <v>0.60613481118700863</v>
-      </c>
-      <c r="Y29" s="10">
-        <f t="shared" ref="Y29" si="242">+Y7/X7-1</f>
-        <v>-0.27242818167228378</v>
-      </c>
-      <c r="Z29" s="10">
-        <f t="shared" si="236"/>
-        <v>0.15220028675416342</v>
-      </c>
-      <c r="AA29" s="10">
-        <f t="shared" si="236"/>
         <v>8.643629750167503E-2</v>
       </c>
       <c r="AL29" s="10" t="s">
@@ -5933,51 +5938,51 @@
       <c r="F30" s="29"/>
       <c r="G30" s="29"/>
       <c r="H30" s="29">
+        <f t="shared" si="234"/>
+        <v>0.19788918205804751</v>
+      </c>
+      <c r="I30" s="29">
+        <f t="shared" si="234"/>
+        <v>0.16826923076923084</v>
+      </c>
+      <c r="J30" s="29">
+        <f t="shared" si="234"/>
+        <v>0.10367170626349886</v>
+      </c>
+      <c r="K30" s="29">
+        <f t="shared" si="234"/>
+        <v>0.19203747072599531</v>
+      </c>
+      <c r="L30" s="29">
+        <f t="shared" si="234"/>
+        <v>0.32378854625550657</v>
+      </c>
+      <c r="M30" s="29">
+        <f t="shared" si="234"/>
+        <v>0.56378600823045266</v>
+      </c>
+      <c r="V30" s="10">
+        <f t="shared" ref="V30" si="242">+V8/U8-1</f>
+        <v>7.2566371681415998E-2</v>
+      </c>
+      <c r="W30" s="10">
+        <f t="shared" ref="W30:X30" si="243">+W8/V8-1</f>
+        <v>-0.13118811881188119</v>
+      </c>
+      <c r="X30" s="10">
+        <f t="shared" si="243"/>
+        <v>1.0047483380816713</v>
+      </c>
+      <c r="Y30" s="10">
+        <f t="shared" ref="Y30" si="244">+Y8/X8-1</f>
+        <v>-0.26859308384651825</v>
+      </c>
+      <c r="Z30" s="10">
         <f t="shared" si="235"/>
-        <v>0.19788918205804751</v>
-      </c>
-      <c r="I30" s="29">
+        <v>5.8290155440414715E-3</v>
+      </c>
+      <c r="AA30" s="10">
         <f t="shared" si="235"/>
-        <v>0.16826923076923084</v>
-      </c>
-      <c r="J30" s="29">
-        <f t="shared" si="235"/>
-        <v>0.10367170626349886</v>
-      </c>
-      <c r="K30" s="29">
-        <f t="shared" si="235"/>
-        <v>0.19203747072599531</v>
-      </c>
-      <c r="L30" s="29">
-        <f t="shared" si="235"/>
-        <v>0.32378854625550657</v>
-      </c>
-      <c r="M30" s="29">
-        <f t="shared" si="235"/>
-        <v>0.56378600823045266</v>
-      </c>
-      <c r="V30" s="10">
-        <f t="shared" ref="V30" si="243">+V8/U8-1</f>
-        <v>7.2566371681415998E-2</v>
-      </c>
-      <c r="W30" s="10">
-        <f t="shared" ref="W30:X30" si="244">+W8/V8-1</f>
-        <v>-0.13118811881188119</v>
-      </c>
-      <c r="X30" s="10">
-        <f t="shared" si="244"/>
-        <v>1.0047483380816713</v>
-      </c>
-      <c r="Y30" s="10">
-        <f t="shared" ref="Y30" si="245">+Y8/X8-1</f>
-        <v>-0.26859308384651825</v>
-      </c>
-      <c r="Z30" s="10">
-        <f t="shared" si="236"/>
-        <v>5.8290155440414715E-3</v>
-      </c>
-      <c r="AA30" s="10">
-        <f t="shared" si="236"/>
         <v>0.20927237604636195</v>
       </c>
       <c r="AL30" s="10" t="s">
@@ -5985,7 +5990,7 @@
       </c>
       <c r="AM30" s="3">
         <f>+AM28/AM29</f>
-        <v>215.13045247601889</v>
+        <v>180.08839666684094</v>
       </c>
     </row>
     <row r="31" spans="2:238" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -5998,51 +6003,51 @@
       <c r="F31" s="29"/>
       <c r="G31" s="29"/>
       <c r="H31" s="29">
+        <f t="shared" si="234"/>
+        <v>0.36758893280632421</v>
+      </c>
+      <c r="I31" s="29">
+        <f t="shared" si="234"/>
+        <v>0.72030651340996177</v>
+      </c>
+      <c r="J31" s="29">
+        <f t="shared" si="234"/>
+        <v>1.0284697508896796</v>
+      </c>
+      <c r="K31" s="29">
+        <f t="shared" si="234"/>
+        <v>0.72340425531914887</v>
+      </c>
+      <c r="L31" s="29">
+        <f t="shared" si="234"/>
+        <v>0.69364161849710992</v>
+      </c>
+      <c r="M31" s="29">
+        <f t="shared" si="234"/>
+        <v>0.31848552338530056</v>
+      </c>
+      <c r="V31" s="10">
+        <f t="shared" ref="V31" si="245">+V9/U9-1</f>
+        <v>9.2043681747269845E-2</v>
+      </c>
+      <c r="W31" s="10">
+        <f t="shared" ref="W31:X31" si="246">+W9/V9-1</f>
+        <v>-0.23428571428571432</v>
+      </c>
+      <c r="X31" s="10">
+        <f t="shared" si="246"/>
+        <v>5.5970149253731449E-2</v>
+      </c>
+      <c r="Y31" s="10">
+        <f t="shared" ref="Y31" si="247">+Y9/X9-1</f>
+        <v>0.59540636042402828</v>
+      </c>
+      <c r="Z31" s="10">
         <f t="shared" si="235"/>
-        <v>0.36758893280632421</v>
-      </c>
-      <c r="I31" s="29">
+        <v>0.20819490586932443</v>
+      </c>
+      <c r="AA31" s="10">
         <f t="shared" si="235"/>
-        <v>0.72030651340996177</v>
-      </c>
-      <c r="J31" s="29">
-        <f t="shared" si="235"/>
-        <v>1.0284697508896796</v>
-      </c>
-      <c r="K31" s="29">
-        <f t="shared" si="235"/>
-        <v>0.72340425531914887</v>
-      </c>
-      <c r="L31" s="29">
-        <f t="shared" si="235"/>
-        <v>0.69364161849710992</v>
-      </c>
-      <c r="M31" s="29">
-        <f t="shared" si="235"/>
-        <v>0.31848552338530056</v>
-      </c>
-      <c r="V31" s="10">
-        <f t="shared" ref="V31" si="246">+V9/U9-1</f>
-        <v>9.2043681747269845E-2</v>
-      </c>
-      <c r="W31" s="10">
-        <f t="shared" ref="W31:X31" si="247">+W9/V9-1</f>
-        <v>-0.23428571428571432</v>
-      </c>
-      <c r="X31" s="10">
-        <f t="shared" si="247"/>
-        <v>5.5970149253731449E-2</v>
-      </c>
-      <c r="Y31" s="10">
-        <f t="shared" ref="Y31" si="248">+Y9/X9-1</f>
-        <v>0.59540636042402828</v>
-      </c>
-      <c r="Z31" s="10">
-        <f t="shared" si="236"/>
-        <v>0.20819490586932443</v>
-      </c>
-      <c r="AA31" s="10">
-        <f t="shared" si="236"/>
         <v>0.55270394133822176</v>
       </c>
       <c r="AL31" s="10" t="s">
@@ -6063,56 +6068,56 @@
       <c r="F32" s="29"/>
       <c r="G32" s="29"/>
       <c r="H32" s="29">
+        <f t="shared" si="234"/>
+        <v>0.33333333333333326</v>
+      </c>
+      <c r="I32" s="29">
+        <f t="shared" si="234"/>
+        <v>0.32876712328767121</v>
+      </c>
+      <c r="J32" s="29">
+        <f t="shared" si="234"/>
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="K32" s="29">
+        <f t="shared" si="234"/>
+        <v>0.42307692307692313</v>
+      </c>
+      <c r="L32" s="29">
+        <f t="shared" si="234"/>
+        <v>0.96590909090909083</v>
+      </c>
+      <c r="M32" s="29">
+        <f t="shared" si="234"/>
+        <v>0.79381443298969079</v>
+      </c>
+      <c r="V32" s="10">
+        <f t="shared" ref="V32" si="248">+V10/U10-1</f>
+        <v>-0.34159061277705349</v>
+      </c>
+      <c r="W32" s="10">
+        <f t="shared" ref="W32:X32" si="249">+W10/V10-1</f>
+        <v>0.2495049504950495</v>
+      </c>
+      <c r="X32" s="10">
+        <f t="shared" si="249"/>
+        <v>0.84152139461172748</v>
+      </c>
+      <c r="Y32" s="10">
+        <f t="shared" ref="Y32" si="250">+Y10/X10-1</f>
+        <v>-0.60843373493975905</v>
+      </c>
+      <c r="Z32" s="10">
         <f t="shared" si="235"/>
-        <v>0.33333333333333326</v>
-      </c>
-      <c r="I32" s="29">
+        <v>-0.32747252747252742</v>
+      </c>
+      <c r="AA32" s="10">
         <f t="shared" si="235"/>
-        <v>0.32876712328767121</v>
-      </c>
-      <c r="J32" s="29">
-        <f t="shared" si="235"/>
-        <v>0.39999999999999991</v>
-      </c>
-      <c r="K32" s="29">
-        <f t="shared" si="235"/>
-        <v>0.42307692307692313</v>
-      </c>
-      <c r="L32" s="29">
-        <f t="shared" si="235"/>
-        <v>0.96590909090909083</v>
-      </c>
-      <c r="M32" s="29">
-        <f t="shared" si="235"/>
-        <v>0.79381443298969079</v>
-      </c>
-      <c r="V32" s="10">
-        <f t="shared" ref="V32" si="249">+V10/U10-1</f>
-        <v>-0.34159061277705349</v>
-      </c>
-      <c r="W32" s="10">
-        <f t="shared" ref="W32:X32" si="250">+W10/V10-1</f>
-        <v>0.2495049504950495</v>
-      </c>
-      <c r="X32" s="10">
-        <f t="shared" si="250"/>
-        <v>0.84152139461172748</v>
-      </c>
-      <c r="Y32" s="10">
-        <f t="shared" ref="Y32" si="251">+Y10/X10-1</f>
-        <v>-0.60843373493975905</v>
-      </c>
-      <c r="Z32" s="10">
-        <f t="shared" si="236"/>
-        <v>-0.32747252747252742</v>
-      </c>
-      <c r="AA32" s="10">
-        <f t="shared" si="236"/>
         <v>0.2712418300653594</v>
       </c>
       <c r="AM32" s="10">
         <f>+AM30/AM31-1</f>
-        <v>0.18203545316493885</v>
+        <v>-1.0503315017357462E-2</v>
       </c>
     </row>
     <row r="33" spans="2:37" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -6125,91 +6130,91 @@
       <c r="F33" s="29"/>
       <c r="G33" s="29"/>
       <c r="H33" s="29">
+        <f t="shared" si="234"/>
+        <v>1.2240319834160065</v>
+      </c>
+      <c r="I33" s="29">
+        <f t="shared" si="234"/>
+        <v>0.93609271523178816</v>
+      </c>
+      <c r="J33" s="29">
+        <f t="shared" si="234"/>
+        <v>0.77944170474596208</v>
+      </c>
+      <c r="K33" s="29">
+        <f t="shared" si="234"/>
+        <v>0.69182921210259551</v>
+      </c>
+      <c r="L33" s="29">
+        <f t="shared" si="234"/>
+        <v>0.5560252996005326</v>
+      </c>
+      <c r="M33" s="29">
+        <f t="shared" si="234"/>
+        <v>0.62493586454592109</v>
+      </c>
+      <c r="V33" s="10">
+        <f t="shared" ref="V33" si="251">+V11/U11-1</f>
+        <v>-6.8111983612154314E-2</v>
+      </c>
+      <c r="W33" s="10">
+        <f t="shared" ref="W33:X33" si="252">+W11/V11-1</f>
+        <v>0.52729437625938824</v>
+      </c>
+      <c r="X33" s="10">
+        <f t="shared" si="252"/>
+        <v>0.61403298350824587</v>
+      </c>
+      <c r="Y33" s="10">
+        <f t="shared" ref="Y33" si="253">+Y11/X11-1</f>
+        <v>2.2293230289069932E-3</v>
+      </c>
+      <c r="Z33" s="10">
         <f t="shared" si="235"/>
-        <v>1.2240319834160065</v>
-      </c>
-      <c r="I33" s="29">
+        <v>1.2585452658115224</v>
+      </c>
+      <c r="AA33" s="10">
         <f t="shared" si="235"/>
-        <v>0.93609271523178816</v>
-      </c>
-      <c r="J33" s="29">
-        <f t="shared" si="235"/>
-        <v>0.77944170474596208</v>
-      </c>
-      <c r="K33" s="29">
-        <f t="shared" si="235"/>
-        <v>0.69182921210259551</v>
-      </c>
-      <c r="L33" s="29">
-        <f t="shared" si="235"/>
-        <v>0.5560252996005326</v>
-      </c>
-      <c r="M33" s="29">
-        <f t="shared" si="235"/>
-        <v>0.62493586454592109</v>
-      </c>
-      <c r="V33" s="10">
-        <f t="shared" ref="V33" si="252">+V11/U11-1</f>
-        <v>-6.8111983612154314E-2</v>
-      </c>
-      <c r="W33" s="10">
-        <f t="shared" ref="W33:X33" si="253">+W11/V11-1</f>
-        <v>0.52729437625938824</v>
-      </c>
-      <c r="X33" s="10">
-        <f t="shared" si="253"/>
-        <v>0.61403298350824587</v>
-      </c>
-      <c r="Y33" s="10">
-        <f t="shared" ref="Y33" si="254">+Y11/X11-1</f>
-        <v>2.2293230289069932E-3</v>
-      </c>
-      <c r="Z33" s="10">
-        <f t="shared" si="236"/>
-        <v>1.2585452658115224</v>
-      </c>
-      <c r="AA33" s="10">
-        <f t="shared" si="236"/>
         <v>1.1420340763599355</v>
       </c>
       <c r="AB33" s="10">
-        <f t="shared" ref="AB33" si="255">+AB11/AA11-1</f>
+        <f t="shared" ref="AB33" si="254">+AB11/AA11-1</f>
         <v>0.63077312122117757</v>
       </c>
       <c r="AC33" s="10">
-        <f t="shared" ref="AC33" si="256">+AC11/AB11-1</f>
-        <v>0.39999999999999991</v>
+        <f t="shared" ref="AC33" si="255">+AC11/AB11-1</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AD33" s="10">
-        <f t="shared" ref="AD33" si="257">+AD11/AC11-1</f>
-        <v>0.39999999999999991</v>
+        <f t="shared" ref="AD33" si="256">+AD11/AC11-1</f>
+        <v>0.25</v>
       </c>
       <c r="AE33" s="10">
-        <f t="shared" ref="AE33" si="258">+AE11/AD11-1</f>
+        <f t="shared" ref="AE33" si="257">+AE11/AD11-1</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="AF33" s="10">
-        <f t="shared" ref="AF33" si="259">+AF11/AE11-1</f>
+        <f t="shared" ref="AF33" si="258">+AF11/AE11-1</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="AG33" s="10">
-        <f t="shared" ref="AG33" si="260">+AG11/AF11-1</f>
+        <f t="shared" ref="AG33" si="259">+AG11/AF11-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="AH33" s="10">
-        <f t="shared" ref="AH33" si="261">+AH11/AG11-1</f>
+        <f t="shared" ref="AH33" si="260">+AH11/AG11-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="AI33" s="10">
-        <f t="shared" ref="AI33" si="262">+AI11/AH11-1</f>
+        <f t="shared" ref="AI33" si="261">+AI11/AH11-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="AJ33" s="10">
-        <f t="shared" ref="AJ33:AK33" si="263">+AJ11/AI11-1</f>
+        <f t="shared" ref="AJ33:AK33" si="262">+AJ11/AI11-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="AK33" s="10">
-        <f t="shared" si="263"/>
+        <f t="shared" si="262"/>
         <v>0.10000000000000009</v>
       </c>
     </row>
@@ -6223,47 +6228,47 @@
         <v>37</v>
       </c>
       <c r="D36" s="29">
-        <f t="shared" ref="D36:K37" si="264">+D4/$K$11</f>
+        <f t="shared" ref="D36:K37" si="263">+D4/$K$11</f>
         <v>0.19545186328355499</v>
       </c>
       <c r="E36" s="29">
+        <f t="shared" si="263"/>
+        <v>0.27025554899913756</v>
+      </c>
+      <c r="F36" s="29">
+        <f t="shared" si="263"/>
+        <v>0.34208615133221371</v>
+      </c>
+      <c r="G36" s="29">
+        <f t="shared" si="263"/>
+        <v>0.4401071217829422</v>
+      </c>
+      <c r="H36" s="29">
+        <f t="shared" si="263"/>
+        <v>0.51300440288684124</v>
+      </c>
+      <c r="I36" s="29">
+        <f t="shared" si="263"/>
+        <v>0.62738867958785349</v>
+      </c>
+      <c r="J36" s="29">
+        <f t="shared" si="263"/>
+        <v>0.73886795878534794</v>
+      </c>
+      <c r="K36" s="29">
+        <f t="shared" si="263"/>
+        <v>0.77515773228632379</v>
+      </c>
+      <c r="L36" s="29">
+        <f t="shared" ref="L36:N36" si="264">+L4/$K$11</f>
+        <v>0.76809949616449547</v>
+      </c>
+      <c r="M36" s="29">
         <f t="shared" si="264"/>
-        <v>0.27025554899913756</v>
-      </c>
-      <c r="F36" s="29">
+        <v>0.97653306704189546</v>
+      </c>
+      <c r="N36" s="10">
         <f t="shared" si="264"/>
-        <v>0.34208615133221371</v>
-      </c>
-      <c r="G36" s="29">
-        <f t="shared" si="264"/>
-        <v>0.4401071217829422</v>
-      </c>
-      <c r="H36" s="29">
-        <f t="shared" si="264"/>
-        <v>0.51300440288684124</v>
-      </c>
-      <c r="I36" s="29">
-        <f t="shared" si="264"/>
-        <v>0.62738867958785349</v>
-      </c>
-      <c r="J36" s="29">
-        <f t="shared" si="264"/>
-        <v>0.73886795878534794</v>
-      </c>
-      <c r="K36" s="29">
-        <f t="shared" si="264"/>
-        <v>0.77515773228632379</v>
-      </c>
-      <c r="L36" s="29">
-        <f t="shared" ref="L36:N36" si="265">+L4/$K$11</f>
-        <v>0.76809949616449547</v>
-      </c>
-      <c r="M36" s="29">
-        <f t="shared" si="265"/>
-        <v>0.97653306704189546</v>
-      </c>
-      <c r="N36" s="10">
-        <f t="shared" si="265"/>
         <v>0</v>
       </c>
     </row>
@@ -6272,47 +6277,47 @@
         <v>38</v>
       </c>
       <c r="D37" s="29">
-        <f t="shared" si="264"/>
+        <f t="shared" si="263"/>
         <v>3.8831646316553947E-2</v>
       </c>
       <c r="E37" s="29">
-        <f t="shared" si="264"/>
+        <f t="shared" si="263"/>
         <v>5.9143933548182107E-2</v>
       </c>
       <c r="F37" s="29">
-        <f t="shared" si="264"/>
+        <f t="shared" si="263"/>
         <v>7.5598020970450722E-2</v>
       </c>
       <c r="G37" s="29">
-        <f t="shared" si="264"/>
+        <f t="shared" si="263"/>
         <v>7.1966774091053509E-2</v>
       </c>
       <c r="H37" s="29">
-        <f t="shared" si="264"/>
+        <f t="shared" si="263"/>
         <v>8.3246334710181114E-2</v>
       </c>
       <c r="I37" s="29">
-        <f t="shared" si="264"/>
+        <f t="shared" si="263"/>
         <v>7.0968181199219285E-2</v>
       </c>
       <c r="J37" s="29">
-        <f t="shared" si="264"/>
+        <f t="shared" si="263"/>
         <v>6.8630566020607325E-2</v>
       </c>
       <c r="K37" s="29">
-        <f t="shared" si="264"/>
+        <f t="shared" si="263"/>
         <v>0.1125005673823249</v>
       </c>
       <c r="L37" s="29">
-        <f t="shared" ref="L37:N37" si="266">+L5/$K$11</f>
+        <f t="shared" ref="L37:N37" si="265">+L5/$K$11</f>
         <v>0.16458626480867869</v>
       </c>
       <c r="M37" s="29">
-        <f t="shared" si="266"/>
+        <f t="shared" si="265"/>
         <v>0.18580636376015613</v>
       </c>
       <c r="N37" s="10">
-        <f t="shared" si="266"/>
+        <f t="shared" si="265"/>
         <v>0</v>
       </c>
     </row>
@@ -6321,47 +6326,47 @@
         <v>39</v>
       </c>
       <c r="D38" s="29">
-        <f t="shared" ref="D38" si="267">+D6/$K$11</f>
+        <f t="shared" ref="D38" si="266">+D6/$K$11</f>
         <v>0.23428350960010894</v>
       </c>
       <c r="E38" s="29">
-        <f t="shared" ref="E38:F38" si="268">+E6/$K$11</f>
+        <f t="shared" ref="E38:F38" si="267">+E6/$K$11</f>
         <v>0.32939948254731971</v>
       </c>
       <c r="F38" s="29">
-        <f t="shared" si="268"/>
+        <f t="shared" si="267"/>
         <v>0.41768417230266441</v>
       </c>
       <c r="G38" s="29">
-        <f t="shared" ref="G38" si="269">+G6/$K$11</f>
+        <f t="shared" ref="G38" si="268">+G6/$K$11</f>
         <v>0.51207389587399577</v>
       </c>
       <c r="H38" s="29">
-        <f t="shared" ref="H38" si="270">+H6/$K$11</f>
+        <f t="shared" ref="H38" si="269">+H6/$K$11</f>
         <v>0.59625073759702241</v>
       </c>
       <c r="I38" s="29">
-        <f t="shared" ref="I38:K42" si="271">+I6/$K$11</f>
+        <f t="shared" ref="I38:K42" si="270">+I6/$K$11</f>
         <v>0.69835686078707271</v>
       </c>
       <c r="J38" s="29">
-        <f t="shared" ref="J38" si="272">+J6/$K$11</f>
+        <f t="shared" ref="J38" si="271">+J6/$K$11</f>
         <v>0.8074985248059553</v>
       </c>
       <c r="K38" s="29">
-        <f t="shared" si="271"/>
+        <f t="shared" si="270"/>
         <v>0.88765829966864873</v>
       </c>
       <c r="L38" s="29">
-        <f t="shared" ref="L38:N38" si="273">+L6/$K$11</f>
+        <f t="shared" ref="L38:N38" si="272">+L6/$K$11</f>
         <v>0.93268576097317413</v>
       </c>
       <c r="M38" s="29">
-        <f t="shared" si="273"/>
+        <f t="shared" si="272"/>
         <v>1.1623394308020516</v>
       </c>
       <c r="N38" s="10">
-        <f t="shared" si="273"/>
+        <f t="shared" si="272"/>
         <v>0</v>
       </c>
     </row>
@@ -6370,47 +6375,47 @@
         <v>40</v>
       </c>
       <c r="D39" s="29">
-        <f t="shared" ref="D39" si="274">+D7/$K$11</f>
+        <f t="shared" ref="D39" si="273">+D7/$K$11</f>
         <v>5.6420498388634201E-2</v>
       </c>
       <c r="E39" s="29">
-        <f t="shared" ref="E39:F39" si="275">+E7/$K$11</f>
+        <f t="shared" ref="E39:F39" si="274">+E7/$K$11</f>
         <v>6.481775679724025E-2</v>
       </c>
       <c r="F39" s="29">
-        <f t="shared" si="275"/>
+        <f t="shared" si="274"/>
         <v>6.5022014434206341E-2</v>
       </c>
       <c r="G39" s="29">
-        <f t="shared" ref="G39" si="276">+G7/$K$11</f>
+        <f t="shared" ref="G39" si="275">+G7/$K$11</f>
         <v>6.0074440561027641E-2</v>
       </c>
       <c r="H39" s="29">
-        <f t="shared" ref="H39" si="277">+H7/$K$11</f>
+        <f t="shared" ref="H39" si="276">+H7/$K$11</f>
         <v>6.5362443829149838E-2</v>
       </c>
       <c r="I39" s="29">
-        <f t="shared" si="271"/>
+        <f t="shared" si="270"/>
         <v>7.4417865734646635E-2</v>
       </c>
       <c r="J39" s="29">
-        <f t="shared" ref="J39" si="278">+J7/$K$11</f>
+        <f t="shared" ref="J39" si="277">+J7/$K$11</f>
         <v>5.7736825382415688E-2</v>
       </c>
       <c r="K39" s="29">
-        <f t="shared" si="271"/>
+        <f t="shared" si="270"/>
         <v>8.5402387544823211E-2</v>
       </c>
       <c r="L39" s="29">
-        <f t="shared" ref="L39:N39" si="279">+L7/$K$11</f>
+        <f t="shared" ref="L39:N39" si="278">+L7/$K$11</f>
         <v>9.7294721074849072E-2</v>
       </c>
       <c r="M39" s="29">
-        <f t="shared" si="279"/>
+        <f t="shared" si="278"/>
         <v>9.6795424628931953E-2</v>
       </c>
       <c r="N39" s="10">
-        <f t="shared" si="279"/>
+        <f t="shared" si="278"/>
         <v>0</v>
       </c>
     </row>
@@ -6419,47 +6424,47 @@
         <v>41</v>
       </c>
       <c r="D40" s="29">
-        <f t="shared" ref="D40" si="280">+D8/$K$11</f>
+        <f t="shared" ref="D40" si="279">+D8/$K$11</f>
         <v>8.6015160455721485E-3</v>
       </c>
       <c r="E40" s="29">
-        <f t="shared" ref="E40:F40" si="281">+E8/$K$11</f>
+        <f t="shared" ref="E40:F40" si="280">+E8/$K$11</f>
         <v>9.4412418864327531E-3</v>
       </c>
       <c r="F40" s="29">
-        <f t="shared" si="281"/>
+        <f t="shared" si="280"/>
         <v>1.0507920657255684E-2</v>
       </c>
       <c r="G40" s="29">
-        <f t="shared" ref="G40" si="282">+G8/$K$11</f>
+        <f t="shared" ref="G40" si="281">+G8/$K$11</f>
         <v>9.6908901093913126E-3</v>
       </c>
       <c r="H40" s="29">
-        <f t="shared" ref="H40" si="283">+H8/$K$11</f>
+        <f t="shared" ref="H40" si="282">+H8/$K$11</f>
         <v>1.0303663020289592E-2</v>
       </c>
       <c r="I40" s="29">
-        <f t="shared" si="271"/>
+        <f t="shared" si="270"/>
         <v>1.1029912396169034E-2</v>
       </c>
       <c r="J40" s="29">
-        <f t="shared" ref="J40" si="284">+J8/$K$11</f>
+        <f t="shared" ref="J40" si="283">+J8/$K$11</f>
         <v>1.1597294721074848E-2</v>
       </c>
       <c r="K40" s="29">
-        <f t="shared" si="271"/>
+        <f t="shared" si="270"/>
         <v>1.1551904135082385E-2</v>
       </c>
       <c r="L40" s="29">
-        <f t="shared" ref="L40:N40" si="285">+L8/$K$11</f>
+        <f t="shared" ref="L40:N40" si="284">+L8/$K$11</f>
         <v>1.3639871090735781E-2</v>
       </c>
       <c r="M40" s="29">
-        <f t="shared" si="285"/>
+        <f t="shared" si="284"/>
         <v>1.7248422677136763E-2</v>
       </c>
       <c r="N40" s="10">
-        <f t="shared" si="285"/>
+        <f t="shared" si="284"/>
         <v>0</v>
       </c>
     </row>
@@ -6468,47 +6473,47 @@
         <v>42</v>
       </c>
       <c r="D41" s="29">
-        <f t="shared" ref="D41" si="286">+D9/$K$11</f>
+        <f t="shared" ref="D41" si="285">+D9/$K$11</f>
         <v>5.741909128046843E-3</v>
       </c>
       <c r="E41" s="29">
-        <f t="shared" ref="E41:F41" si="287">+E9/$K$11</f>
+        <f t="shared" ref="E41:F41" si="286">+E9/$K$11</f>
         <v>5.923471472016704E-3</v>
       </c>
       <c r="F41" s="29">
-        <f t="shared" si="287"/>
+        <f t="shared" si="286"/>
         <v>6.3773773319413555E-3</v>
       </c>
       <c r="G41" s="29">
-        <f t="shared" ref="G41" si="288">+G9/$K$11</f>
+        <f t="shared" ref="G41" si="287">+G9/$K$11</f>
         <v>7.4667513957605196E-3</v>
       </c>
       <c r="H41" s="29">
-        <f t="shared" ref="H41" si="289">+H9/$K$11</f>
+        <f t="shared" ref="H41" si="288">+H9/$K$11</f>
         <v>7.8525713766964735E-3</v>
       </c>
       <c r="I41" s="29">
-        <f t="shared" si="271"/>
+        <f t="shared" si="270"/>
         <v>1.019018655530843E-2</v>
       </c>
       <c r="J41" s="29">
-        <f t="shared" ref="J41" si="290">+J9/$K$11</f>
+        <f t="shared" ref="J41" si="289">+J9/$K$11</f>
         <v>1.2936317007852572E-2</v>
       </c>
       <c r="K41" s="29">
-        <f t="shared" si="271"/>
+        <f t="shared" si="270"/>
         <v>1.2868231128863874E-2</v>
       </c>
       <c r="L41" s="29">
-        <f t="shared" ref="L41:N41" si="291">+L9/$K$11</f>
+        <f t="shared" ref="L41:N41" si="290">+L9/$K$11</f>
         <v>1.3299441695792292E-2</v>
       </c>
       <c r="M41" s="29">
-        <f t="shared" si="291"/>
+        <f t="shared" si="290"/>
         <v>1.3435613453769688E-2</v>
       </c>
       <c r="N41" s="10">
-        <f t="shared" si="291"/>
+        <f t="shared" si="290"/>
         <v>0</v>
       </c>
     </row>
@@ -6517,47 +6522,47 @@
         <v>43</v>
       </c>
       <c r="D42" s="29">
-        <f t="shared" ref="D42" si="292">+D10/$K$11</f>
+        <f t="shared" ref="D42" si="291">+D10/$K$11</f>
         <v>1.4978893377513504E-3</v>
       </c>
       <c r="E42" s="29">
-        <f t="shared" ref="E42:F42" si="293">+E10/$K$11</f>
+        <f t="shared" ref="E42:F42" si="292">+E10/$K$11</f>
         <v>1.6567563887249785E-3</v>
       </c>
       <c r="F42" s="29">
-        <f t="shared" si="293"/>
+        <f t="shared" si="292"/>
         <v>2.0425763696609324E-3</v>
       </c>
       <c r="G42" s="29">
-        <f t="shared" ref="G42" si="294">+G10/$K$11</f>
+        <f t="shared" ref="G42" si="293">+G10/$K$11</f>
         <v>1.7702328537061414E-3</v>
       </c>
       <c r="H42" s="29">
-        <f t="shared" ref="H42" si="295">+H10/$K$11</f>
+        <f t="shared" ref="H42" si="294">+H10/$K$11</f>
         <v>1.9971857836684672E-3</v>
       </c>
       <c r="I42" s="29">
-        <f t="shared" si="271"/>
+        <f t="shared" si="270"/>
         <v>2.2014434206345606E-3</v>
       </c>
       <c r="J42" s="29">
-        <f t="shared" ref="J42" si="296">+J10/$K$11</f>
+        <f t="shared" ref="J42" si="295">+J10/$K$11</f>
         <v>2.8596069175253051E-3</v>
       </c>
       <c r="K42" s="29">
-        <f t="shared" si="271"/>
+        <f t="shared" si="270"/>
         <v>2.5191775225818164E-3</v>
       </c>
       <c r="L42" s="29">
-        <f t="shared" ref="L42:N42" si="297">+L10/$K$11</f>
+        <f t="shared" ref="L42:N42" si="296">+L10/$K$11</f>
         <v>3.9262856883482368E-3</v>
       </c>
       <c r="M42" s="29">
-        <f t="shared" si="297"/>
+        <f t="shared" si="296"/>
         <v>3.9489809813444687E-3</v>
       </c>
       <c r="N42" s="10">
-        <f t="shared" si="297"/>
+        <f t="shared" si="296"/>
         <v>0</v>
       </c>
     </row>
@@ -6570,35 +6575,35 @@
         <v>0.64627363737486099</v>
       </c>
       <c r="D44" s="29">
-        <f t="shared" ref="D44:J44" si="298">(D11-D12)/D11</f>
+        <f t="shared" ref="D44:J44" si="297">(D11-D12)/D11</f>
         <v>0.7005256533649219</v>
       </c>
       <c r="E44" s="29">
-        <f t="shared" si="298"/>
+        <f t="shared" si="297"/>
         <v>0.73951434878587197</v>
       </c>
       <c r="F44" s="29">
-        <f t="shared" si="298"/>
+        <f t="shared" si="297"/>
         <v>0.75967063294575399</v>
       </c>
       <c r="G44" s="29">
-        <f t="shared" si="298"/>
+        <f t="shared" si="297"/>
         <v>0.78352019659038552</v>
       </c>
       <c r="H44" s="29">
-        <f t="shared" si="298"/>
+        <f t="shared" si="297"/>
         <v>0.75146471371504664</v>
       </c>
       <c r="I44" s="29">
-        <f t="shared" si="298"/>
+        <f t="shared" si="297"/>
         <v>0.74556752750698363</v>
       </c>
       <c r="J44" s="29">
-        <f t="shared" si="298"/>
+        <f t="shared" si="297"/>
         <v>0.73026365970862683</v>
       </c>
       <c r="K44" s="29">
-        <f t="shared" ref="K44" si="299">(K11-K12)/K11</f>
+        <f t="shared" ref="K44" si="298">(K11-K12)/K11</f>
         <v>0.60523807362353044</v>
       </c>
       <c r="L44" s="29">
@@ -6606,76 +6611,76 @@
         <v>0.72423678411740799</v>
       </c>
       <c r="M44" s="29">
-        <f t="shared" ref="M44:N44" si="300">(M11-M12)/M11</f>
+        <f t="shared" ref="M44:N44" si="299">(M11-M12)/M11</f>
         <v>0.7341157071185489</v>
       </c>
       <c r="N44" s="10">
+        <f t="shared" si="299"/>
+        <v>0.74</v>
+      </c>
+      <c r="V44" s="10">
+        <f t="shared" ref="V44:AJ44" si="300">(V11-V12)/V11</f>
+        <v>0.61989375343469499</v>
+      </c>
+      <c r="W44" s="10">
         <f t="shared" si="300"/>
-        <v>0.74</v>
-      </c>
-      <c r="V44" s="10">
-        <f t="shared" ref="V44:AJ44" si="301">(V11-V12)/V11</f>
-        <v>0.61989375343469499</v>
-      </c>
-      <c r="W44" s="10">
-        <f t="shared" si="301"/>
         <v>0.62344827586206897</v>
       </c>
       <c r="X44" s="10">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.64929033216913135</v>
       </c>
       <c r="Y44" s="10">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.56928894490991322</v>
       </c>
       <c r="Z44" s="10">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.72717573290436954</v>
       </c>
       <c r="AA44" s="10">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.74988697058169917</v>
       </c>
       <c r="AB44" s="10">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.70705931554289958</v>
       </c>
       <c r="AC44" s="10">
-        <f t="shared" si="301"/>
-        <v>0.70705931554289969</v>
+        <f t="shared" si="300"/>
+        <v>0.70705931554289958</v>
       </c>
       <c r="AD44" s="10">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.70705931554289958</v>
       </c>
       <c r="AE44" s="10">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.70705931554289958</v>
       </c>
       <c r="AF44" s="10">
-        <f t="shared" si="301"/>
-        <v>0.70705931554289969</v>
+        <f t="shared" si="300"/>
+        <v>0.70705931554289958</v>
       </c>
       <c r="AG44" s="10">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
+        <v>0.70705931554289947</v>
+      </c>
+      <c r="AH44" s="10">
+        <f t="shared" si="300"/>
         <v>0.70705931554289958</v>
       </c>
-      <c r="AH44" s="10">
-        <f t="shared" si="301"/>
-        <v>0.70705931554289969</v>
-      </c>
       <c r="AI44" s="10">
-        <f t="shared" si="301"/>
-        <v>0.70705931554289969</v>
+        <f t="shared" si="300"/>
+        <v>0.70705931554289958</v>
       </c>
       <c r="AJ44" s="10">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v>0.70705931554289958</v>
       </c>
       <c r="AK44" s="10">
-        <f t="shared" ref="AK44" si="302">(AK11-AK12)/AK11</f>
-        <v>0.70705931554289969</v>
+        <f t="shared" ref="AK44" si="301">(AK11-AK12)/AK11</f>
+        <v>0.70705931554289958</v>
       </c>
     </row>
     <row r="45" spans="2:37" x14ac:dyDescent="0.2">
@@ -6687,112 +6692,112 @@
         <v>0.29755283648498332</v>
       </c>
       <c r="D45" s="29">
-        <f t="shared" ref="D45:J45" si="303">+D15/D11</f>
+        <f t="shared" ref="D45:J45" si="302">+D15/D11</f>
         <v>0.50344265936181243</v>
       </c>
       <c r="E45" s="29">
-        <f t="shared" si="303"/>
+        <f t="shared" si="302"/>
         <v>0.5748896247240618</v>
       </c>
       <c r="F45" s="29">
-        <f t="shared" si="303"/>
+        <f t="shared" si="302"/>
         <v>0.61597973125820027</v>
       </c>
       <c r="G45" s="29">
-        <f t="shared" si="303"/>
+        <f t="shared" si="302"/>
         <v>0.64924742743050223</v>
       </c>
       <c r="H45" s="29">
-        <f t="shared" si="303"/>
+        <f t="shared" si="302"/>
         <v>0.62057256990679099</v>
       </c>
       <c r="I45" s="29">
-        <f t="shared" si="303"/>
+        <f t="shared" si="302"/>
         <v>0.62336810900176731</v>
       </c>
       <c r="J45" s="29">
-        <f t="shared" si="303"/>
+        <f t="shared" si="302"/>
         <v>0.61104472299204193</v>
       </c>
       <c r="K45" s="29">
-        <f t="shared" ref="K45" si="304">+K15/K11</f>
+        <f t="shared" ref="K45" si="303">+K15/K11</f>
         <v>0.49108074985248057</v>
       </c>
       <c r="L45" s="29">
-        <f t="shared" ref="L45:N45" si="305">+L15/L11</f>
+        <f t="shared" ref="L45:N45" si="304">+L15/L11</f>
         <v>0.60843334830883766</v>
       </c>
       <c r="M45" s="29">
+        <f t="shared" si="304"/>
+        <v>0.63168789250254365</v>
+      </c>
+      <c r="N45" s="10">
+        <f t="shared" si="304"/>
+        <v>0.63692307692307693</v>
+      </c>
+      <c r="V45" s="10">
+        <f t="shared" ref="V45:AJ45" si="305">+V15/V11</f>
+        <v>0.2606704524638212</v>
+      </c>
+      <c r="W45" s="10">
         <f t="shared" si="305"/>
-        <v>0.63168789250254365</v>
-      </c>
-      <c r="N45" s="10">
+        <v>0.27178410794602698</v>
+      </c>
+      <c r="X45" s="10">
         <f t="shared" si="305"/>
-        <v>0.63692307692307693</v>
-      </c>
-      <c r="V45" s="10">
-        <f t="shared" ref="V45:AJ45" si="306">+V15/V11</f>
-        <v>0.2606704524638212</v>
-      </c>
-      <c r="W45" s="10">
-        <f t="shared" si="306"/>
-        <v>0.27178410794602698</v>
-      </c>
-      <c r="X45" s="10">
-        <f t="shared" si="306"/>
         <v>0.37307720888756779</v>
       </c>
       <c r="Y45" s="10">
-        <f t="shared" si="306"/>
+        <f t="shared" si="305"/>
         <v>0.20675465262845702</v>
       </c>
       <c r="Z45" s="10">
-        <f t="shared" si="306"/>
+        <f t="shared" si="305"/>
         <v>0.54121663766783756</v>
       </c>
       <c r="AA45" s="10">
-        <f t="shared" si="306"/>
+        <f t="shared" si="305"/>
         <v>0.62417526839697468</v>
       </c>
       <c r="AB45" s="10">
-        <f t="shared" si="306"/>
+        <f t="shared" si="305"/>
         <v>0.59906677756318982</v>
       </c>
       <c r="AC45" s="10">
-        <f t="shared" si="306"/>
+        <f t="shared" si="305"/>
+        <v>0.59906677756318982</v>
+      </c>
+      <c r="AD45" s="10">
+        <f t="shared" si="305"/>
+        <v>0.59906677756318982</v>
+      </c>
+      <c r="AE45" s="10">
+        <f t="shared" si="305"/>
+        <v>0.59906677756318982</v>
+      </c>
+      <c r="AF45" s="10">
+        <f t="shared" si="305"/>
+        <v>0.59906677756318982</v>
+      </c>
+      <c r="AG45" s="10">
+        <f t="shared" si="305"/>
         <v>0.59906677756318993</v>
       </c>
-      <c r="AD45" s="10">
-        <f t="shared" si="306"/>
+      <c r="AH45" s="10">
+        <f t="shared" si="305"/>
+        <v>0.59906677756318982</v>
+      </c>
+      <c r="AI45" s="10">
+        <f t="shared" si="305"/>
         <v>0.59906677756318993</v>
       </c>
-      <c r="AE45" s="10">
-        <f t="shared" si="306"/>
+      <c r="AJ45" s="10">
+        <f t="shared" si="305"/>
         <v>0.59906677756318993</v>
       </c>
-      <c r="AF45" s="10">
-        <f t="shared" si="306"/>
-        <v>0.59906677756318993</v>
-      </c>
-      <c r="AG45" s="10">
-        <f t="shared" si="306"/>
-        <v>0.59906677756318993</v>
-      </c>
-      <c r="AH45" s="10">
-        <f t="shared" si="306"/>
-        <v>0.59906677756318993</v>
-      </c>
-      <c r="AI45" s="10">
-        <f t="shared" si="306"/>
-        <v>0.59906677756318993</v>
-      </c>
-      <c r="AJ45" s="10">
-        <f t="shared" si="306"/>
-        <v>0.59906677756318993</v>
-      </c>
       <c r="AK45" s="10">
-        <f t="shared" ref="AK45" si="307">+AK15/AK11</f>
-        <v>0.59906677756319004</v>
+        <f t="shared" ref="AK45" si="306">+AK15/AK11</f>
+        <v>0.59906677756318982</v>
       </c>
     </row>
     <row r="46" spans="2:37" x14ac:dyDescent="0.2">
@@ -7218,39 +7223,39 @@
         <v>54</v>
       </c>
       <c r="C59" s="25">
-        <f t="shared" ref="C59:K59" si="308">+SUM(C49:C58)</f>
+        <f t="shared" ref="C59:K59" si="307">+SUM(C49:C58)</f>
         <v>44460</v>
       </c>
       <c r="D59" s="25">
-        <f t="shared" si="308"/>
+        <f t="shared" si="307"/>
         <v>49555</v>
       </c>
       <c r="E59" s="25">
-        <f t="shared" si="308"/>
+        <f t="shared" si="307"/>
         <v>54148</v>
       </c>
       <c r="F59" s="25">
-        <f t="shared" si="308"/>
+        <f t="shared" si="307"/>
         <v>65728</v>
       </c>
       <c r="G59" s="25">
-        <f t="shared" si="308"/>
+        <f t="shared" si="307"/>
         <v>77072</v>
       </c>
       <c r="H59" s="25">
-        <f t="shared" si="308"/>
+        <f t="shared" si="307"/>
         <v>85227</v>
       </c>
       <c r="I59" s="25">
-        <f t="shared" si="308"/>
+        <f t="shared" si="307"/>
         <v>96013</v>
       </c>
       <c r="J59" s="25">
-        <f t="shared" si="308"/>
+        <f t="shared" si="307"/>
         <v>111601</v>
       </c>
       <c r="K59" s="25">
-        <f t="shared" si="308"/>
+        <f t="shared" si="307"/>
         <v>125254</v>
       </c>
       <c r="L59" s="25">
@@ -7524,47 +7529,47 @@
         <v>48</v>
       </c>
       <c r="C68" s="25">
-        <f t="shared" ref="C68:K68" si="309">+SUM(C61:C67)</f>
+        <f t="shared" ref="C68:K68" si="308">+SUM(C61:C67)</f>
         <v>44460</v>
       </c>
       <c r="D68" s="25">
+        <f t="shared" si="308"/>
+        <v>49555</v>
+      </c>
+      <c r="E68" s="25">
+        <f t="shared" si="308"/>
+        <v>54148</v>
+      </c>
+      <c r="F68" s="25">
+        <f t="shared" si="308"/>
+        <v>65728</v>
+      </c>
+      <c r="G68" s="25">
+        <f t="shared" si="308"/>
+        <v>77072</v>
+      </c>
+      <c r="H68" s="25">
+        <f t="shared" si="308"/>
+        <v>85227</v>
+      </c>
+      <c r="I68" s="25">
+        <f t="shared" si="308"/>
+        <v>96013</v>
+      </c>
+      <c r="J68" s="25">
+        <f t="shared" si="308"/>
+        <v>111601</v>
+      </c>
+      <c r="K68" s="25">
+        <f t="shared" si="308"/>
+        <v>125254</v>
+      </c>
+      <c r="L68" s="25">
+        <f t="shared" ref="L68:M68" si="309">+SUM(L61:L67)</f>
+        <v>140740</v>
+      </c>
+      <c r="M68" s="25">
         <f t="shared" si="309"/>
-        <v>49555</v>
-      </c>
-      <c r="E68" s="25">
-        <f t="shared" si="309"/>
-        <v>54148</v>
-      </c>
-      <c r="F68" s="25">
-        <f t="shared" si="309"/>
-        <v>65728</v>
-      </c>
-      <c r="G68" s="25">
-        <f t="shared" si="309"/>
-        <v>77072</v>
-      </c>
-      <c r="H68" s="25">
-        <f t="shared" si="309"/>
-        <v>85227</v>
-      </c>
-      <c r="I68" s="25">
-        <f t="shared" si="309"/>
-        <v>96013</v>
-      </c>
-      <c r="J68" s="25">
-        <f t="shared" si="309"/>
-        <v>111601</v>
-      </c>
-      <c r="K68" s="25">
-        <f t="shared" si="309"/>
-        <v>125254</v>
-      </c>
-      <c r="L68" s="25">
-        <f t="shared" ref="L68:M68" si="310">+SUM(L61:L67)</f>
-        <v>140740</v>
-      </c>
-      <c r="M68" s="25">
-        <f t="shared" si="310"/>
         <v>161148</v>
       </c>
     </row>
@@ -7577,43 +7582,43 @@
         <v>10954</v>
       </c>
       <c r="D70" s="25">
-        <f t="shared" ref="D70:K70" si="311">SUM(D63:D64)</f>
+        <f t="shared" ref="D70:K70" si="310">SUM(D63:D64)</f>
         <v>9705</v>
       </c>
       <c r="E70" s="25">
+        <f t="shared" si="310"/>
+        <v>9706</v>
+      </c>
+      <c r="F70" s="25">
+        <f t="shared" si="310"/>
+        <v>9709</v>
+      </c>
+      <c r="G70" s="25">
+        <f t="shared" si="310"/>
+        <v>9710</v>
+      </c>
+      <c r="H70" s="25">
+        <f t="shared" si="310"/>
+        <v>8461</v>
+      </c>
+      <c r="I70" s="25">
+        <f t="shared" si="310"/>
+        <v>8462</v>
+      </c>
+      <c r="J70" s="25">
+        <f t="shared" si="310"/>
+        <v>8463</v>
+      </c>
+      <c r="K70" s="25">
+        <f t="shared" si="310"/>
+        <v>8464</v>
+      </c>
+      <c r="L70" s="25">
+        <f t="shared" ref="L70:M70" si="311">SUM(L63:L64)</f>
+        <v>8466</v>
+      </c>
+      <c r="M70" s="25">
         <f t="shared" si="311"/>
-        <v>9706</v>
-      </c>
-      <c r="F70" s="25">
-        <f t="shared" si="311"/>
-        <v>9709</v>
-      </c>
-      <c r="G70" s="25">
-        <f t="shared" si="311"/>
-        <v>9710</v>
-      </c>
-      <c r="H70" s="25">
-        <f t="shared" si="311"/>
-        <v>8461</v>
-      </c>
-      <c r="I70" s="25">
-        <f t="shared" si="311"/>
-        <v>8462</v>
-      </c>
-      <c r="J70" s="25">
-        <f t="shared" si="311"/>
-        <v>8463</v>
-      </c>
-      <c r="K70" s="25">
-        <f t="shared" si="311"/>
-        <v>8464</v>
-      </c>
-      <c r="L70" s="25">
-        <f t="shared" ref="L70:M70" si="312">SUM(L63:L64)</f>
-        <v>8466</v>
-      </c>
-      <c r="M70" s="25">
-        <f t="shared" si="312"/>
         <v>8467</v>
       </c>
     </row>
@@ -7626,43 +7631,43 @@
         <v>15320</v>
       </c>
       <c r="D71" s="25">
-        <f t="shared" ref="D71:K71" si="313">+D49</f>
+        <f t="shared" ref="D71:K71" si="312">+D49</f>
         <v>16023</v>
       </c>
       <c r="E71" s="25">
+        <f t="shared" si="312"/>
+        <v>18281</v>
+      </c>
+      <c r="F71" s="25">
+        <f t="shared" si="312"/>
+        <v>25984</v>
+      </c>
+      <c r="G71" s="25">
+        <f t="shared" si="312"/>
+        <v>31438</v>
+      </c>
+      <c r="H71" s="25">
+        <f t="shared" si="312"/>
+        <v>34800</v>
+      </c>
+      <c r="I71" s="25">
+        <f t="shared" si="312"/>
+        <v>38487</v>
+      </c>
+      <c r="J71" s="25">
+        <f t="shared" si="312"/>
+        <v>43210</v>
+      </c>
+      <c r="K71" s="25">
+        <f t="shared" si="312"/>
+        <v>53691</v>
+      </c>
+      <c r="L71" s="25">
+        <f t="shared" ref="L71:M71" si="313">+L49</f>
+        <v>56791</v>
+      </c>
+      <c r="M71" s="25">
         <f t="shared" si="313"/>
-        <v>18281</v>
-      </c>
-      <c r="F71" s="25">
-        <f t="shared" si="313"/>
-        <v>25984</v>
-      </c>
-      <c r="G71" s="25">
-        <f t="shared" si="313"/>
-        <v>31438</v>
-      </c>
-      <c r="H71" s="25">
-        <f t="shared" si="313"/>
-        <v>34800</v>
-      </c>
-      <c r="I71" s="25">
-        <f t="shared" si="313"/>
-        <v>38487</v>
-      </c>
-      <c r="J71" s="25">
-        <f t="shared" si="313"/>
-        <v>43210</v>
-      </c>
-      <c r="K71" s="25">
-        <f t="shared" si="313"/>
-        <v>53691</v>
-      </c>
-      <c r="L71" s="25">
-        <f t="shared" ref="L71:M71" si="314">+L49</f>
-        <v>56791</v>
-      </c>
-      <c r="M71" s="25">
-        <f t="shared" si="314"/>
         <v>60608</v>
       </c>
     </row>
@@ -7675,43 +7680,43 @@
         <v>4366</v>
       </c>
       <c r="D72" s="25">
-        <f t="shared" ref="D72:K72" si="315">+D71-D70</f>
+        <f t="shared" ref="D72:K72" si="314">+D71-D70</f>
         <v>6318</v>
       </c>
       <c r="E72" s="25">
+        <f t="shared" si="314"/>
+        <v>8575</v>
+      </c>
+      <c r="F72" s="25">
+        <f t="shared" si="314"/>
+        <v>16275</v>
+      </c>
+      <c r="G72" s="25">
+        <f t="shared" si="314"/>
+        <v>21728</v>
+      </c>
+      <c r="H72" s="25">
+        <f t="shared" si="314"/>
+        <v>26339</v>
+      </c>
+      <c r="I72" s="25">
+        <f t="shared" si="314"/>
+        <v>30025</v>
+      </c>
+      <c r="J72" s="25">
+        <f t="shared" si="314"/>
+        <v>34747</v>
+      </c>
+      <c r="K72" s="25">
+        <f t="shared" si="314"/>
+        <v>45227</v>
+      </c>
+      <c r="L72" s="25">
+        <f t="shared" ref="L72:M72" si="315">+L71-L70</f>
+        <v>48325</v>
+      </c>
+      <c r="M72" s="25">
         <f t="shared" si="315"/>
-        <v>8575</v>
-      </c>
-      <c r="F72" s="25">
-        <f t="shared" si="315"/>
-        <v>16275</v>
-      </c>
-      <c r="G72" s="25">
-        <f t="shared" si="315"/>
-        <v>21728</v>
-      </c>
-      <c r="H72" s="25">
-        <f t="shared" si="315"/>
-        <v>26339</v>
-      </c>
-      <c r="I72" s="25">
-        <f t="shared" si="315"/>
-        <v>30025</v>
-      </c>
-      <c r="J72" s="25">
-        <f t="shared" si="315"/>
-        <v>34747</v>
-      </c>
-      <c r="K72" s="25">
-        <f t="shared" si="315"/>
-        <v>45227</v>
-      </c>
-      <c r="L72" s="25">
-        <f t="shared" ref="L72:M72" si="316">+L71-L70</f>
-        <v>48325</v>
-      </c>
-      <c r="M72" s="25">
-        <f t="shared" si="316"/>
         <v>52141</v>
       </c>
     </row>
@@ -7724,57 +7729,57 @@
         <v>18549</v>
       </c>
       <c r="D73" s="25">
-        <f t="shared" ref="D73:K73" si="317">+D67-D56-D55</f>
+        <f t="shared" ref="D73:K73" si="316">+D67-D56-D55</f>
         <v>21676</v>
       </c>
       <c r="E73" s="25">
+        <f t="shared" si="316"/>
+        <v>27584</v>
+      </c>
+      <c r="F73" s="25">
+        <f t="shared" si="316"/>
+        <v>37436</v>
+      </c>
+      <c r="G73" s="25">
+        <f t="shared" si="316"/>
+        <v>43703</v>
+      </c>
+      <c r="H73" s="25">
+        <f t="shared" si="316"/>
+        <v>52583</v>
+      </c>
+      <c r="I73" s="25">
+        <f t="shared" si="316"/>
+        <v>60337</v>
+      </c>
+      <c r="J73" s="25">
+        <f t="shared" si="316"/>
+        <v>73332</v>
+      </c>
+      <c r="K73" s="25">
+        <f t="shared" si="316"/>
+        <v>77576</v>
+      </c>
+      <c r="L73" s="25">
+        <f t="shared" ref="L73:M73" si="317">+L67-L56-L55</f>
+        <v>93621</v>
+      </c>
+      <c r="M73" s="25">
         <f t="shared" si="317"/>
-        <v>27584</v>
-      </c>
-      <c r="F73" s="25">
-        <f t="shared" si="317"/>
-        <v>37436</v>
-      </c>
-      <c r="G73" s="25">
-        <f t="shared" si="317"/>
-        <v>43703</v>
-      </c>
-      <c r="H73" s="25">
-        <f t="shared" si="317"/>
-        <v>52583</v>
-      </c>
-      <c r="I73" s="25">
-        <f t="shared" si="317"/>
-        <v>60337</v>
-      </c>
-      <c r="J73" s="25">
-        <f t="shared" si="317"/>
-        <v>73332</v>
-      </c>
-      <c r="K73" s="25">
-        <f t="shared" si="317"/>
-        <v>77576</v>
-      </c>
-      <c r="L73" s="25">
-        <f t="shared" ref="L73:M73" si="318">+L67-L56-L55</f>
-        <v>93621</v>
-      </c>
-      <c r="M73" s="25">
-        <f t="shared" si="318"/>
         <v>111700</v>
       </c>
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="H74" s="30">
-        <f t="shared" ref="H74:J74" si="319">SUM(E120:H120)/H73</f>
+        <f t="shared" ref="H74:J74" si="318">SUM(E120:H120)/H73</f>
         <v>0.63176311735732082</v>
       </c>
       <c r="I74" s="30">
-        <f t="shared" si="319"/>
+        <f t="shared" si="318"/>
         <v>0.82927556888807863</v>
       </c>
       <c r="J74" s="30">
-        <f t="shared" si="319"/>
+        <f t="shared" si="318"/>
         <v>0.89438444335351552</v>
       </c>
       <c r="K74" s="30">
@@ -7803,31 +7808,31 @@
         <v>209</v>
       </c>
       <c r="F76" s="25">
-        <f t="shared" ref="F76:L76" si="320">+F50/SUM(C11:F11) * 365</f>
+        <f t="shared" ref="F76:L76" si="319">+F50/SUM(C11:F11) * 365</f>
         <v>59.906683956534586</v>
       </c>
       <c r="G76" s="25">
-        <f t="shared" si="320"/>
+        <f t="shared" si="319"/>
         <v>56.575137262767313</v>
       </c>
       <c r="H76" s="25">
-        <f t="shared" si="320"/>
+        <f t="shared" si="319"/>
         <v>53.559762011068763</v>
       </c>
       <c r="I76" s="25">
-        <f t="shared" si="320"/>
+        <f t="shared" si="319"/>
         <v>57.014231607942151</v>
       </c>
       <c r="J76" s="25">
-        <f t="shared" si="320"/>
+        <f t="shared" si="319"/>
         <v>64.512785734537957</v>
       </c>
       <c r="K76" s="25">
-        <f t="shared" si="320"/>
+        <f t="shared" si="319"/>
         <v>54.393024273642396</v>
       </c>
       <c r="L76" s="25">
-        <f t="shared" si="320"/>
+        <f t="shared" si="319"/>
         <v>61.433499981842175</v>
       </c>
       <c r="M76" s="25">
@@ -7840,31 +7845,31 @@
         <v>210</v>
       </c>
       <c r="F77" s="25">
-        <f t="shared" ref="F77:L77" si="321">(+F51/SUM(C12:F12)) * 365</f>
+        <f t="shared" ref="F77:L77" si="320">(+F51/SUM(C12:F12)) * 365</f>
         <v>115.99362252572048</v>
       </c>
       <c r="G77" s="25">
-        <f t="shared" si="321"/>
+        <f t="shared" si="320"/>
         <v>108.56505199086989</v>
       </c>
       <c r="H77" s="25">
-        <f t="shared" si="321"/>
+        <f t="shared" si="320"/>
         <v>105.30666493775932</v>
       </c>
       <c r="I77" s="25">
-        <f t="shared" si="321"/>
+        <f t="shared" si="320"/>
         <v>102.17650501060639</v>
       </c>
       <c r="J77" s="25">
-        <f t="shared" si="321"/>
+        <f t="shared" si="320"/>
         <v>112.72404179049603</v>
       </c>
       <c r="K77" s="25">
-        <f t="shared" si="321"/>
+        <f t="shared" si="320"/>
         <v>93.175920711791875</v>
       </c>
       <c r="L77" s="25">
-        <f t="shared" si="321"/>
+        <f t="shared" si="320"/>
         <v>109.61942230875771</v>
       </c>
       <c r="M77" s="25">
@@ -7877,31 +7882,31 @@
         <v>211</v>
       </c>
       <c r="F78" s="25">
-        <f t="shared" ref="F78:L78" si="322">+(F61/SUM(C12:F12)) * 365</f>
+        <f t="shared" ref="F78:L78" si="321">+(F61/SUM(C12:F12)) * 365</f>
         <v>59.270501173214605</v>
       </c>
       <c r="G78" s="25">
-        <f t="shared" si="322"/>
+        <f t="shared" si="321"/>
         <v>50.265026629469943</v>
       </c>
       <c r="H78" s="25">
-        <f t="shared" si="322"/>
+        <f t="shared" si="321"/>
         <v>58.056708160442597</v>
       </c>
       <c r="I78" s="25">
-        <f t="shared" si="322"/>
+        <f t="shared" si="321"/>
         <v>71.459476263623728</v>
       </c>
       <c r="J78" s="25">
-        <f t="shared" si="322"/>
+        <f t="shared" si="321"/>
         <v>70.564355525598216</v>
       </c>
       <c r="K78" s="25">
-        <f t="shared" si="322"/>
+        <f t="shared" si="321"/>
         <v>60.272891091339112</v>
       </c>
       <c r="L78" s="25">
-        <f t="shared" si="322"/>
+        <f t="shared" si="321"/>
         <v>66.407595495694423</v>
       </c>
       <c r="M78" s="25">
@@ -7917,31 +7922,31 @@
       <c r="D79" s="32"/>
       <c r="E79" s="32"/>
       <c r="F79" s="32">
-        <f t="shared" ref="F79:L79" si="323">+SUM(F76:F77)-F78</f>
+        <f t="shared" ref="F79:L79" si="322">+SUM(F76:F77)-F78</f>
         <v>116.62980530904048</v>
       </c>
       <c r="G79" s="32">
-        <f t="shared" si="323"/>
+        <f t="shared" si="322"/>
         <v>114.87516262416726</v>
       </c>
       <c r="H79" s="32">
-        <f t="shared" si="323"/>
+        <f t="shared" si="322"/>
         <v>100.8097187883855</v>
       </c>
       <c r="I79" s="32">
-        <f t="shared" si="323"/>
+        <f t="shared" si="322"/>
         <v>87.731260354924828</v>
       </c>
       <c r="J79" s="32">
-        <f t="shared" si="323"/>
+        <f t="shared" si="322"/>
         <v>106.67247199943577</v>
       </c>
       <c r="K79" s="32">
-        <f t="shared" si="323"/>
+        <f t="shared" si="322"/>
         <v>87.296053894095138</v>
       </c>
       <c r="L79" s="32">
-        <f t="shared" si="323"/>
+        <f t="shared" si="322"/>
         <v>104.64532679490547</v>
       </c>
       <c r="M79" s="32">
@@ -8638,31 +8643,31 @@
         <v>78</v>
       </c>
       <c r="G120" s="25">
-        <f t="shared" ref="G120:M120" si="324">+G97+G103</f>
+        <f t="shared" ref="G120:M120" si="323">+G97+G103</f>
         <v>19708</v>
       </c>
       <c r="H120" s="25">
-        <f t="shared" si="324"/>
+        <f t="shared" si="323"/>
         <v>13512</v>
       </c>
       <c r="I120" s="25">
-        <f t="shared" si="324"/>
+        <f t="shared" si="323"/>
         <v>16816</v>
       </c>
       <c r="J120" s="25">
-        <f t="shared" si="324"/>
+        <f t="shared" si="323"/>
         <v>15551</v>
       </c>
       <c r="K120" s="25">
-        <f t="shared" si="324"/>
+        <f t="shared" si="323"/>
         <v>26187</v>
       </c>
       <c r="L120" s="25">
-        <f t="shared" si="324"/>
+        <f t="shared" si="323"/>
         <v>13471</v>
       </c>
       <c r="M120" s="25">
-        <f t="shared" si="324"/>
+        <f t="shared" si="323"/>
         <v>22113</v>
       </c>
     </row>
@@ -8671,31 +8676,31 @@
         <v>79</v>
       </c>
       <c r="G121" s="25">
-        <f t="shared" ref="G121:M121" si="325">+G21</f>
+        <f t="shared" ref="G121:M121" si="324">+G21</f>
         <v>14046</v>
       </c>
       <c r="H121" s="25">
-        <f t="shared" si="325"/>
+        <f t="shared" si="324"/>
         <v>16599</v>
       </c>
       <c r="I121" s="25">
-        <f t="shared" si="325"/>
+        <f t="shared" si="324"/>
         <v>19309</v>
       </c>
       <c r="J121" s="25">
-        <f t="shared" si="325"/>
+        <f t="shared" si="324"/>
         <v>32926</v>
       </c>
       <c r="K121" s="25">
-        <f t="shared" si="325"/>
+        <f t="shared" si="324"/>
         <v>18775</v>
       </c>
       <c r="L121" s="25">
-        <f t="shared" si="325"/>
+        <f t="shared" si="324"/>
         <v>26546</v>
       </c>
       <c r="M121" s="25">
-        <f t="shared" si="325"/>
+        <f t="shared" si="324"/>
         <v>31910</v>
       </c>
     </row>
@@ -8708,23 +8713,23 @@
         <v>-369</v>
       </c>
       <c r="H123" s="25">
-        <f t="shared" ref="H123:L123" si="326">+H103</f>
+        <f t="shared" ref="H123:L123" si="325">+H103</f>
         <v>-977</v>
       </c>
       <c r="I123" s="25">
-        <f t="shared" si="326"/>
+        <f t="shared" si="325"/>
         <v>-813</v>
       </c>
       <c r="J123" s="25">
-        <f t="shared" si="326"/>
+        <f t="shared" si="325"/>
         <v>-1077</v>
       </c>
       <c r="K123" s="25">
-        <f t="shared" si="326"/>
+        <f t="shared" si="325"/>
         <v>-1227</v>
       </c>
       <c r="L123" s="25">
-        <f t="shared" si="326"/>
+        <f t="shared" si="325"/>
         <v>-1894</v>
       </c>
     </row>
@@ -8737,23 +8742,23 @@
         <v>410</v>
       </c>
       <c r="H124" s="25">
-        <f t="shared" ref="H124:L124" si="327">+H87</f>
+        <f t="shared" ref="H124:L124" si="326">+H87</f>
         <v>433</v>
       </c>
       <c r="I124" s="25">
-        <f t="shared" si="327"/>
+        <f t="shared" si="326"/>
         <v>478</v>
       </c>
       <c r="J124" s="25">
-        <f t="shared" si="327"/>
+        <f t="shared" si="326"/>
         <v>543</v>
       </c>
       <c r="K124" s="25">
-        <f t="shared" si="327"/>
+        <f t="shared" si="326"/>
         <v>611</v>
       </c>
       <c r="L124" s="25">
-        <f t="shared" si="327"/>
+        <f t="shared" si="326"/>
         <v>668</v>
       </c>
     </row>
@@ -8823,27 +8828,27 @@
         <v>1300</v>
       </c>
       <c r="H129" s="32">
-        <f t="shared" ref="H129:M129" si="328">SUM(H127:H128)</f>
+        <f t="shared" ref="H129:M129" si="327">SUM(H127:H128)</f>
         <v>1423</v>
       </c>
       <c r="I129" s="32">
-        <f t="shared" si="328"/>
+        <f t="shared" si="327"/>
         <v>1587</v>
       </c>
       <c r="J129" s="32">
-        <f t="shared" si="328"/>
+        <f t="shared" si="327"/>
         <v>1751</v>
       </c>
       <c r="K129" s="32">
-        <f t="shared" si="328"/>
+        <f t="shared" si="327"/>
         <v>1760</v>
       </c>
       <c r="L129" s="32">
-        <f t="shared" si="328"/>
+        <f t="shared" si="327"/>
         <v>1918</v>
       </c>
       <c r="M129" s="32">
-        <f t="shared" si="328"/>
+        <f t="shared" si="327"/>
         <v>2449</v>
       </c>
     </row>
@@ -8905,81 +8910,81 @@
         <v>0.46</v>
       </c>
       <c r="D131" s="33">
-        <f t="shared" ref="D131:M131" si="329">+D130/D129</f>
+        <f t="shared" ref="D131:M131" si="328">+D130/D129</f>
         <v>0.44</v>
       </c>
       <c r="E131" s="33">
-        <f t="shared" si="329"/>
+        <f t="shared" si="328"/>
         <v>0.42</v>
       </c>
       <c r="F131" s="33">
-        <f t="shared" si="329"/>
+        <f t="shared" si="328"/>
         <v>0.4</v>
       </c>
       <c r="G131" s="33">
-        <f t="shared" si="329"/>
+        <f t="shared" si="328"/>
         <v>0.38</v>
       </c>
       <c r="H131" s="33">
-        <f t="shared" si="329"/>
+        <f t="shared" si="328"/>
         <v>0.37</v>
       </c>
       <c r="I131" s="33">
-        <f t="shared" si="329"/>
+        <f t="shared" si="328"/>
         <v>0.36999999999999994</v>
       </c>
       <c r="J131" s="33">
-        <f t="shared" si="329"/>
+        <f t="shared" si="328"/>
         <v>0.39</v>
       </c>
       <c r="K131" s="33">
-        <f t="shared" si="329"/>
+        <f t="shared" si="328"/>
         <v>0.39</v>
       </c>
       <c r="L131" s="33">
-        <f t="shared" si="329"/>
+        <f t="shared" si="328"/>
         <v>0.4</v>
       </c>
       <c r="M131" s="33">
-        <f t="shared" si="329"/>
+        <f t="shared" si="328"/>
         <v>0.4</v>
       </c>
     </row>
     <row r="132" spans="2:13" x14ac:dyDescent="0.2">
       <c r="D132" s="29">
-        <f t="shared" ref="D132:L132" si="330">+D129/C129-1</f>
+        <f t="shared" ref="D132:L132" si="329">+D129/C129-1</f>
         <v>0.1220657276995305</v>
       </c>
       <c r="E132" s="29">
-        <f t="shared" si="330"/>
+        <f t="shared" si="329"/>
         <v>0.24965132496513243</v>
       </c>
       <c r="F132" s="29">
-        <f t="shared" si="330"/>
+        <f t="shared" si="329"/>
         <v>0.2276785714285714</v>
       </c>
       <c r="G132" s="29">
-        <f t="shared" si="330"/>
+        <f t="shared" si="329"/>
         <v>0.18181818181818188</v>
       </c>
       <c r="H132" s="29">
-        <f t="shared" si="330"/>
+        <f t="shared" si="329"/>
         <v>9.4615384615384546E-2</v>
       </c>
       <c r="I132" s="29">
-        <f t="shared" si="330"/>
+        <f t="shared" si="329"/>
         <v>0.11524947294448351</v>
       </c>
       <c r="J132" s="29">
-        <f t="shared" si="330"/>
+        <f t="shared" si="329"/>
         <v>0.10333963453056083</v>
       </c>
       <c r="K132" s="29">
-        <f t="shared" si="330"/>
+        <f t="shared" si="329"/>
         <v>5.1399200456880845E-3</v>
       </c>
       <c r="L132" s="29">
-        <f t="shared" si="330"/>
+        <f t="shared" si="329"/>
         <v>8.9772727272727337E-2</v>
       </c>
       <c r="M132" s="29">
@@ -8992,39 +8997,39 @@
         <v>200</v>
       </c>
       <c r="D133" s="25">
-        <f t="shared" ref="D133:L133" si="331">+D129-C129</f>
+        <f t="shared" ref="D133:L133" si="330">+D129-C129</f>
         <v>78</v>
       </c>
       <c r="E133" s="25">
-        <f t="shared" si="331"/>
+        <f t="shared" si="330"/>
         <v>179</v>
       </c>
       <c r="F133" s="25">
-        <f t="shared" si="331"/>
+        <f t="shared" si="330"/>
         <v>204</v>
       </c>
       <c r="G133" s="25">
-        <f t="shared" si="331"/>
+        <f t="shared" si="330"/>
         <v>200</v>
       </c>
       <c r="H133" s="25">
-        <f t="shared" si="331"/>
+        <f t="shared" si="330"/>
         <v>123</v>
       </c>
       <c r="I133" s="25">
-        <f t="shared" si="331"/>
+        <f t="shared" si="330"/>
         <v>164</v>
       </c>
       <c r="J133" s="25">
-        <f t="shared" si="331"/>
+        <f t="shared" si="330"/>
         <v>164</v>
       </c>
       <c r="K133" s="25">
-        <f t="shared" si="331"/>
+        <f t="shared" si="330"/>
         <v>9</v>
       </c>
       <c r="L133" s="25">
-        <f t="shared" si="331"/>
+        <f t="shared" si="330"/>
         <v>158</v>
       </c>
       <c r="M133" s="34">

--- a/Semiconductor/NVDA.xlsx
+++ b/Semiconductor/NVDA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameelbrannon/Library/CloudStorage/Dropbox/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C3E322-F500-7941-98EA-F1C8E552939F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6004F3F5-5A14-8C44-BB22-B92968F279D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6940" yWindow="1640" windowWidth="44260" windowHeight="24640" activeTab="2" xr2:uid="{834EDAA3-D05C-5B48-B7D6-13D13D56A97E}"/>
+    <workbookView xWindow="22900" yWindow="1460" windowWidth="27800" windowHeight="24640" activeTab="2" xr2:uid="{834EDAA3-D05C-5B48-B7D6-13D13D56A97E}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="225">
   <si>
     <t>P</t>
   </si>
@@ -268,12 +268,6 @@
     <t>CFFF</t>
   </si>
   <si>
-    <t>Free Cash Flow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NI </t>
-  </si>
-  <si>
     <t>Press Release</t>
   </si>
   <si>
@@ -619,12 +613,6 @@
     <t>Colette Kress</t>
   </si>
   <si>
-    <t>Capex</t>
-  </si>
-  <si>
-    <t>Depre</t>
-  </si>
-  <si>
     <t>cRPO</t>
   </si>
   <si>
@@ -695,6 +683,36 @@
   </si>
   <si>
     <t>Upside</t>
+  </si>
+  <si>
+    <t>CFFO Less Capex</t>
+  </si>
+  <si>
+    <t>CFFO Less Capen, SBC, Depreciation</t>
+  </si>
+  <si>
+    <t>CFFO Less Capex, SBC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-marketable equity securities </t>
+  </si>
+  <si>
+    <t>Prepaid supply and capacity agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income tax recievable </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid royalties </t>
+  </si>
+  <si>
+    <t>Raw materials</t>
+  </si>
+  <si>
+    <t>WIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finished goods </t>
   </si>
 </sst>
 </file>
@@ -709,7 +727,7 @@
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="0&quot;E&quot;"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -806,6 +824,13 @@
       <i/>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF424242"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -948,7 +973,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1011,11 +1036,7 @@
     <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1028,16 +1049,12 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1045,7 +1062,6 @@
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1078,6 +1094,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1087,6 +1112,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF424242"/>
+      <color rgb="FF0096FF"/>
       <color rgb="FF0432FF"/>
     </mruColors>
   </colors>
@@ -1113,7 +1140,7 @@
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>46213</xdr:colOff>
-      <xdr:row>135</xdr:row>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>52631</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1163,7 +1190,7 @@
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>63500</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1552,7 +1579,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>1</v>
@@ -1570,7 +1597,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>2</v>
@@ -1580,7 +1607,7 @@
         <v>4422600</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.2">
@@ -1596,7 +1623,7 @@
         <v>Q325</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.2">
@@ -1615,7 +1642,7 @@
         <v>Q325</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.2">
@@ -1630,17 +1657,17 @@
         <v>4370459</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L9" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L10" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.2">
@@ -1649,7 +1676,7 @@
         <v>179422600</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.2">
@@ -1658,34 +1685,34 @@
         <v>7383.6460905349795</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L13" s="13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L14" s="13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.2">
       <c r="I15" s="9"/>
       <c r="L15" s="13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>16</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.2">
@@ -1693,13 +1720,13 @@
         <v>17</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I17" s="10">
         <v>45874</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
@@ -1707,7 +1734,7 @@
         <v>40400</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
@@ -1715,7 +1742,7 @@
         <v>45874</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.2">
@@ -1723,7 +1750,7 @@
         <v>45874</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
@@ -1731,13 +1758,13 @@
         <v>45853</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="I22" s="9"/>
       <c r="L22" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.2">
@@ -1745,267 +1772,267 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L25" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L26" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L27" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L28" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L29" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L30" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L31" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L33" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L34" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L36" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L37" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L38" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L39" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L42" s="15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L43" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L44" s="13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L45" s="13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L46" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L47" s="13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L48" s="14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="49" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L49" s="13" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="50" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L50" s="13" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="51" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L51" s="14" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="52" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L52" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="53" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L53" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="56" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L56" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="57" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L57" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="58" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L58" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="59" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L59" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="60" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L60" s="13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="61" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L61" s="13" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="62" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L62" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="63" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L63" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="64" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L64" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L65" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="68" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L68" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="69" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L69" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="70" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L70" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="71" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L71" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="72" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L72" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="73" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L73" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="74" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L74" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="75" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L75" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="76" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L76" s="13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="77" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L77" s="13" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="78" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L78" s="13" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="79" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L79" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="80" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L80" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="81" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L81" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="82" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L82" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="83" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L83" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="84" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L84" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="87" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L87" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2032,42 +2059,42 @@
   <sheetData>
     <row r="3" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B3" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B5" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B6" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B7" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B8" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B9" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B10" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B11" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.2">
@@ -2075,76 +2102,76 @@
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B14" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B15" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B16" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B17" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B20" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B21" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B22" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B25" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B26" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2178,8 +2205,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3324D012-FEF5-4D43-9CF5-2CE00AF5A8E7}">
-  <dimension ref="B2:ID132"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <dimension ref="B2:ID136"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" outlineLevelRow="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="27" customWidth="1"/>
     <col min="2" max="2" width="39.33203125" style="27" bestFit="1" customWidth="1"/>
@@ -2187,7 +2214,9 @@
     <col min="5" max="6" width="8.1640625" style="26" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.5" style="26" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="8.1640625" style="26" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="8.6640625" style="26" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="26" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.6640625" style="26" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.6640625" style="26" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7.5" style="26" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="10.83203125" style="27"/>
     <col min="17" max="20" width="5.83203125" style="26" bestFit="1" customWidth="1"/>
@@ -2202,7 +2231,7 @@
   <sheetData>
     <row r="2" spans="2:238" s="16" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B2" s="16" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C2" s="17"/>
       <c r="D2" s="17">
@@ -2228,9 +2257,11 @@
         <v>45774</v>
       </c>
       <c r="L2" s="17">
-        <v>45896</v>
-      </c>
-      <c r="M2" s="17"/>
+        <v>45865</v>
+      </c>
+      <c r="M2" s="17">
+        <v>46321</v>
+      </c>
       <c r="N2" s="17"/>
       <c r="Q2" s="17"/>
       <c r="R2" s="17"/>
@@ -2298,7 +2329,7 @@
         <v>19</v>
       </c>
       <c r="N3" s="20" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="Q3" s="20">
         <v>2015</v>
@@ -2308,7 +2339,7 @@
         <v>2016</v>
       </c>
       <c r="S3" s="20">
-        <f t="shared" ref="S3:AL3" si="0">+R3+1</f>
+        <f t="shared" ref="S3:AA3" si="0">+R3+1</f>
         <v>2017</v>
       </c>
       <c r="T3" s="20">
@@ -3776,203 +3807,85 @@
       <c r="AL11" s="31"/>
     </row>
     <row r="12" spans="2:238" x14ac:dyDescent="0.15">
-      <c r="B12" s="32" t="s">
-        <v>215</v>
-      </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="34">
+      <c r="B12" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="D12" s="32">
         <f t="shared" ref="D12:L12" si="204">+D11/C11-1</f>
         <v>0.87805895439377091</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="32">
         <f t="shared" si="204"/>
         <v>0.34152661582882948</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="32">
         <f t="shared" si="204"/>
         <v>0.21981236203090515</v>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="32">
         <f t="shared" si="204"/>
         <v>0.17830158801972584</v>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="32">
         <f t="shared" si="204"/>
         <v>0.1534326524343419</v>
       </c>
-      <c r="I12" s="34">
+      <c r="I12" s="32">
         <f t="shared" si="204"/>
         <v>0.16784287616511318</v>
       </c>
-      <c r="J12" s="34">
+      <c r="J12" s="32">
         <f t="shared" si="204"/>
         <v>0.12111624194743742</v>
       </c>
-      <c r="K12" s="34">
+      <c r="K12" s="32">
         <f t="shared" si="204"/>
         <v>0.12028679667437903</v>
       </c>
-      <c r="L12" s="34">
+      <c r="L12" s="32">
         <f t="shared" si="204"/>
         <v>6.0846080522899637E-2</v>
       </c>
-      <c r="M12" s="34">
+      <c r="M12" s="32">
         <f>+M11/L11-1</f>
         <v>0.21956228740132211</v>
       </c>
-      <c r="N12" s="33"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="33"/>
-      <c r="S12" s="33"/>
-      <c r="T12" s="33"/>
-      <c r="U12" s="33"/>
-      <c r="V12" s="33"/>
-      <c r="W12" s="33"/>
-      <c r="X12" s="33"/>
-      <c r="Y12" s="33"/>
-      <c r="Z12" s="33"/>
-      <c r="AA12" s="33"/>
-      <c r="AB12" s="33"/>
-      <c r="AC12" s="33"/>
-      <c r="AD12" s="33"/>
-      <c r="AE12" s="33"/>
-      <c r="AF12" s="33"/>
-      <c r="AG12" s="33"/>
-      <c r="AH12" s="33"/>
-      <c r="AI12" s="33"/>
-      <c r="AJ12" s="33"/>
-      <c r="AK12" s="33"/>
     </row>
     <row r="13" spans="2:238" x14ac:dyDescent="0.15">
-      <c r="B13" s="32" t="s">
-        <v>216</v>
-      </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34">
-        <f t="shared" ref="E13:L13" si="205">+G11/C11-1</f>
+      <c r="B13" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32">
+        <f t="shared" ref="G13:L13" si="205">+G11/C11-1</f>
         <v>2.6212458286985538</v>
       </c>
-      <c r="H13" s="34">
+      <c r="H13" s="32">
         <f t="shared" si="205"/>
         <v>1.2240319834160065</v>
       </c>
-      <c r="I13" s="34">
+      <c r="I13" s="32">
         <f t="shared" si="205"/>
         <v>0.93609271523178816</v>
       </c>
-      <c r="J13" s="34">
+      <c r="J13" s="32">
         <f t="shared" si="205"/>
         <v>0.77944170474596208</v>
       </c>
-      <c r="K13" s="34">
+      <c r="K13" s="32">
         <f t="shared" si="205"/>
         <v>0.69182921210259551</v>
       </c>
-      <c r="L13" s="34">
+      <c r="L13" s="32">
         <f t="shared" si="205"/>
         <v>0.5560252996005326</v>
       </c>
-      <c r="M13" s="34">
+      <c r="M13" s="32">
         <f>+M11/I11-1</f>
         <v>0.62493586454592109</v>
       </c>
-      <c r="N13" s="33"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="33"/>
-      <c r="S13" s="33"/>
-      <c r="T13" s="33"/>
-      <c r="U13" s="33"/>
-      <c r="V13" s="33"/>
-      <c r="W13" s="33"/>
-      <c r="X13" s="33"/>
-      <c r="Y13" s="33"/>
-      <c r="Z13" s="33"/>
-      <c r="AA13" s="33"/>
-      <c r="AB13" s="33"/>
-      <c r="AC13" s="33"/>
-      <c r="AD13" s="33"/>
-      <c r="AE13" s="33"/>
-      <c r="AF13" s="33"/>
-      <c r="AG13" s="33"/>
-      <c r="AH13" s="33"/>
-      <c r="AI13" s="33"/>
-      <c r="AJ13" s="33"/>
-      <c r="AK13" s="33"/>
-    </row>
-    <row r="14" spans="2:238" x14ac:dyDescent="0.15">
-      <c r="B14" s="32"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="33"/>
-      <c r="S14" s="33"/>
-      <c r="T14" s="33"/>
-      <c r="U14" s="33"/>
-      <c r="V14" s="33"/>
-      <c r="W14" s="33"/>
-      <c r="X14" s="33"/>
-      <c r="Y14" s="33"/>
-      <c r="Z14" s="33"/>
-      <c r="AA14" s="33"/>
-      <c r="AB14" s="33"/>
-      <c r="AC14" s="33"/>
-      <c r="AD14" s="33"/>
-      <c r="AE14" s="33"/>
-      <c r="AF14" s="33"/>
-      <c r="AG14" s="33"/>
-      <c r="AH14" s="33"/>
-      <c r="AI14" s="33"/>
-      <c r="AJ14" s="33"/>
-      <c r="AK14" s="33"/>
-    </row>
-    <row r="15" spans="2:238" x14ac:dyDescent="0.15">
-      <c r="B15" s="32"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="33"/>
-      <c r="T15" s="33"/>
-      <c r="U15" s="33"/>
-      <c r="V15" s="33"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="33"/>
-      <c r="Y15" s="33"/>
-      <c r="Z15" s="33"/>
-      <c r="AA15" s="33"/>
-      <c r="AB15" s="33"/>
-      <c r="AC15" s="33"/>
-      <c r="AD15" s="33"/>
-      <c r="AE15" s="33"/>
-      <c r="AF15" s="33"/>
-      <c r="AG15" s="33"/>
-      <c r="AH15" s="33"/>
-      <c r="AI15" s="33"/>
-      <c r="AJ15" s="33"/>
-      <c r="AK15" s="33"/>
     </row>
     <row r="16" spans="2:238" x14ac:dyDescent="0.15">
       <c r="B16" s="27" t="s">
@@ -3987,7 +3900,7 @@
       <c r="E16" s="24">
         <v>4720</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="33">
         <f t="shared" ref="F16:F22" si="206">+Z16-SUM(C16:E16)</f>
         <v>5312</v>
       </c>
@@ -4098,7 +4011,7 @@
       <c r="E17" s="24">
         <v>2294</v>
       </c>
-      <c r="F17" s="35">
+      <c r="F17" s="33">
         <f t="shared" si="206"/>
         <v>2466</v>
       </c>
@@ -4208,7 +4121,7 @@
       <c r="E18" s="24">
         <v>689</v>
       </c>
-      <c r="F18" s="35">
+      <c r="F18" s="33">
         <f t="shared" si="206"/>
         <v>710</v>
       </c>
@@ -4444,7 +4357,7 @@
       <c r="E20" s="24">
         <v>234</v>
       </c>
-      <c r="F20" s="35">
+      <c r="F20" s="33">
         <f t="shared" si="206"/>
         <v>295</v>
       </c>
@@ -4555,7 +4468,7 @@
       <c r="E21" s="24">
         <v>-63</v>
       </c>
-      <c r="F21" s="35">
+      <c r="F21" s="33">
         <f t="shared" si="206"/>
         <v>-63</v>
       </c>
@@ -4666,7 +4579,7 @@
       <c r="E22" s="24">
         <v>-66</v>
       </c>
-      <c r="F22" s="35">
+      <c r="F22" s="33">
         <f t="shared" si="206"/>
         <v>259</v>
       </c>
@@ -4902,7 +4815,7 @@
       <c r="E24" s="24">
         <v>1279</v>
       </c>
-      <c r="F24" s="35">
+      <c r="F24" s="33">
         <f>+Z24-SUM(C24:E24)</f>
         <v>1820</v>
       </c>
@@ -6034,87 +5947,87 @@
         <v>24515.682607508588</v>
       </c>
     </row>
-    <row r="27" spans="2:238" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B27" s="36" t="s">
+    <row r="27" spans="2:238" s="34" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B27" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="37">
+      <c r="C27" s="35">
         <f>+C25/C26</f>
         <v>0.82048192771084338</v>
       </c>
-      <c r="D27" s="37">
+      <c r="D27" s="35">
         <f>+D25/D26</f>
         <v>0.24757941906057454</v>
       </c>
-      <c r="E27" s="37">
+      <c r="E27" s="35">
         <f>+E25/E26</f>
         <v>0.37060946271050521</v>
       </c>
-      <c r="F27" s="37">
+      <c r="F27" s="35">
         <f>+Z27-SUM(C27:E27)</f>
         <v>-0.24540697628224395</v>
       </c>
-      <c r="G27" s="37">
+      <c r="G27" s="35">
         <f>+G25/G26</f>
         <v>0.57072040957295522</v>
       </c>
-      <c r="H27" s="37">
+      <c r="H27" s="35">
         <f>+H25/H26</f>
         <v>0.66802157115260785</v>
       </c>
-      <c r="I27" s="37">
+      <c r="I27" s="35">
         <f>+I25/I26</f>
         <v>0.77940582869136998</v>
       </c>
-      <c r="J27" s="37">
+      <c r="J27" s="35">
         <f t="shared" si="199"/>
         <v>1.323248739526786</v>
       </c>
-      <c r="K27" s="37">
+      <c r="K27" s="35">
         <f>+K25/K26</f>
         <v>0.7628702612652879</v>
       </c>
-      <c r="L27" s="38">
+      <c r="L27" s="36">
         <f>+L25/L26</f>
         <v>1.0820968530898418</v>
       </c>
-      <c r="M27" s="38">
+      <c r="M27" s="36">
         <f>+M25/M26</f>
         <v>1.3033533472205203</v>
       </c>
-      <c r="N27" s="38">
+      <c r="N27" s="36">
         <f>+N25/N26</f>
         <v>1.4617810795501087</v>
       </c>
-      <c r="Q27" s="38"/>
-      <c r="R27" s="38"/>
-      <c r="S27" s="38"/>
-      <c r="T27" s="38"/>
-      <c r="U27" s="38">
+      <c r="Q27" s="36"/>
+      <c r="R27" s="36"/>
+      <c r="S27" s="36"/>
+      <c r="T27" s="36"/>
+      <c r="U27" s="36">
         <f t="shared" ref="U27:AA27" si="231">+U25/U26</f>
         <v>6.6256000000000004</v>
       </c>
-      <c r="V27" s="38">
+      <c r="V27" s="36">
         <f t="shared" si="231"/>
         <v>4.5242718446601939</v>
       </c>
-      <c r="W27" s="38">
+      <c r="W27" s="36">
         <f t="shared" si="231"/>
         <v>6.8980891719745223</v>
       </c>
-      <c r="X27" s="38">
+      <c r="X27" s="36">
         <f t="shared" si="231"/>
         <v>3.8469428007889546</v>
       </c>
-      <c r="Y27" s="38">
+      <c r="Y27" s="36">
         <f t="shared" si="231"/>
         <v>0.22820103709613082</v>
       </c>
-      <c r="Z27" s="38">
+      <c r="Z27" s="36">
         <f t="shared" si="231"/>
         <v>1.1932638331996792</v>
       </c>
-      <c r="AA27" s="38">
+      <c r="AA27" s="36">
         <f t="shared" si="231"/>
         <v>3.341396548943719</v>
       </c>
@@ -6122,2455 +6035,2395 @@
         <f t="shared" si="209"/>
         <v>4.6101015411257587</v>
       </c>
-      <c r="AC27" s="38">
+      <c r="AC27" s="36">
         <f>+AC25/AC26</f>
         <v>5.9286438360847109</v>
       </c>
-      <c r="AD27" s="38">
+      <c r="AD27" s="36">
         <f t="shared" ref="AD27:AK27" si="232">+AD25/AD26</f>
         <v>7.3570646556235735</v>
       </c>
-      <c r="AE27" s="38">
+      <c r="AE27" s="36">
         <f t="shared" si="232"/>
         <v>8.7854854751624369</v>
       </c>
-      <c r="AF27" s="38">
+      <c r="AF27" s="36">
         <f t="shared" si="232"/>
         <v>10.499590458609072</v>
       </c>
-      <c r="AG27" s="38">
+      <c r="AG27" s="36">
         <f t="shared" si="232"/>
         <v>11.528053448677056</v>
       </c>
-      <c r="AH27" s="38">
+      <c r="AH27" s="36">
         <f t="shared" si="232"/>
         <v>12.659362737751838</v>
       </c>
-      <c r="AI27" s="38">
+      <c r="AI27" s="36">
         <f t="shared" si="232"/>
         <v>13.903802955734099</v>
       </c>
-      <c r="AJ27" s="38">
+      <c r="AJ27" s="36">
         <f t="shared" si="232"/>
         <v>15.272687195514584</v>
       </c>
-      <c r="AK27" s="38">
+      <c r="AK27" s="36">
         <f t="shared" si="232"/>
         <v>16.778459859273116</v>
       </c>
-      <c r="AL27" s="38"/>
+      <c r="AL27" s="36"/>
     </row>
     <row r="28" spans="2:238" x14ac:dyDescent="0.15">
-      <c r="G28" s="39">
+      <c r="G28" s="32">
         <f>+G16/G11</f>
         <v>0.21647980340961451</v>
       </c>
-      <c r="H28" s="39">
+      <c r="H28" s="32">
         <f t="shared" ref="H28:N28" si="233">+H16/H11</f>
         <v>0.24853528628495339</v>
       </c>
-      <c r="I28" s="39">
+      <c r="I28" s="32">
         <f t="shared" si="233"/>
         <v>0.25443247249301637</v>
       </c>
-      <c r="J28" s="39">
+      <c r="J28" s="32">
         <f t="shared" si="233"/>
         <v>0.26973634029137322</v>
       </c>
-      <c r="K28" s="39">
+      <c r="K28" s="32">
         <f t="shared" si="233"/>
         <v>0.39476192637646951</v>
       </c>
-      <c r="L28" s="39">
+      <c r="L28" s="32">
         <f t="shared" si="233"/>
         <v>0.27576321588259206</v>
       </c>
-      <c r="M28" s="39">
+      <c r="M28" s="32">
         <f t="shared" si="233"/>
         <v>0.2658842928814511</v>
       </c>
-      <c r="N28" s="39">
+      <c r="N28" s="32">
         <f t="shared" si="233"/>
         <v>0.26</v>
       </c>
-      <c r="U28" s="39">
-        <f>+U17/U11</f>
-        <v>0.20279959030385797</v>
-      </c>
-      <c r="V28" s="39">
-        <f t="shared" ref="V28:AD28" si="234">+V17/V11</f>
-        <v>0.25911339073090311</v>
-      </c>
-      <c r="W28" s="39">
-        <f t="shared" si="234"/>
-        <v>0.2353223388305847</v>
-      </c>
-      <c r="X28" s="39">
-        <f t="shared" si="234"/>
-        <v>0.19573456193802483</v>
-      </c>
-      <c r="Y28" s="39">
-        <f t="shared" si="234"/>
-        <v>0.27207681471046191</v>
-      </c>
-      <c r="Z28" s="39">
-        <f t="shared" si="234"/>
-        <v>0.14239519385443683</v>
-      </c>
-      <c r="AA28" s="39">
-        <f t="shared" si="234"/>
-        <v>9.8960129351632606E-2</v>
-      </c>
-      <c r="AB28" s="39">
-        <f t="shared" si="234"/>
-        <v>8.4511608892397477E-2</v>
-      </c>
-      <c r="AC28" s="39">
-        <f t="shared" si="234"/>
-        <v>8.4511608892397477E-2</v>
-      </c>
-      <c r="AD28" s="39">
-        <f t="shared" si="234"/>
-        <v>8.4511608892397477E-2</v>
-      </c>
-      <c r="AE28" s="39">
-        <f t="shared" ref="AE28" si="235">+AE17/AE11</f>
-        <v>8.4511608892397477E-2</v>
-      </c>
+      <c r="U28" s="32"/>
+      <c r="V28" s="32"/>
+      <c r="W28" s="32"/>
+      <c r="X28" s="32"/>
+      <c r="Y28" s="32"/>
+      <c r="Z28" s="32"/>
+      <c r="AA28" s="32"/>
+      <c r="AB28" s="32"/>
+      <c r="AC28" s="32"/>
+      <c r="AD28" s="32"/>
+      <c r="AE28" s="32"/>
     </row>
     <row r="29" spans="2:238" x14ac:dyDescent="0.15">
       <c r="B29" s="30" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="30" spans="2:238" s="43" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="40" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="30" spans="2:238" s="37" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41">
-        <f>+H4/D4-1</f>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38">
+        <f t="shared" ref="H30:M37" si="234">+H4/D4-1</f>
         <v>1.6247097073850441</v>
       </c>
-      <c r="I30" s="41">
-        <f>+I4/E4-1</f>
+      <c r="I30" s="38">
+        <f t="shared" si="234"/>
         <v>1.321464561639234</v>
       </c>
-      <c r="J30" s="41">
-        <f>+J4/F4-1</f>
+      <c r="J30" s="38">
+        <f t="shared" si="234"/>
         <v>1.1598885424268559</v>
       </c>
-      <c r="K30" s="41">
-        <f>+K4/G4-1</f>
+      <c r="K30" s="38">
+        <f t="shared" si="234"/>
         <v>0.76129331683168311</v>
       </c>
-      <c r="L30" s="41">
-        <f>+L4/H4-1</f>
+      <c r="L30" s="38">
+        <f t="shared" si="234"/>
         <v>0.49725712263316235</v>
       </c>
-      <c r="M30" s="41">
-        <f>+M4/I4-1</f>
+      <c r="M30" s="38">
+        <f t="shared" si="234"/>
         <v>0.55650412386051218</v>
       </c>
-      <c r="N30" s="41"/>
-      <c r="O30" s="42"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="41"/>
-      <c r="S30" s="41"/>
-      <c r="T30" s="41"/>
-      <c r="U30" s="41"/>
-      <c r="V30" s="41"/>
-      <c r="W30" s="41"/>
-      <c r="X30" s="41"/>
-      <c r="Y30" s="41"/>
-      <c r="Z30" s="41">
-        <f>+Z4/Y4-1</f>
+      <c r="N30" s="38"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="39"/>
+      <c r="Q30" s="38"/>
+      <c r="R30" s="38"/>
+      <c r="S30" s="38"/>
+      <c r="T30" s="38"/>
+      <c r="U30" s="38"/>
+      <c r="V30" s="38"/>
+      <c r="W30" s="38"/>
+      <c r="X30" s="38"/>
+      <c r="Y30" s="38"/>
+      <c r="Z30" s="38">
+        <f t="shared" ref="Z30:AA37" si="235">+Z4/Y4-1</f>
         <v>2.4417248387381814</v>
       </c>
-      <c r="AA30" s="41">
-        <f>+AA4/Z4-1</f>
+      <c r="AA30" s="38">
+        <f t="shared" si="235"/>
         <v>1.6237740693196407</v>
       </c>
-      <c r="AB30" s="41"/>
-      <c r="AC30" s="41"/>
-      <c r="AD30" s="41"/>
-      <c r="AE30" s="41"/>
-      <c r="AF30" s="41"/>
-      <c r="AG30" s="41"/>
-      <c r="AH30" s="41"/>
-      <c r="AI30" s="41"/>
-      <c r="AJ30" s="41"/>
-      <c r="AK30" s="41"/>
-      <c r="AL30" s="54" t="s">
-        <v>201</v>
-      </c>
-      <c r="AM30" s="55">
+      <c r="AB30" s="38"/>
+      <c r="AC30" s="38"/>
+      <c r="AD30" s="38"/>
+      <c r="AE30" s="38"/>
+      <c r="AF30" s="38"/>
+      <c r="AG30" s="38"/>
+      <c r="AH30" s="38"/>
+      <c r="AI30" s="38"/>
+      <c r="AJ30" s="38"/>
+      <c r="AK30" s="38"/>
+      <c r="AL30" s="49" t="s">
+        <v>197</v>
+      </c>
+      <c r="AM30" s="50">
         <v>0.01</v>
       </c>
     </row>
-    <row r="31" spans="2:238" s="43" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="40" t="s">
+    <row r="31" spans="2:238" s="37" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B31" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41">
-        <f>+H5/D5-1</f>
+      <c r="C31" s="38"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38">
+        <f t="shared" si="234"/>
         <v>1.1437755698421976</v>
       </c>
-      <c r="I31" s="41">
-        <f>+I5/E5-1</f>
+      <c r="I31" s="38">
+        <f t="shared" si="234"/>
         <v>0.19992325402916356</v>
       </c>
-      <c r="J31" s="41">
-        <f>+J5/F5-1</f>
+      <c r="J31" s="38">
+        <f t="shared" si="234"/>
         <v>-9.2164515160612415E-2</v>
       </c>
-      <c r="K31" s="41">
-        <f>+K5/G5-1</f>
+      <c r="K31" s="38">
+        <f t="shared" si="234"/>
         <v>0.56322926521602024</v>
       </c>
-      <c r="L31" s="41">
-        <f>+L5/H5-1</f>
+      <c r="L31" s="38">
+        <f t="shared" si="234"/>
         <v>0.97709923664122145</v>
       </c>
-      <c r="M31" s="41">
-        <f>+M5/I5-1</f>
+      <c r="M31" s="38">
+        <f t="shared" si="234"/>
         <v>1.618164374800128</v>
       </c>
-      <c r="N31" s="41"/>
-      <c r="O31" s="42"/>
-      <c r="P31" s="42"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="41"/>
-      <c r="S31" s="41"/>
-      <c r="T31" s="41"/>
-      <c r="U31" s="41"/>
-      <c r="V31" s="41"/>
-      <c r="W31" s="41"/>
-      <c r="X31" s="41"/>
-      <c r="Y31" s="41"/>
-      <c r="Z31" s="41">
-        <f>+Z5/Y5-1</f>
+      <c r="N31" s="38"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="39"/>
+      <c r="Q31" s="38"/>
+      <c r="R31" s="38"/>
+      <c r="S31" s="38"/>
+      <c r="T31" s="38"/>
+      <c r="U31" s="38"/>
+      <c r="V31" s="38"/>
+      <c r="W31" s="38"/>
+      <c r="X31" s="38"/>
+      <c r="Y31" s="38"/>
+      <c r="Z31" s="38">
+        <f t="shared" si="235"/>
         <v>1.3251084598698482</v>
       </c>
-      <c r="AA31" s="41">
-        <f>+AA5/Z5-1</f>
+      <c r="AA31" s="38">
+        <f t="shared" si="235"/>
         <v>0.51486880466472296</v>
       </c>
-      <c r="AB31" s="41"/>
-      <c r="AC31" s="41"/>
-      <c r="AD31" s="41"/>
-      <c r="AE31" s="41"/>
-      <c r="AF31" s="41"/>
-      <c r="AG31" s="41"/>
-      <c r="AH31" s="41"/>
-      <c r="AI31" s="41"/>
-      <c r="AJ31" s="41"/>
-      <c r="AK31" s="41"/>
-      <c r="AL31" s="56" t="s">
-        <v>202</v>
-      </c>
-      <c r="AM31" s="57">
+      <c r="AB31" s="38"/>
+      <c r="AC31" s="38"/>
+      <c r="AD31" s="38"/>
+      <c r="AE31" s="38"/>
+      <c r="AF31" s="38"/>
+      <c r="AG31" s="38"/>
+      <c r="AH31" s="38"/>
+      <c r="AI31" s="38"/>
+      <c r="AJ31" s="38"/>
+      <c r="AK31" s="38"/>
+      <c r="AL31" s="51" t="s">
+        <v>198</v>
+      </c>
+      <c r="AM31" s="52">
         <v>0.08</v>
       </c>
     </row>
-    <row r="32" spans="2:238" s="48" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="44" t="s">
+    <row r="32" spans="2:238" s="40" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45">
-        <f>+H6/D6-1</f>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41">
+        <f t="shared" si="234"/>
         <v>1.5449966095127388</v>
       </c>
-      <c r="I32" s="45">
-        <f>+I6/E6-1</f>
+      <c r="I32" s="41">
+        <f t="shared" si="234"/>
         <v>1.1200909466721787</v>
       </c>
-      <c r="J32" s="45">
-        <f>+J6/F6-1</f>
+      <c r="J32" s="41">
+        <f t="shared" si="234"/>
         <v>0.93327537491849588</v>
       </c>
-      <c r="K32" s="45">
-        <f>+K6/G6-1</f>
+      <c r="K32" s="41">
+        <f t="shared" si="234"/>
         <v>0.73345743030625354</v>
       </c>
-      <c r="L32" s="45">
-        <f>+L6/H6-1</f>
+      <c r="L32" s="41">
+        <f t="shared" si="234"/>
         <v>0.56425091352009749</v>
       </c>
-      <c r="M32" s="45">
-        <f>+M6/I6-1</f>
+      <c r="M32" s="41">
+        <f t="shared" si="234"/>
         <v>0.66439179747164534</v>
       </c>
-      <c r="N32" s="45"/>
-      <c r="O32" s="46"/>
-      <c r="P32" s="46"/>
-      <c r="Q32" s="45"/>
-      <c r="R32" s="45"/>
-      <c r="S32" s="45"/>
-      <c r="T32" s="45"/>
-      <c r="U32" s="45"/>
-      <c r="V32" s="45">
+      <c r="N32" s="41"/>
+      <c r="O32" s="42"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="41"/>
+      <c r="S32" s="41"/>
+      <c r="T32" s="41"/>
+      <c r="U32" s="41"/>
+      <c r="V32" s="41">
         <f t="shared" ref="V32" si="236">+V6/U6-1</f>
         <v>1.7394270122783162E-2</v>
       </c>
-      <c r="W32" s="45">
+      <c r="W32" s="41">
         <f t="shared" ref="W32:X32" si="237">+W6/V6-1</f>
         <v>1.2447200804559166</v>
       </c>
-      <c r="X32" s="45">
+      <c r="X32" s="41">
         <f t="shared" si="237"/>
         <v>0.5849761051373954</v>
       </c>
-      <c r="Y32" s="45">
+      <c r="Y32" s="41">
         <f t="shared" ref="Y32" si="238">+Y6/X6-1</f>
         <v>0.4138320927164798</v>
       </c>
-      <c r="Z32" s="45">
-        <f>+Z6/Y6-1</f>
+      <c r="Z32" s="41">
+        <f t="shared" si="235"/>
         <v>2.1672775741419525</v>
       </c>
-      <c r="AA32" s="45">
-        <f>+AA6/Z6-1</f>
+      <c r="AA32" s="41">
+        <f t="shared" si="235"/>
         <v>1.4236927932667016</v>
       </c>
-      <c r="AB32" s="45"/>
-      <c r="AC32" s="45"/>
-      <c r="AD32" s="45"/>
-      <c r="AE32" s="45"/>
-      <c r="AF32" s="45"/>
-      <c r="AG32" s="45"/>
-      <c r="AH32" s="45"/>
-      <c r="AI32" s="45"/>
-      <c r="AJ32" s="45"/>
-      <c r="AK32" s="45"/>
-      <c r="AL32" s="60" t="s">
-        <v>203</v>
-      </c>
-      <c r="AM32" s="61">
+      <c r="AB32" s="41"/>
+      <c r="AC32" s="41"/>
+      <c r="AD32" s="41"/>
+      <c r="AE32" s="41"/>
+      <c r="AF32" s="41"/>
+      <c r="AG32" s="41"/>
+      <c r="AH32" s="41"/>
+      <c r="AI32" s="41"/>
+      <c r="AJ32" s="41"/>
+      <c r="AK32" s="41"/>
+      <c r="AL32" s="55" t="s">
+        <v>199</v>
+      </c>
+      <c r="AM32" s="56">
         <f>NPV(AM31,AB25:ID25)</f>
         <v>4376148.0390042346</v>
       </c>
     </row>
-    <row r="33" spans="2:39" s="43" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="40" t="s">
+    <row r="33" spans="2:39" s="37" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41">
-        <f>+H7/D7-1</f>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38">
+        <f t="shared" si="234"/>
         <v>0.15848753016894612</v>
       </c>
-      <c r="I33" s="41">
-        <f>+I7/E7-1</f>
+      <c r="I33" s="38">
+        <f t="shared" si="234"/>
         <v>0.14810924369747891</v>
       </c>
-      <c r="J33" s="41">
-        <f>+J7/F7-1</f>
+      <c r="J33" s="38">
+        <f t="shared" si="234"/>
         <v>-0.11204188481675392</v>
       </c>
-      <c r="K33" s="41">
-        <f>+K7/G7-1</f>
+      <c r="K33" s="38">
+        <f t="shared" si="234"/>
         <v>0.42160936909709101</v>
       </c>
-      <c r="L33" s="41">
-        <f>+L7/H7-1</f>
+      <c r="L33" s="38">
+        <f t="shared" si="234"/>
         <v>0.48854166666666665</v>
       </c>
-      <c r="M33" s="41">
-        <f>+M7/I7-1</f>
+      <c r="M33" s="38">
+        <f t="shared" si="234"/>
         <v>0.30070143336383048</v>
       </c>
-      <c r="N33" s="41"/>
-      <c r="O33" s="42"/>
-      <c r="P33" s="42"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="41"/>
-      <c r="S33" s="41"/>
-      <c r="T33" s="41"/>
-      <c r="U33" s="41"/>
-      <c r="V33" s="41">
+      <c r="N33" s="38"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="39"/>
+      <c r="Q33" s="38"/>
+      <c r="R33" s="38"/>
+      <c r="S33" s="38"/>
+      <c r="T33" s="38"/>
+      <c r="U33" s="38"/>
+      <c r="V33" s="38">
         <f t="shared" ref="V33" si="239">+V7/U7-1</f>
         <v>-0.11655459494076204</v>
       </c>
-      <c r="W33" s="41">
+      <c r="W33" s="38">
         <f t="shared" ref="W33:X33" si="240">+W7/V7-1</f>
         <v>0.40612540775643358</v>
       </c>
-      <c r="X33" s="41">
+      <c r="X33" s="38">
         <f t="shared" si="240"/>
         <v>0.60613481118700863</v>
       </c>
-      <c r="Y33" s="41">
+      <c r="Y33" s="38">
         <f t="shared" ref="Y33" si="241">+Y7/X7-1</f>
         <v>-0.27242818167228378</v>
       </c>
-      <c r="Z33" s="41">
-        <f>+Z7/Y7-1</f>
+      <c r="Z33" s="38">
+        <f t="shared" si="235"/>
         <v>0.15220028675416342</v>
       </c>
-      <c r="AA33" s="41">
-        <f>+AA7/Z7-1</f>
+      <c r="AA33" s="38">
+        <f t="shared" si="235"/>
         <v>8.643629750167503E-2</v>
       </c>
-      <c r="AB33" s="41"/>
-      <c r="AC33" s="41"/>
-      <c r="AD33" s="41"/>
-      <c r="AE33" s="41"/>
-      <c r="AF33" s="41"/>
-      <c r="AG33" s="41"/>
-      <c r="AH33" s="41"/>
-      <c r="AI33" s="41"/>
-      <c r="AJ33" s="41"/>
-      <c r="AK33" s="41"/>
-      <c r="AL33" s="56" t="s">
+      <c r="AB33" s="38"/>
+      <c r="AC33" s="38"/>
+      <c r="AD33" s="38"/>
+      <c r="AE33" s="38"/>
+      <c r="AF33" s="38"/>
+      <c r="AG33" s="38"/>
+      <c r="AH33" s="38"/>
+      <c r="AI33" s="38"/>
+      <c r="AJ33" s="38"/>
+      <c r="AK33" s="38"/>
+      <c r="AL33" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="AM33" s="58">
+      <c r="AM33" s="53">
         <f>+Main!G4</f>
         <v>24300</v>
       </c>
     </row>
-    <row r="34" spans="2:39" s="43" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="40" t="s">
+    <row r="34" spans="2:39" s="37" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B34" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="41">
-        <f>+H8/D8-1</f>
+      <c r="C34" s="38"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38">
+        <f t="shared" si="234"/>
         <v>0.19788918205804751</v>
       </c>
-      <c r="I34" s="41">
-        <f>+I8/E8-1</f>
+      <c r="I34" s="38">
+        <f t="shared" si="234"/>
         <v>0.16826923076923084</v>
       </c>
-      <c r="J34" s="41">
-        <f>+J8/F8-1</f>
+      <c r="J34" s="38">
+        <f t="shared" si="234"/>
         <v>0.10367170626349886</v>
       </c>
-      <c r="K34" s="41">
-        <f>+K8/G8-1</f>
+      <c r="K34" s="38">
+        <f t="shared" si="234"/>
         <v>0.19203747072599531</v>
       </c>
-      <c r="L34" s="41">
-        <f>+L8/H8-1</f>
+      <c r="L34" s="38">
+        <f t="shared" si="234"/>
         <v>0.32378854625550657</v>
       </c>
-      <c r="M34" s="41">
-        <f>+M8/I8-1</f>
+      <c r="M34" s="38">
+        <f t="shared" si="234"/>
         <v>0.56378600823045266</v>
       </c>
-      <c r="N34" s="41"/>
-      <c r="O34" s="42"/>
-      <c r="P34" s="42"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="41"/>
-      <c r="S34" s="41"/>
-      <c r="T34" s="41"/>
-      <c r="U34" s="41"/>
-      <c r="V34" s="41">
+      <c r="N34" s="38"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="39"/>
+      <c r="Q34" s="38"/>
+      <c r="R34" s="38"/>
+      <c r="S34" s="38"/>
+      <c r="T34" s="38"/>
+      <c r="U34" s="38"/>
+      <c r="V34" s="38">
         <f t="shared" ref="V34" si="242">+V8/U8-1</f>
         <v>7.2566371681415998E-2</v>
       </c>
-      <c r="W34" s="41">
+      <c r="W34" s="38">
         <f t="shared" ref="W34:X34" si="243">+W8/V8-1</f>
         <v>-0.13118811881188119</v>
       </c>
-      <c r="X34" s="41">
+      <c r="X34" s="38">
         <f t="shared" si="243"/>
         <v>1.0047483380816713</v>
       </c>
-      <c r="Y34" s="41">
+      <c r="Y34" s="38">
         <f t="shared" ref="Y34" si="244">+Y8/X8-1</f>
         <v>-0.26859308384651825</v>
       </c>
-      <c r="Z34" s="41">
-        <f>+Z8/Y8-1</f>
+      <c r="Z34" s="38">
+        <f t="shared" si="235"/>
         <v>5.8290155440414715E-3</v>
       </c>
-      <c r="AA34" s="41">
-        <f>+AA8/Z8-1</f>
+      <c r="AA34" s="38">
+        <f t="shared" si="235"/>
         <v>0.20927237604636195</v>
       </c>
-      <c r="AB34" s="41"/>
-      <c r="AC34" s="41"/>
-      <c r="AD34" s="41"/>
-      <c r="AE34" s="41"/>
-      <c r="AF34" s="41"/>
-      <c r="AG34" s="41"/>
-      <c r="AH34" s="41"/>
-      <c r="AI34" s="41"/>
-      <c r="AJ34" s="41"/>
-      <c r="AK34" s="41"/>
-      <c r="AL34" s="60" t="s">
-        <v>204</v>
-      </c>
-      <c r="AM34" s="62">
+      <c r="AB34" s="38"/>
+      <c r="AC34" s="38"/>
+      <c r="AD34" s="38"/>
+      <c r="AE34" s="38"/>
+      <c r="AF34" s="38"/>
+      <c r="AG34" s="38"/>
+      <c r="AH34" s="38"/>
+      <c r="AI34" s="38"/>
+      <c r="AJ34" s="38"/>
+      <c r="AK34" s="38"/>
+      <c r="AL34" s="55" t="s">
+        <v>200</v>
+      </c>
+      <c r="AM34" s="57">
         <f>+AM32/AM33</f>
         <v>180.08839666684094</v>
       </c>
     </row>
-    <row r="35" spans="2:39" s="43" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="40" t="s">
+    <row r="35" spans="2:39" s="37" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B35" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="41">
-        <f>+H9/D9-1</f>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38">
+        <f t="shared" si="234"/>
         <v>0.36758893280632421</v>
       </c>
-      <c r="I35" s="41">
-        <f>+I9/E9-1</f>
+      <c r="I35" s="38">
+        <f t="shared" si="234"/>
         <v>0.72030651340996177</v>
       </c>
-      <c r="J35" s="41">
-        <f>+J9/F9-1</f>
+      <c r="J35" s="38">
+        <f t="shared" si="234"/>
         <v>1.0284697508896796</v>
       </c>
-      <c r="K35" s="41">
-        <f>+K9/G9-1</f>
+      <c r="K35" s="38">
+        <f t="shared" si="234"/>
         <v>0.72340425531914887</v>
       </c>
-      <c r="L35" s="41">
-        <f>+L9/H9-1</f>
+      <c r="L35" s="38">
+        <f t="shared" si="234"/>
         <v>0.69364161849710992</v>
       </c>
-      <c r="M35" s="41">
-        <f>+M9/I9-1</f>
+      <c r="M35" s="38">
+        <f t="shared" si="234"/>
         <v>0.31848552338530056</v>
       </c>
-      <c r="N35" s="41"/>
-      <c r="O35" s="42"/>
-      <c r="P35" s="42"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="41"/>
-      <c r="S35" s="41"/>
-      <c r="T35" s="41"/>
-      <c r="U35" s="41"/>
-      <c r="V35" s="41">
+      <c r="N35" s="38"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="39"/>
+      <c r="Q35" s="38"/>
+      <c r="R35" s="38"/>
+      <c r="S35" s="38"/>
+      <c r="T35" s="38"/>
+      <c r="U35" s="38"/>
+      <c r="V35" s="38">
         <f t="shared" ref="V35" si="245">+V9/U9-1</f>
         <v>9.2043681747269845E-2</v>
       </c>
-      <c r="W35" s="41">
+      <c r="W35" s="38">
         <f t="shared" ref="W35:X35" si="246">+W9/V9-1</f>
         <v>-0.23428571428571432</v>
       </c>
-      <c r="X35" s="41">
+      <c r="X35" s="38">
         <f t="shared" si="246"/>
         <v>5.5970149253731449E-2</v>
       </c>
-      <c r="Y35" s="41">
+      <c r="Y35" s="38">
         <f t="shared" ref="Y35" si="247">+Y9/X9-1</f>
         <v>0.59540636042402828</v>
       </c>
-      <c r="Z35" s="41">
-        <f>+Z9/Y9-1</f>
+      <c r="Z35" s="38">
+        <f t="shared" si="235"/>
         <v>0.20819490586932443</v>
       </c>
-      <c r="AA35" s="41">
-        <f>+AA9/Z9-1</f>
+      <c r="AA35" s="38">
+        <f t="shared" si="235"/>
         <v>0.55270394133822176</v>
       </c>
-      <c r="AB35" s="41"/>
-      <c r="AC35" s="41"/>
-      <c r="AD35" s="41"/>
-      <c r="AE35" s="41"/>
-      <c r="AF35" s="41"/>
-      <c r="AG35" s="41"/>
-      <c r="AH35" s="41"/>
-      <c r="AI35" s="41"/>
-      <c r="AJ35" s="41"/>
-      <c r="AK35" s="41"/>
-      <c r="AL35" s="56" t="s">
-        <v>205</v>
-      </c>
-      <c r="AM35" s="59">
+      <c r="AB35" s="38"/>
+      <c r="AC35" s="38"/>
+      <c r="AD35" s="38"/>
+      <c r="AE35" s="38"/>
+      <c r="AF35" s="38"/>
+      <c r="AG35" s="38"/>
+      <c r="AH35" s="38"/>
+      <c r="AI35" s="38"/>
+      <c r="AJ35" s="38"/>
+      <c r="AK35" s="38"/>
+      <c r="AL35" s="51" t="s">
+        <v>201</v>
+      </c>
+      <c r="AM35" s="54">
         <f>+Main!G3</f>
         <v>182</v>
       </c>
     </row>
-    <row r="36" spans="2:39" s="43" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="40" t="s">
+    <row r="36" spans="2:39" s="37" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="41">
-        <f>+H10/D10-1</f>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38">
+        <f t="shared" si="234"/>
         <v>0.33333333333333326</v>
       </c>
-      <c r="I36" s="41">
-        <f>+I10/E10-1</f>
+      <c r="I36" s="38">
+        <f t="shared" si="234"/>
         <v>0.32876712328767121</v>
       </c>
-      <c r="J36" s="41">
-        <f>+J10/F10-1</f>
+      <c r="J36" s="38">
+        <f t="shared" si="234"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="K36" s="41">
-        <f>+K10/G10-1</f>
+      <c r="K36" s="38">
+        <f t="shared" si="234"/>
         <v>0.42307692307692313</v>
       </c>
-      <c r="L36" s="41">
-        <f>+L10/H10-1</f>
+      <c r="L36" s="38">
+        <f t="shared" si="234"/>
         <v>0.96590909090909083</v>
       </c>
-      <c r="M36" s="41">
-        <f>+M10/I10-1</f>
+      <c r="M36" s="38">
+        <f t="shared" si="234"/>
         <v>0.79381443298969079</v>
       </c>
-      <c r="N36" s="41"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="41"/>
-      <c r="S36" s="41"/>
-      <c r="T36" s="41"/>
-      <c r="U36" s="41"/>
-      <c r="V36" s="41">
+      <c r="N36" s="38"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="39"/>
+      <c r="Q36" s="38"/>
+      <c r="R36" s="38"/>
+      <c r="S36" s="38"/>
+      <c r="T36" s="38"/>
+      <c r="U36" s="38"/>
+      <c r="V36" s="38">
         <f t="shared" ref="V36" si="248">+V10/U10-1</f>
         <v>-0.34159061277705349</v>
       </c>
-      <c r="W36" s="41">
+      <c r="W36" s="38">
         <f t="shared" ref="W36:X36" si="249">+W10/V10-1</f>
         <v>0.2495049504950495</v>
       </c>
-      <c r="X36" s="41">
+      <c r="X36" s="38">
         <f t="shared" si="249"/>
         <v>0.84152139461172748</v>
       </c>
-      <c r="Y36" s="41">
+      <c r="Y36" s="38">
         <f t="shared" ref="Y36" si="250">+Y10/X10-1</f>
         <v>-0.60843373493975905</v>
       </c>
-      <c r="Z36" s="41">
-        <f>+Z10/Y10-1</f>
+      <c r="Z36" s="38">
+        <f t="shared" si="235"/>
         <v>-0.32747252747252742</v>
       </c>
-      <c r="AA36" s="41">
-        <f>+AA10/Z10-1</f>
+      <c r="AA36" s="38">
+        <f t="shared" si="235"/>
         <v>0.2712418300653594</v>
       </c>
-      <c r="AB36" s="41"/>
-      <c r="AC36" s="41"/>
-      <c r="AD36" s="41"/>
-      <c r="AE36" s="41"/>
-      <c r="AF36" s="41"/>
-      <c r="AG36" s="41"/>
-      <c r="AH36" s="41"/>
-      <c r="AI36" s="41"/>
-      <c r="AJ36" s="41"/>
-      <c r="AK36" s="41"/>
-      <c r="AL36" s="63" t="s">
-        <v>218</v>
-      </c>
-      <c r="AM36" s="64">
+      <c r="AB36" s="38"/>
+      <c r="AC36" s="38"/>
+      <c r="AD36" s="38"/>
+      <c r="AE36" s="38"/>
+      <c r="AF36" s="38"/>
+      <c r="AG36" s="38"/>
+      <c r="AH36" s="38"/>
+      <c r="AI36" s="38"/>
+      <c r="AJ36" s="38"/>
+      <c r="AK36" s="38"/>
+      <c r="AL36" s="58" t="s">
+        <v>214</v>
+      </c>
+      <c r="AM36" s="59">
         <f>+AM34/AM35-1</f>
         <v>-1.0503315017357462E-2</v>
       </c>
     </row>
-    <row r="37" spans="2:39" s="48" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="44" t="s">
+    <row r="37" spans="2:39" s="40" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="45"/>
-      <c r="H37" s="45">
-        <f>+H11/D11-1</f>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41">
+        <f t="shared" si="234"/>
         <v>1.2240319834160065</v>
       </c>
-      <c r="I37" s="45">
-        <f>+I11/E11-1</f>
+      <c r="I37" s="41">
+        <f t="shared" si="234"/>
         <v>0.93609271523178816</v>
       </c>
-      <c r="J37" s="45">
-        <f>+J11/F11-1</f>
+      <c r="J37" s="41">
+        <f t="shared" si="234"/>
         <v>0.77944170474596208</v>
       </c>
-      <c r="K37" s="45">
-        <f>+K11/G11-1</f>
+      <c r="K37" s="41">
+        <f t="shared" si="234"/>
         <v>0.69182921210259551</v>
       </c>
-      <c r="L37" s="45">
-        <f>+L11/H11-1</f>
+      <c r="L37" s="41">
+        <f t="shared" si="234"/>
         <v>0.5560252996005326</v>
       </c>
-      <c r="M37" s="45">
-        <f>+M11/I11-1</f>
+      <c r="M37" s="41">
+        <f t="shared" si="234"/>
         <v>0.62493586454592109</v>
       </c>
-      <c r="N37" s="45"/>
-      <c r="O37" s="46"/>
-      <c r="P37" s="46"/>
-      <c r="Q37" s="45"/>
-      <c r="R37" s="45"/>
-      <c r="S37" s="45"/>
-      <c r="T37" s="45"/>
-      <c r="U37" s="45"/>
-      <c r="V37" s="45">
+      <c r="N37" s="41"/>
+      <c r="O37" s="42"/>
+      <c r="P37" s="42"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="41"/>
+      <c r="S37" s="41"/>
+      <c r="T37" s="41"/>
+      <c r="U37" s="41"/>
+      <c r="V37" s="41">
         <f t="shared" ref="V37" si="251">+V11/U11-1</f>
         <v>-6.8111983612154314E-2</v>
       </c>
-      <c r="W37" s="45">
+      <c r="W37" s="41">
         <f t="shared" ref="W37:X37" si="252">+W11/V11-1</f>
         <v>0.52729437625938824</v>
       </c>
-      <c r="X37" s="45">
+      <c r="X37" s="41">
         <f t="shared" si="252"/>
         <v>0.61403298350824587</v>
       </c>
-      <c r="Y37" s="45">
+      <c r="Y37" s="41">
         <f t="shared" ref="Y37" si="253">+Y11/X11-1</f>
         <v>2.2293230289069932E-3</v>
       </c>
-      <c r="Z37" s="45">
-        <f>+Z11/Y11-1</f>
+      <c r="Z37" s="41">
+        <f t="shared" si="235"/>
         <v>1.2585452658115224</v>
       </c>
-      <c r="AA37" s="45">
-        <f>+AA11/Z11-1</f>
+      <c r="AA37" s="41">
+        <f t="shared" si="235"/>
         <v>1.1420340763599355</v>
       </c>
-      <c r="AB37" s="45">
+      <c r="AB37" s="41">
         <f t="shared" ref="AB37" si="254">+AB11/AA11-1</f>
         <v>0.63077312122117757</v>
       </c>
-      <c r="AC37" s="45">
+      <c r="AC37" s="41">
         <f t="shared" ref="AC37" si="255">+AC11/AB11-1</f>
         <v>0.30000000000000004</v>
       </c>
-      <c r="AD37" s="45">
+      <c r="AD37" s="41">
         <f t="shared" ref="AD37" si="256">+AD11/AC11-1</f>
         <v>0.25</v>
       </c>
-      <c r="AE37" s="45">
+      <c r="AE37" s="41">
         <f t="shared" ref="AE37" si="257">+AE11/AD11-1</f>
         <v>0.19999999999999996</v>
       </c>
-      <c r="AF37" s="45">
+      <c r="AF37" s="41">
         <f t="shared" ref="AF37" si="258">+AF11/AE11-1</f>
         <v>0.19999999999999996</v>
       </c>
-      <c r="AG37" s="45">
+      <c r="AG37" s="41">
         <f t="shared" ref="AG37" si="259">+AG11/AF11-1</f>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AH37" s="45">
+      <c r="AH37" s="41">
         <f t="shared" ref="AH37" si="260">+AH11/AG11-1</f>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AI37" s="45">
+      <c r="AI37" s="41">
         <f t="shared" ref="AI37" si="261">+AI11/AH11-1</f>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AJ37" s="45">
+      <c r="AJ37" s="41">
         <f t="shared" ref="AJ37:AK37" si="262">+AJ11/AI11-1</f>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AK37" s="45">
+      <c r="AK37" s="41">
         <f t="shared" si="262"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AL37" s="47"/>
+      <c r="AL37" s="43"/>
     </row>
     <row r="38" spans="2:39" x14ac:dyDescent="0.15">
-      <c r="C38" s="49"/>
-      <c r="D38" s="49"/>
-      <c r="E38" s="49"/>
-      <c r="F38" s="49"/>
-      <c r="G38" s="49"/>
-      <c r="H38" s="49"/>
-      <c r="I38" s="49"/>
-      <c r="J38" s="49"/>
-      <c r="K38" s="49"/>
-      <c r="L38" s="49"/>
-      <c r="M38" s="49"/>
-      <c r="N38" s="49"/>
-      <c r="O38" s="50"/>
-      <c r="P38" s="50"/>
-      <c r="Q38" s="49"/>
-      <c r="R38" s="49"/>
-      <c r="S38" s="49"/>
-      <c r="T38" s="49"/>
-      <c r="U38" s="49"/>
-      <c r="V38" s="49"/>
-      <c r="W38" s="49"/>
-      <c r="X38" s="49"/>
-      <c r="Y38" s="49"/>
-      <c r="Z38" s="49"/>
-      <c r="AA38" s="49"/>
-      <c r="AB38" s="49"/>
-      <c r="AC38" s="49"/>
-      <c r="AD38" s="49"/>
-      <c r="AE38" s="49"/>
-      <c r="AF38" s="49"/>
-      <c r="AG38" s="49"/>
-      <c r="AH38" s="49"/>
-      <c r="AI38" s="49"/>
-      <c r="AJ38" s="49"/>
-      <c r="AK38" s="49"/>
+      <c r="B38" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="44"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="44"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="44"/>
+      <c r="H38" s="44"/>
+      <c r="I38" s="38">
+        <f>+I49/E49-1</f>
+        <v>1.1053005853071496</v>
+      </c>
+      <c r="J38" s="38">
+        <f>+J49/F49-1</f>
+        <v>0.6629464285714286</v>
+      </c>
+      <c r="K38" s="38">
+        <f>+K49/G49-1</f>
+        <v>0.70783764870538834</v>
+      </c>
+      <c r="L38" s="38">
+        <f>+L49/H49-1</f>
+        <v>0.63192528735632192</v>
+      </c>
+      <c r="M38" s="38">
+        <f>+M49/I49-1</f>
+        <v>0.57476550523553405</v>
+      </c>
+      <c r="N38" s="44"/>
+      <c r="O38" s="45"/>
+      <c r="P38" s="45"/>
+      <c r="Q38" s="44"/>
+      <c r="R38" s="44"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="44"/>
+      <c r="V38" s="44"/>
+      <c r="W38" s="44"/>
+      <c r="X38" s="44"/>
+      <c r="Y38" s="44"/>
+      <c r="Z38" s="44"/>
+      <c r="AA38" s="44"/>
+      <c r="AB38" s="44"/>
+      <c r="AC38" s="44"/>
+      <c r="AD38" s="44"/>
+      <c r="AE38" s="44"/>
+      <c r="AF38" s="44"/>
+      <c r="AG38" s="44"/>
+      <c r="AH38" s="44"/>
+      <c r="AI38" s="44"/>
+      <c r="AJ38" s="44"/>
+      <c r="AK38" s="44"/>
     </row>
     <row r="39" spans="2:39" x14ac:dyDescent="0.15">
-      <c r="B39" s="27" t="s">
-        <v>212</v>
-      </c>
-      <c r="C39" s="49"/>
-      <c r="D39" s="49"/>
-      <c r="E39" s="49"/>
-      <c r="F39" s="49"/>
-      <c r="G39" s="49"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="49"/>
-      <c r="K39" s="49"/>
-      <c r="L39" s="49"/>
-      <c r="M39" s="49"/>
-      <c r="N39" s="49"/>
-      <c r="O39" s="50"/>
-      <c r="P39" s="50"/>
-      <c r="Q39" s="49"/>
-      <c r="R39" s="49"/>
-      <c r="S39" s="49"/>
-      <c r="T39" s="49"/>
-      <c r="U39" s="49"/>
-      <c r="V39" s="49"/>
-      <c r="W39" s="49"/>
-      <c r="X39" s="49"/>
-      <c r="Y39" s="49"/>
-      <c r="Z39" s="49"/>
-      <c r="AA39" s="49"/>
-      <c r="AB39" s="49"/>
-      <c r="AC39" s="49"/>
-      <c r="AD39" s="49"/>
-      <c r="AE39" s="49"/>
-      <c r="AF39" s="49"/>
-      <c r="AG39" s="49"/>
-      <c r="AH39" s="49"/>
-      <c r="AI39" s="49"/>
-      <c r="AJ39" s="49"/>
-      <c r="AK39" s="49"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="44"/>
+      <c r="F39" s="44"/>
+      <c r="G39" s="44"/>
+      <c r="H39" s="44"/>
+      <c r="I39" s="44"/>
+      <c r="J39" s="44"/>
+      <c r="K39" s="44"/>
+      <c r="L39" s="44"/>
+      <c r="M39" s="44"/>
+      <c r="N39" s="44"/>
+      <c r="O39" s="45"/>
+      <c r="P39" s="45"/>
+      <c r="Q39" s="44"/>
+      <c r="R39" s="44"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="44"/>
+      <c r="V39" s="44"/>
+      <c r="W39" s="44"/>
+      <c r="X39" s="44"/>
+      <c r="Y39" s="44"/>
+      <c r="Z39" s="44"/>
+      <c r="AA39" s="44"/>
+      <c r="AB39" s="44"/>
+      <c r="AC39" s="44"/>
+      <c r="AD39" s="44"/>
+      <c r="AE39" s="44"/>
+      <c r="AF39" s="44"/>
+      <c r="AG39" s="44"/>
+      <c r="AH39" s="44"/>
+      <c r="AI39" s="44"/>
+      <c r="AJ39" s="44"/>
+      <c r="AK39" s="44"/>
     </row>
     <row r="40" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B40" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" s="41">
-        <f>(C11-C16)/C11</f>
-        <v>0.64627363737486099</v>
-      </c>
-      <c r="D40" s="41">
-        <f>(D11-D16)/D11</f>
-        <v>0.7005256533649219</v>
-      </c>
-      <c r="E40" s="41">
-        <f>(E11-E16)/E11</f>
-        <v>0.73951434878587197</v>
-      </c>
-      <c r="F40" s="41">
-        <f>(F11-F16)/F11</f>
-        <v>0.75967063294575399</v>
-      </c>
-      <c r="G40" s="41">
-        <f>(G11-G16)/G11</f>
-        <v>0.78352019659038552</v>
-      </c>
-      <c r="H40" s="41">
-        <f>(H11-H16)/H11</f>
-        <v>0.75146471371504664</v>
-      </c>
-      <c r="I40" s="41">
-        <f>(I11-I16)/I11</f>
-        <v>0.74556752750698363</v>
-      </c>
-      <c r="J40" s="41">
-        <f>(J11-J16)/J11</f>
-        <v>0.73026365970862683</v>
-      </c>
-      <c r="K40" s="41">
-        <f>(K11-K16)/K11</f>
-        <v>0.60523807362353044</v>
-      </c>
-      <c r="L40" s="41">
-        <f>(L11-L16)/L11</f>
-        <v>0.72423678411740799</v>
-      </c>
-      <c r="M40" s="41">
-        <f>(M11-M16)/M11</f>
-        <v>0.7341157071185489</v>
-      </c>
-      <c r="N40" s="41">
-        <f>(N11-N16)/N11</f>
-        <v>0.74</v>
-      </c>
-      <c r="O40" s="50"/>
-      <c r="P40" s="50"/>
-      <c r="Q40" s="49"/>
-      <c r="R40" s="49"/>
-      <c r="S40" s="49"/>
-      <c r="T40" s="49"/>
-      <c r="U40" s="49"/>
-      <c r="V40" s="41">
-        <f>(V11-V16)/V11</f>
-        <v>0.61989375343469499</v>
-      </c>
-      <c r="W40" s="41">
-        <f>(W11-W16)/W11</f>
-        <v>0.62344827586206897</v>
-      </c>
-      <c r="X40" s="41">
-        <f>(X11-X16)/X11</f>
-        <v>0.64929033216913135</v>
-      </c>
-      <c r="Y40" s="41">
-        <f>(Y11-Y16)/Y11</f>
-        <v>0.56928894490991322</v>
-      </c>
-      <c r="Z40" s="41">
-        <f>(Z11-Z16)/Z11</f>
-        <v>0.72717573290436954</v>
-      </c>
-      <c r="AA40" s="41">
-        <f>(AA11-AA16)/AA11</f>
-        <v>0.74988697058169917</v>
-      </c>
-      <c r="AB40" s="41">
-        <f>(AB11-AB16)/AB11</f>
-        <v>0.70705931554289958</v>
-      </c>
-      <c r="AC40" s="41">
-        <f>(AC11-AC16)/AC11</f>
-        <v>0.70705931554289958</v>
-      </c>
-      <c r="AD40" s="41">
-        <f>(AD11-AD16)/AD11</f>
-        <v>0.70705931554289958</v>
-      </c>
-      <c r="AE40" s="41">
-        <f>(AE11-AE16)/AE11</f>
-        <v>0.70705931554289958</v>
-      </c>
-      <c r="AF40" s="41">
-        <f>(AF11-AF16)/AF11</f>
-        <v>0.70705931554289958</v>
-      </c>
-      <c r="AG40" s="41">
-        <f>(AG11-AG16)/AG11</f>
-        <v>0.70705931554289947</v>
-      </c>
-      <c r="AH40" s="41">
-        <f>(AH11-AH16)/AH11</f>
-        <v>0.70705931554289958</v>
-      </c>
-      <c r="AI40" s="41">
-        <f>(AI11-AI16)/AI11</f>
-        <v>0.70705931554289958</v>
-      </c>
-      <c r="AJ40" s="41">
-        <f>(AJ11-AJ16)/AJ11</f>
-        <v>0.70705931554289958</v>
-      </c>
-      <c r="AK40" s="41">
-        <f>(AK11-AK16)/AK11</f>
-        <v>0.70705931554289958</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="C40" s="44"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="44"/>
+      <c r="F40" s="44"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="44"/>
+      <c r="I40" s="44"/>
+      <c r="J40" s="44"/>
+      <c r="K40" s="44"/>
+      <c r="L40" s="44"/>
+      <c r="M40" s="44"/>
+      <c r="N40" s="44"/>
+      <c r="O40" s="45"/>
+      <c r="P40" s="45"/>
+      <c r="Q40" s="44"/>
+      <c r="R40" s="44"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="44"/>
+      <c r="V40" s="44"/>
+      <c r="W40" s="44"/>
+      <c r="X40" s="44"/>
+      <c r="Y40" s="44"/>
+      <c r="Z40" s="44"/>
+      <c r="AA40" s="44"/>
+      <c r="AB40" s="44"/>
+      <c r="AC40" s="44"/>
+      <c r="AD40" s="44"/>
+      <c r="AE40" s="44"/>
+      <c r="AF40" s="44"/>
+      <c r="AG40" s="44"/>
+      <c r="AH40" s="44"/>
+      <c r="AI40" s="44"/>
+      <c r="AJ40" s="44"/>
+      <c r="AK40" s="44"/>
     </row>
     <row r="41" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B41" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" s="38">
+        <f t="shared" ref="C41:N41" si="263">(C11-C16)/C11</f>
+        <v>0.64627363737486099</v>
+      </c>
+      <c r="D41" s="38">
+        <f t="shared" si="263"/>
+        <v>0.7005256533649219</v>
+      </c>
+      <c r="E41" s="38">
+        <f t="shared" si="263"/>
+        <v>0.73951434878587197</v>
+      </c>
+      <c r="F41" s="38">
+        <f t="shared" si="263"/>
+        <v>0.75967063294575399</v>
+      </c>
+      <c r="G41" s="38">
+        <f t="shared" si="263"/>
+        <v>0.78352019659038552</v>
+      </c>
+      <c r="H41" s="38">
+        <f t="shared" si="263"/>
+        <v>0.75146471371504664</v>
+      </c>
+      <c r="I41" s="38">
+        <f t="shared" si="263"/>
+        <v>0.74556752750698363</v>
+      </c>
+      <c r="J41" s="38">
+        <f t="shared" si="263"/>
+        <v>0.73026365970862683</v>
+      </c>
+      <c r="K41" s="38">
+        <f t="shared" si="263"/>
+        <v>0.60523807362353044</v>
+      </c>
+      <c r="L41" s="38">
+        <f t="shared" si="263"/>
+        <v>0.72423678411740799</v>
+      </c>
+      <c r="M41" s="38">
+        <f t="shared" si="263"/>
+        <v>0.7341157071185489</v>
+      </c>
+      <c r="N41" s="38">
+        <f t="shared" si="263"/>
+        <v>0.74</v>
+      </c>
+      <c r="O41" s="45"/>
+      <c r="P41" s="45"/>
+      <c r="Q41" s="44"/>
+      <c r="R41" s="44"/>
+      <c r="S41" s="44"/>
+      <c r="T41" s="44"/>
+      <c r="U41" s="44"/>
+      <c r="V41" s="38">
+        <f t="shared" ref="V41:AK41" si="264">(V11-V16)/V11</f>
+        <v>0.61989375343469499</v>
+      </c>
+      <c r="W41" s="38">
+        <f t="shared" si="264"/>
+        <v>0.62344827586206897</v>
+      </c>
+      <c r="X41" s="38">
+        <f t="shared" si="264"/>
+        <v>0.64929033216913135</v>
+      </c>
+      <c r="Y41" s="38">
+        <f t="shared" si="264"/>
+        <v>0.56928894490991322</v>
+      </c>
+      <c r="Z41" s="38">
+        <f t="shared" si="264"/>
+        <v>0.72717573290436954</v>
+      </c>
+      <c r="AA41" s="38">
+        <f t="shared" si="264"/>
+        <v>0.74988697058169917</v>
+      </c>
+      <c r="AB41" s="38">
+        <f t="shared" si="264"/>
+        <v>0.70705931554289958</v>
+      </c>
+      <c r="AC41" s="38">
+        <f t="shared" si="264"/>
+        <v>0.70705931554289958</v>
+      </c>
+      <c r="AD41" s="38">
+        <f t="shared" si="264"/>
+        <v>0.70705931554289958</v>
+      </c>
+      <c r="AE41" s="38">
+        <f t="shared" si="264"/>
+        <v>0.70705931554289958</v>
+      </c>
+      <c r="AF41" s="38">
+        <f t="shared" si="264"/>
+        <v>0.70705931554289958</v>
+      </c>
+      <c r="AG41" s="38">
+        <f t="shared" si="264"/>
+        <v>0.70705931554289947</v>
+      </c>
+      <c r="AH41" s="38">
+        <f t="shared" si="264"/>
+        <v>0.70705931554289958</v>
+      </c>
+      <c r="AI41" s="38">
+        <f t="shared" si="264"/>
+        <v>0.70705931554289958</v>
+      </c>
+      <c r="AJ41" s="38">
+        <f t="shared" si="264"/>
+        <v>0.70705931554289958</v>
+      </c>
+      <c r="AK41" s="38">
+        <f t="shared" si="264"/>
+        <v>0.70705931554289958</v>
+      </c>
+    </row>
+    <row r="42" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="B42" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="41">
+      <c r="C42" s="38">
         <f>+C16/C11</f>
         <v>0.35372636262513907</v>
       </c>
-      <c r="D41" s="41">
-        <f t="shared" ref="D41:N41" si="263">+D16/D11</f>
+      <c r="D42" s="38">
+        <f t="shared" ref="D42:N42" si="265">+D16/D11</f>
         <v>0.2994743466350781</v>
       </c>
-      <c r="E41" s="41">
-        <f t="shared" si="263"/>
+      <c r="E42" s="38">
+        <f t="shared" si="265"/>
         <v>0.26048565121412803</v>
       </c>
-      <c r="F41" s="41">
-        <f t="shared" si="263"/>
+      <c r="F42" s="38">
+        <f t="shared" si="265"/>
         <v>0.24032936705424604</v>
       </c>
-      <c r="G41" s="41">
-        <f t="shared" si="263"/>
+      <c r="G42" s="38">
+        <f t="shared" si="265"/>
         <v>0.21647980340961451</v>
       </c>
-      <c r="H41" s="41">
-        <f t="shared" si="263"/>
+      <c r="H42" s="38">
+        <f t="shared" si="265"/>
         <v>0.24853528628495339</v>
       </c>
-      <c r="I41" s="41">
-        <f t="shared" si="263"/>
+      <c r="I42" s="38">
+        <f t="shared" si="265"/>
         <v>0.25443247249301637</v>
       </c>
-      <c r="J41" s="41">
-        <f t="shared" si="263"/>
+      <c r="J42" s="38">
+        <f t="shared" si="265"/>
         <v>0.26973634029137322</v>
       </c>
-      <c r="K41" s="41">
-        <f t="shared" si="263"/>
+      <c r="K42" s="38">
+        <f t="shared" si="265"/>
         <v>0.39476192637646951</v>
       </c>
-      <c r="L41" s="41">
-        <f t="shared" si="263"/>
+      <c r="L42" s="38">
+        <f t="shared" si="265"/>
         <v>0.27576321588259206</v>
       </c>
-      <c r="M41" s="41">
-        <f t="shared" si="263"/>
+      <c r="M42" s="38">
+        <f t="shared" si="265"/>
         <v>0.2658842928814511</v>
       </c>
-      <c r="N41" s="41">
-        <f t="shared" si="263"/>
+      <c r="N42" s="38">
+        <f t="shared" si="265"/>
         <v>0.26</v>
       </c>
-      <c r="O41" s="50"/>
-      <c r="P41" s="50"/>
-      <c r="Q41" s="49"/>
-      <c r="R41" s="49"/>
-      <c r="S41" s="49"/>
-      <c r="T41" s="49"/>
-      <c r="U41" s="49"/>
-      <c r="V41" s="41">
-        <f t="shared" ref="V41:AA41" si="264">+V16/V11</f>
+      <c r="O42" s="45"/>
+      <c r="P42" s="45"/>
+      <c r="Q42" s="44"/>
+      <c r="R42" s="44"/>
+      <c r="S42" s="44"/>
+      <c r="T42" s="44"/>
+      <c r="U42" s="44"/>
+      <c r="V42" s="38">
+        <f t="shared" ref="V42:AA42" si="266">+V16/V11</f>
         <v>0.38010624656530501</v>
       </c>
-      <c r="W41" s="41">
-        <f t="shared" si="264"/>
+      <c r="W42" s="38">
+        <f t="shared" si="266"/>
         <v>0.37655172413793103</v>
       </c>
-      <c r="X41" s="41">
-        <f t="shared" si="264"/>
+      <c r="X42" s="38">
+        <f t="shared" si="266"/>
         <v>0.35070966783086871</v>
       </c>
-      <c r="Y41" s="41">
-        <f t="shared" si="264"/>
+      <c r="Y42" s="38">
+        <f t="shared" si="266"/>
         <v>0.43071105509008673</v>
       </c>
-      <c r="Z41" s="41">
-        <f t="shared" si="264"/>
+      <c r="Z42" s="38">
+        <f t="shared" si="266"/>
         <v>0.27282426709563046</v>
       </c>
-      <c r="AA41" s="41">
-        <f t="shared" si="264"/>
+      <c r="AA42" s="38">
+        <f t="shared" si="266"/>
         <v>0.25011302941830083</v>
       </c>
-      <c r="AB41" s="41">
-        <f t="shared" ref="AB41:AK41" si="265">+AB16/AB11</f>
+      <c r="AB42" s="38">
+        <f t="shared" ref="AB42:AK42" si="267">+AB16/AB11</f>
         <v>0.29294068445710042</v>
       </c>
-      <c r="AC41" s="41">
-        <f t="shared" si="265"/>
+      <c r="AC42" s="38">
+        <f t="shared" si="267"/>
         <v>0.29294068445710042</v>
       </c>
-      <c r="AD41" s="41">
-        <f t="shared" si="265"/>
+      <c r="AD42" s="38">
+        <f t="shared" si="267"/>
         <v>0.29294068445710042</v>
       </c>
-      <c r="AE41" s="41">
-        <f t="shared" si="265"/>
+      <c r="AE42" s="38">
+        <f t="shared" si="267"/>
         <v>0.29294068445710042</v>
       </c>
-      <c r="AF41" s="41">
-        <f t="shared" si="265"/>
+      <c r="AF42" s="38">
+        <f t="shared" si="267"/>
         <v>0.29294068445710042</v>
       </c>
-      <c r="AG41" s="41">
-        <f t="shared" si="265"/>
+      <c r="AG42" s="38">
+        <f t="shared" si="267"/>
         <v>0.29294068445710042</v>
       </c>
-      <c r="AH41" s="41">
-        <f t="shared" si="265"/>
+      <c r="AH42" s="38">
+        <f t="shared" si="267"/>
         <v>0.29294068445710042</v>
       </c>
-      <c r="AI41" s="41">
-        <f t="shared" si="265"/>
+      <c r="AI42" s="38">
+        <f t="shared" si="267"/>
         <v>0.29294068445710042</v>
       </c>
-      <c r="AJ41" s="41">
-        <f t="shared" si="265"/>
+      <c r="AJ42" s="38">
+        <f t="shared" si="267"/>
         <v>0.29294068445710042</v>
       </c>
-      <c r="AK41" s="41">
-        <f t="shared" si="265"/>
+      <c r="AK42" s="38">
+        <f t="shared" si="267"/>
         <v>0.29294068445710042</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.15">
-      <c r="B42" s="27" t="s">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="B43" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C42" s="41">
+      <c r="C43" s="38">
         <f>+C17/C11</f>
         <v>0.26070634037819801</v>
       </c>
-      <c r="D42" s="41">
-        <f t="shared" ref="D42:N42" si="266">+D17/D11</f>
+      <c r="D43" s="38">
+        <f t="shared" ref="D43:N43" si="268">+D17/D11</f>
         <v>0.15103279780854373</v>
       </c>
-      <c r="E42" s="41">
-        <f t="shared" si="266"/>
+      <c r="E43" s="38">
+        <f t="shared" si="268"/>
         <v>0.12660044150110375</v>
       </c>
-      <c r="F42" s="41">
-        <f t="shared" si="266"/>
+      <c r="F43" s="38">
+        <f t="shared" si="268"/>
         <v>0.11156856535311949</v>
       </c>
-      <c r="G42" s="41">
-        <f t="shared" si="266"/>
+      <c r="G43" s="38">
+        <f t="shared" si="268"/>
         <v>0.10443864229765012</v>
       </c>
-      <c r="H42" s="41">
-        <f t="shared" si="266"/>
+      <c r="H43" s="38">
+        <f t="shared" si="268"/>
         <v>0.10286284953395473</v>
       </c>
-      <c r="I42" s="41">
-        <f t="shared" si="266"/>
+      <c r="I43" s="38">
+        <f t="shared" si="268"/>
         <v>9.6630750812382413E-2</v>
       </c>
-      <c r="J42" s="41">
-        <f t="shared" si="266"/>
+      <c r="J43" s="38">
+        <f t="shared" si="268"/>
         <v>9.4429330553507412E-2</v>
       </c>
-      <c r="K42" s="41">
-        <f t="shared" si="266"/>
+      <c r="K43" s="38">
+        <f t="shared" si="268"/>
         <v>9.0531523761971766E-2</v>
       </c>
-      <c r="L42" s="41">
-        <f t="shared" si="266"/>
+      <c r="L43" s="38">
+        <f t="shared" si="268"/>
         <v>9.1799841687525405E-2</v>
       </c>
-      <c r="M42" s="41">
-        <f t="shared" si="266"/>
+      <c r="M43" s="38">
+        <f t="shared" si="268"/>
         <v>8.2535171736308463E-2</v>
       </c>
-      <c r="N42" s="41">
-        <f t="shared" si="266"/>
+      <c r="N43" s="38">
+        <f t="shared" si="268"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="O42" s="50"/>
-      <c r="P42" s="50"/>
-      <c r="Q42" s="49"/>
-      <c r="R42" s="49"/>
-      <c r="S42" s="49"/>
-      <c r="T42" s="49"/>
-      <c r="U42" s="49"/>
-      <c r="V42" s="41">
-        <f t="shared" ref="V42:AA42" si="267">+V17/V11</f>
+      <c r="O43" s="45"/>
+      <c r="P43" s="45"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="44"/>
+      <c r="V43" s="38">
+        <f t="shared" ref="V43:AA43" si="269">+V17/V11</f>
         <v>0.25911339073090311</v>
       </c>
-      <c r="W42" s="41">
-        <f t="shared" si="267"/>
+      <c r="W43" s="38">
+        <f t="shared" si="269"/>
         <v>0.2353223388305847</v>
       </c>
-      <c r="X42" s="41">
-        <f t="shared" si="267"/>
+      <c r="X43" s="38">
+        <f t="shared" si="269"/>
         <v>0.19573456193802483</v>
       </c>
-      <c r="Y42" s="41">
-        <f t="shared" si="267"/>
+      <c r="Y43" s="38">
+        <f t="shared" si="269"/>
         <v>0.27207681471046191</v>
       </c>
-      <c r="Z42" s="41">
-        <f t="shared" si="267"/>
+      <c r="Z43" s="38">
+        <f t="shared" si="269"/>
         <v>0.14239519385443683</v>
       </c>
-      <c r="AA42" s="41">
-        <f t="shared" si="267"/>
+      <c r="AA43" s="38">
+        <f t="shared" si="269"/>
         <v>9.8960129351632606E-2</v>
       </c>
-      <c r="AB42" s="41">
-        <f t="shared" ref="AB42:AK42" si="268">+AB17/AB11</f>
+      <c r="AB43" s="38">
+        <f t="shared" ref="AB43:AK43" si="270">+AB17/AB11</f>
         <v>8.4511608892397477E-2</v>
       </c>
-      <c r="AC42" s="41">
-        <f t="shared" si="268"/>
+      <c r="AC43" s="38">
+        <f t="shared" si="270"/>
         <v>8.4511608892397477E-2</v>
       </c>
-      <c r="AD42" s="41">
-        <f t="shared" si="268"/>
+      <c r="AD43" s="38">
+        <f t="shared" si="270"/>
         <v>8.4511608892397477E-2</v>
       </c>
-      <c r="AE42" s="41">
-        <f t="shared" si="268"/>
+      <c r="AE43" s="38">
+        <f t="shared" si="270"/>
         <v>8.4511608892397477E-2</v>
       </c>
-      <c r="AF42" s="41">
-        <f t="shared" si="268"/>
+      <c r="AF43" s="38">
+        <f t="shared" si="270"/>
         <v>8.4511608892397477E-2</v>
       </c>
-      <c r="AG42" s="41">
-        <f t="shared" si="268"/>
+      <c r="AG43" s="38">
+        <f t="shared" si="270"/>
         <v>8.4511608892397477E-2</v>
       </c>
-      <c r="AH42" s="41">
-        <f t="shared" si="268"/>
+      <c r="AH43" s="38">
+        <f t="shared" si="270"/>
         <v>8.4511608892397477E-2</v>
       </c>
-      <c r="AI42" s="41">
-        <f t="shared" si="268"/>
+      <c r="AI43" s="38">
+        <f t="shared" si="270"/>
         <v>8.4511608892397477E-2</v>
       </c>
-      <c r="AJ42" s="41">
-        <f t="shared" si="268"/>
+      <c r="AJ43" s="38">
+        <f t="shared" si="270"/>
         <v>8.4511608892397477E-2</v>
       </c>
-      <c r="AK42" s="41">
-        <f t="shared" si="268"/>
+      <c r="AK43" s="38">
+        <f t="shared" si="270"/>
         <v>8.4511608892397477E-2</v>
       </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.15">
-      <c r="B43" s="27" t="s">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="B44" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C43" s="41">
+      <c r="C44" s="38">
         <f>+C18/C11</f>
         <v>8.8014460511679646E-2</v>
       </c>
-      <c r="D43" s="41">
-        <f t="shared" ref="D43:N43" si="269">+D18/D11</f>
+      <c r="D44" s="38">
+        <f t="shared" ref="D44:N44" si="271">+D18/D11</f>
         <v>4.6050196194565782E-2</v>
       </c>
-      <c r="E43" s="41">
-        <f t="shared" si="269"/>
+      <c r="E44" s="38">
+        <f t="shared" si="271"/>
         <v>3.8024282560706404E-2</v>
       </c>
-      <c r="F43" s="41">
-        <f t="shared" si="269"/>
+      <c r="F44" s="38">
+        <f t="shared" si="271"/>
         <v>3.2122336334434239E-2</v>
       </c>
-      <c r="G43" s="41">
-        <f t="shared" si="269"/>
+      <c r="G44" s="38">
+        <f t="shared" si="271"/>
         <v>2.9834126862233145E-2</v>
       </c>
-      <c r="H43" s="41">
-        <f t="shared" si="269"/>
+      <c r="H44" s="38">
+        <f t="shared" si="271"/>
         <v>2.8029294274300932E-2</v>
       </c>
-      <c r="I43" s="41">
-        <f t="shared" si="269"/>
+      <c r="I44" s="38">
+        <f t="shared" si="271"/>
         <v>2.5568667692833932E-2</v>
       </c>
-      <c r="J43" s="41">
-        <f t="shared" si="269"/>
+      <c r="J44" s="38">
+        <f t="shared" si="271"/>
         <v>2.478960616307747E-2</v>
       </c>
-      <c r="K43" s="41">
-        <f t="shared" si="269"/>
+      <c r="K44" s="38">
+        <f t="shared" si="271"/>
         <v>2.3625800009078116E-2</v>
       </c>
-      <c r="L43" s="41">
-        <f t="shared" si="269"/>
+      <c r="L44" s="38">
+        <f t="shared" si="271"/>
         <v>2.4003594121044861E-2</v>
       </c>
-      <c r="M43" s="41">
-        <f t="shared" si="269"/>
+      <c r="M44" s="38">
+        <f t="shared" si="271"/>
         <v>1.9892642879696873E-2</v>
       </c>
-      <c r="N43" s="41">
-        <f t="shared" si="269"/>
+      <c r="N44" s="38">
+        <f t="shared" si="271"/>
         <v>2.6153846153846153E-2</v>
       </c>
-      <c r="O43" s="50"/>
-      <c r="P43" s="50"/>
-      <c r="Q43" s="49"/>
-      <c r="R43" s="49"/>
-      <c r="S43" s="49"/>
-      <c r="T43" s="49"/>
-      <c r="U43" s="49"/>
-      <c r="V43" s="41">
-        <f t="shared" ref="V43:AA43" si="270">+V18/V11</f>
+      <c r="O44" s="45"/>
+      <c r="P44" s="45"/>
+      <c r="Q44" s="44"/>
+      <c r="R44" s="44"/>
+      <c r="S44" s="44"/>
+      <c r="T44" s="44"/>
+      <c r="U44" s="44"/>
+      <c r="V44" s="38">
+        <f t="shared" ref="V44:AA44" si="272">+V18/V11</f>
         <v>0.10010991023997069</v>
       </c>
-      <c r="W43" s="41">
-        <f t="shared" si="270"/>
+      <c r="W44" s="38">
+        <f t="shared" si="272"/>
         <v>0.11634182908545727</v>
       </c>
-      <c r="X43" s="41">
-        <f t="shared" si="270"/>
+      <c r="X44" s="38">
+        <f t="shared" si="272"/>
         <v>8.0478561343538674E-2</v>
       </c>
-      <c r="Y43" s="41">
-        <f t="shared" si="270"/>
+      <c r="Y44" s="38">
+        <f t="shared" si="272"/>
         <v>9.0457477570994288E-2</v>
       </c>
-      <c r="Z43" s="41">
-        <f t="shared" si="270"/>
+      <c r="Z44" s="38">
+        <f t="shared" si="272"/>
         <v>4.3563901382095135E-2</v>
       </c>
-      <c r="AA43" s="41">
-        <f t="shared" si="270"/>
+      <c r="AA44" s="38">
+        <f t="shared" si="272"/>
         <v>2.6751572833091947E-2</v>
       </c>
-      <c r="AB43" s="41">
-        <f t="shared" ref="AB43:AK43" si="271">+AB18/AB11</f>
+      <c r="AB44" s="38">
+        <f t="shared" ref="AB44:AK44" si="273">+AB18/AB11</f>
         <v>2.3480929087312218E-2</v>
       </c>
-      <c r="AC43" s="41">
-        <f t="shared" si="271"/>
+      <c r="AC44" s="38">
+        <f t="shared" si="273"/>
         <v>2.3480929087312218E-2</v>
       </c>
-      <c r="AD43" s="41">
-        <f t="shared" si="271"/>
+      <c r="AD44" s="38">
+        <f t="shared" si="273"/>
         <v>2.3480929087312218E-2</v>
       </c>
-      <c r="AE43" s="41">
-        <f t="shared" si="271"/>
+      <c r="AE44" s="38">
+        <f t="shared" si="273"/>
         <v>2.3480929087312218E-2</v>
       </c>
-      <c r="AF43" s="41">
-        <f t="shared" si="271"/>
+      <c r="AF44" s="38">
+        <f t="shared" si="273"/>
         <v>2.3480929087312218E-2</v>
       </c>
-      <c r="AG43" s="41">
-        <f t="shared" si="271"/>
+      <c r="AG44" s="38">
+        <f t="shared" si="273"/>
         <v>2.3480929087312218E-2</v>
       </c>
-      <c r="AH43" s="41">
-        <f t="shared" si="271"/>
+      <c r="AH44" s="38">
+        <f t="shared" si="273"/>
         <v>2.3480929087312218E-2</v>
       </c>
-      <c r="AI43" s="41">
-        <f t="shared" si="271"/>
+      <c r="AI44" s="38">
+        <f t="shared" si="273"/>
         <v>2.3480929087312218E-2</v>
       </c>
-      <c r="AJ43" s="41">
-        <f t="shared" si="271"/>
+      <c r="AJ44" s="38">
+        <f t="shared" si="273"/>
         <v>2.3480929087312218E-2</v>
       </c>
-      <c r="AK43" s="41">
-        <f t="shared" si="271"/>
+      <c r="AK44" s="38">
+        <f t="shared" si="273"/>
         <v>2.3480929087312214E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.15">
-      <c r="B44" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C44" s="41">
-        <f>+C19/C11</f>
-        <v>0.29755283648498332</v>
-      </c>
-      <c r="D44" s="41">
-        <f>+D19/D11</f>
-        <v>0.50344265936181243</v>
-      </c>
-      <c r="E44" s="41">
-        <f>+E19/E11</f>
-        <v>0.5748896247240618</v>
-      </c>
-      <c r="F44" s="41">
-        <f>+F19/F11</f>
-        <v>0.61597973125820027</v>
-      </c>
-      <c r="G44" s="41">
-        <f>+G19/G11</f>
-        <v>0.64924742743050223</v>
-      </c>
-      <c r="H44" s="41">
-        <f>+H19/H11</f>
-        <v>0.62057256990679099</v>
-      </c>
-      <c r="I44" s="41">
-        <f>+I19/I11</f>
-        <v>0.62336810900176731</v>
-      </c>
-      <c r="J44" s="41">
-        <f>+J19/J11</f>
-        <v>0.61104472299204193</v>
-      </c>
-      <c r="K44" s="41">
-        <f>+K19/K11</f>
-        <v>0.49108074985248057</v>
-      </c>
-      <c r="L44" s="41">
-        <f>+L19/L11</f>
-        <v>0.60843334830883766</v>
-      </c>
-      <c r="M44" s="41">
-        <f>+M19/M11</f>
-        <v>0.63168789250254365</v>
-      </c>
-      <c r="N44" s="41">
-        <f>+N19/N11</f>
-        <v>0.63692307692307693</v>
-      </c>
-      <c r="O44" s="50"/>
-      <c r="P44" s="50"/>
-      <c r="Q44" s="49"/>
-      <c r="R44" s="49"/>
-      <c r="S44" s="49"/>
-      <c r="T44" s="49"/>
-      <c r="U44" s="49"/>
-      <c r="V44" s="41">
-        <f>+V19/V11</f>
-        <v>0.2606704524638212</v>
-      </c>
-      <c r="W44" s="41">
-        <f>+W19/W11</f>
-        <v>0.27178410794602698</v>
-      </c>
-      <c r="X44" s="41">
-        <f>+X19/X11</f>
-        <v>0.37307720888756779</v>
-      </c>
-      <c r="Y44" s="41">
-        <f>+Y19/Y11</f>
-        <v>0.20675465262845702</v>
-      </c>
-      <c r="Z44" s="41">
-        <f>+Z19/Z11</f>
-        <v>0.54121663766783756</v>
-      </c>
-      <c r="AA44" s="41">
-        <f>+AA19/AA11</f>
-        <v>0.62417526839697468</v>
-      </c>
-      <c r="AB44" s="41">
-        <f>+AB19/AB11</f>
-        <v>0.59906677756318982</v>
-      </c>
-      <c r="AC44" s="41">
-        <f>+AC19/AC11</f>
-        <v>0.59906677756318982</v>
-      </c>
-      <c r="AD44" s="41">
-        <f>+AD19/AD11</f>
-        <v>0.59906677756318982</v>
-      </c>
-      <c r="AE44" s="41">
-        <f>+AE19/AE11</f>
-        <v>0.59906677756318982</v>
-      </c>
-      <c r="AF44" s="41">
-        <f>+AF19/AF11</f>
-        <v>0.59906677756318982</v>
-      </c>
-      <c r="AG44" s="41">
-        <f>+AG19/AG11</f>
-        <v>0.59906677756318993</v>
-      </c>
-      <c r="AH44" s="41">
-        <f>+AH19/AH11</f>
-        <v>0.59906677756318982</v>
-      </c>
-      <c r="AI44" s="41">
-        <f>+AI19/AI11</f>
-        <v>0.59906677756318993</v>
-      </c>
-      <c r="AJ44" s="41">
-        <f>+AJ19/AJ11</f>
-        <v>0.59906677756318993</v>
-      </c>
-      <c r="AK44" s="41">
-        <f>+AK19/AK11</f>
-        <v>0.59906677756318982</v>
       </c>
     </row>
     <row r="45" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B45" s="27" t="s">
-        <v>213</v>
-      </c>
-      <c r="C45" s="41">
+        <v>44</v>
+      </c>
+      <c r="C45" s="38">
+        <f t="shared" ref="C45:N45" si="274">+C19/C11</f>
+        <v>0.29755283648498332</v>
+      </c>
+      <c r="D45" s="38">
+        <f t="shared" si="274"/>
+        <v>0.50344265936181243</v>
+      </c>
+      <c r="E45" s="38">
+        <f t="shared" si="274"/>
+        <v>0.5748896247240618</v>
+      </c>
+      <c r="F45" s="38">
+        <f t="shared" si="274"/>
+        <v>0.61597973125820027</v>
+      </c>
+      <c r="G45" s="38">
+        <f t="shared" si="274"/>
+        <v>0.64924742743050223</v>
+      </c>
+      <c r="H45" s="38">
+        <f t="shared" si="274"/>
+        <v>0.62057256990679099</v>
+      </c>
+      <c r="I45" s="38">
+        <f t="shared" si="274"/>
+        <v>0.62336810900176731</v>
+      </c>
+      <c r="J45" s="38">
+        <f t="shared" si="274"/>
+        <v>0.61104472299204193</v>
+      </c>
+      <c r="K45" s="38">
+        <f t="shared" si="274"/>
+        <v>0.49108074985248057</v>
+      </c>
+      <c r="L45" s="38">
+        <f t="shared" si="274"/>
+        <v>0.60843334830883766</v>
+      </c>
+      <c r="M45" s="38">
+        <f t="shared" si="274"/>
+        <v>0.63168789250254365</v>
+      </c>
+      <c r="N45" s="38">
+        <f t="shared" si="274"/>
+        <v>0.63692307692307693</v>
+      </c>
+      <c r="O45" s="45"/>
+      <c r="P45" s="45"/>
+      <c r="Q45" s="44"/>
+      <c r="R45" s="44"/>
+      <c r="S45" s="44"/>
+      <c r="T45" s="44"/>
+      <c r="U45" s="44"/>
+      <c r="V45" s="38">
+        <f t="shared" ref="V45:AK45" si="275">+V19/V11</f>
+        <v>0.2606704524638212</v>
+      </c>
+      <c r="W45" s="38">
+        <f t="shared" si="275"/>
+        <v>0.27178410794602698</v>
+      </c>
+      <c r="X45" s="38">
+        <f t="shared" si="275"/>
+        <v>0.37307720888756779</v>
+      </c>
+      <c r="Y45" s="38">
+        <f t="shared" si="275"/>
+        <v>0.20675465262845702</v>
+      </c>
+      <c r="Z45" s="38">
+        <f t="shared" si="275"/>
+        <v>0.54121663766783756</v>
+      </c>
+      <c r="AA45" s="38">
+        <f t="shared" si="275"/>
+        <v>0.62417526839697468</v>
+      </c>
+      <c r="AB45" s="38">
+        <f t="shared" si="275"/>
+        <v>0.59906677756318982</v>
+      </c>
+      <c r="AC45" s="38">
+        <f t="shared" si="275"/>
+        <v>0.59906677756318982</v>
+      </c>
+      <c r="AD45" s="38">
+        <f t="shared" si="275"/>
+        <v>0.59906677756318982</v>
+      </c>
+      <c r="AE45" s="38">
+        <f t="shared" si="275"/>
+        <v>0.59906677756318982</v>
+      </c>
+      <c r="AF45" s="38">
+        <f t="shared" si="275"/>
+        <v>0.59906677756318982</v>
+      </c>
+      <c r="AG45" s="38">
+        <f t="shared" si="275"/>
+        <v>0.59906677756318993</v>
+      </c>
+      <c r="AH45" s="38">
+        <f t="shared" si="275"/>
+        <v>0.59906677756318982</v>
+      </c>
+      <c r="AI45" s="38">
+        <f t="shared" si="275"/>
+        <v>0.59906677756318993</v>
+      </c>
+      <c r="AJ45" s="38">
+        <f t="shared" si="275"/>
+        <v>0.59906677756318993</v>
+      </c>
+      <c r="AK45" s="38">
+        <f t="shared" si="275"/>
+        <v>0.59906677756318982</v>
+      </c>
+    </row>
+    <row r="46" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="B46" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="C46" s="38">
         <f>+C23/C11</f>
         <v>0.30714682981090102</v>
       </c>
-      <c r="D45" s="41">
-        <f t="shared" ref="D45:N45" si="272">+D23/D11</f>
+      <c r="D46" s="38">
+        <f t="shared" ref="D46:N46" si="276">+D23/D11</f>
         <v>0.51684311838306063</v>
       </c>
-      <c r="E45" s="41">
-        <f t="shared" si="272"/>
+      <c r="E46" s="38">
+        <f t="shared" si="276"/>
         <v>0.58068432671081682</v>
       </c>
-      <c r="F45" s="41">
-        <f t="shared" si="272"/>
+      <c r="F46" s="38">
+        <f t="shared" si="276"/>
         <v>0.63819391032891459</v>
       </c>
-      <c r="G45" s="41">
-        <f t="shared" si="272"/>
+      <c r="G46" s="38">
+        <f t="shared" si="276"/>
         <v>0.65969129166026719</v>
       </c>
-      <c r="H45" s="41">
-        <f t="shared" si="272"/>
+      <c r="H46" s="38">
+        <f t="shared" si="276"/>
         <v>0.63961384820239675</v>
       </c>
-      <c r="I45" s="41">
-        <f t="shared" si="272"/>
+      <c r="I46" s="38">
+        <f t="shared" si="276"/>
         <v>0.63610968587879824</v>
       </c>
-      <c r="J45" s="41">
-        <f t="shared" si="272"/>
+      <c r="J46" s="38">
+        <f t="shared" si="276"/>
         <v>0.64363987694185243</v>
       </c>
-      <c r="K45" s="41">
-        <f t="shared" si="272"/>
+      <c r="K46" s="38">
+        <f t="shared" si="276"/>
         <v>0.49725386954745587</v>
       </c>
-      <c r="L45" s="41">
-        <f t="shared" si="272"/>
+      <c r="L46" s="38">
+        <f t="shared" si="276"/>
         <v>0.67026078771152897</v>
       </c>
-      <c r="M45" s="41">
-        <f t="shared" si="272"/>
+      <c r="M46" s="38">
+        <f t="shared" si="276"/>
         <v>0.66547380977440973</v>
       </c>
-      <c r="N45" s="41">
-        <f t="shared" si="272"/>
+      <c r="N46" s="38">
+        <f t="shared" si="276"/>
         <v>0.65457338773417628</v>
       </c>
-      <c r="O45" s="50"/>
-      <c r="P45" s="50"/>
-      <c r="Q45" s="49"/>
-      <c r="R45" s="49"/>
-      <c r="S45" s="49"/>
-      <c r="T45" s="49"/>
-      <c r="U45" s="41">
-        <f t="shared" ref="U45:V45" si="273">+U23/U11</f>
+      <c r="O46" s="45"/>
+      <c r="P46" s="45"/>
+      <c r="Q46" s="44"/>
+      <c r="R46" s="44"/>
+      <c r="S46" s="44"/>
+      <c r="T46" s="44"/>
+      <c r="U46" s="38">
+        <f t="shared" ref="U46:V46" si="277">+U23/U11</f>
         <v>0.33253670194605667</v>
       </c>
-      <c r="V45" s="41">
-        <f t="shared" si="273"/>
+      <c r="V46" s="38">
+        <f t="shared" si="277"/>
         <v>0.27202784392745927</v>
       </c>
-      <c r="W45" s="41">
-        <f t="shared" ref="W45:AB45" si="274">+W23/W11</f>
+      <c r="W46" s="38">
+        <f t="shared" ref="W46:AB46" si="278">+W23/W11</f>
         <v>0.26440779610194903</v>
       </c>
-      <c r="X45" s="41">
-        <f t="shared" si="274"/>
+      <c r="X46" s="38">
+        <f t="shared" si="278"/>
         <v>0.36936167050605634</v>
       </c>
-      <c r="Y45" s="41">
-        <f t="shared" si="274"/>
+      <c r="Y46" s="38">
+        <f t="shared" si="278"/>
         <v>0.20516052494995179</v>
       </c>
-      <c r="Z45" s="41">
-        <f t="shared" si="274"/>
+      <c r="Z46" s="38">
+        <f t="shared" si="278"/>
         <v>0.55510324677456424</v>
       </c>
-      <c r="AA45" s="41">
-        <f t="shared" si="274"/>
+      <c r="AA46" s="38">
+        <f t="shared" si="278"/>
         <v>0.64389219675548093</v>
       </c>
-      <c r="AB45" s="41">
-        <f t="shared" si="274"/>
+      <c r="AB46" s="38">
+        <f t="shared" ref="AB46:AC46" si="279">+AB23/AB11</f>
         <v>0.62836634479759723</v>
       </c>
-      <c r="AC45" s="49"/>
-      <c r="AD45" s="49"/>
-      <c r="AE45" s="49"/>
-      <c r="AF45" s="49"/>
-      <c r="AG45" s="49"/>
-      <c r="AH45" s="49"/>
-      <c r="AI45" s="49"/>
-      <c r="AJ45" s="49"/>
-      <c r="AK45" s="49"/>
-    </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.15">
-      <c r="B46" s="27" t="s">
-        <v>214</v>
-      </c>
-      <c r="C46" s="41">
+      <c r="AC46" s="38">
+        <f t="shared" si="279"/>
+        <v>0.62160490620504172</v>
+      </c>
+      <c r="AD46" s="38">
+        <f t="shared" ref="AD46:AK46" si="280">+AD23/AD11</f>
+        <v>0.61709728047667134</v>
+      </c>
+      <c r="AE46" s="38">
+        <f t="shared" si="280"/>
+        <v>0.61409219665775772</v>
+      </c>
+      <c r="AF46" s="38">
+        <f t="shared" si="280"/>
+        <v>0.61158796014199646</v>
+      </c>
+      <c r="AG46" s="38">
+        <f t="shared" si="280"/>
+        <v>0.61044967081665047</v>
+      </c>
+      <c r="AH46" s="38">
+        <f t="shared" si="280"/>
+        <v>0.60941486233906306</v>
+      </c>
+      <c r="AI46" s="38">
+        <f t="shared" si="280"/>
+        <v>0.60847412735943829</v>
+      </c>
+      <c r="AJ46" s="38">
+        <f t="shared" si="280"/>
+        <v>0.60761891374159749</v>
+      </c>
+      <c r="AK46" s="38">
+        <f t="shared" si="280"/>
+        <v>0.60684144681628771</v>
+      </c>
+    </row>
+    <row r="47" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="B47" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="C47" s="38">
         <f>+C24/C23</f>
         <v>7.5147125396106837E-2</v>
       </c>
-      <c r="D46" s="41">
-        <f t="shared" ref="D46:N46" si="275">+D24/D23</f>
+      <c r="D47" s="38">
+        <f t="shared" ref="D47:N47" si="281">+D24/D23</f>
         <v>0.11359404096834265</v>
       </c>
-      <c r="E46" s="41">
-        <f t="shared" si="275"/>
+      <c r="E47" s="38">
+        <f t="shared" si="281"/>
         <v>0.12155483748336818</v>
       </c>
-      <c r="F46" s="41">
-        <f t="shared" si="275"/>
+      <c r="F47" s="38">
+        <f t="shared" si="281"/>
         <v>0.12902311073302142</v>
       </c>
-      <c r="G46" s="41">
-        <f t="shared" si="275"/>
+      <c r="G47" s="38">
+        <f t="shared" si="281"/>
         <v>0.18246900646062511</v>
       </c>
-      <c r="H46" s="41">
-        <f t="shared" si="275"/>
+      <c r="H47" s="38">
+        <f t="shared" si="281"/>
         <v>0.1360986780472572</v>
       </c>
-      <c r="I46" s="41">
-        <f t="shared" si="275"/>
+      <c r="I47" s="38">
+        <f t="shared" si="281"/>
         <v>0.13474637031726117</v>
       </c>
-      <c r="J46" s="41">
-        <f t="shared" si="275"/>
+      <c r="J47" s="38">
+        <f t="shared" si="281"/>
         <v>-0.30065178747777999</v>
       </c>
-      <c r="K46" s="41">
-        <f t="shared" si="275"/>
+      <c r="K47" s="38">
+        <f t="shared" si="281"/>
         <v>0.1430853491556367</v>
       </c>
-      <c r="L46" s="41">
-        <f t="shared" si="275"/>
+      <c r="L47" s="38">
+        <f t="shared" si="281"/>
         <v>0.15269709543568466</v>
       </c>
-      <c r="M46" s="41">
-        <f t="shared" si="275"/>
+      <c r="M47" s="38">
+        <f t="shared" si="281"/>
         <v>0.15884647827920709</v>
       </c>
-      <c r="N46" s="41">
-        <f t="shared" si="275"/>
+      <c r="N47" s="38">
+        <f t="shared" si="281"/>
         <v>0.15884647827920709</v>
       </c>
-      <c r="O46" s="50"/>
-      <c r="P46" s="50"/>
-      <c r="Q46" s="49"/>
-      <c r="R46" s="49"/>
-      <c r="S46" s="49"/>
-      <c r="T46" s="49"/>
-      <c r="U46" s="41">
-        <f t="shared" ref="U46:V46" si="276">+U24/U23</f>
+      <c r="O47" s="45"/>
+      <c r="P47" s="45"/>
+      <c r="Q47" s="44"/>
+      <c r="R47" s="44"/>
+      <c r="S47" s="44"/>
+      <c r="T47" s="44"/>
+      <c r="U47" s="38">
+        <f t="shared" ref="U47:V47" si="282">+U24/U23</f>
         <v>-6.2885010266940447E-2</v>
       </c>
-      <c r="V46" s="41">
-        <f t="shared" si="276"/>
+      <c r="V47" s="38">
+        <f t="shared" si="282"/>
         <v>5.8585858585858588E-2</v>
       </c>
-      <c r="W46" s="41">
-        <f t="shared" ref="W46:AB46" si="277">+W24/W23</f>
+      <c r="W47" s="38">
+        <f t="shared" ref="W47:AB47" si="283">+W24/W23</f>
         <v>1.7464277613971423E-2</v>
       </c>
-      <c r="X46" s="41">
-        <f t="shared" si="277"/>
+      <c r="X47" s="38">
+        <f t="shared" si="283"/>
         <v>1.9012171813700834E-2</v>
       </c>
-      <c r="Y46" s="41">
-        <f t="shared" si="277"/>
+      <c r="Y47" s="38">
+        <f t="shared" si="283"/>
         <v>-3.379110950487893E-2</v>
       </c>
-      <c r="Z46" s="41">
-        <f t="shared" si="277"/>
+      <c r="Z47" s="38">
+        <f t="shared" si="283"/>
         <v>0.1199952687917677</v>
       </c>
-      <c r="AA46" s="41">
-        <f t="shared" si="277"/>
+      <c r="AA47" s="38">
+        <f t="shared" si="283"/>
         <v>1.3638635660390832E-2</v>
       </c>
-      <c r="AB46" s="41">
-        <f t="shared" si="277"/>
+      <c r="AB47" s="38">
+        <f t="shared" ref="AB47:AC47" si="284">+AB24/AB23</f>
         <v>0.15482334526152502</v>
       </c>
-      <c r="AC46" s="49"/>
-      <c r="AD46" s="49"/>
-      <c r="AE46" s="49"/>
-      <c r="AF46" s="49"/>
-      <c r="AG46" s="49"/>
-      <c r="AH46" s="49"/>
-      <c r="AI46" s="49"/>
-      <c r="AJ46" s="49"/>
-      <c r="AK46" s="49"/>
-    </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.15">
-      <c r="B48" s="27" t="s">
+      <c r="AC47" s="38">
+        <f t="shared" si="284"/>
+        <v>0.15482334526152502</v>
+      </c>
+      <c r="AD47" s="38">
+        <f t="shared" ref="AD47:AK47" si="285">+AD24/AD23</f>
+        <v>0.15482334526152502</v>
+      </c>
+      <c r="AE47" s="38">
+        <f t="shared" si="285"/>
+        <v>0.15482334526152502</v>
+      </c>
+      <c r="AF47" s="38">
+        <f t="shared" si="285"/>
+        <v>0.15482334526152502</v>
+      </c>
+      <c r="AG47" s="38">
+        <f t="shared" si="285"/>
+        <v>0.15482334526152502</v>
+      </c>
+      <c r="AH47" s="38">
+        <f t="shared" si="285"/>
+        <v>0.15482334526152502</v>
+      </c>
+      <c r="AI47" s="38">
+        <f t="shared" si="285"/>
+        <v>0.15482334526152502</v>
+      </c>
+      <c r="AJ47" s="38">
+        <f t="shared" si="285"/>
+        <v>0.15482334526152502</v>
+      </c>
+      <c r="AK47" s="38">
+        <f t="shared" si="285"/>
+        <v>0.15482334526152502</v>
+      </c>
+    </row>
+    <row r="49" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B49" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="24">
+      <c r="C49" s="24">
         <v>15320</v>
       </c>
-      <c r="D48" s="24">
+      <c r="D49" s="24">
         <v>16023</v>
       </c>
-      <c r="E48" s="24">
+      <c r="E49" s="24">
         <v>18281</v>
       </c>
-      <c r="F48" s="24">
+      <c r="F49" s="24">
         <v>25984</v>
       </c>
-      <c r="G48" s="24">
+      <c r="G49" s="24">
         <v>31438</v>
       </c>
-      <c r="H48" s="24">
+      <c r="H49" s="24">
         <v>34800</v>
       </c>
-      <c r="I48" s="24">
+      <c r="I49" s="24">
         <v>38487</v>
       </c>
-      <c r="J48" s="24">
+      <c r="J49" s="24">
         <v>43210</v>
       </c>
-      <c r="K48" s="24">
+      <c r="K49" s="24">
         <v>53691</v>
       </c>
-      <c r="L48" s="24">
+      <c r="L49" s="24">
         <f>11639+45152</f>
         <v>56791</v>
       </c>
-      <c r="M48" s="24">
+      <c r="M49" s="24">
         <v>60608</v>
       </c>
-      <c r="N48" s="24"/>
-    </row>
-    <row r="49" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B49" s="27" t="s">
+      <c r="N49" s="24"/>
+    </row>
+    <row r="50" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B50" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="C49" s="24">
+      <c r="C50" s="24">
         <v>4080</v>
       </c>
-      <c r="D49" s="24">
+      <c r="D50" s="24">
         <v>7066</v>
       </c>
-      <c r="E49" s="24">
+      <c r="E50" s="24">
         <v>8309</v>
       </c>
-      <c r="F49" s="24">
+      <c r="F50" s="24">
         <v>9999</v>
       </c>
-      <c r="G49" s="24">
+      <c r="G50" s="24">
         <v>12365</v>
       </c>
-      <c r="H49" s="24">
+      <c r="H50" s="24">
         <v>14132</v>
       </c>
-      <c r="I49" s="24">
+      <c r="I50" s="24">
         <v>17693</v>
       </c>
-      <c r="J49" s="24">
+      <c r="J50" s="24">
         <v>23065</v>
       </c>
-      <c r="K49" s="24">
+      <c r="K50" s="24">
         <v>22132</v>
       </c>
-      <c r="L49" s="24">
+      <c r="L50" s="24">
         <v>27808</v>
       </c>
-      <c r="M49" s="24">
+      <c r="M50" s="24">
         <v>33391</v>
       </c>
-      <c r="N49" s="24"/>
-    </row>
-    <row r="50" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B50" s="27" t="s">
+      <c r="N50" s="24"/>
+    </row>
+    <row r="51" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B51" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C50" s="24">
+      <c r="C51" s="24">
         <v>4611</v>
       </c>
-      <c r="D50" s="24">
+      <c r="D51" s="24">
         <v>4319</v>
       </c>
-      <c r="E50" s="24">
+      <c r="E51" s="24">
         <v>4779</v>
       </c>
-      <c r="F50" s="24">
+      <c r="F51" s="24">
         <v>5282</v>
       </c>
-      <c r="G50" s="24">
+      <c r="G51" s="24">
         <v>5864</v>
       </c>
-      <c r="H50" s="24">
+      <c r="H51" s="24">
         <v>6675</v>
       </c>
-      <c r="I50" s="24">
+      <c r="I51" s="24">
         <v>7654</v>
       </c>
-      <c r="J50" s="24">
+      <c r="J51" s="24">
         <v>10080</v>
       </c>
-      <c r="K50" s="24">
+      <c r="K51" s="24">
         <v>11333</v>
       </c>
-      <c r="L50" s="24">
+      <c r="L51" s="24">
         <v>14962</v>
       </c>
-      <c r="M50" s="24">
+      <c r="M51" s="24">
         <v>19784</v>
       </c>
-      <c r="N50" s="24"/>
-    </row>
-    <row r="51" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B51" s="27" t="s">
+      <c r="N51" s="24"/>
+    </row>
+    <row r="52" spans="2:14" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
+      <c r="B52" s="60" t="s">
+        <v>222</v>
+      </c>
+      <c r="C52" s="61"/>
+      <c r="D52" s="61"/>
+      <c r="E52" s="61"/>
+      <c r="F52" s="61"/>
+      <c r="G52" s="61"/>
+      <c r="H52" s="61"/>
+      <c r="I52" s="61"/>
+      <c r="J52" s="61">
+        <v>3408</v>
+      </c>
+      <c r="K52" s="61">
+        <v>2525</v>
+      </c>
+      <c r="L52" s="61">
+        <v>1843</v>
+      </c>
+      <c r="M52" s="61">
+        <v>4209</v>
+      </c>
+      <c r="N52" s="24"/>
+    </row>
+    <row r="53" spans="2:14" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
+      <c r="B53" s="60" t="s">
+        <v>223</v>
+      </c>
+      <c r="C53" s="61"/>
+      <c r="D53" s="61"/>
+      <c r="E53" s="61"/>
+      <c r="F53" s="61"/>
+      <c r="G53" s="61"/>
+      <c r="H53" s="61"/>
+      <c r="I53" s="61"/>
+      <c r="J53" s="61">
+        <v>3399</v>
+      </c>
+      <c r="K53" s="61">
+        <v>5339</v>
+      </c>
+      <c r="L53" s="61">
+        <v>4411</v>
+      </c>
+      <c r="M53" s="61">
+        <v>8735</v>
+      </c>
+      <c r="N53" s="24"/>
+    </row>
+    <row r="54" spans="2:14" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
+      <c r="B54" s="60" t="s">
+        <v>224</v>
+      </c>
+      <c r="C54" s="61"/>
+      <c r="D54" s="61"/>
+      <c r="E54" s="61"/>
+      <c r="F54" s="61"/>
+      <c r="G54" s="61"/>
+      <c r="H54" s="61"/>
+      <c r="I54" s="61"/>
+      <c r="J54" s="61">
+        <v>3273</v>
+      </c>
+      <c r="K54" s="61">
+        <v>3469</v>
+      </c>
+      <c r="L54" s="61">
+        <v>8708</v>
+      </c>
+      <c r="M54" s="61">
+        <v>6840</v>
+      </c>
+      <c r="N54" s="24"/>
+    </row>
+    <row r="55" spans="2:14" collapsed="1" x14ac:dyDescent="0.15">
+      <c r="B55" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="C51" s="24">
+      <c r="C55" s="24">
         <v>872</v>
       </c>
-      <c r="D51" s="24">
+      <c r="D55" s="24">
         <v>1389</v>
       </c>
-      <c r="E51" s="24">
+      <c r="E55" s="24">
         <v>1289</v>
       </c>
-      <c r="F51" s="24">
+      <c r="F55" s="24">
         <v>3080</v>
       </c>
-      <c r="G51" s="24">
+      <c r="G55" s="24">
         <v>4062</v>
       </c>
-      <c r="H51" s="24">
+      <c r="H55" s="24">
         <v>4026</v>
       </c>
-      <c r="I51" s="24">
+      <c r="I55" s="24">
         <v>3806</v>
       </c>
-      <c r="J51" s="24">
+      <c r="J55" s="24">
         <v>3771</v>
       </c>
-      <c r="K51" s="24">
+      <c r="K55" s="24">
         <v>2779</v>
       </c>
-      <c r="L51" s="24">
+      <c r="L55" s="24">
         <v>2658</v>
       </c>
-      <c r="M51" s="24">
+      <c r="M55" s="24">
         <v>2709</v>
       </c>
-      <c r="N51" s="24"/>
-    </row>
-    <row r="52" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B52" s="27" t="s">
+      <c r="N55" s="24"/>
+    </row>
+    <row r="56" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B56" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="C52" s="24">
+      <c r="C56" s="24">
         <v>3740</v>
       </c>
-      <c r="D52" s="24">
+      <c r="D56" s="24">
         <v>3799</v>
       </c>
-      <c r="E52" s="24">
+      <c r="E56" s="24">
         <v>3844</v>
       </c>
-      <c r="F52" s="24">
+      <c r="F56" s="24">
         <v>3914</v>
       </c>
-      <c r="G52" s="24">
+      <c r="G56" s="24">
         <v>4006</v>
       </c>
-      <c r="H52" s="24">
+      <c r="H56" s="24">
         <v>4885</v>
       </c>
-      <c r="I52" s="24">
+      <c r="I56" s="24">
         <v>5343</v>
       </c>
-      <c r="J52" s="24">
+      <c r="J56" s="24">
         <v>6283</v>
       </c>
-      <c r="K52" s="24">
+      <c r="K56" s="24">
         <v>7136</v>
       </c>
-      <c r="L52" s="24">
+      <c r="L56" s="24">
         <v>9141</v>
       </c>
-      <c r="M52" s="24">
+      <c r="M56" s="24">
         <v>9780</v>
       </c>
-      <c r="N52" s="24"/>
-    </row>
-    <row r="53" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B53" s="27" t="s">
+      <c r="N56" s="24"/>
+    </row>
+    <row r="57" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B57" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="C53" s="24">
+      <c r="C57" s="24">
         <v>1094</v>
       </c>
-      <c r="D53" s="24">
+      <c r="D57" s="24">
         <v>1235</v>
       </c>
-      <c r="E53" s="24">
+      <c r="E57" s="24">
         <v>1316</v>
       </c>
-      <c r="F53" s="24">
+      <c r="F57" s="24">
         <v>1346</v>
       </c>
-      <c r="G53" s="24">
+      <c r="G57" s="24">
         <v>1532</v>
       </c>
-      <c r="H53" s="24">
+      <c r="H57" s="24">
         <v>1556</v>
       </c>
-      <c r="I53" s="24">
+      <c r="I57" s="24">
         <v>1755</v>
       </c>
-      <c r="J53" s="24">
+      <c r="J57" s="24">
         <v>1793</v>
       </c>
-      <c r="K53" s="24">
+      <c r="K57" s="24">
         <v>1810</v>
       </c>
-      <c r="L53" s="24">
+      <c r="L57" s="24">
         <v>2084</v>
       </c>
-      <c r="M53" s="24">
+      <c r="M57" s="24">
         <v>2281</v>
       </c>
-      <c r="N53" s="24"/>
-    </row>
-    <row r="54" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B54" s="27" t="s">
+      <c r="N57" s="24"/>
+    </row>
+    <row r="58" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B58" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="C54" s="24">
+      <c r="C58" s="24">
         <v>4430</v>
       </c>
-      <c r="D54" s="24">
+      <c r="D58" s="24">
         <v>4430</v>
       </c>
-      <c r="E54" s="24">
+      <c r="E58" s="24">
         <v>4430</v>
       </c>
-      <c r="F54" s="24">
+      <c r="F58" s="24">
         <v>4430</v>
       </c>
-      <c r="G54" s="24">
+      <c r="G58" s="24">
         <v>4453</v>
       </c>
-      <c r="H54" s="24">
+      <c r="H58" s="24">
         <v>4622</v>
       </c>
-      <c r="I54" s="24">
+      <c r="I58" s="24">
         <v>4724</v>
       </c>
-      <c r="J54" s="24">
+      <c r="J58" s="24">
         <v>5188</v>
       </c>
-      <c r="K54" s="24">
+      <c r="K58" s="24">
         <v>5498</v>
       </c>
-      <c r="L54" s="24">
+      <c r="L58" s="24">
         <v>5755</v>
       </c>
-      <c r="M54" s="24">
+      <c r="M58" s="24">
         <v>6261</v>
       </c>
-      <c r="N54" s="24"/>
-    </row>
-    <row r="55" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B55" s="27" t="s">
+      <c r="N58" s="24"/>
+    </row>
+    <row r="59" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B59" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="C55" s="24">
+      <c r="C59" s="24">
         <v>1541</v>
       </c>
-      <c r="D55" s="24">
+      <c r="D59" s="24">
         <v>1395</v>
       </c>
-      <c r="E55" s="24">
+      <c r="E59" s="24">
         <v>1251</v>
       </c>
-      <c r="F55" s="24">
+      <c r="F59" s="24">
         <v>1112</v>
       </c>
-      <c r="G55" s="24">
+      <c r="G59" s="24">
         <v>986</v>
       </c>
-      <c r="H55" s="24">
+      <c r="H59" s="24">
         <v>952</v>
       </c>
-      <c r="I55" s="24">
+      <c r="I59" s="24">
         <v>838</v>
       </c>
-      <c r="J55" s="24">
+      <c r="J59" s="24">
         <v>807</v>
       </c>
-      <c r="K55" s="24">
+      <c r="K59" s="24">
         <v>769</v>
       </c>
-      <c r="L55" s="24">
+      <c r="L59" s="24">
         <v>755</v>
       </c>
-      <c r="M55" s="24">
+      <c r="M59" s="24">
         <v>936</v>
       </c>
-      <c r="N55" s="24"/>
-    </row>
-    <row r="56" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B56" s="27" t="s">
+      <c r="N59" s="24"/>
+    </row>
+    <row r="60" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B60" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C56" s="24">
+      <c r="C60" s="24">
         <v>4568</v>
       </c>
-      <c r="D56" s="24">
+      <c r="D60" s="24">
         <v>5398</v>
       </c>
-      <c r="E56" s="24">
+      <c r="E60" s="24">
         <v>5982</v>
       </c>
-      <c r="F56" s="24">
+      <c r="F60" s="24">
         <v>6081</v>
       </c>
-      <c r="G56" s="24">
+      <c r="G60" s="24">
         <v>7798</v>
       </c>
-      <c r="H56" s="24">
+      <c r="H60" s="24">
         <v>9578</v>
       </c>
-      <c r="I56" s="24">
+      <c r="I60" s="24">
         <v>10276</v>
       </c>
-      <c r="J56" s="24">
+      <c r="J60" s="24">
         <v>10979</v>
       </c>
-      <c r="K56" s="24">
+      <c r="K60" s="24">
         <v>13318</v>
       </c>
-      <c r="L56" s="24">
+      <c r="L60" s="24">
         <v>13570</v>
       </c>
-      <c r="M56" s="24">
+      <c r="M60" s="24">
         <v>13674</v>
       </c>
-      <c r="N56" s="24"/>
-    </row>
-    <row r="57" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B57" s="27" t="s">
+      <c r="N60" s="24"/>
+    </row>
+    <row r="61" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B61" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="C57" s="24">
+      <c r="C61" s="24">
         <v>4204</v>
       </c>
-      <c r="D57" s="24">
+      <c r="D61" s="24">
         <v>4501</v>
       </c>
-      <c r="E57" s="24">
+      <c r="E61" s="24">
         <v>4667</v>
       </c>
-      <c r="F57" s="24">
+      <c r="F61" s="24">
         <v>4500</v>
       </c>
-      <c r="G57" s="24">
+      <c r="G61" s="24">
         <v>4568</v>
       </c>
-      <c r="H57" s="24">
+      <c r="H61" s="24">
         <v>4001</v>
       </c>
-      <c r="I57" s="24">
+      <c r="I61" s="24">
         <v>5437</v>
       </c>
-      <c r="J57" s="24">
+      <c r="J61" s="24">
         <v>6425</v>
       </c>
-      <c r="K57" s="24">
+      <c r="K61" s="24">
         <v>6788</v>
       </c>
-      <c r="L57" s="24">
+      <c r="L61" s="24">
         <v>7216</v>
       </c>
-      <c r="M57" s="24">
+      <c r="M61" s="24">
         <v>11724</v>
       </c>
-      <c r="N57" s="24"/>
-    </row>
-    <row r="58" spans="2:38" s="30" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B58" s="30" t="s">
+      <c r="N61" s="24"/>
+    </row>
+    <row r="62" spans="2:14" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
+      <c r="B62" s="60" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="61"/>
+      <c r="D62" s="61"/>
+      <c r="E62" s="61"/>
+      <c r="F62" s="61"/>
+      <c r="G62" s="61"/>
+      <c r="H62" s="61"/>
+      <c r="I62" s="61"/>
+      <c r="J62" s="61">
+        <v>3387</v>
+      </c>
+      <c r="K62" s="61">
+        <v>3240</v>
+      </c>
+      <c r="L62" s="61">
+        <v>3799</v>
+      </c>
+      <c r="M62" s="62">
+        <v>8187</v>
+      </c>
+      <c r="N62" s="24"/>
+    </row>
+    <row r="63" spans="2:14" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
+      <c r="B63" s="60" t="s">
+        <v>219</v>
+      </c>
+      <c r="C63" s="61"/>
+      <c r="D63" s="61"/>
+      <c r="E63" s="61"/>
+      <c r="F63" s="61"/>
+      <c r="G63" s="61"/>
+      <c r="H63" s="61"/>
+      <c r="I63" s="61"/>
+      <c r="J63" s="61">
+        <v>1747</v>
+      </c>
+      <c r="K63" s="61">
+        <v>2079</v>
+      </c>
+      <c r="L63" s="61">
+        <v>1776</v>
+      </c>
+      <c r="M63" s="61">
+        <v>1536</v>
+      </c>
+      <c r="N63" s="24"/>
+    </row>
+    <row r="64" spans="2:14" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="60" t="s">
+        <v>220</v>
+      </c>
+      <c r="C64" s="61"/>
+      <c r="D64" s="61"/>
+      <c r="E64" s="61"/>
+      <c r="F64" s="61"/>
+      <c r="G64" s="61"/>
+      <c r="H64" s="61"/>
+      <c r="I64" s="61"/>
+      <c r="J64" s="61">
+        <v>750</v>
+      </c>
+      <c r="K64" s="61">
+        <v>895</v>
+      </c>
+      <c r="L64" s="61">
+        <v>1042</v>
+      </c>
+      <c r="M64" s="61">
+        <v>1369</v>
+      </c>
+      <c r="N64" s="24"/>
+    </row>
+    <row r="65" spans="2:38" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
+      <c r="B65" s="60" t="s">
+        <v>221</v>
+      </c>
+      <c r="C65" s="61"/>
+      <c r="D65" s="61"/>
+      <c r="E65" s="61"/>
+      <c r="F65" s="61"/>
+      <c r="G65" s="61"/>
+      <c r="H65" s="61"/>
+      <c r="I65" s="61"/>
+      <c r="J65" s="61"/>
+      <c r="K65" s="61">
+        <v>334</v>
+      </c>
+      <c r="L65" s="61">
+        <v>327</v>
+      </c>
+      <c r="M65" s="61"/>
+      <c r="N65" s="24"/>
+    </row>
+    <row r="66" spans="2:38" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
+      <c r="B66" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="C66" s="61"/>
+      <c r="D66" s="61"/>
+      <c r="E66" s="61"/>
+      <c r="F66" s="61"/>
+      <c r="G66" s="61"/>
+      <c r="H66" s="61"/>
+      <c r="I66" s="61"/>
+      <c r="J66" s="61">
+        <v>541</v>
+      </c>
+      <c r="K66" s="61">
+        <v>240</v>
+      </c>
+      <c r="L66" s="61">
+        <v>272</v>
+      </c>
+      <c r="M66" s="61">
+        <v>632</v>
+      </c>
+      <c r="N66" s="24"/>
+    </row>
+    <row r="67" spans="2:38" s="30" customFormat="1" collapsed="1" x14ac:dyDescent="0.15">
+      <c r="B67" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C58" s="31">
-        <f t="shared" ref="C58:K58" si="278">+SUM(C48:C57)</f>
+      <c r="C67" s="31">
+        <f t="shared" ref="C67:H67" si="286">+SUM(C55:C61,C49:C51)</f>
         <v>44460</v>
       </c>
-      <c r="D58" s="31">
-        <f t="shared" si="278"/>
+      <c r="D67" s="31">
+        <f t="shared" si="286"/>
         <v>49555</v>
       </c>
-      <c r="E58" s="31">
-        <f t="shared" si="278"/>
+      <c r="E67" s="31">
+        <f t="shared" si="286"/>
         <v>54148</v>
       </c>
-      <c r="F58" s="31">
-        <f t="shared" si="278"/>
+      <c r="F67" s="31">
+        <f t="shared" si="286"/>
         <v>65728</v>
       </c>
-      <c r="G58" s="31">
-        <f t="shared" si="278"/>
+      <c r="G67" s="31">
+        <f t="shared" si="286"/>
         <v>77072</v>
       </c>
-      <c r="H58" s="31">
-        <f t="shared" si="278"/>
+      <c r="H67" s="31">
+        <f t="shared" si="286"/>
         <v>85227</v>
       </c>
-      <c r="I58" s="31">
-        <f t="shared" si="278"/>
+      <c r="I67" s="31">
+        <f>+SUM(I55:I61,I49:I51)</f>
         <v>96013</v>
       </c>
-      <c r="J58" s="31">
-        <f t="shared" si="278"/>
+      <c r="J67" s="31">
+        <f>+SUM(J55:J61,J49:J51)</f>
         <v>111601</v>
       </c>
-      <c r="K58" s="31">
-        <f t="shared" si="278"/>
+      <c r="K67" s="31">
+        <f>+SUM(K55:K61,K49:K51)</f>
         <v>125254</v>
       </c>
-      <c r="L58" s="31">
-        <f>+SUM(L48:L57)</f>
+      <c r="L67" s="31">
+        <f>+SUM(L55:L61,L49:L51)</f>
         <v>140740</v>
       </c>
-      <c r="M58" s="31">
-        <f>+SUM(M48:M57)</f>
-        <v>161148</v>
-      </c>
-      <c r="N58" s="31"/>
-      <c r="Q58" s="31"/>
-      <c r="R58" s="31"/>
-      <c r="S58" s="31"/>
-      <c r="T58" s="31"/>
-      <c r="U58" s="31"/>
-      <c r="V58" s="31"/>
-      <c r="W58" s="31"/>
-      <c r="X58" s="31"/>
-      <c r="Y58" s="31"/>
-      <c r="Z58" s="31"/>
-      <c r="AA58" s="31"/>
-      <c r="AB58" s="31"/>
-      <c r="AC58" s="31"/>
-      <c r="AD58" s="31"/>
-      <c r="AE58" s="31"/>
-      <c r="AF58" s="31"/>
-      <c r="AG58" s="31"/>
-      <c r="AH58" s="31"/>
-      <c r="AI58" s="31"/>
-      <c r="AJ58" s="31"/>
-      <c r="AK58" s="31"/>
-      <c r="AL58" s="31"/>
-    </row>
-    <row r="60" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B60" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="C60" s="24">
-        <v>1141</v>
-      </c>
-      <c r="D60" s="24">
-        <v>1929</v>
-      </c>
-      <c r="E60" s="24">
-        <v>2380</v>
-      </c>
-      <c r="F60" s="24">
-        <v>2699</v>
-      </c>
-      <c r="G60" s="24">
-        <v>2715</v>
-      </c>
-      <c r="H60" s="24">
-        <v>3680</v>
-      </c>
-      <c r="I60" s="24">
-        <v>5353</v>
-      </c>
-      <c r="J60" s="24">
-        <v>6310</v>
-      </c>
-      <c r="K60" s="24">
-        <v>7331</v>
-      </c>
-      <c r="L60" s="24">
-        <v>9064</v>
-      </c>
-      <c r="M60" s="24">
-        <v>8624</v>
-      </c>
-    </row>
-    <row r="61" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B61" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="C61" s="24">
-        <v>4869</v>
-      </c>
-      <c r="D61" s="24">
-        <v>7156</v>
-      </c>
-      <c r="E61" s="24">
-        <v>5472</v>
-      </c>
-      <c r="F61" s="24">
-        <v>6682</v>
-      </c>
-      <c r="G61" s="24">
-        <v>11258</v>
-      </c>
-      <c r="H61" s="24">
-        <v>10289</v>
-      </c>
-      <c r="I61" s="24">
-        <v>11126</v>
-      </c>
-      <c r="J61" s="24">
-        <v>11737</v>
-      </c>
-      <c r="K61" s="24">
-        <v>19211</v>
-      </c>
-      <c r="L61" s="24">
-        <v>15193</v>
-      </c>
-      <c r="M61" s="24">
-        <v>16452</v>
-      </c>
-    </row>
-    <row r="62" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B62" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="C62" s="24">
-        <v>1250</v>
-      </c>
-      <c r="D62" s="24">
-        <v>1249</v>
-      </c>
-      <c r="E62" s="24">
-        <v>1249</v>
-      </c>
-      <c r="F62" s="24">
-        <v>1250</v>
-      </c>
-      <c r="G62" s="24">
-        <v>1250</v>
-      </c>
-      <c r="H62" s="24">
-        <v>0</v>
-      </c>
-      <c r="I62" s="24"/>
-      <c r="J62" s="24"/>
-      <c r="K62" s="24"/>
-      <c r="L62" s="24">
-        <v>0</v>
-      </c>
-      <c r="M62" s="24">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="63" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B63" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="C63" s="24">
-        <v>9704</v>
-      </c>
-      <c r="D63" s="24">
-        <v>8456</v>
-      </c>
-      <c r="E63" s="24">
-        <v>8457</v>
-      </c>
-      <c r="F63" s="24">
-        <v>8459</v>
-      </c>
-      <c r="G63" s="24">
-        <v>8460</v>
-      </c>
-      <c r="H63" s="24">
-        <v>8461</v>
-      </c>
-      <c r="I63" s="24">
-        <v>8462</v>
-      </c>
-      <c r="J63" s="24">
-        <v>8463</v>
-      </c>
-      <c r="K63" s="24">
-        <v>8464</v>
-      </c>
-      <c r="L63" s="24">
-        <v>8466</v>
-      </c>
-      <c r="M63" s="24">
-        <v>7468</v>
-      </c>
-    </row>
-    <row r="64" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B64" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="C64" s="24">
-        <v>939</v>
-      </c>
-      <c r="D64" s="24">
-        <v>1041</v>
-      </c>
-      <c r="E64" s="24">
-        <v>1091</v>
-      </c>
-      <c r="F64" s="24">
-        <v>1119</v>
-      </c>
-      <c r="G64" s="24">
-        <v>1281</v>
-      </c>
-      <c r="H64" s="24">
-        <v>1304</v>
-      </c>
-      <c r="I64" s="24">
-        <v>1490</v>
-      </c>
-      <c r="J64" s="24">
-        <v>1519</v>
-      </c>
-      <c r="K64" s="24">
-        <v>1521</v>
-      </c>
-      <c r="L64" s="24">
-        <v>1831</v>
-      </c>
-      <c r="M64" s="24">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B65" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="C65" s="24">
-        <v>2037</v>
-      </c>
-      <c r="D65" s="24">
-        <v>2223</v>
-      </c>
-      <c r="E65" s="24">
-        <v>2234</v>
-      </c>
-      <c r="F65" s="24">
-        <v>2541</v>
-      </c>
-      <c r="G65" s="24">
-        <v>2966</v>
-      </c>
-      <c r="H65" s="24">
-        <v>3336</v>
-      </c>
-      <c r="I65" s="24">
-        <v>3683</v>
-      </c>
-      <c r="J65" s="24">
-        <v>4245</v>
-      </c>
-      <c r="K65" s="24">
-        <v>4884</v>
-      </c>
-      <c r="L65" s="24">
-        <v>6055</v>
-      </c>
-      <c r="M65" s="24">
-        <v>6694</v>
-      </c>
-    </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B66" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C66" s="24">
-        <v>24520</v>
-      </c>
-      <c r="D66" s="24">
-        <v>27501</v>
-      </c>
-      <c r="E66" s="24">
-        <v>33265</v>
-      </c>
-      <c r="F66" s="24">
-        <v>42978</v>
-      </c>
-      <c r="G66" s="24">
-        <v>49142</v>
-      </c>
-      <c r="H66" s="24">
-        <v>58157</v>
-      </c>
-      <c r="I66" s="24">
-        <v>65899</v>
-      </c>
-      <c r="J66" s="24">
-        <v>79327</v>
-      </c>
-      <c r="K66" s="24">
-        <v>83843</v>
-      </c>
-      <c r="L66" s="24">
-        <v>100131</v>
-      </c>
-      <c r="M66" s="24">
-        <v>118897</v>
-      </c>
-    </row>
-    <row r="67" spans="2:38" s="30" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B67" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="C67" s="31">
-        <f t="shared" ref="C67:K67" si="279">+SUM(C60:C66)</f>
-        <v>44460</v>
-      </c>
-      <c r="D67" s="31">
-        <f t="shared" si="279"/>
-        <v>49555</v>
-      </c>
-      <c r="E67" s="31">
-        <f t="shared" si="279"/>
-        <v>54148</v>
-      </c>
-      <c r="F67" s="31">
-        <f t="shared" si="279"/>
-        <v>65728</v>
-      </c>
-      <c r="G67" s="31">
-        <f t="shared" si="279"/>
-        <v>77072</v>
-      </c>
-      <c r="H67" s="31">
-        <f t="shared" si="279"/>
-        <v>85227</v>
-      </c>
-      <c r="I67" s="31">
-        <f t="shared" si="279"/>
-        <v>96013</v>
-      </c>
-      <c r="J67" s="31">
-        <f t="shared" si="279"/>
-        <v>111601</v>
-      </c>
-      <c r="K67" s="31">
-        <f t="shared" si="279"/>
-        <v>125254</v>
-      </c>
-      <c r="L67" s="31">
-        <f t="shared" ref="L67:M67" si="280">+SUM(L60:L66)</f>
-        <v>140740</v>
-      </c>
       <c r="M67" s="31">
-        <f t="shared" si="280"/>
+        <f>+SUM(M55:M61,M49:M51)</f>
         <v>161148</v>
       </c>
       <c r="N67" s="31"/>
@@ -8599,1154 +8452,1394 @@
     </row>
     <row r="69" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B69" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="C69" s="26">
-        <f>SUM(C62:C63)</f>
-        <v>10954</v>
-      </c>
-      <c r="D69" s="26">
-        <f t="shared" ref="D69:K69" si="281">SUM(D62:D63)</f>
-        <v>9705</v>
-      </c>
-      <c r="E69" s="26">
-        <f t="shared" si="281"/>
-        <v>9706</v>
-      </c>
-      <c r="F69" s="26">
-        <f t="shared" si="281"/>
-        <v>9709</v>
-      </c>
-      <c r="G69" s="26">
-        <f t="shared" si="281"/>
-        <v>9710</v>
-      </c>
-      <c r="H69" s="26">
-        <f t="shared" si="281"/>
-        <v>8461</v>
-      </c>
-      <c r="I69" s="26">
-        <f t="shared" si="281"/>
-        <v>8462</v>
-      </c>
-      <c r="J69" s="26">
-        <f t="shared" si="281"/>
-        <v>8463</v>
-      </c>
-      <c r="K69" s="26">
-        <f t="shared" si="281"/>
-        <v>8464</v>
-      </c>
-      <c r="L69" s="26">
-        <f t="shared" ref="L69:M69" si="282">SUM(L62:L63)</f>
-        <v>8466</v>
-      </c>
-      <c r="M69" s="26">
-        <f t="shared" si="282"/>
-        <v>8467</v>
+        <v>47</v>
+      </c>
+      <c r="C69" s="24">
+        <v>1141</v>
+      </c>
+      <c r="D69" s="24">
+        <v>1929</v>
+      </c>
+      <c r="E69" s="24">
+        <v>2380</v>
+      </c>
+      <c r="F69" s="24">
+        <v>2699</v>
+      </c>
+      <c r="G69" s="24">
+        <v>2715</v>
+      </c>
+      <c r="H69" s="24">
+        <v>3680</v>
+      </c>
+      <c r="I69" s="24">
+        <v>5353</v>
+      </c>
+      <c r="J69" s="24">
+        <v>6310</v>
+      </c>
+      <c r="K69" s="24">
+        <v>7331</v>
+      </c>
+      <c r="L69" s="24">
+        <v>9064</v>
+      </c>
+      <c r="M69" s="24">
+        <v>8624</v>
       </c>
     </row>
     <row r="70" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B70" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="C70" s="26">
-        <f>+C48</f>
-        <v>15320</v>
-      </c>
-      <c r="D70" s="26">
-        <f t="shared" ref="D70:K70" si="283">+D48</f>
-        <v>16023</v>
-      </c>
-      <c r="E70" s="26">
-        <f t="shared" si="283"/>
-        <v>18281</v>
-      </c>
-      <c r="F70" s="26">
-        <f t="shared" si="283"/>
-        <v>25984</v>
-      </c>
-      <c r="G70" s="26">
-        <f t="shared" si="283"/>
-        <v>31438</v>
-      </c>
-      <c r="H70" s="26">
-        <f t="shared" si="283"/>
-        <v>34800</v>
-      </c>
-      <c r="I70" s="26">
-        <f t="shared" si="283"/>
-        <v>38487</v>
-      </c>
-      <c r="J70" s="26">
-        <f t="shared" si="283"/>
-        <v>43210</v>
-      </c>
-      <c r="K70" s="26">
-        <f t="shared" si="283"/>
-        <v>53691</v>
-      </c>
-      <c r="L70" s="26">
-        <f t="shared" ref="L70:M70" si="284">+L48</f>
-        <v>56791</v>
-      </c>
-      <c r="M70" s="26">
-        <f t="shared" si="284"/>
-        <v>60608</v>
+        <v>48</v>
+      </c>
+      <c r="C70" s="24">
+        <v>4869</v>
+      </c>
+      <c r="D70" s="24">
+        <v>7156</v>
+      </c>
+      <c r="E70" s="24">
+        <v>5472</v>
+      </c>
+      <c r="F70" s="24">
+        <v>6682</v>
+      </c>
+      <c r="G70" s="24">
+        <v>11258</v>
+      </c>
+      <c r="H70" s="24">
+        <v>10289</v>
+      </c>
+      <c r="I70" s="24">
+        <v>11126</v>
+      </c>
+      <c r="J70" s="24">
+        <v>11737</v>
+      </c>
+      <c r="K70" s="24">
+        <v>19211</v>
+      </c>
+      <c r="L70" s="24">
+        <v>15193</v>
+      </c>
+      <c r="M70" s="24">
+        <v>16452</v>
       </c>
     </row>
     <row r="71" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B71" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="C71" s="26">
-        <f>+C70-C69</f>
-        <v>4366</v>
-      </c>
-      <c r="D71" s="26">
-        <f t="shared" ref="D71:K71" si="285">+D70-D69</f>
-        <v>6318</v>
-      </c>
-      <c r="E71" s="26">
-        <f t="shared" si="285"/>
-        <v>8575</v>
-      </c>
-      <c r="F71" s="26">
-        <f t="shared" si="285"/>
-        <v>16275</v>
-      </c>
-      <c r="G71" s="26">
-        <f t="shared" si="285"/>
-        <v>21728</v>
-      </c>
-      <c r="H71" s="26">
-        <f t="shared" si="285"/>
-        <v>26339</v>
-      </c>
-      <c r="I71" s="26">
-        <f t="shared" si="285"/>
-        <v>30025</v>
-      </c>
-      <c r="J71" s="26">
-        <f t="shared" si="285"/>
-        <v>34747</v>
-      </c>
-      <c r="K71" s="26">
-        <f t="shared" si="285"/>
-        <v>45227</v>
-      </c>
-      <c r="L71" s="26">
-        <f t="shared" ref="L71:M71" si="286">+L70-L69</f>
-        <v>48325</v>
-      </c>
-      <c r="M71" s="26">
-        <f t="shared" si="286"/>
-        <v>52141</v>
+        <v>64</v>
+      </c>
+      <c r="C71" s="24">
+        <v>1250</v>
+      </c>
+      <c r="D71" s="24">
+        <v>1249</v>
+      </c>
+      <c r="E71" s="24">
+        <v>1249</v>
+      </c>
+      <c r="F71" s="24">
+        <v>1250</v>
+      </c>
+      <c r="G71" s="24">
+        <v>1250</v>
+      </c>
+      <c r="H71" s="24">
+        <v>0</v>
+      </c>
+      <c r="I71" s="24"/>
+      <c r="J71" s="24"/>
+      <c r="K71" s="24"/>
+      <c r="L71" s="24">
+        <v>0</v>
+      </c>
+      <c r="M71" s="24">
+        <v>999</v>
       </c>
     </row>
     <row r="72" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B72" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="C72" s="26">
-        <f>+C66-C55-C54</f>
-        <v>18549</v>
-      </c>
-      <c r="D72" s="26">
-        <f t="shared" ref="D72:K72" si="287">+D66-D55-D54</f>
-        <v>21676</v>
-      </c>
-      <c r="E72" s="26">
-        <f t="shared" si="287"/>
-        <v>27584</v>
-      </c>
-      <c r="F72" s="26">
-        <f t="shared" si="287"/>
-        <v>37436</v>
-      </c>
-      <c r="G72" s="26">
-        <f t="shared" si="287"/>
-        <v>43703</v>
-      </c>
-      <c r="H72" s="26">
-        <f t="shared" si="287"/>
-        <v>52583</v>
-      </c>
-      <c r="I72" s="26">
-        <f t="shared" si="287"/>
-        <v>60337</v>
-      </c>
-      <c r="J72" s="26">
-        <f t="shared" si="287"/>
-        <v>73332</v>
-      </c>
-      <c r="K72" s="26">
-        <f t="shared" si="287"/>
-        <v>77576</v>
-      </c>
-      <c r="L72" s="26">
-        <f t="shared" ref="L72:M72" si="288">+L66-L55-L54</f>
-        <v>93621</v>
-      </c>
-      <c r="M72" s="26">
-        <f t="shared" si="288"/>
-        <v>111700</v>
+        <v>49</v>
+      </c>
+      <c r="C72" s="24">
+        <v>9704</v>
+      </c>
+      <c r="D72" s="24">
+        <v>8456</v>
+      </c>
+      <c r="E72" s="24">
+        <v>8457</v>
+      </c>
+      <c r="F72" s="24">
+        <v>8459</v>
+      </c>
+      <c r="G72" s="24">
+        <v>8460</v>
+      </c>
+      <c r="H72" s="24">
+        <v>8461</v>
+      </c>
+      <c r="I72" s="24">
+        <v>8462</v>
+      </c>
+      <c r="J72" s="24">
+        <v>8463</v>
+      </c>
+      <c r="K72" s="24">
+        <v>8464</v>
+      </c>
+      <c r="L72" s="24">
+        <v>8466</v>
+      </c>
+      <c r="M72" s="24">
+        <v>7468</v>
       </c>
     </row>
     <row r="73" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="H73" s="51">
-        <f t="shared" ref="H73:J73" si="289">SUM(E119:H119)/H72</f>
-        <v>0.63176311735732082</v>
-      </c>
-      <c r="I73" s="51">
-        <f t="shared" si="289"/>
-        <v>0.82927556888807863</v>
-      </c>
-      <c r="J73" s="51">
-        <f t="shared" si="289"/>
-        <v>0.89438444335351552</v>
-      </c>
-      <c r="K73" s="51">
-        <f>SUM(H119:K119)/K72</f>
-        <v>0.9289728782097556</v>
-      </c>
-      <c r="L73" s="51">
-        <f>SUM(I119:L119)/L72</f>
-        <v>0.76932525822198006</v>
-      </c>
-      <c r="M73" s="51">
-        <f>SUM(J119:M119)/M72</f>
-        <v>0.69222918531781563</v>
+      <c r="B73" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C73" s="24">
+        <v>939</v>
+      </c>
+      <c r="D73" s="24">
+        <v>1041</v>
+      </c>
+      <c r="E73" s="24">
+        <v>1091</v>
+      </c>
+      <c r="F73" s="24">
+        <v>1119</v>
+      </c>
+      <c r="G73" s="24">
+        <v>1281</v>
+      </c>
+      <c r="H73" s="24">
+        <v>1304</v>
+      </c>
+      <c r="I73" s="24">
+        <v>1490</v>
+      </c>
+      <c r="J73" s="24">
+        <v>1519</v>
+      </c>
+      <c r="K73" s="24">
+        <v>1521</v>
+      </c>
+      <c r="L73" s="24">
+        <v>1831</v>
+      </c>
+      <c r="M73" s="24">
+        <v>2014</v>
       </c>
     </row>
     <row r="74" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="H74" s="51"/>
-      <c r="I74" s="51"/>
-      <c r="J74" s="51"/>
-      <c r="K74" s="51"/>
-      <c r="L74" s="51"/>
-      <c r="M74" s="51"/>
+      <c r="B74" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="C74" s="24">
+        <v>2037</v>
+      </c>
+      <c r="D74" s="24">
+        <v>2223</v>
+      </c>
+      <c r="E74" s="24">
+        <v>2234</v>
+      </c>
+      <c r="F74" s="24">
+        <v>2541</v>
+      </c>
+      <c r="G74" s="24">
+        <v>2966</v>
+      </c>
+      <c r="H74" s="24">
+        <v>3336</v>
+      </c>
+      <c r="I74" s="24">
+        <v>3683</v>
+      </c>
+      <c r="J74" s="24">
+        <v>4245</v>
+      </c>
+      <c r="K74" s="24">
+        <v>4884</v>
+      </c>
+      <c r="L74" s="24">
+        <v>6055</v>
+      </c>
+      <c r="M74" s="24">
+        <v>6694</v>
+      </c>
     </row>
     <row r="75" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B75" s="27" t="s">
-        <v>207</v>
-      </c>
-      <c r="F75" s="26">
-        <f>+F49/SUM(C11:F11) * 365</f>
-        <v>59.906683956534586</v>
-      </c>
-      <c r="G75" s="26">
-        <f>+G49/SUM(D11:G11) * 365</f>
-        <v>56.575137262767313</v>
-      </c>
-      <c r="H75" s="26">
-        <f>+H49/SUM(E11:H11) * 365</f>
-        <v>53.559762011068763</v>
-      </c>
-      <c r="I75" s="26">
-        <f>+I49/SUM(F11:I11) * 365</f>
-        <v>57.014231607942151</v>
-      </c>
-      <c r="J75" s="26">
-        <f>+J49/SUM(G11:J11) * 365</f>
-        <v>64.512785734537957</v>
-      </c>
-      <c r="K75" s="26">
-        <f>+K49/SUM(H11:K11) * 365</f>
-        <v>54.393024273642396</v>
-      </c>
-      <c r="L75" s="26">
-        <f>+L49/SUM(I11:L11) * 365</f>
-        <v>61.433499981842175</v>
-      </c>
-      <c r="M75" s="26">
-        <f>+M49/SUM(J11:M11) * 365</f>
-        <v>65.125492941189037</v>
-      </c>
-    </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B76" s="27" t="s">
-        <v>208</v>
-      </c>
-      <c r="F76" s="26">
-        <f>(+F50/SUM(C16:F16)) * 365</f>
-        <v>115.99362252572048</v>
-      </c>
-      <c r="G76" s="26">
-        <f>(+G50/SUM(D16:G16)) * 365</f>
-        <v>108.56505199086989</v>
-      </c>
-      <c r="H76" s="26">
-        <f>(+H50/SUM(E16:H16)) * 365</f>
-        <v>105.30666493775932</v>
-      </c>
-      <c r="I76" s="26">
-        <f>(+I50/SUM(F16:I16)) * 365</f>
-        <v>102.17650501060639</v>
-      </c>
-      <c r="J76" s="26">
-        <f>(+J50/SUM(G16:J16)) * 365</f>
-        <v>112.72404179049603</v>
-      </c>
-      <c r="K76" s="26">
-        <f>(+K50/SUM(H16:K16)) * 365</f>
-        <v>93.175920711791875</v>
-      </c>
-      <c r="L76" s="26">
-        <f>(+L50/SUM(I16:L16)) * 365</f>
-        <v>109.61942230875771</v>
-      </c>
-      <c r="M76" s="26">
-        <f>(+M50/SUM(J16:M16)) * 365</f>
-        <v>128.83425512934878</v>
-      </c>
-    </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B77" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="F77" s="26">
-        <f>+(F60/SUM(C16:F16)) * 365</f>
-        <v>59.270501173214605</v>
-      </c>
-      <c r="G77" s="26">
-        <f>+(G60/SUM(D16:G16)) * 365</f>
-        <v>50.265026629469943</v>
-      </c>
-      <c r="H77" s="26">
-        <f>+(H60/SUM(E16:H16)) * 365</f>
-        <v>58.056708160442597</v>
-      </c>
-      <c r="I77" s="26">
-        <f>+(I60/SUM(F16:I16)) * 365</f>
-        <v>71.459476263623728</v>
-      </c>
-      <c r="J77" s="26">
-        <f>+(J60/SUM(G16:J16)) * 365</f>
-        <v>70.564355525598216</v>
-      </c>
-      <c r="K77" s="26">
-        <f>+(K60/SUM(H16:K16)) * 365</f>
-        <v>60.272891091339112</v>
-      </c>
-      <c r="L77" s="26">
-        <f>+(L60/SUM(I16:L16)) * 365</f>
-        <v>66.407595495694423</v>
-      </c>
-      <c r="M77" s="26">
-        <f>+(M60/SUM(J16:M16)) * 365</f>
-        <v>56.159857270294381</v>
-      </c>
-    </row>
-    <row r="78" spans="2:38" s="30" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B78" s="30" t="s">
-        <v>210</v>
-      </c>
-      <c r="C78" s="31"/>
-      <c r="D78" s="31"/>
-      <c r="E78" s="31"/>
-      <c r="F78" s="31">
-        <f t="shared" ref="F78:L78" si="290">+SUM(F75:F76)-F77</f>
-        <v>116.62980530904048</v>
-      </c>
-      <c r="G78" s="31">
+        <v>45</v>
+      </c>
+      <c r="C75" s="24">
+        <v>24520</v>
+      </c>
+      <c r="D75" s="24">
+        <v>27501</v>
+      </c>
+      <c r="E75" s="24">
+        <v>33265</v>
+      </c>
+      <c r="F75" s="24">
+        <v>42978</v>
+      </c>
+      <c r="G75" s="24">
+        <v>49142</v>
+      </c>
+      <c r="H75" s="24">
+        <v>58157</v>
+      </c>
+      <c r="I75" s="24">
+        <v>65899</v>
+      </c>
+      <c r="J75" s="24">
+        <v>79327</v>
+      </c>
+      <c r="K75" s="24">
+        <v>83843</v>
+      </c>
+      <c r="L75" s="24">
+        <v>100131</v>
+      </c>
+      <c r="M75" s="24">
+        <v>118897</v>
+      </c>
+    </row>
+    <row r="76" spans="2:38" s="30" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B76" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C76" s="31">
+        <f t="shared" ref="C76:K76" si="287">+SUM(C69:C75)</f>
+        <v>44460</v>
+      </c>
+      <c r="D76" s="31">
+        <f t="shared" si="287"/>
+        <v>49555</v>
+      </c>
+      <c r="E76" s="31">
+        <f t="shared" si="287"/>
+        <v>54148</v>
+      </c>
+      <c r="F76" s="31">
+        <f t="shared" si="287"/>
+        <v>65728</v>
+      </c>
+      <c r="G76" s="31">
+        <f t="shared" si="287"/>
+        <v>77072</v>
+      </c>
+      <c r="H76" s="31">
+        <f t="shared" si="287"/>
+        <v>85227</v>
+      </c>
+      <c r="I76" s="31">
+        <f t="shared" si="287"/>
+        <v>96013</v>
+      </c>
+      <c r="J76" s="31">
+        <f t="shared" si="287"/>
+        <v>111601</v>
+      </c>
+      <c r="K76" s="31">
+        <f t="shared" si="287"/>
+        <v>125254</v>
+      </c>
+      <c r="L76" s="31">
+        <f t="shared" ref="L76:M76" si="288">+SUM(L69:L75)</f>
+        <v>140740</v>
+      </c>
+      <c r="M76" s="31">
+        <f t="shared" si="288"/>
+        <v>161148</v>
+      </c>
+      <c r="N76" s="31"/>
+      <c r="Q76" s="31"/>
+      <c r="R76" s="31"/>
+      <c r="S76" s="31"/>
+      <c r="T76" s="31"/>
+      <c r="U76" s="31"/>
+      <c r="V76" s="31"/>
+      <c r="W76" s="31"/>
+      <c r="X76" s="31"/>
+      <c r="Y76" s="31"/>
+      <c r="Z76" s="31"/>
+      <c r="AA76" s="31"/>
+      <c r="AB76" s="31"/>
+      <c r="AC76" s="31"/>
+      <c r="AD76" s="31"/>
+      <c r="AE76" s="31"/>
+      <c r="AF76" s="31"/>
+      <c r="AG76" s="31"/>
+      <c r="AH76" s="31"/>
+      <c r="AI76" s="31"/>
+      <c r="AJ76" s="31"/>
+      <c r="AK76" s="31"/>
+      <c r="AL76" s="31"/>
+    </row>
+    <row r="78" spans="2:38" x14ac:dyDescent="0.15">
+      <c r="B78" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="C78" s="26">
+        <f>SUM(C71:C72)</f>
+        <v>10954</v>
+      </c>
+      <c r="D78" s="26">
+        <f t="shared" ref="D78:K78" si="289">SUM(D71:D72)</f>
+        <v>9705</v>
+      </c>
+      <c r="E78" s="26">
+        <f t="shared" si="289"/>
+        <v>9706</v>
+      </c>
+      <c r="F78" s="26">
+        <f t="shared" si="289"/>
+        <v>9709</v>
+      </c>
+      <c r="G78" s="26">
+        <f t="shared" si="289"/>
+        <v>9710</v>
+      </c>
+      <c r="H78" s="26">
+        <f t="shared" si="289"/>
+        <v>8461</v>
+      </c>
+      <c r="I78" s="26">
+        <f t="shared" si="289"/>
+        <v>8462</v>
+      </c>
+      <c r="J78" s="26">
+        <f t="shared" si="289"/>
+        <v>8463</v>
+      </c>
+      <c r="K78" s="26">
+        <f t="shared" si="289"/>
+        <v>8464</v>
+      </c>
+      <c r="L78" s="26">
+        <f t="shared" ref="L78:M78" si="290">SUM(L71:L72)</f>
+        <v>8466</v>
+      </c>
+      <c r="M78" s="26">
         <f t="shared" si="290"/>
-        <v>114.87516262416726</v>
-      </c>
-      <c r="H78" s="31">
-        <f t="shared" si="290"/>
-        <v>100.8097187883855</v>
-      </c>
-      <c r="I78" s="31">
-        <f t="shared" si="290"/>
-        <v>87.731260354924828</v>
-      </c>
-      <c r="J78" s="31">
-        <f t="shared" si="290"/>
-        <v>106.67247199943577</v>
-      </c>
-      <c r="K78" s="31">
-        <f t="shared" si="290"/>
-        <v>87.296053894095138</v>
-      </c>
-      <c r="L78" s="31">
-        <f t="shared" si="290"/>
-        <v>104.64532679490547</v>
-      </c>
-      <c r="M78" s="31">
-        <f>+SUM(M75:M76)-M77</f>
-        <v>137.79989080024342</v>
-      </c>
-      <c r="N78" s="31"/>
-      <c r="Q78" s="31"/>
-      <c r="R78" s="31"/>
-      <c r="S78" s="31"/>
-      <c r="T78" s="31"/>
-      <c r="U78" s="31"/>
-      <c r="V78" s="31"/>
-      <c r="W78" s="31"/>
-      <c r="X78" s="31"/>
-      <c r="Y78" s="31"/>
-      <c r="Z78" s="31"/>
-      <c r="AA78" s="31"/>
-      <c r="AB78" s="31"/>
-      <c r="AC78" s="31"/>
-      <c r="AD78" s="31"/>
-      <c r="AE78" s="31"/>
-      <c r="AF78" s="31"/>
-      <c r="AG78" s="31"/>
-      <c r="AH78" s="31"/>
-      <c r="AI78" s="31"/>
-      <c r="AJ78" s="31"/>
-      <c r="AK78" s="31"/>
-      <c r="AL78" s="31"/>
+        <v>8467</v>
+      </c>
     </row>
     <row r="79" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="H79" s="51"/>
-      <c r="I79" s="51"/>
-      <c r="J79" s="51"/>
-      <c r="K79" s="51"/>
-      <c r="L79" s="51"/>
-      <c r="M79" s="51"/>
+      <c r="B79" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="C79" s="26">
+        <f>+C49</f>
+        <v>15320</v>
+      </c>
+      <c r="D79" s="26">
+        <f>+D49</f>
+        <v>16023</v>
+      </c>
+      <c r="E79" s="26">
+        <f>+E49</f>
+        <v>18281</v>
+      </c>
+      <c r="F79" s="26">
+        <f>+F49</f>
+        <v>25984</v>
+      </c>
+      <c r="G79" s="26">
+        <f>+G49</f>
+        <v>31438</v>
+      </c>
+      <c r="H79" s="26">
+        <f>+H49</f>
+        <v>34800</v>
+      </c>
+      <c r="I79" s="26">
+        <f>+I49</f>
+        <v>38487</v>
+      </c>
+      <c r="J79" s="26">
+        <f>+J49</f>
+        <v>43210</v>
+      </c>
+      <c r="K79" s="26">
+        <f>+K49</f>
+        <v>53691</v>
+      </c>
+      <c r="L79" s="26">
+        <f>+L49</f>
+        <v>56791</v>
+      </c>
+      <c r="M79" s="26">
+        <f>+M49</f>
+        <v>60608</v>
+      </c>
     </row>
     <row r="80" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="H80" s="51"/>
-      <c r="I80" s="51"/>
-      <c r="J80" s="51"/>
-      <c r="K80" s="51"/>
-      <c r="L80" s="51"/>
-      <c r="M80" s="51"/>
+      <c r="B80" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="C80" s="26">
+        <f>+C79-C78</f>
+        <v>4366</v>
+      </c>
+      <c r="D80" s="26">
+        <f t="shared" ref="D80:K80" si="291">+D79-D78</f>
+        <v>6318</v>
+      </c>
+      <c r="E80" s="26">
+        <f t="shared" si="291"/>
+        <v>8575</v>
+      </c>
+      <c r="F80" s="26">
+        <f t="shared" si="291"/>
+        <v>16275</v>
+      </c>
+      <c r="G80" s="26">
+        <f t="shared" si="291"/>
+        <v>21728</v>
+      </c>
+      <c r="H80" s="26">
+        <f t="shared" si="291"/>
+        <v>26339</v>
+      </c>
+      <c r="I80" s="26">
+        <f t="shared" si="291"/>
+        <v>30025</v>
+      </c>
+      <c r="J80" s="26">
+        <f t="shared" si="291"/>
+        <v>34747</v>
+      </c>
+      <c r="K80" s="26">
+        <f t="shared" si="291"/>
+        <v>45227</v>
+      </c>
+      <c r="L80" s="26">
+        <f t="shared" ref="L80:M80" si="292">+L79-L78</f>
+        <v>48325</v>
+      </c>
+      <c r="M80" s="26">
+        <f t="shared" si="292"/>
+        <v>52141</v>
+      </c>
     </row>
     <row r="81" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="H81" s="51"/>
-      <c r="I81" s="51"/>
-      <c r="J81" s="51"/>
-      <c r="K81" s="51"/>
-      <c r="L81" s="51"/>
-      <c r="M81" s="51"/>
+      <c r="B81" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="C81" s="26">
+        <f>+C75-C59-C58</f>
+        <v>18549</v>
+      </c>
+      <c r="D81" s="26">
+        <f>+D75-D59-D58</f>
+        <v>21676</v>
+      </c>
+      <c r="E81" s="26">
+        <f>+E75-E59-E58</f>
+        <v>27584</v>
+      </c>
+      <c r="F81" s="26">
+        <f>+F75-F59-F58</f>
+        <v>37436</v>
+      </c>
+      <c r="G81" s="26">
+        <f>+G75-G59-G58</f>
+        <v>43703</v>
+      </c>
+      <c r="H81" s="26">
+        <f>+H75-H59-H58</f>
+        <v>52583</v>
+      </c>
+      <c r="I81" s="26">
+        <f>+I75-I59-I58</f>
+        <v>60337</v>
+      </c>
+      <c r="J81" s="26">
+        <f>+J75-J59-J58</f>
+        <v>73332</v>
+      </c>
+      <c r="K81" s="26">
+        <f>+K75-K59-K58</f>
+        <v>77576</v>
+      </c>
+      <c r="L81" s="26">
+        <f>+L75-L59-L58</f>
+        <v>93621</v>
+      </c>
+      <c r="M81" s="26">
+        <f>+M75-M59-M58</f>
+        <v>111700</v>
+      </c>
     </row>
     <row r="82" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="H82" s="51"/>
-      <c r="I82" s="51"/>
-      <c r="J82" s="51"/>
-      <c r="K82" s="51"/>
-      <c r="L82" s="51"/>
-      <c r="M82" s="51"/>
+      <c r="H82" s="46">
+        <f>SUM(E125:H125)/H81</f>
+        <v>0.63176311735732082</v>
+      </c>
+      <c r="I82" s="46">
+        <f>SUM(F125:I125)/I81</f>
+        <v>0.82927556888807863</v>
+      </c>
+      <c r="J82" s="46">
+        <f>SUM(G125:J125)/J81</f>
+        <v>0.89438444335351552</v>
+      </c>
+      <c r="K82" s="46">
+        <f>SUM(H125:K125)/K81</f>
+        <v>0.9289728782097556</v>
+      </c>
+      <c r="L82" s="46">
+        <f>SUM(I125:L125)/L81</f>
+        <v>0.76932525822198006</v>
+      </c>
+      <c r="M82" s="46">
+        <f>SUM(J125:M125)/M81</f>
+        <v>0.69222918531781563</v>
+      </c>
     </row>
     <row r="83" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="I83" s="52" t="s">
-        <v>63</v>
-      </c>
+      <c r="H83" s="46"/>
+      <c r="I83" s="46"/>
+      <c r="J83" s="46"/>
+      <c r="K83" s="46"/>
+      <c r="L83" s="46"/>
+      <c r="M83" s="46"/>
     </row>
     <row r="84" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B84" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C84" s="24"/>
-      <c r="D84" s="24"/>
-      <c r="E84" s="24"/>
-      <c r="F84" s="24"/>
-      <c r="G84" s="24">
-        <v>14881</v>
-      </c>
-      <c r="H84" s="24">
-        <v>16599</v>
-      </c>
-      <c r="I84" s="24">
-        <v>19309</v>
-      </c>
-      <c r="J84" s="24">
-        <v>22091</v>
-      </c>
-      <c r="K84" s="24">
-        <v>18775</v>
-      </c>
-      <c r="L84" s="24"/>
-      <c r="M84" s="24"/>
+        <v>203</v>
+      </c>
+      <c r="F84" s="26">
+        <f>+F50/SUM(C11:F11) * 365</f>
+        <v>59.906683956534586</v>
+      </c>
+      <c r="G84" s="26">
+        <f>+G50/SUM(D11:G11) * 365</f>
+        <v>56.575137262767313</v>
+      </c>
+      <c r="H84" s="26">
+        <f>+H50/SUM(E11:H11) * 365</f>
+        <v>53.559762011068763</v>
+      </c>
+      <c r="I84" s="26">
+        <f>+I50/SUM(F11:I11) * 365</f>
+        <v>57.014231607942151</v>
+      </c>
+      <c r="J84" s="26">
+        <f>+J50/SUM(G11:J11) * 365</f>
+        <v>64.512785734537957</v>
+      </c>
+      <c r="K84" s="26">
+        <f>+K50/SUM(H11:K11) * 365</f>
+        <v>54.393024273642396</v>
+      </c>
+      <c r="L84" s="26">
+        <f>+L50/SUM(I11:L11) * 365</f>
+        <v>61.433499981842175</v>
+      </c>
+      <c r="M84" s="26">
+        <f>+M50/SUM(J11:M11) * 365</f>
+        <v>65.125492941189037</v>
+      </c>
+      <c r="N84" s="24">
+        <f>+M50/M11</f>
+        <v>0.58574536013752942</v>
+      </c>
     </row>
     <row r="85" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B85" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C85" s="24"/>
-      <c r="D85" s="24"/>
-      <c r="E85" s="24"/>
-      <c r="F85" s="24"/>
-      <c r="G85" s="24">
-        <v>1011</v>
-      </c>
-      <c r="H85" s="24">
-        <v>1154</v>
-      </c>
-      <c r="I85" s="24">
-        <v>1252</v>
-      </c>
-      <c r="J85" s="24">
-        <v>1321</v>
-      </c>
-      <c r="K85" s="24">
-        <v>1474</v>
-      </c>
-      <c r="L85" s="24"/>
-      <c r="M85" s="24"/>
+        <v>204</v>
+      </c>
+      <c r="F85" s="26">
+        <f>(+F51/SUM(C16:F16)) * 365</f>
+        <v>115.99362252572048</v>
+      </c>
+      <c r="G85" s="26">
+        <f>(+G51/SUM(D16:G16)) * 365</f>
+        <v>108.56505199086989</v>
+      </c>
+      <c r="H85" s="26">
+        <f>(+H51/SUM(E16:H16)) * 365</f>
+        <v>105.30666493775932</v>
+      </c>
+      <c r="I85" s="26">
+        <f>(+I51/SUM(F16:I16)) * 365</f>
+        <v>102.17650501060639</v>
+      </c>
+      <c r="J85" s="26">
+        <f>(+J51/SUM(G16:J16)) * 365</f>
+        <v>112.72404179049603</v>
+      </c>
+      <c r="K85" s="26">
+        <f>(+K51/SUM(H16:K16)) * 365</f>
+        <v>93.175920711791875</v>
+      </c>
+      <c r="L85" s="26">
+        <f>(+L51/SUM(I16:L16)) * 365</f>
+        <v>109.61942230875771</v>
+      </c>
+      <c r="M85" s="26">
+        <f>(+M51/SUM(J16:M16)) * 365</f>
+        <v>128.83425512934878</v>
+      </c>
+      <c r="N85" s="24">
+        <f>+N84*91</f>
+        <v>53.30282777251518</v>
+      </c>
     </row>
     <row r="86" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B86" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="C86" s="24"/>
-      <c r="D86" s="24"/>
-      <c r="E86" s="24"/>
-      <c r="F86" s="24"/>
-      <c r="G86" s="24">
-        <v>410</v>
-      </c>
-      <c r="H86" s="24">
-        <v>433</v>
-      </c>
-      <c r="I86" s="24">
-        <v>478</v>
-      </c>
-      <c r="J86" s="24">
-        <v>543</v>
-      </c>
-      <c r="K86" s="24">
-        <v>611</v>
-      </c>
-      <c r="L86" s="24">
-        <v>668</v>
-      </c>
-      <c r="M86" s="24"/>
-    </row>
-    <row r="87" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B87" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="C87" s="24"/>
-      <c r="D87" s="24"/>
-      <c r="E87" s="24"/>
-      <c r="F87" s="24"/>
-      <c r="G87" s="24">
-        <v>-69</v>
-      </c>
-      <c r="H87" s="24">
-        <v>-193</v>
-      </c>
-      <c r="I87" s="24">
-        <v>-37</v>
-      </c>
-      <c r="J87" s="24">
-        <v>-727</v>
-      </c>
-      <c r="K87" s="24">
-        <v>175</v>
-      </c>
-      <c r="L87" s="24"/>
-      <c r="M87" s="24"/>
+        <v>205</v>
+      </c>
+      <c r="F86" s="26">
+        <f>+(F69/SUM(C16:F16)) * 365</f>
+        <v>59.270501173214605</v>
+      </c>
+      <c r="G86" s="26">
+        <f>+(G69/SUM(D16:G16)) * 365</f>
+        <v>50.265026629469943</v>
+      </c>
+      <c r="H86" s="26">
+        <f>+(H69/SUM(E16:H16)) * 365</f>
+        <v>58.056708160442597</v>
+      </c>
+      <c r="I86" s="26">
+        <f>+(I69/SUM(F16:I16)) * 365</f>
+        <v>71.459476263623728</v>
+      </c>
+      <c r="J86" s="26">
+        <f>+(J69/SUM(G16:J16)) * 365</f>
+        <v>70.564355525598216</v>
+      </c>
+      <c r="K86" s="26">
+        <f>+(K69/SUM(H16:K16)) * 365</f>
+        <v>60.272891091339112</v>
+      </c>
+      <c r="L86" s="26">
+        <f>+(L69/SUM(I16:L16)) * 365</f>
+        <v>66.407595495694423</v>
+      </c>
+      <c r="M86" s="26">
+        <f>+(M69/SUM(J16:M16)) * 365</f>
+        <v>56.159857270294381</v>
+      </c>
+    </row>
+    <row r="87" spans="2:38" s="30" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B87" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C87" s="31"/>
+      <c r="D87" s="31"/>
+      <c r="E87" s="31"/>
+      <c r="F87" s="31">
+        <f t="shared" ref="F87:L87" si="293">+SUM(F84:F85)-F86</f>
+        <v>116.62980530904048</v>
+      </c>
+      <c r="G87" s="31">
+        <f t="shared" si="293"/>
+        <v>114.87516262416726</v>
+      </c>
+      <c r="H87" s="31">
+        <f t="shared" si="293"/>
+        <v>100.8097187883855</v>
+      </c>
+      <c r="I87" s="31">
+        <f t="shared" si="293"/>
+        <v>87.731260354924828</v>
+      </c>
+      <c r="J87" s="31">
+        <f t="shared" si="293"/>
+        <v>106.67247199943577</v>
+      </c>
+      <c r="K87" s="31">
+        <f t="shared" si="293"/>
+        <v>87.296053894095138</v>
+      </c>
+      <c r="L87" s="31">
+        <f t="shared" si="293"/>
+        <v>104.64532679490547</v>
+      </c>
+      <c r="M87" s="31">
+        <f>+SUM(M84:M85)-M86</f>
+        <v>137.79989080024342</v>
+      </c>
+      <c r="N87" s="31"/>
+      <c r="Q87" s="31"/>
+      <c r="R87" s="31"/>
+      <c r="S87" s="31"/>
+      <c r="T87" s="31"/>
+      <c r="U87" s="31"/>
+      <c r="V87" s="31"/>
+      <c r="W87" s="31"/>
+      <c r="X87" s="31"/>
+      <c r="Y87" s="31"/>
+      <c r="Z87" s="31"/>
+      <c r="AA87" s="31"/>
+      <c r="AB87" s="31"/>
+      <c r="AC87" s="31"/>
+      <c r="AD87" s="31"/>
+      <c r="AE87" s="31"/>
+      <c r="AF87" s="31"/>
+      <c r="AG87" s="31"/>
+      <c r="AH87" s="31"/>
+      <c r="AI87" s="31"/>
+      <c r="AJ87" s="31"/>
+      <c r="AK87" s="31"/>
+      <c r="AL87" s="31"/>
     </row>
     <row r="88" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B88" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C88" s="24"/>
-      <c r="D88" s="24"/>
-      <c r="E88" s="24"/>
-      <c r="F88" s="24"/>
-      <c r="G88" s="24">
-        <v>-1577</v>
-      </c>
-      <c r="H88" s="24">
-        <v>-1699</v>
-      </c>
-      <c r="I88" s="24">
-        <v>-602</v>
-      </c>
-      <c r="J88" s="24">
-        <v>-598</v>
-      </c>
-      <c r="K88" s="24">
-        <v>-2177</v>
-      </c>
-      <c r="L88" s="24"/>
-      <c r="M88" s="24"/>
+      <c r="H88" s="46"/>
+      <c r="I88" s="46"/>
+      <c r="J88" s="46"/>
+      <c r="K88" s="46"/>
+      <c r="L88" s="46"/>
+      <c r="M88" s="46"/>
     </row>
     <row r="89" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B89" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C89" s="24"/>
-      <c r="D89" s="24"/>
-      <c r="E89" s="24"/>
-      <c r="F89" s="24"/>
-      <c r="G89" s="24">
-        <v>-145</v>
-      </c>
-      <c r="H89" s="24">
-        <v>-144</v>
-      </c>
-      <c r="I89" s="24">
-        <v>-79</v>
-      </c>
-      <c r="J89" s="24">
-        <v>-138</v>
-      </c>
-      <c r="K89" s="24">
-        <v>-98</v>
-      </c>
-      <c r="L89" s="24"/>
-      <c r="M89" s="24"/>
+      <c r="I89" s="47" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="90" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B90" s="27" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="C90" s="24"/>
       <c r="D90" s="24"/>
       <c r="E90" s="24"/>
       <c r="F90" s="24"/>
       <c r="G90" s="24">
-        <v>2366</v>
+        <v>14881</v>
       </c>
       <c r="H90" s="24">
-        <v>-1767</v>
+        <v>16599</v>
       </c>
       <c r="I90" s="24">
-        <v>-3561</v>
+        <v>19309</v>
       </c>
       <c r="J90" s="24">
-        <v>-5370</v>
+        <v>22091</v>
       </c>
       <c r="K90" s="24">
-        <v>933</v>
-      </c>
-      <c r="L90" s="24"/>
-      <c r="M90" s="24"/>
+        <v>18775</v>
+      </c>
+      <c r="L90" s="24">
+        <v>26422</v>
+      </c>
+      <c r="M90" s="24">
+        <v>31910</v>
+      </c>
     </row>
     <row r="91" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B91" s="27" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C91" s="24"/>
       <c r="D91" s="24"/>
       <c r="E91" s="24"/>
       <c r="F91" s="24"/>
       <c r="G91" s="24">
-        <v>-577</v>
+        <v>1011</v>
       </c>
       <c r="H91" s="24">
-        <v>-803</v>
+        <v>1154</v>
       </c>
       <c r="I91" s="24">
-        <v>-978</v>
+        <v>1252</v>
       </c>
       <c r="J91" s="24">
-        <v>-2424</v>
+        <v>1321</v>
       </c>
       <c r="K91" s="24">
-        <v>-1258</v>
-      </c>
-      <c r="L91" s="24"/>
-      <c r="M91" s="24"/>
+        <v>1474</v>
+      </c>
+      <c r="L91" s="24">
+        <v>1624</v>
+      </c>
+      <c r="M91" s="24">
+        <v>1655</v>
+      </c>
     </row>
     <row r="92" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B92" s="27" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C92" s="24"/>
       <c r="D92" s="24"/>
       <c r="E92" s="24"/>
       <c r="F92" s="24"/>
       <c r="G92" s="24">
-        <v>-726</v>
+        <v>410</v>
       </c>
       <c r="H92" s="24">
-        <v>714</v>
+        <v>433</v>
       </c>
       <c r="I92" s="24">
-        <v>-714</v>
+        <v>478</v>
       </c>
       <c r="J92" s="24">
-        <v>331</v>
+        <v>543</v>
       </c>
       <c r="K92" s="24">
-        <v>560</v>
-      </c>
-      <c r="L92" s="24"/>
-      <c r="M92" s="24"/>
+        <v>611</v>
+      </c>
+      <c r="L92" s="24">
+        <v>668</v>
+      </c>
+      <c r="M92" s="24">
+        <v>752</v>
+      </c>
     </row>
     <row r="93" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B93" s="27" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C93" s="24"/>
       <c r="D93" s="24"/>
       <c r="E93" s="24"/>
       <c r="F93" s="24"/>
       <c r="G93" s="24">
-        <v>-22</v>
+        <v>-69</v>
       </c>
       <c r="H93" s="24">
-        <v>823</v>
+        <v>-193</v>
       </c>
       <c r="I93" s="24">
-        <v>1689</v>
+        <v>-37</v>
       </c>
       <c r="J93" s="24">
-        <v>867</v>
+        <v>-727</v>
       </c>
       <c r="K93" s="24">
-        <v>941</v>
-      </c>
-      <c r="L93" s="24"/>
-      <c r="M93" s="24"/>
+        <v>175</v>
+      </c>
+      <c r="L93" s="24">
+        <v>-2247</v>
+      </c>
+      <c r="M93" s="24">
+        <v>-1354</v>
+      </c>
     </row>
     <row r="94" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B94" s="27" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C94" s="24"/>
       <c r="D94" s="24"/>
       <c r="E94" s="24"/>
       <c r="F94" s="24"/>
       <c r="G94" s="24">
-        <v>4202</v>
+        <v>-1577</v>
       </c>
       <c r="H94" s="24">
-        <v>-888</v>
+        <v>-1699</v>
       </c>
       <c r="I94" s="24">
-        <v>606</v>
+        <v>-602</v>
       </c>
       <c r="J94" s="24">
-        <v>360</v>
+        <v>-598</v>
       </c>
       <c r="K94" s="24">
-        <v>7128</v>
-      </c>
-      <c r="L94" s="24"/>
-      <c r="M94" s="24"/>
+        <v>-2177</v>
+      </c>
+      <c r="L94" s="24">
+        <v>18</v>
+      </c>
+      <c r="M94" s="24">
+        <v>124</v>
+      </c>
     </row>
     <row r="95" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B95" s="27" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C95" s="24"/>
       <c r="D95" s="24"/>
       <c r="E95" s="24"/>
       <c r="F95" s="24"/>
       <c r="G95" s="24">
-        <v>323</v>
+        <v>-145</v>
       </c>
       <c r="H95" s="24">
-        <v>260</v>
+        <v>-144</v>
       </c>
       <c r="I95" s="24">
-        <v>266</v>
+        <v>-79</v>
       </c>
       <c r="J95" s="24">
-        <v>372</v>
+        <v>-138</v>
       </c>
       <c r="K95" s="24">
-        <v>350</v>
-      </c>
-      <c r="L95" s="24"/>
-      <c r="M95" s="24"/>
-    </row>
-    <row r="96" spans="2:38" s="30" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B96" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C96" s="31"/>
-      <c r="D96" s="31"/>
-      <c r="E96" s="31"/>
-      <c r="F96" s="31"/>
-      <c r="G96" s="31">
-        <f>+SUM(G84:G95)</f>
-        <v>20077</v>
-      </c>
-      <c r="H96" s="31">
-        <f>+SUM(H84:H95)</f>
-        <v>14489</v>
-      </c>
-      <c r="I96" s="31">
-        <f>+SUM(I84:I95)</f>
-        <v>17629</v>
-      </c>
-      <c r="J96" s="31">
-        <f>+SUM(J84:J95)</f>
-        <v>16628</v>
-      </c>
-      <c r="K96" s="31">
-        <f>+SUM(K84:K95)</f>
-        <v>27414</v>
-      </c>
-      <c r="L96" s="31">
-        <v>15365</v>
-      </c>
-      <c r="M96" s="31">
-        <v>23750</v>
-      </c>
-      <c r="N96" s="31"/>
-      <c r="Q96" s="31"/>
-      <c r="R96" s="31"/>
-      <c r="S96" s="31"/>
-      <c r="T96" s="31"/>
-      <c r="U96" s="31"/>
-      <c r="V96" s="31"/>
-      <c r="W96" s="31"/>
-      <c r="X96" s="31"/>
-      <c r="Y96" s="31"/>
-      <c r="Z96" s="31"/>
-      <c r="AA96" s="31"/>
-      <c r="AB96" s="31"/>
-      <c r="AC96" s="31"/>
-      <c r="AD96" s="31"/>
-      <c r="AE96" s="31"/>
-      <c r="AF96" s="31"/>
-      <c r="AG96" s="31"/>
-      <c r="AH96" s="31"/>
-      <c r="AI96" s="31"/>
-      <c r="AJ96" s="31"/>
-      <c r="AK96" s="31"/>
-      <c r="AL96" s="31"/>
+        <v>-98</v>
+      </c>
+      <c r="L95" s="24">
+        <v>-100</v>
+      </c>
+      <c r="M95" s="24">
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="96" spans="2:38" x14ac:dyDescent="0.15">
+      <c r="B96" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C96" s="24"/>
+      <c r="D96" s="24"/>
+      <c r="E96" s="24"/>
+      <c r="F96" s="24"/>
+      <c r="G96" s="24">
+        <v>2366</v>
+      </c>
+      <c r="H96" s="24">
+        <v>-1767</v>
+      </c>
+      <c r="I96" s="24">
+        <v>-3561</v>
+      </c>
+      <c r="J96" s="24">
+        <v>-5370</v>
+      </c>
+      <c r="K96" s="24">
+        <v>933</v>
+      </c>
+      <c r="L96" s="24">
+        <v>-5675</v>
+      </c>
+      <c r="M96" s="24">
+        <v>-5583</v>
+      </c>
+    </row>
+    <row r="97" spans="2:38" x14ac:dyDescent="0.15">
+      <c r="B97" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C97" s="24"/>
+      <c r="D97" s="24"/>
+      <c r="E97" s="24"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="24">
+        <v>-577</v>
+      </c>
+      <c r="H97" s="24">
+        <v>-803</v>
+      </c>
+      <c r="I97" s="24">
+        <v>-978</v>
+      </c>
+      <c r="J97" s="24">
+        <v>-2424</v>
+      </c>
+      <c r="K97" s="24">
+        <v>-1258</v>
+      </c>
+      <c r="L97" s="24">
+        <v>-3622</v>
+      </c>
+      <c r="M97" s="24">
+        <v>-4823</v>
+      </c>
     </row>
     <row r="98" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B98" s="27" t="s">
-        <v>175</v>
+        <v>68</v>
       </c>
       <c r="C98" s="24"/>
       <c r="D98" s="24"/>
       <c r="E98" s="24"/>
       <c r="F98" s="24"/>
       <c r="G98" s="24">
-        <v>4004</v>
+        <v>-726</v>
       </c>
       <c r="H98" s="24">
-        <v>4094</v>
+        <v>714</v>
       </c>
       <c r="I98" s="24">
-        <v>1386</v>
+        <v>-714</v>
       </c>
       <c r="J98" s="24">
-        <v>1710</v>
+        <v>331</v>
       </c>
       <c r="K98" s="24">
-        <v>3122</v>
-      </c>
-      <c r="L98" s="24"/>
-      <c r="M98" s="24"/>
+        <v>560</v>
+      </c>
+      <c r="L98" s="24">
+        <v>387</v>
+      </c>
+      <c r="M98" s="24">
+        <v>-89</v>
+      </c>
     </row>
     <row r="99" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B99" s="27" t="s">
-        <v>176</v>
+        <v>47</v>
       </c>
       <c r="C99" s="24"/>
       <c r="D99" s="24"/>
       <c r="E99" s="24"/>
       <c r="F99" s="24"/>
       <c r="G99" s="24">
-        <v>149</v>
+        <v>-22</v>
       </c>
       <c r="H99" s="24">
-        <v>15</v>
+        <v>823</v>
       </c>
       <c r="I99" s="24">
-        <v>154</v>
+        <v>1689</v>
       </c>
       <c r="J99" s="24">
-        <v>177</v>
+        <v>867</v>
       </c>
       <c r="K99" s="24">
-        <v>467</v>
-      </c>
-      <c r="L99" s="24"/>
-      <c r="M99" s="24"/>
+        <v>941</v>
+      </c>
+      <c r="L99" s="24">
+        <v>1314</v>
+      </c>
+      <c r="M99" s="24">
+        <v>-223</v>
+      </c>
     </row>
     <row r="100" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B100" s="27" t="s">
-        <v>177</v>
+        <v>69</v>
       </c>
       <c r="C100" s="24"/>
       <c r="D100" s="24"/>
       <c r="E100" s="24"/>
       <c r="F100" s="24"/>
       <c r="G100" s="24">
-        <v>55</v>
+        <v>4202</v>
       </c>
       <c r="H100" s="24">
-        <v>0</v>
+        <v>-888</v>
       </c>
       <c r="I100" s="24">
-        <v>0</v>
+        <v>606</v>
       </c>
       <c r="J100" s="24">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="K100" s="24">
-        <v>0</v>
-      </c>
-      <c r="L100" s="24"/>
-      <c r="M100" s="24"/>
+        <v>7128</v>
+      </c>
+      <c r="L100" s="24">
+        <v>-4053</v>
+      </c>
+      <c r="M100" s="24">
+        <v>1129</v>
+      </c>
     </row>
     <row r="101" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B101" s="27" t="s">
-        <v>178</v>
+        <v>51</v>
       </c>
       <c r="C101" s="24"/>
       <c r="D101" s="24"/>
       <c r="E101" s="24"/>
       <c r="F101" s="24"/>
       <c r="G101" s="24">
-        <v>-9303</v>
+        <v>323</v>
       </c>
       <c r="H101" s="24">
-        <v>-5744</v>
+        <v>260</v>
       </c>
       <c r="I101" s="24">
-        <v>-4518</v>
+        <v>266</v>
       </c>
       <c r="J101" s="24">
-        <v>-7010</v>
+        <v>372</v>
       </c>
       <c r="K101" s="24">
-        <v>-6456</v>
-      </c>
-      <c r="L101" s="24"/>
-      <c r="M101" s="24"/>
-    </row>
-    <row r="102" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B102" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="C102" s="24"/>
-      <c r="D102" s="24"/>
-      <c r="E102" s="24"/>
-      <c r="F102" s="24"/>
-      <c r="G102" s="24">
-        <v>-369</v>
-      </c>
-      <c r="H102" s="24">
-        <v>-977</v>
-      </c>
-      <c r="I102" s="24">
-        <v>-813</v>
-      </c>
-      <c r="J102" s="24">
-        <v>-1077</v>
-      </c>
-      <c r="K102" s="24">
-        <v>-1227</v>
-      </c>
-      <c r="L102" s="24">
-        <v>-1894</v>
-      </c>
-      <c r="M102" s="24">
-        <v>-1637</v>
-      </c>
-    </row>
-    <row r="103" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B103" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="C103" s="24"/>
-      <c r="D103" s="24"/>
-      <c r="E103" s="24"/>
-      <c r="F103" s="24"/>
-      <c r="G103" s="24">
-        <v>-190</v>
-      </c>
-      <c r="H103" s="24">
-        <v>0</v>
-      </c>
-      <c r="I103" s="24">
-        <v>0</v>
-      </c>
-      <c r="J103" s="24">
-        <v>-478</v>
-      </c>
-      <c r="K103" s="24">
-        <v>-649</v>
-      </c>
-      <c r="L103" s="24"/>
-      <c r="M103" s="24"/>
+        <v>350</v>
+      </c>
+      <c r="L101" s="24">
+        <v>629</v>
+      </c>
+      <c r="M101" s="24">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="102" spans="2:38" s="30" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B102" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C102" s="31"/>
+      <c r="D102" s="31"/>
+      <c r="E102" s="31"/>
+      <c r="F102" s="31"/>
+      <c r="G102" s="31">
+        <f>+SUM(G90:G101)</f>
+        <v>20077</v>
+      </c>
+      <c r="H102" s="31">
+        <f>+SUM(H90:H101)</f>
+        <v>14489</v>
+      </c>
+      <c r="I102" s="31">
+        <f>+SUM(I90:I101)</f>
+        <v>17629</v>
+      </c>
+      <c r="J102" s="31">
+        <f>+SUM(J90:J101)</f>
+        <v>16628</v>
+      </c>
+      <c r="K102" s="31">
+        <f>+SUM(K90:K101)</f>
+        <v>27414</v>
+      </c>
+      <c r="L102" s="31">
+        <f>+SUM(L90:L101)</f>
+        <v>15365</v>
+      </c>
+      <c r="M102" s="31">
+        <f>+SUM(M90:M101)</f>
+        <v>23750</v>
+      </c>
+      <c r="N102" s="31"/>
+      <c r="Q102" s="31"/>
+      <c r="R102" s="31"/>
+      <c r="S102" s="31"/>
+      <c r="T102" s="31"/>
+      <c r="U102" s="31"/>
+      <c r="V102" s="31"/>
+      <c r="W102" s="31"/>
+      <c r="X102" s="31"/>
+      <c r="Y102" s="31"/>
+      <c r="Z102" s="31"/>
+      <c r="AA102" s="31"/>
+      <c r="AB102" s="31"/>
+      <c r="AC102" s="31"/>
+      <c r="AD102" s="31"/>
+      <c r="AE102" s="31"/>
+      <c r="AF102" s="31"/>
+      <c r="AG102" s="31"/>
+      <c r="AH102" s="31"/>
+      <c r="AI102" s="31"/>
+      <c r="AJ102" s="31"/>
+      <c r="AK102" s="31"/>
+      <c r="AL102" s="31"/>
     </row>
     <row r="104" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B104" s="27" t="s">
-        <v>71</v>
+        <v>173</v>
       </c>
       <c r="C104" s="24"/>
       <c r="D104" s="24"/>
       <c r="E104" s="24"/>
       <c r="F104" s="24"/>
       <c r="G104" s="24">
-        <v>-39</v>
+        <v>4004</v>
       </c>
       <c r="H104" s="24">
-        <v>-279</v>
+        <v>4094</v>
       </c>
       <c r="I104" s="24">
-        <v>-147</v>
+        <v>1386</v>
       </c>
       <c r="J104" s="24">
-        <v>-542</v>
+        <v>1710</v>
       </c>
       <c r="K104" s="24">
-        <v>-383</v>
-      </c>
-      <c r="L104" s="24"/>
-      <c r="M104" s="24"/>
+        <v>3122</v>
+      </c>
+      <c r="L104" s="24">
+        <v>3130</v>
+      </c>
+      <c r="M104" s="24">
+        <v>2728</v>
+      </c>
     </row>
     <row r="105" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B105" s="27" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C105" s="24"/>
       <c r="D105" s="24"/>
       <c r="E105" s="24"/>
       <c r="F105" s="24"/>
-      <c r="G105" s="24"/>
+      <c r="G105" s="24">
+        <v>149</v>
+      </c>
       <c r="H105" s="24">
-        <v>-344</v>
+        <v>15</v>
       </c>
       <c r="I105" s="24">
-        <v>66</v>
+        <v>154</v>
       </c>
       <c r="J105" s="24">
-        <v>22</v>
-      </c>
-      <c r="K105" s="24"/>
-      <c r="L105" s="24"/>
-      <c r="M105" s="24"/>
+        <v>177</v>
+      </c>
+      <c r="K105" s="24">
+        <v>467</v>
+      </c>
+      <c r="L105" s="24">
+        <v>20</v>
+      </c>
+      <c r="M105" s="24">
+        <v>0</v>
+      </c>
     </row>
     <row r="106" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B106" s="27" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C106" s="24"/>
       <c r="D106" s="24"/>
       <c r="E106" s="24"/>
       <c r="F106" s="24"/>
-      <c r="G106" s="24"/>
+      <c r="G106" s="24">
+        <v>55</v>
+      </c>
       <c r="H106" s="24">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I106" s="24">
-        <v>-473</v>
-      </c>
-      <c r="J106" s="24"/>
-      <c r="K106" s="24"/>
-      <c r="L106" s="24"/>
-      <c r="M106" s="24"/>
-    </row>
-    <row r="107" spans="2:38" s="30" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B107" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="C107" s="31"/>
-      <c r="D107" s="31"/>
-      <c r="E107" s="31"/>
-      <c r="F107" s="31"/>
-      <c r="G107" s="31">
-        <f>+SUM(G98:G104)</f>
-        <v>-5693</v>
-      </c>
-      <c r="H107" s="31">
-        <f>+SUM(H98:H106)</f>
-        <v>-3185</v>
-      </c>
-      <c r="I107" s="31">
-        <f>+SUM(I98:I106)</f>
-        <v>-4345</v>
-      </c>
-      <c r="J107" s="31">
-        <f>+SUM(J98:J106)</f>
-        <v>-7198</v>
-      </c>
-      <c r="K107" s="31">
-        <f>+SUM(K98:K104)</f>
-        <v>-5126</v>
-      </c>
-      <c r="L107" s="31"/>
-      <c r="M107" s="31"/>
-      <c r="N107" s="31"/>
-      <c r="Q107" s="31"/>
-      <c r="R107" s="31"/>
-      <c r="S107" s="31"/>
-      <c r="T107" s="31"/>
-      <c r="U107" s="31"/>
-      <c r="V107" s="31"/>
-      <c r="W107" s="31"/>
-      <c r="X107" s="31"/>
-      <c r="Y107" s="31"/>
-      <c r="Z107" s="31"/>
-      <c r="AA107" s="31"/>
-      <c r="AB107" s="31"/>
-      <c r="AC107" s="31"/>
-      <c r="AD107" s="31"/>
-      <c r="AE107" s="31"/>
-      <c r="AF107" s="31"/>
-      <c r="AG107" s="31"/>
-      <c r="AH107" s="31"/>
-      <c r="AI107" s="31"/>
-      <c r="AJ107" s="31"/>
-      <c r="AK107" s="31"/>
-      <c r="AL107" s="31"/>
+        <v>0</v>
+      </c>
+      <c r="J106" s="24">
+        <v>0</v>
+      </c>
+      <c r="K106" s="24">
+        <v>0</v>
+      </c>
+      <c r="L106" s="24">
+        <v>70</v>
+      </c>
+      <c r="M106" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="2:38" x14ac:dyDescent="0.15">
+      <c r="B107" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="C107" s="24"/>
+      <c r="D107" s="24"/>
+      <c r="E107" s="24"/>
+      <c r="F107" s="24"/>
+      <c r="G107" s="24">
+        <v>-9303</v>
+      </c>
+      <c r="H107" s="24">
+        <v>-5744</v>
+      </c>
+      <c r="I107" s="24">
+        <v>-4518</v>
+      </c>
+      <c r="J107" s="24">
+        <v>-7010</v>
+      </c>
+      <c r="K107" s="24">
+        <v>-6456</v>
+      </c>
+      <c r="L107" s="24">
+        <v>-7812</v>
+      </c>
+      <c r="M107" s="24">
+        <v>-5718</v>
+      </c>
+    </row>
+    <row r="108" spans="2:38" x14ac:dyDescent="0.15">
+      <c r="B108" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="C108" s="24"/>
+      <c r="D108" s="24"/>
+      <c r="E108" s="24"/>
+      <c r="F108" s="24"/>
+      <c r="G108" s="24">
+        <v>-369</v>
+      </c>
+      <c r="H108" s="24">
+        <v>-977</v>
+      </c>
+      <c r="I108" s="24">
+        <v>-813</v>
+      </c>
+      <c r="J108" s="24">
+        <v>-1077</v>
+      </c>
+      <c r="K108" s="24">
+        <v>-1227</v>
+      </c>
+      <c r="L108" s="24">
+        <v>-1894</v>
+      </c>
+      <c r="M108" s="24">
+        <v>-1637</v>
+      </c>
     </row>
     <row r="109" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B109" s="27" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C109" s="24"/>
       <c r="D109" s="24"/>
       <c r="E109" s="24"/>
       <c r="F109" s="24"/>
       <c r="G109" s="24">
-        <v>285</v>
+        <v>-190</v>
       </c>
       <c r="H109" s="24">
         <v>0</v>
       </c>
       <c r="I109" s="24">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="J109" s="24">
-        <v>0</v>
+        <v>-478</v>
       </c>
       <c r="K109" s="24">
-        <v>370</v>
-      </c>
-      <c r="L109" s="24"/>
-      <c r="M109" s="24"/>
+        <v>-649</v>
+      </c>
+      <c r="L109" s="24">
+        <v>-346</v>
+      </c>
+      <c r="M109" s="24">
+        <v>-3706</v>
+      </c>
     </row>
     <row r="110" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B110" s="27" t="s">
-        <v>184</v>
+        <v>71</v>
       </c>
       <c r="C110" s="24"/>
       <c r="D110" s="24"/>
       <c r="E110" s="24"/>
       <c r="F110" s="24"/>
       <c r="G110" s="24">
-        <v>-7740</v>
+        <v>-39</v>
       </c>
       <c r="H110" s="24">
-        <v>-7158</v>
+        <v>-279</v>
       </c>
       <c r="I110" s="24">
-        <v>-10998</v>
+        <v>-147</v>
       </c>
       <c r="J110" s="24">
-        <v>-7810</v>
+        <v>-542</v>
       </c>
       <c r="K110" s="24">
-        <v>-14095</v>
-      </c>
-      <c r="L110" s="24"/>
-      <c r="M110" s="24"/>
+        <v>-383</v>
+      </c>
+      <c r="L110" s="24">
+        <v>-294</v>
+      </c>
+      <c r="M110" s="24">
+        <v>-694</v>
+      </c>
     </row>
     <row r="111" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B111" s="27" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C111" s="24"/>
       <c r="D111" s="24"/>
@@ -9754,11 +9847,13 @@
       <c r="F111" s="24"/>
       <c r="G111" s="24"/>
       <c r="H111" s="24">
-        <v>-1250</v>
-      </c>
-      <c r="I111" s="24"/>
+        <v>-344</v>
+      </c>
+      <c r="I111" s="24">
+        <v>66</v>
+      </c>
       <c r="J111" s="24">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K111" s="24"/>
       <c r="L111" s="24"/>
@@ -9766,373 +9861,510 @@
     </row>
     <row r="112" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B112" s="27" t="s">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="C112" s="24"/>
       <c r="D112" s="24"/>
       <c r="E112" s="24"/>
       <c r="F112" s="24"/>
-      <c r="G112" s="24">
-        <v>-1752</v>
-      </c>
+      <c r="G112" s="24"/>
       <c r="H112" s="24">
-        <v>-1637</v>
+        <v>50</v>
       </c>
       <c r="I112" s="24">
-        <v>-1680</v>
-      </c>
-      <c r="J112" s="24">
-        <v>-1861</v>
-      </c>
-      <c r="K112" s="24">
-        <v>-1532</v>
-      </c>
+        <v>-473</v>
+      </c>
+      <c r="J112" s="24"/>
+      <c r="K112" s="24"/>
       <c r="L112" s="24"/>
       <c r="M112" s="24"/>
     </row>
-    <row r="113" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B113" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C113" s="24"/>
-      <c r="D113" s="24"/>
-      <c r="E113" s="24"/>
-      <c r="F113" s="24"/>
-      <c r="G113" s="24">
-        <v>-98</v>
-      </c>
-      <c r="H113" s="24">
-        <v>-246</v>
-      </c>
-      <c r="I113" s="24">
-        <v>-245</v>
-      </c>
-      <c r="J113" s="24">
-        <v>-245</v>
-      </c>
-      <c r="K113" s="24">
-        <v>-244</v>
-      </c>
-      <c r="L113" s="24"/>
-      <c r="M113" s="24"/>
-    </row>
-    <row r="114" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B114" s="27" t="s">
-        <v>185</v>
-      </c>
-      <c r="C114" s="24"/>
-      <c r="D114" s="24"/>
-      <c r="E114" s="24"/>
-      <c r="F114" s="24"/>
-      <c r="G114" s="24">
-        <v>-40</v>
-      </c>
-      <c r="H114" s="24">
-        <v>-29</v>
-      </c>
-      <c r="I114" s="24">
-        <v>-29</v>
-      </c>
-      <c r="J114" s="24">
-        <v>-32</v>
-      </c>
-      <c r="K114" s="24">
-        <v>-52</v>
-      </c>
-      <c r="L114" s="24"/>
-      <c r="M114" s="24"/>
-    </row>
-    <row r="115" spans="2:38" s="30" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B115" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="C115" s="31"/>
-      <c r="D115" s="31"/>
-      <c r="E115" s="31"/>
-      <c r="F115" s="31"/>
-      <c r="G115" s="31">
-        <f>+SUM(G109:G114)</f>
-        <v>-9345</v>
-      </c>
-      <c r="H115" s="31">
-        <f>+SUM(H109:H114)</f>
-        <v>-10320</v>
-      </c>
-      <c r="I115" s="31">
-        <f>+SUM(I109:I114)</f>
-        <v>-12748</v>
-      </c>
-      <c r="J115" s="31">
-        <f>+SUM(J109:J114)</f>
-        <v>-9948</v>
-      </c>
-      <c r="K115" s="31">
-        <f>+SUM(K109:K114)</f>
-        <v>-15553</v>
-      </c>
-      <c r="L115" s="31"/>
-      <c r="M115" s="31"/>
-      <c r="N115" s="31"/>
-      <c r="Q115" s="31"/>
-      <c r="R115" s="31"/>
-      <c r="S115" s="31"/>
-      <c r="T115" s="31"/>
-      <c r="U115" s="31"/>
-      <c r="V115" s="31"/>
-      <c r="W115" s="31"/>
-      <c r="X115" s="31"/>
-      <c r="Y115" s="31"/>
-      <c r="Z115" s="31"/>
-      <c r="AA115" s="31"/>
-      <c r="AB115" s="31"/>
-      <c r="AC115" s="31"/>
-      <c r="AD115" s="31"/>
-      <c r="AE115" s="31"/>
-      <c r="AF115" s="31"/>
-      <c r="AG115" s="31"/>
-      <c r="AH115" s="31"/>
-      <c r="AI115" s="31"/>
-      <c r="AJ115" s="31"/>
-      <c r="AK115" s="31"/>
-      <c r="AL115" s="31"/>
+    <row r="113" spans="2:38" s="30" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B113" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C113" s="31"/>
+      <c r="D113" s="31"/>
+      <c r="E113" s="31"/>
+      <c r="F113" s="31"/>
+      <c r="G113" s="31">
+        <f>+SUM(G104:G110)</f>
+        <v>-5693</v>
+      </c>
+      <c r="H113" s="31">
+        <f>+SUM(H104:H112)</f>
+        <v>-3185</v>
+      </c>
+      <c r="I113" s="31">
+        <f>+SUM(I104:I112)</f>
+        <v>-4345</v>
+      </c>
+      <c r="J113" s="31">
+        <f>+SUM(J104:J112)</f>
+        <v>-7198</v>
+      </c>
+      <c r="K113" s="31">
+        <f>+SUM(K104:K110)</f>
+        <v>-5126</v>
+      </c>
+      <c r="L113" s="31">
+        <f>+SUM(L104:L110)</f>
+        <v>-7126</v>
+      </c>
+      <c r="M113" s="31">
+        <f>+SUM(M104:M110)</f>
+        <v>-9025</v>
+      </c>
+      <c r="N113" s="31"/>
+      <c r="Q113" s="31"/>
+      <c r="R113" s="31"/>
+      <c r="S113" s="31"/>
+      <c r="T113" s="31"/>
+      <c r="U113" s="31"/>
+      <c r="V113" s="31"/>
+      <c r="W113" s="31"/>
+      <c r="X113" s="31"/>
+      <c r="Y113" s="31"/>
+      <c r="Z113" s="31"/>
+      <c r="AA113" s="31"/>
+      <c r="AB113" s="31"/>
+      <c r="AC113" s="31"/>
+      <c r="AD113" s="31"/>
+      <c r="AE113" s="31"/>
+      <c r="AF113" s="31"/>
+      <c r="AG113" s="31"/>
+      <c r="AH113" s="31"/>
+      <c r="AI113" s="31"/>
+      <c r="AJ113" s="31"/>
+      <c r="AK113" s="31"/>
+      <c r="AL113" s="31"/>
+    </row>
+    <row r="115" spans="2:38" x14ac:dyDescent="0.15">
+      <c r="B115" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="C115" s="24"/>
+      <c r="D115" s="24"/>
+      <c r="E115" s="24"/>
+      <c r="F115" s="24"/>
+      <c r="G115" s="24">
+        <v>285</v>
+      </c>
+      <c r="H115" s="24">
+        <v>0</v>
+      </c>
+      <c r="I115" s="24">
+        <v>204</v>
+      </c>
+      <c r="J115" s="24">
+        <v>0</v>
+      </c>
+      <c r="K115" s="24">
+        <v>370</v>
+      </c>
+      <c r="L115" s="24">
+        <v>0</v>
+      </c>
+      <c r="M115" s="24">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="116" spans="2:38" x14ac:dyDescent="0.15">
+      <c r="B116" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="C116" s="24"/>
+      <c r="D116" s="24"/>
+      <c r="E116" s="24"/>
+      <c r="F116" s="24"/>
+      <c r="G116" s="24">
+        <v>-7740</v>
+      </c>
+      <c r="H116" s="24">
+        <v>-7158</v>
+      </c>
+      <c r="I116" s="24">
+        <v>-10998</v>
+      </c>
+      <c r="J116" s="24">
+        <v>-7810</v>
+      </c>
+      <c r="K116" s="24">
+        <v>-14095</v>
+      </c>
+      <c r="L116" s="24">
+        <v>-9721</v>
+      </c>
+      <c r="M116" s="24">
+        <v>-12456</v>
+      </c>
     </row>
     <row r="117" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B117" s="27" t="s">
-        <v>187</v>
-      </c>
-      <c r="G117" s="26">
-        <f>SUM(G96,G107,G115)</f>
-        <v>5039</v>
-      </c>
-      <c r="H117" s="26">
-        <f>SUM(H96,H107,H115)</f>
-        <v>984</v>
-      </c>
-      <c r="I117" s="26">
-        <f>SUM(I96,I107,I115)</f>
-        <v>536</v>
-      </c>
-      <c r="J117" s="26">
-        <f>SUM(J96,J107,J115)</f>
-        <v>-518</v>
-      </c>
-      <c r="K117" s="26">
-        <f>SUM(K96,K107,K115)</f>
-        <v>6735</v>
+        <v>184</v>
+      </c>
+      <c r="C117" s="24"/>
+      <c r="D117" s="24"/>
+      <c r="E117" s="24"/>
+      <c r="F117" s="24"/>
+      <c r="G117" s="24"/>
+      <c r="H117" s="24">
+        <v>-1250</v>
+      </c>
+      <c r="I117" s="24"/>
+      <c r="J117" s="24">
+        <v>0</v>
+      </c>
+      <c r="K117" s="24"/>
+      <c r="L117" s="24"/>
+      <c r="M117" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="2:38" x14ac:dyDescent="0.15">
+      <c r="B118" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C118" s="24"/>
+      <c r="D118" s="24"/>
+      <c r="E118" s="24"/>
+      <c r="F118" s="24"/>
+      <c r="G118" s="24">
+        <v>-1752</v>
+      </c>
+      <c r="H118" s="24">
+        <v>-1637</v>
+      </c>
+      <c r="I118" s="24">
+        <v>-1680</v>
+      </c>
+      <c r="J118" s="24">
+        <v>-1861</v>
+      </c>
+      <c r="K118" s="24">
+        <v>-1532</v>
+      </c>
+      <c r="L118" s="24">
+        <v>-1848</v>
+      </c>
+      <c r="M118" s="24">
+        <v>-2429</v>
       </c>
     </row>
     <row r="119" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B119" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="G119" s="26">
-        <f t="shared" ref="G119:M119" si="291">+G96+G102</f>
-        <v>19708</v>
-      </c>
-      <c r="H119" s="26">
-        <f t="shared" si="291"/>
-        <v>13512</v>
-      </c>
-      <c r="I119" s="26">
-        <f t="shared" si="291"/>
-        <v>16816</v>
-      </c>
-      <c r="J119" s="26">
-        <f t="shared" si="291"/>
-        <v>15551</v>
-      </c>
-      <c r="K119" s="26">
-        <f t="shared" si="291"/>
-        <v>26187</v>
-      </c>
-      <c r="L119" s="26">
-        <f t="shared" si="291"/>
-        <v>13471</v>
-      </c>
-      <c r="M119" s="26">
-        <f t="shared" si="291"/>
-        <v>22113</v>
+        <v>74</v>
+      </c>
+      <c r="C119" s="24"/>
+      <c r="D119" s="24"/>
+      <c r="E119" s="24"/>
+      <c r="F119" s="24"/>
+      <c r="G119" s="24">
+        <v>-98</v>
+      </c>
+      <c r="H119" s="24">
+        <v>-246</v>
+      </c>
+      <c r="I119" s="24">
+        <v>-245</v>
+      </c>
+      <c r="J119" s="24">
+        <v>-245</v>
+      </c>
+      <c r="K119" s="24">
+        <v>-244</v>
+      </c>
+      <c r="L119" s="24">
+        <v>-244</v>
+      </c>
+      <c r="M119" s="24">
+        <v>-243</v>
       </c>
     </row>
     <row r="120" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B120" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="G120" s="26">
-        <f>+G25</f>
-        <v>14046</v>
-      </c>
-      <c r="H120" s="26">
-        <f>+H25</f>
-        <v>16599</v>
-      </c>
-      <c r="I120" s="26">
-        <f>+I25</f>
-        <v>19309</v>
-      </c>
-      <c r="J120" s="26">
-        <f>+J25</f>
-        <v>32926</v>
-      </c>
-      <c r="K120" s="26">
-        <f>+K25</f>
-        <v>18775</v>
-      </c>
-      <c r="L120" s="26">
-        <f>+L25</f>
-        <v>26546</v>
-      </c>
-      <c r="M120" s="26">
-        <f>+M25</f>
-        <v>31910</v>
-      </c>
-    </row>
-    <row r="122" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B122" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="G122" s="26">
-        <f>+G102</f>
-        <v>-369</v>
-      </c>
-      <c r="H122" s="26">
-        <f t="shared" ref="H122:L122" si="292">+H102</f>
-        <v>-977</v>
-      </c>
-      <c r="I122" s="26">
-        <f t="shared" si="292"/>
-        <v>-813</v>
-      </c>
-      <c r="J122" s="26">
-        <f t="shared" si="292"/>
-        <v>-1077</v>
-      </c>
-      <c r="K122" s="26">
-        <f t="shared" si="292"/>
-        <v>-1227</v>
-      </c>
-      <c r="L122" s="26">
-        <f t="shared" si="292"/>
-        <v>-1894</v>
-      </c>
-    </row>
-    <row r="123" spans="2:38" x14ac:dyDescent="0.15">
-      <c r="B123" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="G123" s="26">
-        <f>+G86</f>
-        <v>410</v>
-      </c>
-      <c r="H123" s="26">
-        <f t="shared" ref="H123:L123" si="293">+H86</f>
-        <v>433</v>
-      </c>
-      <c r="I123" s="26">
-        <f t="shared" si="293"/>
-        <v>478</v>
-      </c>
-      <c r="J123" s="26">
-        <f t="shared" si="293"/>
-        <v>543</v>
-      </c>
-      <c r="K123" s="26">
-        <f t="shared" si="293"/>
-        <v>611</v>
-      </c>
-      <c r="L123" s="26">
-        <f t="shared" si="293"/>
-        <v>668</v>
+        <v>183</v>
+      </c>
+      <c r="C120" s="24"/>
+      <c r="D120" s="24"/>
+      <c r="E120" s="24"/>
+      <c r="F120" s="24"/>
+      <c r="G120" s="24">
+        <v>-40</v>
+      </c>
+      <c r="H120" s="24">
+        <v>-29</v>
+      </c>
+      <c r="I120" s="24">
+        <v>-29</v>
+      </c>
+      <c r="J120" s="24">
+        <v>-32</v>
+      </c>
+      <c r="K120" s="24">
+        <v>-52</v>
+      </c>
+      <c r="L120" s="24">
+        <v>-21</v>
+      </c>
+      <c r="M120" s="24">
+        <v>-24</v>
+      </c>
+    </row>
+    <row r="121" spans="2:38" s="30" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B121" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="C121" s="31"/>
+      <c r="D121" s="31"/>
+      <c r="E121" s="31"/>
+      <c r="F121" s="31"/>
+      <c r="G121" s="31">
+        <f>+SUM(G115:G120)</f>
+        <v>-9345</v>
+      </c>
+      <c r="H121" s="31">
+        <f>+SUM(H115:H120)</f>
+        <v>-10320</v>
+      </c>
+      <c r="I121" s="31">
+        <f>+SUM(I115:I120)</f>
+        <v>-12748</v>
+      </c>
+      <c r="J121" s="31">
+        <f>+SUM(J115:J120)</f>
+        <v>-9948</v>
+      </c>
+      <c r="K121" s="31">
+        <f>+SUM(K115:K120)</f>
+        <v>-15553</v>
+      </c>
+      <c r="L121" s="31">
+        <f>+SUM(L115:L120)</f>
+        <v>-11834</v>
+      </c>
+      <c r="M121" s="31">
+        <f>+SUM(M115:M120)</f>
+        <v>-14878</v>
+      </c>
+      <c r="N121" s="31"/>
+      <c r="Q121" s="31"/>
+      <c r="R121" s="31"/>
+      <c r="S121" s="31"/>
+      <c r="T121" s="31"/>
+      <c r="U121" s="31"/>
+      <c r="V121" s="31"/>
+      <c r="W121" s="31"/>
+      <c r="X121" s="31"/>
+      <c r="Y121" s="31"/>
+      <c r="Z121" s="31"/>
+      <c r="AA121" s="31"/>
+      <c r="AB121" s="31"/>
+      <c r="AC121" s="31"/>
+      <c r="AD121" s="31"/>
+      <c r="AE121" s="31"/>
+      <c r="AF121" s="31"/>
+      <c r="AG121" s="31"/>
+      <c r="AH121" s="31"/>
+      <c r="AI121" s="31"/>
+      <c r="AJ121" s="31"/>
+      <c r="AK121" s="31"/>
+      <c r="AL121" s="31"/>
+    </row>
+    <row r="123" spans="2:38" s="30" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B123" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="C123" s="31"/>
+      <c r="D123" s="31"/>
+      <c r="E123" s="31"/>
+      <c r="F123" s="31"/>
+      <c r="G123" s="31">
+        <f>SUM(G102,G113,G121)</f>
+        <v>5039</v>
+      </c>
+      <c r="H123" s="31">
+        <f>SUM(H102,H113,H121)</f>
+        <v>984</v>
+      </c>
+      <c r="I123" s="31">
+        <f>SUM(I102,I113,I121)</f>
+        <v>536</v>
+      </c>
+      <c r="J123" s="31">
+        <f>SUM(J102,J113,J121)</f>
+        <v>-518</v>
+      </c>
+      <c r="K123" s="31">
+        <f>SUM(K102,K113,K121)</f>
+        <v>6735</v>
+      </c>
+      <c r="L123" s="31">
+        <f>SUM(L102,L113,L121)</f>
+        <v>-3595</v>
+      </c>
+      <c r="M123" s="31">
+        <f>SUM(M102,M113,M121)</f>
+        <v>-153</v>
+      </c>
+      <c r="N123" s="31"/>
+      <c r="Q123" s="31"/>
+      <c r="R123" s="31"/>
+      <c r="S123" s="31"/>
+      <c r="T123" s="31"/>
+      <c r="U123" s="31"/>
+      <c r="V123" s="31"/>
+      <c r="W123" s="31"/>
+      <c r="X123" s="31"/>
+      <c r="Y123" s="31"/>
+      <c r="Z123" s="31"/>
+      <c r="AA123" s="31"/>
+      <c r="AB123" s="31"/>
+      <c r="AC123" s="31"/>
+      <c r="AD123" s="31"/>
+      <c r="AE123" s="31"/>
+      <c r="AF123" s="31"/>
+      <c r="AG123" s="31"/>
+      <c r="AH123" s="31"/>
+      <c r="AI123" s="31"/>
+      <c r="AJ123" s="31"/>
+      <c r="AK123" s="31"/>
+      <c r="AL123" s="31"/>
+    </row>
+    <row r="125" spans="2:38" x14ac:dyDescent="0.15">
+      <c r="B125" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="G125" s="26">
+        <f t="shared" ref="G125:M125" si="294">+G102+G108</f>
+        <v>19708</v>
+      </c>
+      <c r="H125" s="26">
+        <f t="shared" si="294"/>
+        <v>13512</v>
+      </c>
+      <c r="I125" s="26">
+        <f t="shared" si="294"/>
+        <v>16816</v>
+      </c>
+      <c r="J125" s="26">
+        <f t="shared" si="294"/>
+        <v>15551</v>
+      </c>
+      <c r="K125" s="26">
+        <f t="shared" si="294"/>
+        <v>26187</v>
+      </c>
+      <c r="L125" s="26">
+        <f>+L102+L108</f>
+        <v>13471</v>
+      </c>
+      <c r="M125" s="26">
+        <f t="shared" si="294"/>
+        <v>22113</v>
       </c>
     </row>
     <row r="126" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B126" s="27" t="s">
-        <v>199</v>
+        <v>217</v>
+      </c>
+      <c r="G126" s="26">
+        <f>+G102+G108-G91</f>
+        <v>18697</v>
       </c>
       <c r="H126" s="26">
-        <v>1300</v>
+        <f t="shared" ref="H126:M126" si="295">+H102+H108-H91</f>
+        <v>12358</v>
       </c>
       <c r="I126" s="26">
-        <v>1400</v>
+        <f t="shared" si="295"/>
+        <v>15564</v>
       </c>
       <c r="J126" s="26">
-        <v>1600</v>
+        <f t="shared" si="295"/>
+        <v>14230</v>
       </c>
       <c r="K126" s="26">
-        <v>1600</v>
+        <f t="shared" si="295"/>
+        <v>24713</v>
       </c>
       <c r="L126" s="26">
-        <v>1800</v>
+        <f t="shared" si="295"/>
+        <v>11847</v>
       </c>
       <c r="M126" s="26">
-        <v>2000</v>
+        <f t="shared" si="295"/>
+        <v>20458</v>
       </c>
     </row>
     <row r="127" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B127" s="27" t="s">
-        <v>200</v>
+        <v>216</v>
+      </c>
+      <c r="G127" s="26">
+        <f>+G102-G91-G92+G108</f>
+        <v>18287</v>
       </c>
       <c r="H127" s="26">
-        <v>123</v>
+        <f t="shared" ref="H127:M127" si="296">+H102-H91-H92+H108</f>
+        <v>11925</v>
       </c>
       <c r="I127" s="26">
-        <v>187</v>
+        <f t="shared" si="296"/>
+        <v>15086</v>
       </c>
       <c r="J127" s="26">
-        <v>151</v>
+        <f t="shared" si="296"/>
+        <v>13687</v>
       </c>
       <c r="K127" s="26">
-        <v>160</v>
+        <f t="shared" si="296"/>
+        <v>24102</v>
       </c>
       <c r="L127" s="26">
-        <v>118</v>
+        <f t="shared" si="296"/>
+        <v>11179</v>
       </c>
       <c r="M127" s="26">
-        <v>449</v>
+        <f t="shared" si="296"/>
+        <v>19706</v>
       </c>
     </row>
     <row r="128" spans="2:38" s="30" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B128" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="C128" s="31">
-        <v>639</v>
-      </c>
-      <c r="D128" s="31">
-        <v>717</v>
-      </c>
-      <c r="E128" s="31">
-        <v>896</v>
-      </c>
-      <c r="F128" s="31">
-        <v>1100</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="C128" s="31"/>
+      <c r="D128" s="31"/>
+      <c r="E128" s="31"/>
+      <c r="F128" s="31"/>
       <c r="G128" s="31">
-        <v>1300</v>
+        <f t="shared" ref="G128:M128" si="297">+G25</f>
+        <v>14046</v>
       </c>
       <c r="H128" s="31">
-        <f t="shared" ref="H128:M128" si="294">SUM(H126:H127)</f>
-        <v>1423</v>
+        <f t="shared" si="297"/>
+        <v>16599</v>
       </c>
       <c r="I128" s="31">
-        <f t="shared" si="294"/>
-        <v>1587</v>
+        <f t="shared" si="297"/>
+        <v>19309</v>
       </c>
       <c r="J128" s="31">
-        <f t="shared" si="294"/>
-        <v>1751</v>
+        <f t="shared" si="297"/>
+        <v>32926</v>
       </c>
       <c r="K128" s="31">
-        <f t="shared" si="294"/>
-        <v>1760</v>
+        <f t="shared" si="297"/>
+        <v>18775</v>
       </c>
       <c r="L128" s="31">
-        <f t="shared" si="294"/>
-        <v>1918</v>
+        <f t="shared" si="297"/>
+        <v>26546</v>
       </c>
       <c r="M128" s="31">
-        <f t="shared" si="294"/>
-        <v>2449</v>
+        <f t="shared" si="297"/>
+        <v>31910</v>
       </c>
       <c r="N128" s="31"/>
       <c r="Q128" s="31"/>
@@ -10158,196 +10390,319 @@
       <c r="AK128" s="31"/>
       <c r="AL128" s="31"/>
     </row>
-    <row r="129" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B129" s="27" t="s">
+    <row r="130" spans="2:38" x14ac:dyDescent="0.15">
+      <c r="B130" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="C129" s="26">
-        <f>+C128*0.46</f>
+      <c r="C130" s="24"/>
+      <c r="D130" s="24"/>
+      <c r="E130" s="24"/>
+      <c r="F130" s="24"/>
+      <c r="G130" s="24"/>
+      <c r="H130" s="24">
+        <v>1300</v>
+      </c>
+      <c r="I130" s="24">
+        <v>1400</v>
+      </c>
+      <c r="J130" s="24">
+        <v>1600</v>
+      </c>
+      <c r="K130" s="24">
+        <v>1600</v>
+      </c>
+      <c r="L130" s="24">
+        <v>1800</v>
+      </c>
+      <c r="M130" s="24">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="131" spans="2:38" x14ac:dyDescent="0.15">
+      <c r="B131" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="C131" s="24"/>
+      <c r="D131" s="24"/>
+      <c r="E131" s="24"/>
+      <c r="F131" s="24"/>
+      <c r="G131" s="24"/>
+      <c r="H131" s="24">
+        <v>123</v>
+      </c>
+      <c r="I131" s="24">
+        <v>187</v>
+      </c>
+      <c r="J131" s="24">
+        <v>151</v>
+      </c>
+      <c r="K131" s="24">
+        <v>160</v>
+      </c>
+      <c r="L131" s="24">
+        <v>118</v>
+      </c>
+      <c r="M131" s="24">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="132" spans="2:38" s="30" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B132" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="C132" s="31">
+        <v>639</v>
+      </c>
+      <c r="D132" s="31">
+        <v>717</v>
+      </c>
+      <c r="E132" s="31">
+        <v>896</v>
+      </c>
+      <c r="F132" s="31">
+        <v>1100</v>
+      </c>
+      <c r="G132" s="31">
+        <v>1300</v>
+      </c>
+      <c r="H132" s="31">
+        <f>SUM(H130:H131)</f>
+        <v>1423</v>
+      </c>
+      <c r="I132" s="31">
+        <f t="shared" ref="I132:M132" si="298">SUM(I130:I131)</f>
+        <v>1587</v>
+      </c>
+      <c r="J132" s="31">
+        <f t="shared" si="298"/>
+        <v>1751</v>
+      </c>
+      <c r="K132" s="31">
+        <f t="shared" si="298"/>
+        <v>1760</v>
+      </c>
+      <c r="L132" s="31">
+        <f t="shared" si="298"/>
+        <v>1918</v>
+      </c>
+      <c r="M132" s="31">
+        <f t="shared" si="298"/>
+        <v>2449</v>
+      </c>
+      <c r="N132" s="31"/>
+      <c r="Q132" s="31"/>
+      <c r="R132" s="31"/>
+      <c r="S132" s="31"/>
+      <c r="T132" s="31"/>
+      <c r="U132" s="31"/>
+      <c r="V132" s="31"/>
+      <c r="W132" s="31"/>
+      <c r="X132" s="31"/>
+      <c r="Y132" s="31"/>
+      <c r="Z132" s="31"/>
+      <c r="AA132" s="31"/>
+      <c r="AB132" s="31"/>
+      <c r="AC132" s="31"/>
+      <c r="AD132" s="31"/>
+      <c r="AE132" s="31"/>
+      <c r="AF132" s="31"/>
+      <c r="AG132" s="31"/>
+      <c r="AH132" s="31"/>
+      <c r="AI132" s="31"/>
+      <c r="AJ132" s="31"/>
+      <c r="AK132" s="31"/>
+      <c r="AL132" s="31"/>
+    </row>
+    <row r="133" spans="2:38" x14ac:dyDescent="0.15">
+      <c r="B133" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="C133" s="26">
+        <f>+C132*0.46</f>
         <v>293.94</v>
       </c>
-      <c r="D129" s="26">
-        <f>+D128*0.44</f>
+      <c r="D133" s="26">
+        <f>+D132*0.44</f>
         <v>315.48</v>
       </c>
-      <c r="E129" s="26">
-        <f>+E128*0.42</f>
+      <c r="E133" s="26">
+        <f>+E132*0.42</f>
         <v>376.32</v>
       </c>
-      <c r="F129" s="26">
-        <f>+F128*0.4</f>
+      <c r="F133" s="26">
+        <f>+F132*0.4</f>
         <v>440</v>
       </c>
-      <c r="G129" s="26">
-        <f>+G128*0.38</f>
+      <c r="G133" s="26">
+        <f>+G132*0.38</f>
         <v>494</v>
       </c>
-      <c r="H129" s="26">
-        <f>+H128*0.37</f>
+      <c r="H133" s="26">
+        <f>+H132*0.37</f>
         <v>526.51</v>
       </c>
-      <c r="I129" s="26">
-        <f>+I128*0.37</f>
+      <c r="I133" s="26">
+        <f>+I132*0.37</f>
         <v>587.18999999999994</v>
       </c>
-      <c r="J129" s="26">
-        <f>+J128*0.39</f>
+      <c r="J133" s="26">
+        <f>+J132*0.39</f>
         <v>682.89</v>
       </c>
-      <c r="K129" s="26">
-        <f>+K128*0.39</f>
+      <c r="K133" s="26">
+        <f>+K132*0.39</f>
         <v>686.4</v>
       </c>
-      <c r="L129" s="26">
-        <f>+L128*0.4</f>
+      <c r="L133" s="26">
+        <f>+L132*0.4</f>
         <v>767.2</v>
       </c>
-      <c r="M129" s="26">
-        <f>+M128*0.4</f>
+      <c r="M133" s="26">
+        <f>+M132*0.4</f>
         <v>979.6</v>
       </c>
     </row>
-    <row r="130" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B130" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="C130" s="39">
-        <f>+C129/C128</f>
+    <row r="134" spans="2:38" x14ac:dyDescent="0.15">
+      <c r="B134" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="C134" s="32">
+        <f>+C133/C132</f>
         <v>0.46</v>
       </c>
-      <c r="D130" s="39">
-        <f t="shared" ref="D130:M130" si="295">+D129/D128</f>
+      <c r="D134" s="32">
+        <f t="shared" ref="D134:M134" si="299">+D133/D132</f>
         <v>0.44</v>
       </c>
-      <c r="E130" s="39">
-        <f t="shared" si="295"/>
+      <c r="E134" s="32">
+        <f t="shared" si="299"/>
         <v>0.42</v>
       </c>
-      <c r="F130" s="39">
-        <f t="shared" si="295"/>
+      <c r="F134" s="32">
+        <f t="shared" si="299"/>
         <v>0.4</v>
       </c>
-      <c r="G130" s="39">
-        <f t="shared" si="295"/>
+      <c r="G134" s="32">
+        <f t="shared" si="299"/>
         <v>0.38</v>
       </c>
-      <c r="H130" s="39">
-        <f t="shared" si="295"/>
+      <c r="H134" s="32">
+        <f t="shared" si="299"/>
         <v>0.37</v>
       </c>
-      <c r="I130" s="39">
-        <f t="shared" si="295"/>
+      <c r="I134" s="32">
+        <f t="shared" si="299"/>
         <v>0.36999999999999994</v>
       </c>
-      <c r="J130" s="39">
-        <f t="shared" si="295"/>
+      <c r="J134" s="32">
+        <f t="shared" si="299"/>
         <v>0.39</v>
       </c>
-      <c r="K130" s="39">
-        <f t="shared" si="295"/>
+      <c r="K134" s="32">
+        <f t="shared" si="299"/>
         <v>0.39</v>
       </c>
-      <c r="L130" s="39">
-        <f t="shared" si="295"/>
+      <c r="L134" s="32">
+        <f t="shared" si="299"/>
         <v>0.4</v>
       </c>
-      <c r="M130" s="39">
-        <f t="shared" si="295"/>
+      <c r="M134" s="32">
+        <f t="shared" si="299"/>
         <v>0.4</v>
       </c>
     </row>
-    <row r="131" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="D131" s="39">
-        <f t="shared" ref="D131:L131" si="296">+D128/C128-1</f>
+    <row r="135" spans="2:38" x14ac:dyDescent="0.15">
+      <c r="D135" s="32">
+        <f>+D132/C132-1</f>
         <v>0.1220657276995305</v>
       </c>
-      <c r="E131" s="39">
-        <f t="shared" si="296"/>
+      <c r="E135" s="32">
+        <f t="shared" ref="E135:L135" si="300">+E132/D132-1</f>
         <v>0.24965132496513243</v>
       </c>
-      <c r="F131" s="39">
-        <f t="shared" si="296"/>
+      <c r="F135" s="32">
+        <f t="shared" si="300"/>
         <v>0.2276785714285714</v>
       </c>
-      <c r="G131" s="39">
-        <f t="shared" si="296"/>
+      <c r="G135" s="32">
+        <f t="shared" si="300"/>
         <v>0.18181818181818188</v>
       </c>
-      <c r="H131" s="39">
-        <f t="shared" si="296"/>
+      <c r="H135" s="32">
+        <f t="shared" si="300"/>
         <v>9.4615384615384546E-2</v>
       </c>
-      <c r="I131" s="39">
-        <f t="shared" si="296"/>
+      <c r="I135" s="32">
+        <f t="shared" si="300"/>
         <v>0.11524947294448351</v>
       </c>
-      <c r="J131" s="39">
-        <f t="shared" si="296"/>
+      <c r="J135" s="32">
+        <f t="shared" si="300"/>
         <v>0.10333963453056083</v>
       </c>
-      <c r="K131" s="39">
-        <f t="shared" si="296"/>
+      <c r="K135" s="32">
+        <f t="shared" si="300"/>
         <v>5.1399200456880845E-3</v>
       </c>
-      <c r="L131" s="39">
-        <f t="shared" si="296"/>
+      <c r="L135" s="32">
+        <f t="shared" si="300"/>
         <v>8.9772727272727337E-2</v>
       </c>
-      <c r="M131" s="39">
-        <f>+M128/L128-1</f>
+      <c r="M135" s="32">
+        <f>+M132/L132-1</f>
         <v>0.27685088633993749</v>
       </c>
     </row>
-    <row r="132" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B132" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="D132" s="26">
-        <f t="shared" ref="D132:L132" si="297">+D128-C128</f>
+    <row r="136" spans="2:38" x14ac:dyDescent="0.15">
+      <c r="B136" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="D136" s="26">
+        <f t="shared" ref="D136:L136" si="301">+D132-C132</f>
         <v>78</v>
       </c>
-      <c r="E132" s="26">
-        <f t="shared" si="297"/>
+      <c r="E136" s="26">
+        <f t="shared" si="301"/>
         <v>179</v>
       </c>
-      <c r="F132" s="26">
-        <f t="shared" si="297"/>
+      <c r="F136" s="26">
+        <f t="shared" si="301"/>
         <v>204</v>
       </c>
-      <c r="G132" s="26">
-        <f t="shared" si="297"/>
+      <c r="G136" s="26">
+        <f t="shared" si="301"/>
         <v>200</v>
       </c>
-      <c r="H132" s="26">
-        <f t="shared" si="297"/>
+      <c r="H136" s="26">
+        <f t="shared" si="301"/>
         <v>123</v>
       </c>
-      <c r="I132" s="26">
-        <f t="shared" si="297"/>
+      <c r="I136" s="26">
+        <f t="shared" si="301"/>
         <v>164</v>
       </c>
-      <c r="J132" s="26">
-        <f t="shared" si="297"/>
+      <c r="J136" s="26">
+        <f t="shared" si="301"/>
         <v>164</v>
       </c>
-      <c r="K132" s="26">
-        <f t="shared" si="297"/>
+      <c r="K136" s="26">
+        <f t="shared" si="301"/>
         <v>9</v>
       </c>
-      <c r="L132" s="26">
-        <f t="shared" si="297"/>
+      <c r="L136" s="26">
+        <f t="shared" si="301"/>
         <v>158</v>
       </c>
-      <c r="M132" s="53">
-        <f>+M128-L128</f>
+      <c r="M136" s="48">
+        <f>+M132-L132</f>
         <v>531</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="B16:J25 B30:I30 B27:J27 B26:E26 G26:I26 C29:J29 B28:F28 AB19:AB28 B6:J11 B31:G31 I31" formula="1"/>
-    <ignoredError sqref="C69:M69" formulaRange="1"/>
+    <ignoredError sqref="B16:J25 B30:I30 B27:J27 B26:E26 G26:J26 C29:J29 B28:F28 AB19:AB27 B6:J11 B31:G31 I31" formula="1"/>
+    <ignoredError sqref="C78:M78" formulaRange="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
